--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="249">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,6 +535,18 @@
     <t>['12', '18', '61']</t>
   </si>
   <si>
+    <t>['25', '82', '90+4']</t>
+  </si>
+  <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['41', '85']</t>
+  </si>
+  <si>
+    <t>['11', '61', '90+3']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -688,9 +700,6 @@
     <t>['90+1']</t>
   </si>
   <si>
-    <t>['55']</t>
-  </si>
-  <si>
     <t>['41']</t>
   </si>
   <si>
@@ -740,6 +749,18 @@
   </si>
   <si>
     <t>['20']</t>
+  </si>
+  <si>
+    <t>['1', '12']</t>
+  </si>
+  <si>
+    <t>['15', '88']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['36']</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1357,7 +1378,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1435,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1563,7 +1584,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1641,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3">
         <v>1.4</v>
@@ -1850,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1975,7 +1996,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2056,7 +2077,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2181,7 +2202,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2259,10 +2280,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2387,7 +2408,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2465,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ7">
         <v>1.2</v>
@@ -2593,7 +2614,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2671,10 +2692,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ8">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3005,7 +3026,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3211,7 +3232,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3417,7 +3438,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3495,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
         <v>0.7</v>
@@ -3704,7 +3725,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ13">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3829,7 +3850,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -3907,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ14">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4035,7 +4056,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4116,7 +4137,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ15">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR15">
         <v>1.44</v>
@@ -4319,7 +4340,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ16">
         <v>1.2</v>
@@ -4525,10 +4546,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR17">
         <v>1.15</v>
@@ -4653,7 +4674,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4731,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR18">
         <v>1.45</v>
@@ -4859,7 +4880,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5352,7 +5373,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ21">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR21">
         <v>1.73</v>
@@ -5477,7 +5498,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5555,10 +5576,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ22">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR22">
         <v>0.55</v>
@@ -5889,7 +5910,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5967,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ24">
         <v>1.6</v>
@@ -6173,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ25">
         <v>0.9</v>
@@ -6301,7 +6322,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6379,10 +6400,10 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ26">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR26">
         <v>1.85</v>
@@ -6585,10 +6606,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ27">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -6713,7 +6734,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6794,7 +6815,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR28">
         <v>1.22</v>
@@ -7125,7 +7146,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7206,7 +7227,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7331,7 +7352,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -7409,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -8027,7 +8048,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34">
         <v>1.6</v>
@@ -8155,7 +8176,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q35">
         <v>2.7</v>
@@ -8233,10 +8254,10 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ35">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR35">
         <v>1.92</v>
@@ -8361,7 +8382,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8439,7 +8460,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.5</v>
@@ -8567,7 +8588,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8773,7 +8794,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8979,7 +9000,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9185,7 +9206,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9263,7 +9284,7 @@
         <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>0.7</v>
@@ -9597,7 +9618,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9678,7 +9699,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR42">
         <v>1.16</v>
@@ -9803,7 +9824,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10087,10 +10108,10 @@
         <v>1.33</v>
       </c>
       <c r="AP44">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10293,7 +10314,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ45">
         <v>0.9</v>
@@ -10421,7 +10442,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10705,10 +10726,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR47">
         <v>1.94</v>
@@ -10911,10 +10932,10 @@
         <v>1.75</v>
       </c>
       <c r="AP48">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR48">
         <v>1.38</v>
@@ -11039,7 +11060,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11117,10 +11138,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ49">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR49">
         <v>1.86</v>
@@ -11245,7 +11266,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11451,7 +11472,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11529,7 +11550,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ51">
         <v>0.9</v>
@@ -11941,7 +11962,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ53">
         <v>1.5</v>
@@ -12150,7 +12171,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ54">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -12275,7 +12296,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12481,7 +12502,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12971,10 +12992,10 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13099,7 +13120,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13180,7 +13201,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ59">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR59">
         <v>1.76</v>
@@ -13383,10 +13404,10 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13589,7 +13610,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ61">
         <v>1.5</v>
@@ -13795,7 +13816,7 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -13923,7 +13944,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14004,7 +14025,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14129,7 +14150,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14207,7 +14228,7 @@
         <v>0.4</v>
       </c>
       <c r="AP64">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ64">
         <v>0.7</v>
@@ -14335,7 +14356,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14416,7 +14437,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ65">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14619,10 +14640,10 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ66">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR66">
         <v>1.86</v>
@@ -14747,7 +14768,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14825,7 +14846,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ67">
         <v>1.2</v>
@@ -14953,7 +14974,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15031,7 +15052,7 @@
         <v>0.4</v>
       </c>
       <c r="AP68">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ68">
         <v>0.9</v>
@@ -15159,7 +15180,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15365,7 +15386,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15446,7 +15467,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ70">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15571,7 +15592,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15652,7 +15673,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR71">
         <v>1.55</v>
@@ -15983,7 +16004,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16061,7 +16082,7 @@
         <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ73">
         <v>1.6</v>
@@ -16267,10 +16288,10 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -16476,7 +16497,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ75">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -16601,7 +16622,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16682,7 +16703,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -16885,7 +16906,7 @@
         <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>1.2</v>
@@ -17091,7 +17112,7 @@
         <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ78">
         <v>0.7</v>
@@ -17297,7 +17318,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17631,7 +17652,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17709,10 +17730,10 @@
         <v>1.43</v>
       </c>
       <c r="AP81">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR81">
         <v>0.99</v>
@@ -17837,7 +17858,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -17915,7 +17936,7 @@
         <v>2.17</v>
       </c>
       <c r="AP82">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ82">
         <v>1.4</v>
@@ -18043,7 +18064,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18249,7 +18270,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18330,7 +18351,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ84">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR84">
         <v>1.54</v>
@@ -18455,7 +18476,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18661,7 +18682,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18739,10 +18760,10 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ86">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -18867,7 +18888,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -18948,7 +18969,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ87">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR87">
         <v>1.52</v>
@@ -19151,10 +19172,10 @@
         <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19357,7 +19378,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ89">
         <v>1.4</v>
@@ -19691,7 +19712,7 @@
         <v>155</v>
       </c>
       <c r="P91" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -19897,7 +19918,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="Q92">
         <v>2.45</v>
@@ -20103,7 +20124,7 @@
         <v>83</v>
       </c>
       <c r="P93" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="Q93">
         <v>4.2</v>
@@ -20181,7 +20202,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ93">
         <v>1.6</v>
@@ -20309,7 +20330,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20387,7 +20408,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20515,7 +20536,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20596,7 +20617,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR95">
         <v>1.3</v>
@@ -20799,7 +20820,7 @@
         <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ96">
         <v>1.5</v>
@@ -20927,7 +20948,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21008,7 +21029,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ97">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21133,7 +21154,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21339,7 +21360,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21420,7 +21441,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ99">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -21545,7 +21566,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21623,7 +21644,7 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100">
         <v>1.5</v>
@@ -21829,7 +21850,7 @@
         <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
         <v>1.4</v>
@@ -21957,7 +21978,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22035,10 +22056,10 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ102">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR102">
         <v>1.93</v>
@@ -22163,7 +22184,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22244,7 +22265,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ103">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR103">
         <v>1.81</v>
@@ -22369,7 +22390,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22575,7 +22596,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22653,10 +22674,10 @@
         <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR105">
         <v>0.93</v>
@@ -22987,7 +23008,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23193,7 +23214,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23271,7 +23292,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ108">
         <v>0.9</v>
@@ -23399,7 +23420,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23477,10 +23498,10 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ109">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR109">
         <v>1.41</v>
@@ -23686,7 +23707,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ110">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -23811,7 +23832,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24095,10 +24116,10 @@
         <v>1.22</v>
       </c>
       <c r="AP112">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ112">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR112">
         <v>1.84</v>
@@ -24301,7 +24322,7 @@
         <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ113">
         <v>0.7</v>
@@ -24429,7 +24450,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24507,10 +24528,10 @@
         <v>1.56</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR114">
         <v>1.86</v>
@@ -24713,7 +24734,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
         <v>1.6</v>
@@ -24922,7 +24943,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ116">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR116">
         <v>1.51</v>
@@ -25125,7 +25146,7 @@
         <v>1.22</v>
       </c>
       <c r="AP117">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ117">
         <v>1.2</v>
@@ -25253,7 +25274,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25459,7 +25480,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25665,7 +25686,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25746,7 +25767,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR120">
         <v>1.76</v>
@@ -25949,7 +25970,7 @@
         <v>1.56</v>
       </c>
       <c r="AP121">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ121">
         <v>1.4</v>
@@ -26028,6 +26049,1242 @@
       </c>
       <c r="BP121">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7487145</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45689.58333333334</v>
+      </c>
+      <c r="F122">
+        <v>21</v>
+      </c>
+      <c r="G122" t="s">
+        <v>74</v>
+      </c>
+      <c r="H122" t="s">
+        <v>73</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>2</v>
+      </c>
+      <c r="N122">
+        <v>3</v>
+      </c>
+      <c r="O122" t="s">
+        <v>128</v>
+      </c>
+      <c r="P122" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q122">
+        <v>3</v>
+      </c>
+      <c r="R122">
+        <v>2.3</v>
+      </c>
+      <c r="S122">
+        <v>3.25</v>
+      </c>
+      <c r="T122">
+        <v>1.33</v>
+      </c>
+      <c r="U122">
+        <v>3.25</v>
+      </c>
+      <c r="V122">
+        <v>2.5</v>
+      </c>
+      <c r="W122">
+        <v>1.5</v>
+      </c>
+      <c r="X122">
+        <v>6.5</v>
+      </c>
+      <c r="Y122">
+        <v>1.11</v>
+      </c>
+      <c r="Z122">
+        <v>2.36</v>
+      </c>
+      <c r="AA122">
+        <v>3.53</v>
+      </c>
+      <c r="AB122">
+        <v>2.75</v>
+      </c>
+      <c r="AC122">
+        <v>1.04</v>
+      </c>
+      <c r="AD122">
+        <v>10</v>
+      </c>
+      <c r="AE122">
+        <v>1.2</v>
+      </c>
+      <c r="AF122">
+        <v>4.5</v>
+      </c>
+      <c r="AG122">
+        <v>1.57</v>
+      </c>
+      <c r="AH122">
+        <v>2.15</v>
+      </c>
+      <c r="AI122">
+        <v>1.53</v>
+      </c>
+      <c r="AJ122">
+        <v>2.38</v>
+      </c>
+      <c r="AK122">
+        <v>1.43</v>
+      </c>
+      <c r="AL122">
+        <v>1.28</v>
+      </c>
+      <c r="AM122">
+        <v>1.55</v>
+      </c>
+      <c r="AN122">
+        <v>2.2</v>
+      </c>
+      <c r="AO122">
+        <v>0.7</v>
+      </c>
+      <c r="AP122">
+        <v>2</v>
+      </c>
+      <c r="AQ122">
+        <v>0.91</v>
+      </c>
+      <c r="AR122">
+        <v>1.78</v>
+      </c>
+      <c r="AS122">
+        <v>1.78</v>
+      </c>
+      <c r="AT122">
+        <v>3.56</v>
+      </c>
+      <c r="AU122">
+        <v>4</v>
+      </c>
+      <c r="AV122">
+        <v>4</v>
+      </c>
+      <c r="AW122">
+        <v>16</v>
+      </c>
+      <c r="AX122">
+        <v>4</v>
+      </c>
+      <c r="AY122">
+        <v>25</v>
+      </c>
+      <c r="AZ122">
+        <v>8</v>
+      </c>
+      <c r="BA122">
+        <v>7</v>
+      </c>
+      <c r="BB122">
+        <v>5</v>
+      </c>
+      <c r="BC122">
+        <v>12</v>
+      </c>
+      <c r="BD122">
+        <v>1.95</v>
+      </c>
+      <c r="BE122">
+        <v>6.4</v>
+      </c>
+      <c r="BF122">
+        <v>2.07</v>
+      </c>
+      <c r="BG122">
+        <v>1.34</v>
+      </c>
+      <c r="BH122">
+        <v>2.9</v>
+      </c>
+      <c r="BI122">
+        <v>1.57</v>
+      </c>
+      <c r="BJ122">
+        <v>2.2</v>
+      </c>
+      <c r="BK122">
+        <v>1.93</v>
+      </c>
+      <c r="BL122">
+        <v>1.74</v>
+      </c>
+      <c r="BM122">
+        <v>2.45</v>
+      </c>
+      <c r="BN122">
+        <v>1.46</v>
+      </c>
+      <c r="BO122">
+        <v>3.2</v>
+      </c>
+      <c r="BP122">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7487146</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45689.58333333334</v>
+      </c>
+      <c r="F123">
+        <v>21</v>
+      </c>
+      <c r="G123" t="s">
+        <v>70</v>
+      </c>
+      <c r="H123" t="s">
+        <v>77</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>3</v>
+      </c>
+      <c r="M123">
+        <v>2</v>
+      </c>
+      <c r="N123">
+        <v>5</v>
+      </c>
+      <c r="O123" t="s">
+        <v>173</v>
+      </c>
+      <c r="P123" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q123">
+        <v>2.5</v>
+      </c>
+      <c r="R123">
+        <v>2.2</v>
+      </c>
+      <c r="S123">
+        <v>4.33</v>
+      </c>
+      <c r="T123">
+        <v>1.36</v>
+      </c>
+      <c r="U123">
+        <v>3</v>
+      </c>
+      <c r="V123">
+        <v>2.75</v>
+      </c>
+      <c r="W123">
+        <v>1.4</v>
+      </c>
+      <c r="X123">
+        <v>8</v>
+      </c>
+      <c r="Y123">
+        <v>1.08</v>
+      </c>
+      <c r="Z123">
+        <v>1.81</v>
+      </c>
+      <c r="AA123">
+        <v>3.65</v>
+      </c>
+      <c r="AB123">
+        <v>4.1</v>
+      </c>
+      <c r="AC123">
+        <v>1.05</v>
+      </c>
+      <c r="AD123">
+        <v>9</v>
+      </c>
+      <c r="AE123">
+        <v>1.28</v>
+      </c>
+      <c r="AF123">
+        <v>3.55</v>
+      </c>
+      <c r="AG123">
+        <v>1.8</v>
+      </c>
+      <c r="AH123">
+        <v>1.94</v>
+      </c>
+      <c r="AI123">
+        <v>1.73</v>
+      </c>
+      <c r="AJ123">
+        <v>2</v>
+      </c>
+      <c r="AK123">
+        <v>1.22</v>
+      </c>
+      <c r="AL123">
+        <v>1.27</v>
+      </c>
+      <c r="AM123">
+        <v>1.93</v>
+      </c>
+      <c r="AN123">
+        <v>2</v>
+      </c>
+      <c r="AO123">
+        <v>1</v>
+      </c>
+      <c r="AP123">
+        <v>2.09</v>
+      </c>
+      <c r="AQ123">
+        <v>0.91</v>
+      </c>
+      <c r="AR123">
+        <v>1.87</v>
+      </c>
+      <c r="AS123">
+        <v>1.4</v>
+      </c>
+      <c r="AT123">
+        <v>3.27</v>
+      </c>
+      <c r="AU123">
+        <v>6</v>
+      </c>
+      <c r="AV123">
+        <v>4</v>
+      </c>
+      <c r="AW123">
+        <v>10</v>
+      </c>
+      <c r="AX123">
+        <v>6</v>
+      </c>
+      <c r="AY123">
+        <v>17</v>
+      </c>
+      <c r="AZ123">
+        <v>10</v>
+      </c>
+      <c r="BA123">
+        <v>3</v>
+      </c>
+      <c r="BB123">
+        <v>1</v>
+      </c>
+      <c r="BC123">
+        <v>4</v>
+      </c>
+      <c r="BD123">
+        <v>1.61</v>
+      </c>
+      <c r="BE123">
+        <v>6.4</v>
+      </c>
+      <c r="BF123">
+        <v>2.55</v>
+      </c>
+      <c r="BG123">
+        <v>1.36</v>
+      </c>
+      <c r="BH123">
+        <v>2.8</v>
+      </c>
+      <c r="BI123">
+        <v>1.6</v>
+      </c>
+      <c r="BJ123">
+        <v>2.14</v>
+      </c>
+      <c r="BK123">
+        <v>1.97</v>
+      </c>
+      <c r="BL123">
+        <v>1.7</v>
+      </c>
+      <c r="BM123">
+        <v>2.5</v>
+      </c>
+      <c r="BN123">
+        <v>1.44</v>
+      </c>
+      <c r="BO123">
+        <v>3.3</v>
+      </c>
+      <c r="BP123">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7487148</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45689.6875</v>
+      </c>
+      <c r="F124">
+        <v>21</v>
+      </c>
+      <c r="G124" t="s">
+        <v>76</v>
+      </c>
+      <c r="H124" t="s">
+        <v>78</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>2</v>
+      </c>
+      <c r="O124" t="s">
+        <v>174</v>
+      </c>
+      <c r="P124" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q124">
+        <v>2.2</v>
+      </c>
+      <c r="R124">
+        <v>2.3</v>
+      </c>
+      <c r="S124">
+        <v>5</v>
+      </c>
+      <c r="T124">
+        <v>1.33</v>
+      </c>
+      <c r="U124">
+        <v>3.25</v>
+      </c>
+      <c r="V124">
+        <v>2.63</v>
+      </c>
+      <c r="W124">
+        <v>1.44</v>
+      </c>
+      <c r="X124">
+        <v>6.5</v>
+      </c>
+      <c r="Y124">
+        <v>1.11</v>
+      </c>
+      <c r="Z124">
+        <v>1.59</v>
+      </c>
+      <c r="AA124">
+        <v>4</v>
+      </c>
+      <c r="AB124">
+        <v>5.1</v>
+      </c>
+      <c r="AC124">
+        <v>1.04</v>
+      </c>
+      <c r="AD124">
+        <v>10</v>
+      </c>
+      <c r="AE124">
+        <v>1.22</v>
+      </c>
+      <c r="AF124">
+        <v>4.2</v>
+      </c>
+      <c r="AG124">
+        <v>1.61</v>
+      </c>
+      <c r="AH124">
+        <v>2.05</v>
+      </c>
+      <c r="AI124">
+        <v>1.73</v>
+      </c>
+      <c r="AJ124">
+        <v>2</v>
+      </c>
+      <c r="AK124">
+        <v>1.17</v>
+      </c>
+      <c r="AL124">
+        <v>1.23</v>
+      </c>
+      <c r="AM124">
+        <v>2.25</v>
+      </c>
+      <c r="AN124">
+        <v>1.9</v>
+      </c>
+      <c r="AO124">
+        <v>1</v>
+      </c>
+      <c r="AP124">
+        <v>1.82</v>
+      </c>
+      <c r="AQ124">
+        <v>1</v>
+      </c>
+      <c r="AR124">
+        <v>1.92</v>
+      </c>
+      <c r="AS124">
+        <v>1.31</v>
+      </c>
+      <c r="AT124">
+        <v>3.23</v>
+      </c>
+      <c r="AU124">
+        <v>7</v>
+      </c>
+      <c r="AV124">
+        <v>6</v>
+      </c>
+      <c r="AW124">
+        <v>15</v>
+      </c>
+      <c r="AX124">
+        <v>6</v>
+      </c>
+      <c r="AY124">
+        <v>26</v>
+      </c>
+      <c r="AZ124">
+        <v>12</v>
+      </c>
+      <c r="BA124">
+        <v>13</v>
+      </c>
+      <c r="BB124">
+        <v>1</v>
+      </c>
+      <c r="BC124">
+        <v>14</v>
+      </c>
+      <c r="BD124">
+        <v>1.48</v>
+      </c>
+      <c r="BE124">
+        <v>6.75</v>
+      </c>
+      <c r="BF124">
+        <v>2.95</v>
+      </c>
+      <c r="BG124">
+        <v>1.27</v>
+      </c>
+      <c r="BH124">
+        <v>3.25</v>
+      </c>
+      <c r="BI124">
+        <v>1.47</v>
+      </c>
+      <c r="BJ124">
+        <v>2.43</v>
+      </c>
+      <c r="BK124">
+        <v>1.74</v>
+      </c>
+      <c r="BL124">
+        <v>1.93</v>
+      </c>
+      <c r="BM124">
+        <v>2.18</v>
+      </c>
+      <c r="BN124">
+        <v>1.58</v>
+      </c>
+      <c r="BO124">
+        <v>2.8</v>
+      </c>
+      <c r="BP124">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7487147</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45690.42708333334</v>
+      </c>
+      <c r="F125">
+        <v>21</v>
+      </c>
+      <c r="G125" t="s">
+        <v>75</v>
+      </c>
+      <c r="H125" t="s">
+        <v>80</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>175</v>
+      </c>
+      <c r="P125" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q125">
+        <v>2.75</v>
+      </c>
+      <c r="R125">
+        <v>2.4</v>
+      </c>
+      <c r="S125">
+        <v>3.4</v>
+      </c>
+      <c r="T125">
+        <v>1.29</v>
+      </c>
+      <c r="U125">
+        <v>3.5</v>
+      </c>
+      <c r="V125">
+        <v>2.25</v>
+      </c>
+      <c r="W125">
+        <v>1.57</v>
+      </c>
+      <c r="X125">
+        <v>5.5</v>
+      </c>
+      <c r="Y125">
+        <v>1.14</v>
+      </c>
+      <c r="Z125">
+        <v>2.14</v>
+      </c>
+      <c r="AA125">
+        <v>3.5</v>
+      </c>
+      <c r="AB125">
+        <v>3.16</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>13</v>
+      </c>
+      <c r="AE125">
+        <v>1.18</v>
+      </c>
+      <c r="AF125">
+        <v>4.75</v>
+      </c>
+      <c r="AG125">
+        <v>1.53</v>
+      </c>
+      <c r="AH125">
+        <v>2.4</v>
+      </c>
+      <c r="AI125">
+        <v>1.44</v>
+      </c>
+      <c r="AJ125">
+        <v>2.63</v>
+      </c>
+      <c r="AK125">
+        <v>1.35</v>
+      </c>
+      <c r="AL125">
+        <v>1.25</v>
+      </c>
+      <c r="AM125">
+        <v>1.67</v>
+      </c>
+      <c r="AN125">
+        <v>1.7</v>
+      </c>
+      <c r="AO125">
+        <v>1.2</v>
+      </c>
+      <c r="AP125">
+        <v>1.82</v>
+      </c>
+      <c r="AQ125">
+        <v>1.09</v>
+      </c>
+      <c r="AR125">
+        <v>1.65</v>
+      </c>
+      <c r="AS125">
+        <v>1.38</v>
+      </c>
+      <c r="AT125">
+        <v>3.03</v>
+      </c>
+      <c r="AU125">
+        <v>8</v>
+      </c>
+      <c r="AV125">
+        <v>7</v>
+      </c>
+      <c r="AW125">
+        <v>8</v>
+      </c>
+      <c r="AX125">
+        <v>7</v>
+      </c>
+      <c r="AY125">
+        <v>17</v>
+      </c>
+      <c r="AZ125">
+        <v>18</v>
+      </c>
+      <c r="BA125">
+        <v>4</v>
+      </c>
+      <c r="BB125">
+        <v>2</v>
+      </c>
+      <c r="BC125">
+        <v>6</v>
+      </c>
+      <c r="BD125">
+        <v>1.89</v>
+      </c>
+      <c r="BE125">
+        <v>6.75</v>
+      </c>
+      <c r="BF125">
+        <v>2.08</v>
+      </c>
+      <c r="BG125">
+        <v>1.17</v>
+      </c>
+      <c r="BH125">
+        <v>4.1</v>
+      </c>
+      <c r="BI125">
+        <v>1.33</v>
+      </c>
+      <c r="BJ125">
+        <v>2.95</v>
+      </c>
+      <c r="BK125">
+        <v>1.52</v>
+      </c>
+      <c r="BL125">
+        <v>2.28</v>
+      </c>
+      <c r="BM125">
+        <v>1.88</v>
+      </c>
+      <c r="BN125">
+        <v>1.92</v>
+      </c>
+      <c r="BO125">
+        <v>2.28</v>
+      </c>
+      <c r="BP125">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7487149</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45690.52083333334</v>
+      </c>
+      <c r="F126">
+        <v>21</v>
+      </c>
+      <c r="G126" t="s">
+        <v>81</v>
+      </c>
+      <c r="H126" t="s">
+        <v>79</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>83</v>
+      </c>
+      <c r="P126" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q126">
+        <v>3.75</v>
+      </c>
+      <c r="R126">
+        <v>2.25</v>
+      </c>
+      <c r="S126">
+        <v>2.63</v>
+      </c>
+      <c r="T126">
+        <v>1.36</v>
+      </c>
+      <c r="U126">
+        <v>3</v>
+      </c>
+      <c r="V126">
+        <v>2.63</v>
+      </c>
+      <c r="W126">
+        <v>1.44</v>
+      </c>
+      <c r="X126">
+        <v>7</v>
+      </c>
+      <c r="Y126">
+        <v>1.1</v>
+      </c>
+      <c r="Z126">
+        <v>3.12</v>
+      </c>
+      <c r="AA126">
+        <v>3.31</v>
+      </c>
+      <c r="AB126">
+        <v>2.24</v>
+      </c>
+      <c r="AC126">
+        <v>1.05</v>
+      </c>
+      <c r="AD126">
+        <v>9.5</v>
+      </c>
+      <c r="AE126">
+        <v>1.25</v>
+      </c>
+      <c r="AF126">
+        <v>3.75</v>
+      </c>
+      <c r="AG126">
+        <v>1.79</v>
+      </c>
+      <c r="AH126">
+        <v>1.95</v>
+      </c>
+      <c r="AI126">
+        <v>1.62</v>
+      </c>
+      <c r="AJ126">
+        <v>2.2</v>
+      </c>
+      <c r="AK126">
+        <v>1.7</v>
+      </c>
+      <c r="AL126">
+        <v>1.25</v>
+      </c>
+      <c r="AM126">
+        <v>1.3</v>
+      </c>
+      <c r="AN126">
+        <v>1.6</v>
+      </c>
+      <c r="AO126">
+        <v>1.5</v>
+      </c>
+      <c r="AP126">
+        <v>1.45</v>
+      </c>
+      <c r="AQ126">
+        <v>1.64</v>
+      </c>
+      <c r="AR126">
+        <v>1.41</v>
+      </c>
+      <c r="AS126">
+        <v>1.8</v>
+      </c>
+      <c r="AT126">
+        <v>3.21</v>
+      </c>
+      <c r="AU126">
+        <v>7</v>
+      </c>
+      <c r="AV126">
+        <v>8</v>
+      </c>
+      <c r="AW126">
+        <v>14</v>
+      </c>
+      <c r="AX126">
+        <v>9</v>
+      </c>
+      <c r="AY126">
+        <v>25</v>
+      </c>
+      <c r="AZ126">
+        <v>19</v>
+      </c>
+      <c r="BA126">
+        <v>6</v>
+      </c>
+      <c r="BB126">
+        <v>5</v>
+      </c>
+      <c r="BC126">
+        <v>11</v>
+      </c>
+      <c r="BD126">
+        <v>2.32</v>
+      </c>
+      <c r="BE126">
+        <v>6.5</v>
+      </c>
+      <c r="BF126">
+        <v>1.74</v>
+      </c>
+      <c r="BG126">
+        <v>1.21</v>
+      </c>
+      <c r="BH126">
+        <v>3.7</v>
+      </c>
+      <c r="BI126">
+        <v>1.38</v>
+      </c>
+      <c r="BJ126">
+        <v>2.7</v>
+      </c>
+      <c r="BK126">
+        <v>1.62</v>
+      </c>
+      <c r="BL126">
+        <v>2.1</v>
+      </c>
+      <c r="BM126">
+        <v>1.98</v>
+      </c>
+      <c r="BN126">
+        <v>1.82</v>
+      </c>
+      <c r="BO126">
+        <v>2.48</v>
+      </c>
+      <c r="BP126">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7487150</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45690.52083333334</v>
+      </c>
+      <c r="F127">
+        <v>21</v>
+      </c>
+      <c r="G127" t="s">
+        <v>71</v>
+      </c>
+      <c r="H127" t="s">
+        <v>72</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>3</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>3</v>
+      </c>
+      <c r="O127" t="s">
+        <v>176</v>
+      </c>
+      <c r="P127" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q127">
+        <v>3</v>
+      </c>
+      <c r="R127">
+        <v>2.2</v>
+      </c>
+      <c r="S127">
+        <v>3.4</v>
+      </c>
+      <c r="T127">
+        <v>1.36</v>
+      </c>
+      <c r="U127">
+        <v>3</v>
+      </c>
+      <c r="V127">
+        <v>2.75</v>
+      </c>
+      <c r="W127">
+        <v>1.4</v>
+      </c>
+      <c r="X127">
+        <v>7</v>
+      </c>
+      <c r="Y127">
+        <v>1.1</v>
+      </c>
+      <c r="Z127">
+        <v>2.3</v>
+      </c>
+      <c r="AA127">
+        <v>3.39</v>
+      </c>
+      <c r="AB127">
+        <v>2.94</v>
+      </c>
+      <c r="AC127">
+        <v>1.05</v>
+      </c>
+      <c r="AD127">
+        <v>9.5</v>
+      </c>
+      <c r="AE127">
+        <v>1.25</v>
+      </c>
+      <c r="AF127">
+        <v>3.75</v>
+      </c>
+      <c r="AG127">
+        <v>1.79</v>
+      </c>
+      <c r="AH127">
+        <v>1.95</v>
+      </c>
+      <c r="AI127">
+        <v>1.62</v>
+      </c>
+      <c r="AJ127">
+        <v>2.2</v>
+      </c>
+      <c r="AK127">
+        <v>1.4</v>
+      </c>
+      <c r="AL127">
+        <v>1.25</v>
+      </c>
+      <c r="AM127">
+        <v>1.55</v>
+      </c>
+      <c r="AN127">
+        <v>1.1</v>
+      </c>
+      <c r="AO127">
+        <v>0.4</v>
+      </c>
+      <c r="AP127">
+        <v>1.27</v>
+      </c>
+      <c r="AQ127">
+        <v>0.36</v>
+      </c>
+      <c r="AR127">
+        <v>1.01</v>
+      </c>
+      <c r="AS127">
+        <v>1.14</v>
+      </c>
+      <c r="AT127">
+        <v>2.15</v>
+      </c>
+      <c r="AU127">
+        <v>4</v>
+      </c>
+      <c r="AV127">
+        <v>3</v>
+      </c>
+      <c r="AW127">
+        <v>7</v>
+      </c>
+      <c r="AX127">
+        <v>11</v>
+      </c>
+      <c r="AY127">
+        <v>13</v>
+      </c>
+      <c r="AZ127">
+        <v>15</v>
+      </c>
+      <c r="BA127">
+        <v>2</v>
+      </c>
+      <c r="BB127">
+        <v>5</v>
+      </c>
+      <c r="BC127">
+        <v>7</v>
+      </c>
+      <c r="BD127">
+        <v>1.9</v>
+      </c>
+      <c r="BE127">
+        <v>6.4</v>
+      </c>
+      <c r="BF127">
+        <v>2.1</v>
+      </c>
+      <c r="BG127">
+        <v>1.35</v>
+      </c>
+      <c r="BH127">
+        <v>2.85</v>
+      </c>
+      <c r="BI127">
+        <v>1.6</v>
+      </c>
+      <c r="BJ127">
+        <v>2.12</v>
+      </c>
+      <c r="BK127">
+        <v>1.96</v>
+      </c>
+      <c r="BL127">
+        <v>1.71</v>
+      </c>
+      <c r="BM127">
+        <v>2.55</v>
+      </c>
+      <c r="BN127">
+        <v>1.43</v>
+      </c>
+      <c r="BO127">
+        <v>3.3</v>
+      </c>
+      <c r="BP127">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="256">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,18 @@
     <t>['11', '61', '90+3']</t>
   </si>
   <si>
+    <t>['64', '79']</t>
+  </si>
+  <si>
+    <t>['13', '85', '89']</t>
+  </si>
+  <si>
+    <t>['76', '90+4']</t>
+  </si>
+  <si>
+    <t>['5', '9', '66', '72', '76', '90+2']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -761,6 +773,15 @@
   </si>
   <si>
     <t>['36']</t>
+  </si>
+  <si>
+    <t>['29', '85']</t>
+  </si>
+  <si>
+    <t>['45', '53', '90+8']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1378,7 +1399,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1584,7 +1605,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1996,7 +2017,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2074,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ5">
         <v>0.91</v>
@@ -2202,7 +2223,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2408,7 +2429,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2489,7 +2510,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ7">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2614,7 +2635,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2898,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ9">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3026,7 +3047,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3104,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ10">
         <v>1.6</v>
@@ -3232,7 +3253,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3313,7 +3334,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ11">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3438,7 +3459,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3519,7 +3540,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ12">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR12">
         <v>2.07</v>
@@ -3722,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13">
         <v>0.91</v>
@@ -3850,7 +3871,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4056,7 +4077,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4134,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ15">
         <v>1.64</v>
@@ -4343,7 +4364,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR16">
         <v>2.11</v>
@@ -4674,7 +4695,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4880,7 +4901,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -4958,7 +4979,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ19">
         <v>1.4</v>
@@ -5167,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR20">
         <v>1.02</v>
@@ -5370,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ21">
         <v>0.36</v>
@@ -5498,7 +5519,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5782,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -5910,7 +5931,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6197,7 +6218,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ25">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR25">
         <v>3.42</v>
@@ -6322,7 +6343,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6734,7 +6755,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6812,7 +6833,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ28">
         <v>0.91</v>
@@ -7021,7 +7042,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ29">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7146,7 +7167,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7224,7 +7245,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ30">
         <v>1.64</v>
@@ -7352,7 +7373,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -7636,10 +7657,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ32">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR32">
         <v>1.68</v>
@@ -7845,7 +7866,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR33">
         <v>1.17</v>
@@ -8176,7 +8197,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q35">
         <v>2.7</v>
@@ -8382,7 +8403,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8463,7 +8484,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
         <v>1.64</v>
@@ -8588,7 +8609,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8666,7 +8687,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ37">
         <v>1.6</v>
@@ -8794,7 +8815,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8872,10 +8893,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR38">
         <v>1.38</v>
@@ -9000,7 +9021,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9206,7 +9227,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9287,7 +9308,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR40">
         <v>1.54</v>
@@ -9490,10 +9511,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR41">
         <v>1.53</v>
@@ -9618,7 +9639,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9824,7 +9845,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -9902,7 +9923,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
         <v>1.4</v>
@@ -10317,7 +10338,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ45">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR45">
         <v>2.03</v>
@@ -10442,7 +10463,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10520,7 +10541,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -11060,7 +11081,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11266,7 +11287,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11344,10 +11365,10 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ50">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR50">
         <v>1.38</v>
@@ -11472,7 +11493,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11553,7 +11574,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ51">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR51">
         <v>1.66</v>
@@ -11965,7 +11986,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ53">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR53">
         <v>1.68</v>
@@ -12296,7 +12317,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12374,10 +12395,10 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ55">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR55">
         <v>1.62</v>
@@ -12502,7 +12523,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12580,7 +12601,7 @@
         <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ56">
         <v>1.4</v>
@@ -12786,7 +12807,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ57">
         <v>1.6</v>
@@ -13120,7 +13141,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13613,7 +13634,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ61">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR61">
         <v>1.01</v>
@@ -13944,7 +13965,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14150,7 +14171,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14231,7 +14252,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ64">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14356,7 +14377,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14434,7 +14455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ65">
         <v>1.09</v>
@@ -14768,7 +14789,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14849,7 +14870,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ67">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR67">
         <v>1.55</v>
@@ -14974,7 +14995,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15055,7 +15076,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ68">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR68">
         <v>1.02</v>
@@ -15180,7 +15201,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15258,7 +15279,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ69">
         <v>1.4</v>
@@ -15386,7 +15407,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15464,7 +15485,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ70">
         <v>0.36</v>
@@ -15592,7 +15613,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15670,7 +15691,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ71">
         <v>1.64</v>
@@ -15876,10 +15897,10 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16004,7 +16025,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16622,7 +16643,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16700,7 +16721,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ76">
         <v>0.91</v>
@@ -16909,7 +16930,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR77">
         <v>1.84</v>
@@ -17115,7 +17136,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ78">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -17527,7 +17548,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR80">
         <v>1.35</v>
@@ -17652,7 +17673,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17858,7 +17879,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18064,7 +18085,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18142,7 +18163,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ83">
         <v>1.6</v>
@@ -18270,7 +18291,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18348,7 +18369,7 @@
         <v>0.83</v>
       </c>
       <c r="AP84">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ84">
         <v>1.09</v>
@@ -18476,7 +18497,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18554,10 +18575,10 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR85">
         <v>1.7</v>
@@ -18682,7 +18703,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18888,7 +18909,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -18966,7 +18987,7 @@
         <v>0.14</v>
       </c>
       <c r="AP87">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ87">
         <v>0.36</v>
@@ -19584,10 +19605,10 @@
         <v>0.71</v>
       </c>
       <c r="AP90">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ90">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -19793,7 +19814,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ91">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR91">
         <v>1.8</v>
@@ -19999,7 +20020,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR92">
         <v>1.84</v>
@@ -20330,7 +20351,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20536,7 +20557,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20823,7 +20844,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ96">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -20948,7 +20969,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21026,7 +21047,7 @@
         <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ97">
         <v>1.09</v>
@@ -21154,7 +21175,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21232,10 +21253,10 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ98">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21360,7 +21381,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21438,7 +21459,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ99">
         <v>0.91</v>
@@ -21566,7 +21587,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21647,7 +21668,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -21978,7 +21999,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22184,7 +22205,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22262,7 +22283,7 @@
         <v>1.63</v>
       </c>
       <c r="AP103">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ103">
         <v>1.64</v>
@@ -22390,7 +22411,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22596,7 +22617,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23008,7 +23029,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23086,10 +23107,10 @@
         <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ107">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23214,7 +23235,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23295,7 +23316,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ108">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23420,7 +23441,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23704,7 +23725,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ110">
         <v>0.36</v>
@@ -23832,7 +23853,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -23910,7 +23931,7 @@
         <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ111">
         <v>1</v>
@@ -24325,7 +24346,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ113">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR113">
         <v>1.39</v>
@@ -24450,7 +24471,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24940,7 +24961,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ116">
         <v>0.91</v>
@@ -25149,7 +25170,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ117">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR117">
         <v>1</v>
@@ -25274,7 +25295,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25355,7 +25376,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25480,7 +25501,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25558,10 +25579,10 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ119">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR119">
         <v>1.76</v>
@@ -25686,7 +25707,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26098,7 +26119,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26304,7 +26325,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26510,7 +26531,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26922,7 +26943,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27285,6 +27306,830 @@
       </c>
       <c r="BP127">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7487152</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45692.6875</v>
+      </c>
+      <c r="F128">
+        <v>22</v>
+      </c>
+      <c r="G128" t="s">
+        <v>78</v>
+      </c>
+      <c r="H128" t="s">
+        <v>74</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>2</v>
+      </c>
+      <c r="N128">
+        <v>4</v>
+      </c>
+      <c r="O128" t="s">
+        <v>177</v>
+      </c>
+      <c r="P128" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q128">
+        <v>3.45</v>
+      </c>
+      <c r="R128">
+        <v>2.15</v>
+      </c>
+      <c r="S128">
+        <v>2.75</v>
+      </c>
+      <c r="T128">
+        <v>1.35</v>
+      </c>
+      <c r="U128">
+        <v>2.95</v>
+      </c>
+      <c r="V128">
+        <v>2.55</v>
+      </c>
+      <c r="W128">
+        <v>1.45</v>
+      </c>
+      <c r="X128">
+        <v>6.75</v>
+      </c>
+      <c r="Y128">
+        <v>1.07</v>
+      </c>
+      <c r="Z128">
+        <v>2.88</v>
+      </c>
+      <c r="AA128">
+        <v>3.34</v>
+      </c>
+      <c r="AB128">
+        <v>2.36</v>
+      </c>
+      <c r="AC128">
+        <v>1.05</v>
+      </c>
+      <c r="AD128">
+        <v>9.5</v>
+      </c>
+      <c r="AE128">
+        <v>1.25</v>
+      </c>
+      <c r="AF128">
+        <v>3.75</v>
+      </c>
+      <c r="AG128">
+        <v>1.79</v>
+      </c>
+      <c r="AH128">
+        <v>1.95</v>
+      </c>
+      <c r="AI128">
+        <v>1.6</v>
+      </c>
+      <c r="AJ128">
+        <v>2.15</v>
+      </c>
+      <c r="AK128">
+        <v>1.62</v>
+      </c>
+      <c r="AL128">
+        <v>1.25</v>
+      </c>
+      <c r="AM128">
+        <v>1.36</v>
+      </c>
+      <c r="AN128">
+        <v>0.9</v>
+      </c>
+      <c r="AO128">
+        <v>0.9</v>
+      </c>
+      <c r="AP128">
+        <v>0.91</v>
+      </c>
+      <c r="AQ128">
+        <v>0.91</v>
+      </c>
+      <c r="AR128">
+        <v>1.49</v>
+      </c>
+      <c r="AS128">
+        <v>1.62</v>
+      </c>
+      <c r="AT128">
+        <v>3.11</v>
+      </c>
+      <c r="AU128">
+        <v>7</v>
+      </c>
+      <c r="AV128">
+        <v>8</v>
+      </c>
+      <c r="AW128">
+        <v>10</v>
+      </c>
+      <c r="AX128">
+        <v>8</v>
+      </c>
+      <c r="AY128">
+        <v>20</v>
+      </c>
+      <c r="AZ128">
+        <v>18</v>
+      </c>
+      <c r="BA128">
+        <v>4</v>
+      </c>
+      <c r="BB128">
+        <v>4</v>
+      </c>
+      <c r="BC128">
+        <v>8</v>
+      </c>
+      <c r="BD128">
+        <v>2.16</v>
+      </c>
+      <c r="BE128">
+        <v>8.5</v>
+      </c>
+      <c r="BF128">
+        <v>1.95</v>
+      </c>
+      <c r="BG128">
+        <v>1.19</v>
+      </c>
+      <c r="BH128">
+        <v>3.74</v>
+      </c>
+      <c r="BI128">
+        <v>1.4</v>
+      </c>
+      <c r="BJ128">
+        <v>2.64</v>
+      </c>
+      <c r="BK128">
+        <v>1.72</v>
+      </c>
+      <c r="BL128">
+        <v>2</v>
+      </c>
+      <c r="BM128">
+        <v>2.15</v>
+      </c>
+      <c r="BN128">
+        <v>1.59</v>
+      </c>
+      <c r="BO128">
+        <v>2.83</v>
+      </c>
+      <c r="BP128">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7487153</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45692.6875</v>
+      </c>
+      <c r="F129">
+        <v>22</v>
+      </c>
+      <c r="G129" t="s">
+        <v>77</v>
+      </c>
+      <c r="H129" t="s">
+        <v>76</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>3</v>
+      </c>
+      <c r="M129">
+        <v>3</v>
+      </c>
+      <c r="N129">
+        <v>6</v>
+      </c>
+      <c r="O129" t="s">
+        <v>178</v>
+      </c>
+      <c r="P129" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q129">
+        <v>3.5</v>
+      </c>
+      <c r="R129">
+        <v>2.15</v>
+      </c>
+      <c r="S129">
+        <v>2.7</v>
+      </c>
+      <c r="T129">
+        <v>1.35</v>
+      </c>
+      <c r="U129">
+        <v>2.95</v>
+      </c>
+      <c r="V129">
+        <v>2.55</v>
+      </c>
+      <c r="W129">
+        <v>1.45</v>
+      </c>
+      <c r="X129">
+        <v>6.3</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
+        <v>3.08</v>
+      </c>
+      <c r="AA129">
+        <v>3.47</v>
+      </c>
+      <c r="AB129">
+        <v>2.18</v>
+      </c>
+      <c r="AC129">
+        <v>1.05</v>
+      </c>
+      <c r="AD129">
+        <v>9.5</v>
+      </c>
+      <c r="AE129">
+        <v>1.25</v>
+      </c>
+      <c r="AF129">
+        <v>3.7</v>
+      </c>
+      <c r="AG129">
+        <v>1.79</v>
+      </c>
+      <c r="AH129">
+        <v>1.95</v>
+      </c>
+      <c r="AI129">
+        <v>1.62</v>
+      </c>
+      <c r="AJ129">
+        <v>2.1</v>
+      </c>
+      <c r="AK129">
+        <v>1.65</v>
+      </c>
+      <c r="AL129">
+        <v>1.25</v>
+      </c>
+      <c r="AM129">
+        <v>1.35</v>
+      </c>
+      <c r="AN129">
+        <v>1.6</v>
+      </c>
+      <c r="AO129">
+        <v>1.2</v>
+      </c>
+      <c r="AP129">
+        <v>1.55</v>
+      </c>
+      <c r="AQ129">
+        <v>1.18</v>
+      </c>
+      <c r="AR129">
+        <v>1.71</v>
+      </c>
+      <c r="AS129">
+        <v>1.58</v>
+      </c>
+      <c r="AT129">
+        <v>3.29</v>
+      </c>
+      <c r="AU129">
+        <v>8</v>
+      </c>
+      <c r="AV129">
+        <v>12</v>
+      </c>
+      <c r="AW129">
+        <v>8</v>
+      </c>
+      <c r="AX129">
+        <v>8</v>
+      </c>
+      <c r="AY129">
+        <v>18</v>
+      </c>
+      <c r="AZ129">
+        <v>20</v>
+      </c>
+      <c r="BA129">
+        <v>6</v>
+      </c>
+      <c r="BB129">
+        <v>8</v>
+      </c>
+      <c r="BC129">
+        <v>14</v>
+      </c>
+      <c r="BD129">
+        <v>2.19</v>
+      </c>
+      <c r="BE129">
+        <v>8.6</v>
+      </c>
+      <c r="BF129">
+        <v>1.92</v>
+      </c>
+      <c r="BG129">
+        <v>1.17</v>
+      </c>
+      <c r="BH129">
+        <v>3.98</v>
+      </c>
+      <c r="BI129">
+        <v>1.35</v>
+      </c>
+      <c r="BJ129">
+        <v>2.74</v>
+      </c>
+      <c r="BK129">
+        <v>1.64</v>
+      </c>
+      <c r="BL129">
+        <v>2.07</v>
+      </c>
+      <c r="BM129">
+        <v>2.09</v>
+      </c>
+      <c r="BN129">
+        <v>1.66</v>
+      </c>
+      <c r="BO129">
+        <v>2.71</v>
+      </c>
+      <c r="BP129">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7487154</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45693.6875</v>
+      </c>
+      <c r="F130">
+        <v>22</v>
+      </c>
+      <c r="G130" t="s">
+        <v>80</v>
+      </c>
+      <c r="H130" t="s">
+        <v>70</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>1</v>
+      </c>
+      <c r="N130">
+        <v>3</v>
+      </c>
+      <c r="O130" t="s">
+        <v>179</v>
+      </c>
+      <c r="P130" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q130">
+        <v>2.9</v>
+      </c>
+      <c r="R130">
+        <v>2.15</v>
+      </c>
+      <c r="S130">
+        <v>3.1</v>
+      </c>
+      <c r="T130">
+        <v>1.32</v>
+      </c>
+      <c r="U130">
+        <v>3.1</v>
+      </c>
+      <c r="V130">
+        <v>2.4</v>
+      </c>
+      <c r="W130">
+        <v>1.49</v>
+      </c>
+      <c r="X130">
+        <v>5.75</v>
+      </c>
+      <c r="Y130">
+        <v>1.11</v>
+      </c>
+      <c r="Z130">
+        <v>2.44</v>
+      </c>
+      <c r="AA130">
+        <v>3.47</v>
+      </c>
+      <c r="AB130">
+        <v>2.68</v>
+      </c>
+      <c r="AC130">
+        <v>1.05</v>
+      </c>
+      <c r="AD130">
+        <v>9.5</v>
+      </c>
+      <c r="AE130">
+        <v>1.22</v>
+      </c>
+      <c r="AF130">
+        <v>4</v>
+      </c>
+      <c r="AG130">
+        <v>1.65</v>
+      </c>
+      <c r="AH130">
+        <v>2.05</v>
+      </c>
+      <c r="AI130">
+        <v>1.57</v>
+      </c>
+      <c r="AJ130">
+        <v>2.25</v>
+      </c>
+      <c r="AK130">
+        <v>1.44</v>
+      </c>
+      <c r="AL130">
+        <v>1.29</v>
+      </c>
+      <c r="AM130">
+        <v>1.52</v>
+      </c>
+      <c r="AN130">
+        <v>1.7</v>
+      </c>
+      <c r="AO130">
+        <v>1.5</v>
+      </c>
+      <c r="AP130">
+        <v>1.82</v>
+      </c>
+      <c r="AQ130">
+        <v>1.36</v>
+      </c>
+      <c r="AR130">
+        <v>1.84</v>
+      </c>
+      <c r="AS130">
+        <v>1.6</v>
+      </c>
+      <c r="AT130">
+        <v>3.44</v>
+      </c>
+      <c r="AU130">
+        <v>4</v>
+      </c>
+      <c r="AV130">
+        <v>5</v>
+      </c>
+      <c r="AW130">
+        <v>16</v>
+      </c>
+      <c r="AX130">
+        <v>2</v>
+      </c>
+      <c r="AY130">
+        <v>29</v>
+      </c>
+      <c r="AZ130">
+        <v>9</v>
+      </c>
+      <c r="BA130">
+        <v>7</v>
+      </c>
+      <c r="BB130">
+        <v>0</v>
+      </c>
+      <c r="BC130">
+        <v>7</v>
+      </c>
+      <c r="BD130">
+        <v>0</v>
+      </c>
+      <c r="BE130">
+        <v>0</v>
+      </c>
+      <c r="BF130">
+        <v>0</v>
+      </c>
+      <c r="BG130">
+        <v>0</v>
+      </c>
+      <c r="BH130">
+        <v>0</v>
+      </c>
+      <c r="BI130">
+        <v>0</v>
+      </c>
+      <c r="BJ130">
+        <v>0</v>
+      </c>
+      <c r="BK130">
+        <v>0</v>
+      </c>
+      <c r="BL130">
+        <v>0</v>
+      </c>
+      <c r="BM130">
+        <v>0</v>
+      </c>
+      <c r="BN130">
+        <v>0</v>
+      </c>
+      <c r="BO130">
+        <v>0</v>
+      </c>
+      <c r="BP130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7487156</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45693.6875</v>
+      </c>
+      <c r="F131">
+        <v>22</v>
+      </c>
+      <c r="G131" t="s">
+        <v>73</v>
+      </c>
+      <c r="H131" t="s">
+        <v>71</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>6</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>7</v>
+      </c>
+      <c r="O131" t="s">
+        <v>180</v>
+      </c>
+      <c r="P131" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q131">
+        <v>1.71</v>
+      </c>
+      <c r="R131">
+        <v>2.65</v>
+      </c>
+      <c r="S131">
+        <v>6.25</v>
+      </c>
+      <c r="T131">
+        <v>1.23</v>
+      </c>
+      <c r="U131">
+        <v>3.8</v>
+      </c>
+      <c r="V131">
+        <v>2.05</v>
+      </c>
+      <c r="W131">
+        <v>1.68</v>
+      </c>
+      <c r="X131">
+        <v>4.4</v>
+      </c>
+      <c r="Y131">
+        <v>1.18</v>
+      </c>
+      <c r="Z131">
+        <v>1.29</v>
+      </c>
+      <c r="AA131">
+        <v>5.9</v>
+      </c>
+      <c r="AB131">
+        <v>8.1</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>17</v>
+      </c>
+      <c r="AE131">
+        <v>1.12</v>
+      </c>
+      <c r="AF131">
+        <v>5.75</v>
+      </c>
+      <c r="AG131">
+        <v>1.4</v>
+      </c>
+      <c r="AH131">
+        <v>2.82</v>
+      </c>
+      <c r="AI131">
+        <v>1.75</v>
+      </c>
+      <c r="AJ131">
+        <v>1.95</v>
+      </c>
+      <c r="AK131">
+        <v>1.08</v>
+      </c>
+      <c r="AL131">
+        <v>1.14</v>
+      </c>
+      <c r="AM131">
+        <v>3.3</v>
+      </c>
+      <c r="AN131">
+        <v>1.8</v>
+      </c>
+      <c r="AO131">
+        <v>0.7</v>
+      </c>
+      <c r="AP131">
+        <v>1.91</v>
+      </c>
+      <c r="AQ131">
+        <v>0.64</v>
+      </c>
+      <c r="AR131">
+        <v>1.95</v>
+      </c>
+      <c r="AS131">
+        <v>1.21</v>
+      </c>
+      <c r="AT131">
+        <v>3.16</v>
+      </c>
+      <c r="AU131">
+        <v>11</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>21</v>
+      </c>
+      <c r="AX131">
+        <v>3</v>
+      </c>
+      <c r="AY131">
+        <v>38</v>
+      </c>
+      <c r="AZ131">
+        <v>7</v>
+      </c>
+      <c r="BA131">
+        <v>8</v>
+      </c>
+      <c r="BB131">
+        <v>2</v>
+      </c>
+      <c r="BC131">
+        <v>10</v>
+      </c>
+      <c r="BD131">
+        <v>0</v>
+      </c>
+      <c r="BE131">
+        <v>0</v>
+      </c>
+      <c r="BF131">
+        <v>0</v>
+      </c>
+      <c r="BG131">
+        <v>0</v>
+      </c>
+      <c r="BH131">
+        <v>0</v>
+      </c>
+      <c r="BI131">
+        <v>0</v>
+      </c>
+      <c r="BJ131">
+        <v>0</v>
+      </c>
+      <c r="BK131">
+        <v>0</v>
+      </c>
+      <c r="BL131">
+        <v>0</v>
+      </c>
+      <c r="BM131">
+        <v>0</v>
+      </c>
+      <c r="BN131">
+        <v>0</v>
+      </c>
+      <c r="BO131">
+        <v>0</v>
+      </c>
+      <c r="BP131">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="258">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,9 @@
     <t>['5', '9', '66', '72', '76', '90+2']</t>
   </si>
   <si>
+    <t>['4', '57']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -782,6 +785,9 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['63', '80']</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1399,7 +1405,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1605,7 +1611,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1686,7 +1692,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ3">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1889,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ4">
         <v>1.09</v>
@@ -2017,7 +2023,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2223,7 +2229,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2429,7 +2435,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2635,7 +2641,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3047,7 +3053,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3128,7 +3134,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ10">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3253,7 +3259,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3331,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>1.36</v>
@@ -3459,7 +3465,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3871,7 +3877,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4077,7 +4083,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4695,7 +4701,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4901,7 +4907,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -4982,7 +4988,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -5185,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ20">
         <v>0.64</v>
@@ -5519,7 +5525,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5931,7 +5937,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6012,7 +6018,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ24">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR24">
         <v>1.94</v>
@@ -6343,7 +6349,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6755,7 +6761,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7039,7 +7045,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>0.64</v>
@@ -7167,7 +7173,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7373,7 +7379,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -7863,7 +7869,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ33">
         <v>1.18</v>
@@ -8072,7 +8078,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ34">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR34">
         <v>2.41</v>
@@ -8197,7 +8203,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q35">
         <v>2.7</v>
@@ -8403,7 +8409,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8609,7 +8615,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8690,7 +8696,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ37">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR37">
         <v>1.76</v>
@@ -8815,7 +8821,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9021,7 +9027,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9099,10 +9105,10 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
         <v>2.16</v>
@@ -9227,7 +9233,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9639,7 +9645,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9717,7 +9723,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ42">
         <v>0.91</v>
@@ -9845,7 +9851,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -9926,7 +9932,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
@@ -10463,7 +10469,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -11081,7 +11087,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11287,7 +11293,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11493,7 +11499,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11777,7 +11783,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -12189,7 +12195,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>0.91</v>
@@ -12317,7 +12323,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12523,7 +12529,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12604,7 +12610,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ56">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR56">
         <v>1.56</v>
@@ -12810,7 +12816,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ57">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR57">
         <v>1.51</v>
@@ -13141,7 +13147,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13219,7 +13225,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
         <v>1.09</v>
@@ -13965,7 +13971,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14043,7 +14049,7 @@
         <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ63">
         <v>1.64</v>
@@ -14171,7 +14177,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14377,7 +14383,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14789,7 +14795,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14995,7 +15001,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15201,7 +15207,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15282,7 +15288,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ69">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
@@ -15407,7 +15413,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15613,7 +15619,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16025,7 +16031,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16106,7 +16112,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ73">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16515,7 +16521,7 @@
         <v>0.17</v>
       </c>
       <c r="AP75">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>0.36</v>
@@ -16643,7 +16649,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17545,7 +17551,7 @@
         <v>0.83</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ80">
         <v>0.91</v>
@@ -17673,7 +17679,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17879,7 +17885,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -17960,7 +17966,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ82">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR82">
         <v>1.87</v>
@@ -18085,7 +18091,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18166,7 +18172,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ83">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18291,7 +18297,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18497,7 +18503,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18703,7 +18709,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18909,7 +18915,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19402,7 +19408,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ89">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR89">
         <v>1.82</v>
@@ -19811,7 +19817,7 @@
         <v>1.57</v>
       </c>
       <c r="AP91">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ91">
         <v>1.18</v>
@@ -20017,7 +20023,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>0.91</v>
@@ -20226,7 +20232,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ93">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR93">
         <v>0.95</v>
@@ -20351,7 +20357,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20557,7 +20563,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20635,7 +20641,7 @@
         <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ95">
         <v>0.91</v>
@@ -20969,7 +20975,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21175,7 +21181,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21381,7 +21387,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21587,7 +21593,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21874,7 +21880,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR101">
         <v>1.77</v>
@@ -21999,7 +22005,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22205,7 +22211,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22411,7 +22417,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22489,10 +22495,10 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ104">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR104">
         <v>1.23</v>
@@ -22617,7 +22623,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22901,7 +22907,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23029,7 +23035,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23235,7 +23241,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23441,7 +23447,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23853,7 +23859,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24471,7 +24477,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24758,7 +24764,7 @@
         <v>2</v>
       </c>
       <c r="AQ115">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25295,7 +25301,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25373,7 +25379,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ118">
         <v>1.36</v>
@@ -25501,7 +25507,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25707,7 +25713,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25785,7 +25791,7 @@
         <v>1.11</v>
       </c>
       <c r="AP120">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
         <v>0.91</v>
@@ -25994,7 +26000,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ121">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR121">
         <v>1.67</v>
@@ -26119,7 +26125,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26325,7 +26331,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26531,7 +26537,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26943,7 +26949,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27355,7 +27361,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27561,7 +27567,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27767,7 +27773,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27973,7 +27979,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28129,6 +28135,418 @@
         <v>0</v>
       </c>
       <c r="BP131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7487151</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45694.6875</v>
+      </c>
+      <c r="F132">
+        <v>22</v>
+      </c>
+      <c r="G132" t="s">
+        <v>79</v>
+      </c>
+      <c r="H132" t="s">
+        <v>75</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>2</v>
+      </c>
+      <c r="L132">
+        <v>2</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>3</v>
+      </c>
+      <c r="O132" t="s">
+        <v>181</v>
+      </c>
+      <c r="P132" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q132">
+        <v>2.15</v>
+      </c>
+      <c r="R132">
+        <v>2.4</v>
+      </c>
+      <c r="S132">
+        <v>4.2</v>
+      </c>
+      <c r="T132">
+        <v>1.26</v>
+      </c>
+      <c r="U132">
+        <v>3.5</v>
+      </c>
+      <c r="V132">
+        <v>2.15</v>
+      </c>
+      <c r="W132">
+        <v>1.6</v>
+      </c>
+      <c r="X132">
+        <v>4.8</v>
+      </c>
+      <c r="Y132">
+        <v>1.15</v>
+      </c>
+      <c r="Z132">
+        <v>1.75</v>
+      </c>
+      <c r="AA132">
+        <v>3.94</v>
+      </c>
+      <c r="AB132">
+        <v>4.1</v>
+      </c>
+      <c r="AC132">
+        <v>1.02</v>
+      </c>
+      <c r="AD132">
+        <v>13</v>
+      </c>
+      <c r="AE132">
+        <v>1.17</v>
+      </c>
+      <c r="AF132">
+        <v>5</v>
+      </c>
+      <c r="AG132">
+        <v>1.53</v>
+      </c>
+      <c r="AH132">
+        <v>2.25</v>
+      </c>
+      <c r="AI132">
+        <v>1.55</v>
+      </c>
+      <c r="AJ132">
+        <v>2.25</v>
+      </c>
+      <c r="AK132">
+        <v>1.2</v>
+      </c>
+      <c r="AL132">
+        <v>1.22</v>
+      </c>
+      <c r="AM132">
+        <v>2.15</v>
+      </c>
+      <c r="AN132">
+        <v>1.9</v>
+      </c>
+      <c r="AO132">
+        <v>1.6</v>
+      </c>
+      <c r="AP132">
+        <v>2</v>
+      </c>
+      <c r="AQ132">
+        <v>1.45</v>
+      </c>
+      <c r="AR132">
+        <v>1.81</v>
+      </c>
+      <c r="AS132">
+        <v>1.6</v>
+      </c>
+      <c r="AT132">
+        <v>3.41</v>
+      </c>
+      <c r="AU132">
+        <v>6</v>
+      </c>
+      <c r="AV132">
+        <v>6</v>
+      </c>
+      <c r="AW132">
+        <v>6</v>
+      </c>
+      <c r="AX132">
+        <v>21</v>
+      </c>
+      <c r="AY132">
+        <v>15</v>
+      </c>
+      <c r="AZ132">
+        <v>39</v>
+      </c>
+      <c r="BA132">
+        <v>4</v>
+      </c>
+      <c r="BB132">
+        <v>9</v>
+      </c>
+      <c r="BC132">
+        <v>13</v>
+      </c>
+      <c r="BD132">
+        <v>0</v>
+      </c>
+      <c r="BE132">
+        <v>0</v>
+      </c>
+      <c r="BF132">
+        <v>0</v>
+      </c>
+      <c r="BG132">
+        <v>0</v>
+      </c>
+      <c r="BH132">
+        <v>0</v>
+      </c>
+      <c r="BI132">
+        <v>0</v>
+      </c>
+      <c r="BJ132">
+        <v>0</v>
+      </c>
+      <c r="BK132">
+        <v>0</v>
+      </c>
+      <c r="BL132">
+        <v>0</v>
+      </c>
+      <c r="BM132">
+        <v>0</v>
+      </c>
+      <c r="BN132">
+        <v>0</v>
+      </c>
+      <c r="BO132">
+        <v>0</v>
+      </c>
+      <c r="BP132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7487155</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45694.6875</v>
+      </c>
+      <c r="F133">
+        <v>22</v>
+      </c>
+      <c r="G133" t="s">
+        <v>72</v>
+      </c>
+      <c r="H133" t="s">
+        <v>81</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>2</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>83</v>
+      </c>
+      <c r="P133" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q133">
+        <v>3.6</v>
+      </c>
+      <c r="R133">
+        <v>2.15</v>
+      </c>
+      <c r="S133">
+        <v>2.6</v>
+      </c>
+      <c r="T133">
+        <v>1.34</v>
+      </c>
+      <c r="U133">
+        <v>2.95</v>
+      </c>
+      <c r="V133">
+        <v>2.55</v>
+      </c>
+      <c r="W133">
+        <v>1.46</v>
+      </c>
+      <c r="X133">
+        <v>6.25</v>
+      </c>
+      <c r="Y133">
+        <v>1.1</v>
+      </c>
+      <c r="Z133">
+        <v>3.63</v>
+      </c>
+      <c r="AA133">
+        <v>3.62</v>
+      </c>
+      <c r="AB133">
+        <v>1.93</v>
+      </c>
+      <c r="AC133">
+        <v>1.05</v>
+      </c>
+      <c r="AD133">
+        <v>9.5</v>
+      </c>
+      <c r="AE133">
+        <v>1.25</v>
+      </c>
+      <c r="AF133">
+        <v>3.75</v>
+      </c>
+      <c r="AG133">
+        <v>1.79</v>
+      </c>
+      <c r="AH133">
+        <v>1.95</v>
+      </c>
+      <c r="AI133">
+        <v>1.66</v>
+      </c>
+      <c r="AJ133">
+        <v>2.05</v>
+      </c>
+      <c r="AK133">
+        <v>1.71</v>
+      </c>
+      <c r="AL133">
+        <v>1.29</v>
+      </c>
+      <c r="AM133">
+        <v>1.31</v>
+      </c>
+      <c r="AN133">
+        <v>1</v>
+      </c>
+      <c r="AO133">
+        <v>1.4</v>
+      </c>
+      <c r="AP133">
+        <v>0.91</v>
+      </c>
+      <c r="AQ133">
+        <v>1.55</v>
+      </c>
+      <c r="AR133">
+        <v>1.28</v>
+      </c>
+      <c r="AS133">
+        <v>1.48</v>
+      </c>
+      <c r="AT133">
+        <v>2.76</v>
+      </c>
+      <c r="AU133">
+        <v>4</v>
+      </c>
+      <c r="AV133">
+        <v>9</v>
+      </c>
+      <c r="AW133">
+        <v>6</v>
+      </c>
+      <c r="AX133">
+        <v>14</v>
+      </c>
+      <c r="AY133">
+        <v>12</v>
+      </c>
+      <c r="AZ133">
+        <v>28</v>
+      </c>
+      <c r="BA133">
+        <v>2</v>
+      </c>
+      <c r="BB133">
+        <v>12</v>
+      </c>
+      <c r="BC133">
+        <v>14</v>
+      </c>
+      <c r="BD133">
+        <v>0</v>
+      </c>
+      <c r="BE133">
+        <v>0</v>
+      </c>
+      <c r="BF133">
+        <v>0</v>
+      </c>
+      <c r="BG133">
+        <v>0</v>
+      </c>
+      <c r="BH133">
+        <v>0</v>
+      </c>
+      <c r="BI133">
+        <v>0</v>
+      </c>
+      <c r="BJ133">
+        <v>0</v>
+      </c>
+      <c r="BK133">
+        <v>0</v>
+      </c>
+      <c r="BL133">
+        <v>0</v>
+      </c>
+      <c r="BM133">
+        <v>0</v>
+      </c>
+      <c r="BN133">
+        <v>0</v>
+      </c>
+      <c r="BO133">
+        <v>0</v>
+      </c>
+      <c r="BP133">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="262">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -562,6 +562,15 @@
     <t>['4', '57']</t>
   </si>
   <si>
+    <t>['27', '32', '36', '72']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['1', '17', '42', '53', '74']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -772,9 +781,6 @@
     <t>['15', '88']</t>
   </si>
   <si>
-    <t>['86']</t>
-  </si>
-  <si>
     <t>['36']</t>
   </si>
   <si>
@@ -788,6 +794,12 @@
   </si>
   <si>
     <t>['63', '80']</t>
+  </si>
+  <si>
+    <t>['45']</t>
+  </si>
+  <si>
+    <t>['37']</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1405,7 +1417,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1483,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1611,7 +1623,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2023,7 +2035,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2101,10 +2113,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2229,7 +2241,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2307,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6">
         <v>1.64</v>
@@ -2435,7 +2447,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2641,7 +2653,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3053,7 +3065,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3259,7 +3271,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3465,7 +3477,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3546,7 +3558,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ12">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR12">
         <v>2.07</v>
@@ -3877,7 +3889,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4083,7 +4095,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4367,7 +4379,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.18</v>
@@ -4576,7 +4588,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ17">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
         <v>1.15</v>
@@ -4701,7 +4713,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4779,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ18">
         <v>1.09</v>
@@ -4907,7 +4919,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -4985,7 +4997,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1.55</v>
@@ -5194,7 +5206,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ20">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR20">
         <v>1.02</v>
@@ -5525,7 +5537,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5937,7 +5949,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6015,7 +6027,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>1.45</v>
@@ -6349,7 +6361,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6761,7 +6773,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6842,7 +6854,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ28">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR28">
         <v>1.22</v>
@@ -7048,7 +7060,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7173,7 +7185,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7379,7 +7391,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -7663,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>0.91</v>
@@ -8203,7 +8215,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q35">
         <v>2.7</v>
@@ -8281,7 +8293,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1.09</v>
@@ -8409,7 +8421,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8487,7 +8499,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ36">
         <v>1.36</v>
@@ -8615,7 +8627,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8821,7 +8833,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9027,7 +9039,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9233,7 +9245,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9311,10 +9323,10 @@
         <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ40">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR40">
         <v>1.54</v>
@@ -9645,7 +9657,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9851,7 +9863,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10469,7 +10481,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10547,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -10756,7 +10768,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ47">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR47">
         <v>1.94</v>
@@ -11087,7 +11099,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11165,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>0.36</v>
@@ -11293,7 +11305,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11374,7 +11386,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ50">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR50">
         <v>1.38</v>
@@ -11499,7 +11511,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -12323,7 +12335,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12529,7 +12541,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12813,7 +12825,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
         <v>1.45</v>
@@ -13022,7 +13034,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ58">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13147,7 +13159,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13431,7 +13443,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60">
         <v>0.36</v>
@@ -13843,7 +13855,7 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -13971,7 +13983,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14177,7 +14189,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14258,7 +14270,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ64">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14383,7 +14395,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14667,7 +14679,7 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>0.91</v>
@@ -14795,7 +14807,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15001,7 +15013,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15207,7 +15219,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15413,7 +15425,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15619,7 +15631,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15697,7 +15709,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
         <v>1.64</v>
@@ -16031,7 +16043,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16649,7 +16661,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16730,7 +16742,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ76">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -16933,7 +16945,7 @@
         <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ77">
         <v>1.18</v>
@@ -17139,10 +17151,10 @@
         <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -17679,7 +17691,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17885,7 +17897,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18091,7 +18103,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18297,7 +18309,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18503,7 +18515,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18581,7 +18593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
         <v>1.36</v>
@@ -18709,7 +18721,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18915,7 +18927,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19199,10 +19211,10 @@
         <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ88">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19405,7 +19417,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
         <v>1.55</v>
@@ -19614,7 +19626,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ90">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -20357,7 +20369,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20563,7 +20575,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20644,7 +20656,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ95">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR95">
         <v>1.3</v>
@@ -20975,7 +20987,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21053,7 +21065,7 @@
         <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.09</v>
@@ -21181,7 +21193,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21262,7 +21274,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ98">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21387,7 +21399,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21593,7 +21605,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21877,7 +21889,7 @@
         <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ101">
         <v>1.55</v>
@@ -22005,7 +22017,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22211,7 +22223,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22417,7 +22429,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22623,7 +22635,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22704,7 +22716,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR105">
         <v>0.93</v>
@@ -23035,7 +23047,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23113,7 +23125,7 @@
         <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>1.18</v>
@@ -23241,7 +23253,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23319,7 +23331,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ108">
         <v>0.91</v>
@@ -23447,7 +23459,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23731,7 +23743,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>0.36</v>
@@ -23859,7 +23871,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24352,7 +24364,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ113">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR113">
         <v>1.39</v>
@@ -24477,7 +24489,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24555,7 +24567,7 @@
         <v>1.56</v>
       </c>
       <c r="AP114">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>1.64</v>
@@ -24761,7 +24773,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ115">
         <v>1.45</v>
@@ -25301,7 +25313,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25507,7 +25519,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25713,7 +25725,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25794,7 +25806,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR120">
         <v>1.76</v>
@@ -26125,7 +26137,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26203,7 +26215,7 @@
         <v>0.7</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ122">
         <v>0.91</v>
@@ -26331,7 +26343,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26409,10 +26421,10 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR123">
         <v>1.87</v>
@@ -26537,7 +26549,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26949,7 +26961,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27361,7 +27373,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27567,7 +27579,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27773,7 +27785,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27979,7 +27991,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28057,10 +28069,10 @@
         <v>0.7</v>
       </c>
       <c r="AP131">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR131">
         <v>1.95</v>
@@ -28391,7 +28403,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28548,6 +28560,624 @@
       </c>
       <c r="BP133">
         <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7784915</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45696.58333333334</v>
+      </c>
+      <c r="F134">
+        <v>23</v>
+      </c>
+      <c r="G134" t="s">
+        <v>74</v>
+      </c>
+      <c r="H134" t="s">
+        <v>71</v>
+      </c>
+      <c r="I134">
+        <v>3</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>4</v>
+      </c>
+      <c r="L134">
+        <v>4</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>5</v>
+      </c>
+      <c r="O134" t="s">
+        <v>182</v>
+      </c>
+      <c r="P134" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q134">
+        <v>1.78</v>
+      </c>
+      <c r="R134">
+        <v>2.6</v>
+      </c>
+      <c r="S134">
+        <v>5.75</v>
+      </c>
+      <c r="T134">
+        <v>1.24</v>
+      </c>
+      <c r="U134">
+        <v>3.6</v>
+      </c>
+      <c r="V134">
+        <v>2.15</v>
+      </c>
+      <c r="W134">
+        <v>1.62</v>
+      </c>
+      <c r="X134">
+        <v>4.75</v>
+      </c>
+      <c r="Y134">
+        <v>1.16</v>
+      </c>
+      <c r="Z134">
+        <v>1.38</v>
+      </c>
+      <c r="AA134">
+        <v>5.03</v>
+      </c>
+      <c r="AB134">
+        <v>7.1</v>
+      </c>
+      <c r="AC134">
+        <v>1.02</v>
+      </c>
+      <c r="AD134">
+        <v>11</v>
+      </c>
+      <c r="AE134">
+        <v>1.17</v>
+      </c>
+      <c r="AF134">
+        <v>5</v>
+      </c>
+      <c r="AG134">
+        <v>1.54</v>
+      </c>
+      <c r="AH134">
+        <v>2.38</v>
+      </c>
+      <c r="AI134">
+        <v>1.77</v>
+      </c>
+      <c r="AJ134">
+        <v>1.93</v>
+      </c>
+      <c r="AK134">
+        <v>1.1</v>
+      </c>
+      <c r="AL134">
+        <v>1.16</v>
+      </c>
+      <c r="AM134">
+        <v>2.95</v>
+      </c>
+      <c r="AN134">
+        <v>2</v>
+      </c>
+      <c r="AO134">
+        <v>0.64</v>
+      </c>
+      <c r="AP134">
+        <v>2.08</v>
+      </c>
+      <c r="AQ134">
+        <v>0.58</v>
+      </c>
+      <c r="AR134">
+        <v>1.83</v>
+      </c>
+      <c r="AS134">
+        <v>1.17</v>
+      </c>
+      <c r="AT134">
+        <v>3</v>
+      </c>
+      <c r="AU134">
+        <v>8</v>
+      </c>
+      <c r="AV134">
+        <v>6</v>
+      </c>
+      <c r="AW134">
+        <v>10</v>
+      </c>
+      <c r="AX134">
+        <v>5</v>
+      </c>
+      <c r="AY134">
+        <v>18</v>
+      </c>
+      <c r="AZ134">
+        <v>13</v>
+      </c>
+      <c r="BA134">
+        <v>5</v>
+      </c>
+      <c r="BB134">
+        <v>6</v>
+      </c>
+      <c r="BC134">
+        <v>11</v>
+      </c>
+      <c r="BD134">
+        <v>1.13</v>
+      </c>
+      <c r="BE134">
+        <v>11.25</v>
+      </c>
+      <c r="BF134">
+        <v>8.5</v>
+      </c>
+      <c r="BG134">
+        <v>1.13</v>
+      </c>
+      <c r="BH134">
+        <v>4.5</v>
+      </c>
+      <c r="BI134">
+        <v>1.28</v>
+      </c>
+      <c r="BJ134">
+        <v>3.05</v>
+      </c>
+      <c r="BK134">
+        <v>1.58</v>
+      </c>
+      <c r="BL134">
+        <v>2.31</v>
+      </c>
+      <c r="BM134">
+        <v>1.97</v>
+      </c>
+      <c r="BN134">
+        <v>1.83</v>
+      </c>
+      <c r="BO134">
+        <v>2.51</v>
+      </c>
+      <c r="BP134">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7784916</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45696.58333333334</v>
+      </c>
+      <c r="F135">
+        <v>23</v>
+      </c>
+      <c r="G135" t="s">
+        <v>70</v>
+      </c>
+      <c r="H135" t="s">
+        <v>78</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>2</v>
+      </c>
+      <c r="O135" t="s">
+        <v>183</v>
+      </c>
+      <c r="P135" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q135">
+        <v>2.3</v>
+      </c>
+      <c r="R135">
+        <v>2.2</v>
+      </c>
+      <c r="S135">
+        <v>4.2</v>
+      </c>
+      <c r="T135">
+        <v>1.33</v>
+      </c>
+      <c r="U135">
+        <v>3</v>
+      </c>
+      <c r="V135">
+        <v>2.5</v>
+      </c>
+      <c r="W135">
+        <v>1.46</v>
+      </c>
+      <c r="X135">
+        <v>6</v>
+      </c>
+      <c r="Y135">
+        <v>1.11</v>
+      </c>
+      <c r="Z135">
+        <v>1.81</v>
+      </c>
+      <c r="AA135">
+        <v>3.75</v>
+      </c>
+      <c r="AB135">
+        <v>4.18</v>
+      </c>
+      <c r="AC135">
+        <v>1.05</v>
+      </c>
+      <c r="AD135">
+        <v>9.5</v>
+      </c>
+      <c r="AE135">
+        <v>1.24</v>
+      </c>
+      <c r="AF135">
+        <v>3.65</v>
+      </c>
+      <c r="AG135">
+        <v>1.75</v>
+      </c>
+      <c r="AH135">
+        <v>1.95</v>
+      </c>
+      <c r="AI135">
+        <v>1.71</v>
+      </c>
+      <c r="AJ135">
+        <v>2</v>
+      </c>
+      <c r="AK135">
+        <v>1.23</v>
+      </c>
+      <c r="AL135">
+        <v>1.26</v>
+      </c>
+      <c r="AM135">
+        <v>1.95</v>
+      </c>
+      <c r="AN135">
+        <v>2.09</v>
+      </c>
+      <c r="AO135">
+        <v>1</v>
+      </c>
+      <c r="AP135">
+        <v>2</v>
+      </c>
+      <c r="AQ135">
+        <v>1</v>
+      </c>
+      <c r="AR135">
+        <v>1.87</v>
+      </c>
+      <c r="AS135">
+        <v>1.32</v>
+      </c>
+      <c r="AT135">
+        <v>3.19</v>
+      </c>
+      <c r="AU135">
+        <v>12</v>
+      </c>
+      <c r="AV135">
+        <v>3</v>
+      </c>
+      <c r="AW135">
+        <v>17</v>
+      </c>
+      <c r="AX135">
+        <v>4</v>
+      </c>
+      <c r="AY135">
+        <v>37</v>
+      </c>
+      <c r="AZ135">
+        <v>8</v>
+      </c>
+      <c r="BA135">
+        <v>10</v>
+      </c>
+      <c r="BB135">
+        <v>1</v>
+      </c>
+      <c r="BC135">
+        <v>11</v>
+      </c>
+      <c r="BD135">
+        <v>1.46</v>
+      </c>
+      <c r="BE135">
+        <v>7.3</v>
+      </c>
+      <c r="BF135">
+        <v>3.7</v>
+      </c>
+      <c r="BG135">
+        <v>1.24</v>
+      </c>
+      <c r="BH135">
+        <v>3.34</v>
+      </c>
+      <c r="BI135">
+        <v>1.51</v>
+      </c>
+      <c r="BJ135">
+        <v>2.48</v>
+      </c>
+      <c r="BK135">
+        <v>1.86</v>
+      </c>
+      <c r="BL135">
+        <v>1.94</v>
+      </c>
+      <c r="BM135">
+        <v>2.3</v>
+      </c>
+      <c r="BN135">
+        <v>1.58</v>
+      </c>
+      <c r="BO135">
+        <v>3.08</v>
+      </c>
+      <c r="BP135">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7784917</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45696.6875</v>
+      </c>
+      <c r="F136">
+        <v>23</v>
+      </c>
+      <c r="G136" t="s">
+        <v>73</v>
+      </c>
+      <c r="H136" t="s">
+        <v>77</v>
+      </c>
+      <c r="I136">
+        <v>3</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>4</v>
+      </c>
+      <c r="L136">
+        <v>5</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>6</v>
+      </c>
+      <c r="O136" t="s">
+        <v>184</v>
+      </c>
+      <c r="P136" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q136">
+        <v>2.15</v>
+      </c>
+      <c r="R136">
+        <v>2.25</v>
+      </c>
+      <c r="S136">
+        <v>4.5</v>
+      </c>
+      <c r="T136">
+        <v>1.31</v>
+      </c>
+      <c r="U136">
+        <v>3.1</v>
+      </c>
+      <c r="V136">
+        <v>2.4</v>
+      </c>
+      <c r="W136">
+        <v>1.5</v>
+      </c>
+      <c r="X136">
+        <v>5.75</v>
+      </c>
+      <c r="Y136">
+        <v>1.12</v>
+      </c>
+      <c r="Z136">
+        <v>1.67</v>
+      </c>
+      <c r="AA136">
+        <v>4.02</v>
+      </c>
+      <c r="AB136">
+        <v>4.74</v>
+      </c>
+      <c r="AC136">
+        <v>1.04</v>
+      </c>
+      <c r="AD136">
+        <v>10</v>
+      </c>
+      <c r="AE136">
+        <v>1.22</v>
+      </c>
+      <c r="AF136">
+        <v>3.95</v>
+      </c>
+      <c r="AG136">
+        <v>1.7</v>
+      </c>
+      <c r="AH136">
+        <v>2.05</v>
+      </c>
+      <c r="AI136">
+        <v>1.71</v>
+      </c>
+      <c r="AJ136">
+        <v>2</v>
+      </c>
+      <c r="AK136">
+        <v>1.19</v>
+      </c>
+      <c r="AL136">
+        <v>1.23</v>
+      </c>
+      <c r="AM136">
+        <v>2.1</v>
+      </c>
+      <c r="AN136">
+        <v>1.91</v>
+      </c>
+      <c r="AO136">
+        <v>0.91</v>
+      </c>
+      <c r="AP136">
+        <v>2</v>
+      </c>
+      <c r="AQ136">
+        <v>0.83</v>
+      </c>
+      <c r="AR136">
+        <v>2.08</v>
+      </c>
+      <c r="AS136">
+        <v>1.37</v>
+      </c>
+      <c r="AT136">
+        <v>3.45</v>
+      </c>
+      <c r="AU136">
+        <v>9</v>
+      </c>
+      <c r="AV136">
+        <v>5</v>
+      </c>
+      <c r="AW136">
+        <v>11</v>
+      </c>
+      <c r="AX136">
+        <v>9</v>
+      </c>
+      <c r="AY136">
+        <v>25</v>
+      </c>
+      <c r="AZ136">
+        <v>17</v>
+      </c>
+      <c r="BA136">
+        <v>5</v>
+      </c>
+      <c r="BB136">
+        <v>6</v>
+      </c>
+      <c r="BC136">
+        <v>11</v>
+      </c>
+      <c r="BD136">
+        <v>1.31</v>
+      </c>
+      <c r="BE136">
+        <v>8.1</v>
+      </c>
+      <c r="BF136">
+        <v>4.85</v>
+      </c>
+      <c r="BG136">
+        <v>1.21</v>
+      </c>
+      <c r="BH136">
+        <v>3.58</v>
+      </c>
+      <c r="BI136">
+        <v>1.43</v>
+      </c>
+      <c r="BJ136">
+        <v>2.54</v>
+      </c>
+      <c r="BK136">
+        <v>1.78</v>
+      </c>
+      <c r="BL136">
+        <v>2</v>
+      </c>
+      <c r="BM136">
+        <v>2.19</v>
+      </c>
+      <c r="BN136">
+        <v>1.65</v>
+      </c>
+      <c r="BO136">
+        <v>2.53</v>
+      </c>
+      <c r="BP136">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="267">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,15 @@
     <t>['1', '17', '42', '53', '74']</t>
   </si>
   <si>
+    <t>['50', '61']</t>
+  </si>
+  <si>
+    <t>['42', '80', '89']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -626,9 +635,6 @@
   </si>
   <si>
     <t>['3']</t>
-  </si>
-  <si>
-    <t>['19']</t>
   </si>
   <si>
     <t>['39', '77']</t>
@@ -800,6 +806,15 @@
   </si>
   <si>
     <t>['37']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['33', '75']</t>
+  </si>
+  <si>
+    <t>['70', '76']</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1417,7 +1432,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1623,7 +1638,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1910,7 +1925,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ4">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2035,7 +2050,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2241,7 +2256,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2322,7 +2337,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ6">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2447,7 +2462,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2525,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ7">
         <v>1.18</v>
@@ -2653,7 +2668,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2731,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ8">
         <v>0.91</v>
@@ -3065,7 +3080,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3271,7 +3286,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3477,7 +3492,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3555,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
         <v>0.58</v>
@@ -3889,7 +3904,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -3967,10 +3982,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4095,7 +4110,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4176,7 +4191,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ15">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR15">
         <v>1.44</v>
@@ -4585,7 +4600,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17">
         <v>0.83</v>
@@ -4713,7 +4728,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4794,7 +4809,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ18">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
         <v>1.45</v>
@@ -4919,7 +4934,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5412,7 +5427,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ21">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR21">
         <v>1.73</v>
@@ -5537,7 +5552,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5949,7 +5964,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6233,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
         <v>0.91</v>
@@ -6361,7 +6376,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6439,10 +6454,10 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR26">
         <v>1.85</v>
@@ -6645,10 +6660,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ27">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -6773,7 +6788,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7185,7 +7200,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7266,7 +7281,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ30">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7391,7 +7406,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -8087,7 +8102,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
         <v>1.45</v>
@@ -8215,7 +8230,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>2.7</v>
@@ -8296,7 +8311,7 @@
         <v>2</v>
       </c>
       <c r="AQ35">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR35">
         <v>1.92</v>
@@ -8421,7 +8436,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8627,7 +8642,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8833,7 +8848,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9039,7 +9054,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9245,7 +9260,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9657,7 +9672,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9863,7 +9878,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10150,7 +10165,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10353,7 +10368,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45">
         <v>0.91</v>
@@ -10481,7 +10496,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10765,7 +10780,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ47">
         <v>0.83</v>
@@ -10971,10 +10986,10 @@
         <v>1.75</v>
       </c>
       <c r="AP48">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ48">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>1.38</v>
@@ -11099,7 +11114,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11180,7 +11195,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR49">
         <v>1.86</v>
@@ -11305,7 +11320,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11511,7 +11526,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11589,7 +11604,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ51">
         <v>0.91</v>
@@ -12001,7 +12016,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ53">
         <v>1.36</v>
@@ -12335,7 +12350,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12541,7 +12556,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -13031,7 +13046,7 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ58">
         <v>0.83</v>
@@ -13159,7 +13174,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13240,7 +13255,7 @@
         <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.76</v>
@@ -13446,7 +13461,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13983,7 +13998,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14064,7 +14079,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ63">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14189,7 +14204,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14267,7 +14282,7 @@
         <v>0.4</v>
       </c>
       <c r="AP64">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ64">
         <v>0.58</v>
@@ -14395,7 +14410,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14476,7 +14491,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ65">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14807,7 +14822,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14885,7 +14900,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ67">
         <v>1.18</v>
@@ -15013,7 +15028,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15219,7 +15234,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15425,7 +15440,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15506,7 +15521,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ70">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15631,7 +15646,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15712,7 +15727,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.55</v>
@@ -16043,7 +16058,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16121,7 +16136,7 @@
         <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ73">
         <v>1.45</v>
@@ -16327,7 +16342,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
         <v>0.91</v>
@@ -16536,7 +16551,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -16661,7 +16676,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17357,7 +17372,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17691,7 +17706,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17772,7 +17787,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>0.99</v>
@@ -17897,7 +17912,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -17975,7 +17990,7 @@
         <v>2.17</v>
       </c>
       <c r="AP82">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ82">
         <v>1.55</v>
@@ -18103,7 +18118,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18309,7 +18324,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18390,7 +18405,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ84">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
         <v>1.54</v>
@@ -18515,7 +18530,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18721,7 +18736,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18799,7 +18814,7 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ86">
         <v>0.91</v>
@@ -18927,7 +18942,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19008,7 +19023,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ87">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR87">
         <v>1.52</v>
@@ -20369,7 +20384,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20447,7 +20462,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20575,7 +20590,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20859,7 +20874,7 @@
         <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96">
         <v>1.36</v>
@@ -20987,7 +21002,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21068,7 +21083,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21193,7 +21208,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21399,7 +21414,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21605,7 +21620,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21683,7 +21698,7 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>1.36</v>
@@ -22017,7 +22032,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22095,10 +22110,10 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ102">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR102">
         <v>1.93</v>
@@ -22223,7 +22238,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22304,7 +22319,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ103">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.81</v>
@@ -22429,7 +22444,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22635,7 +22650,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23047,7 +23062,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23253,7 +23268,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23459,7 +23474,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23537,10 +23552,10 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR109">
         <v>1.41</v>
@@ -23746,7 +23761,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -23871,7 +23886,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24155,10 +24170,10 @@
         <v>1.22</v>
       </c>
       <c r="AP112">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ112">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR112">
         <v>1.84</v>
@@ -24361,7 +24376,7 @@
         <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ113">
         <v>0.58</v>
@@ -24489,7 +24504,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24570,7 +24585,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR114">
         <v>1.86</v>
@@ -25313,7 +25328,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25519,7 +25534,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25725,7 +25740,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26009,7 +26024,7 @@
         <v>1.56</v>
       </c>
       <c r="AP121">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ121">
         <v>1.55</v>
@@ -26137,7 +26152,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26343,7 +26358,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26627,7 +26642,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26833,10 +26848,10 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ125">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR125">
         <v>1.65</v>
@@ -26961,7 +26976,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27039,10 +27054,10 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ126">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27248,7 +27263,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ127">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR127">
         <v>1.01</v>
@@ -27373,7 +27388,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27579,7 +27594,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27785,7 +27800,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27991,7 +28006,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28403,7 +28418,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28609,7 +28624,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28815,7 +28830,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29021,7 +29036,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29178,6 +29193,624 @@
       </c>
       <c r="BP136">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7784918</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45697.42708333334</v>
+      </c>
+      <c r="F137">
+        <v>23</v>
+      </c>
+      <c r="G137" t="s">
+        <v>76</v>
+      </c>
+      <c r="H137" t="s">
+        <v>79</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>2</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+      <c r="N137">
+        <v>3</v>
+      </c>
+      <c r="O137" t="s">
+        <v>185</v>
+      </c>
+      <c r="P137" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q137">
+        <v>2.7</v>
+      </c>
+      <c r="R137">
+        <v>2.2</v>
+      </c>
+      <c r="S137">
+        <v>3.3</v>
+      </c>
+      <c r="T137">
+        <v>1.3</v>
+      </c>
+      <c r="U137">
+        <v>3.2</v>
+      </c>
+      <c r="V137">
+        <v>2.3</v>
+      </c>
+      <c r="W137">
+        <v>1.53</v>
+      </c>
+      <c r="X137">
+        <v>5.25</v>
+      </c>
+      <c r="Y137">
+        <v>1.13</v>
+      </c>
+      <c r="Z137">
+        <v>2.2</v>
+      </c>
+      <c r="AA137">
+        <v>3.5</v>
+      </c>
+      <c r="AB137">
+        <v>3.04</v>
+      </c>
+      <c r="AC137">
+        <v>1.04</v>
+      </c>
+      <c r="AD137">
+        <v>10</v>
+      </c>
+      <c r="AE137">
+        <v>1.19</v>
+      </c>
+      <c r="AF137">
+        <v>4.2</v>
+      </c>
+      <c r="AG137">
+        <v>1.6</v>
+      </c>
+      <c r="AH137">
+        <v>2.1</v>
+      </c>
+      <c r="AI137">
+        <v>1.57</v>
+      </c>
+      <c r="AJ137">
+        <v>2.25</v>
+      </c>
+      <c r="AK137">
+        <v>1.37</v>
+      </c>
+      <c r="AL137">
+        <v>1.28</v>
+      </c>
+      <c r="AM137">
+        <v>1.62</v>
+      </c>
+      <c r="AN137">
+        <v>1.82</v>
+      </c>
+      <c r="AO137">
+        <v>1.64</v>
+      </c>
+      <c r="AP137">
+        <v>1.92</v>
+      </c>
+      <c r="AQ137">
+        <v>1.5</v>
+      </c>
+      <c r="AR137">
+        <v>1.97</v>
+      </c>
+      <c r="AS137">
+        <v>1.81</v>
+      </c>
+      <c r="AT137">
+        <v>3.78</v>
+      </c>
+      <c r="AU137">
+        <v>4</v>
+      </c>
+      <c r="AV137">
+        <v>10</v>
+      </c>
+      <c r="AW137">
+        <v>10</v>
+      </c>
+      <c r="AX137">
+        <v>4</v>
+      </c>
+      <c r="AY137">
+        <v>15</v>
+      </c>
+      <c r="AZ137">
+        <v>15</v>
+      </c>
+      <c r="BA137">
+        <v>10</v>
+      </c>
+      <c r="BB137">
+        <v>2</v>
+      </c>
+      <c r="BC137">
+        <v>12</v>
+      </c>
+      <c r="BD137">
+        <v>1.61</v>
+      </c>
+      <c r="BE137">
+        <v>9.1</v>
+      </c>
+      <c r="BF137">
+        <v>2.76</v>
+      </c>
+      <c r="BG137">
+        <v>1.15</v>
+      </c>
+      <c r="BH137">
+        <v>4.25</v>
+      </c>
+      <c r="BI137">
+        <v>1.31</v>
+      </c>
+      <c r="BJ137">
+        <v>2.92</v>
+      </c>
+      <c r="BK137">
+        <v>1.58</v>
+      </c>
+      <c r="BL137">
+        <v>2.17</v>
+      </c>
+      <c r="BM137">
+        <v>1.99</v>
+      </c>
+      <c r="BN137">
+        <v>1.73</v>
+      </c>
+      <c r="BO137">
+        <v>2.57</v>
+      </c>
+      <c r="BP137">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7784919</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45697.52083333334</v>
+      </c>
+      <c r="F138">
+        <v>23</v>
+      </c>
+      <c r="G138" t="s">
+        <v>75</v>
+      </c>
+      <c r="H138" t="s">
+        <v>72</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>2</v>
+      </c>
+      <c r="L138">
+        <v>3</v>
+      </c>
+      <c r="M138">
+        <v>2</v>
+      </c>
+      <c r="N138">
+        <v>5</v>
+      </c>
+      <c r="O138" t="s">
+        <v>186</v>
+      </c>
+      <c r="P138" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q138">
+        <v>2</v>
+      </c>
+      <c r="R138">
+        <v>2.37</v>
+      </c>
+      <c r="S138">
+        <v>4.8</v>
+      </c>
+      <c r="T138">
+        <v>1.27</v>
+      </c>
+      <c r="U138">
+        <v>3.4</v>
+      </c>
+      <c r="V138">
+        <v>2.2</v>
+      </c>
+      <c r="W138">
+        <v>1.58</v>
+      </c>
+      <c r="X138">
+        <v>5</v>
+      </c>
+      <c r="Y138">
+        <v>1.15</v>
+      </c>
+      <c r="Z138">
+        <v>1.54</v>
+      </c>
+      <c r="AA138">
+        <v>4.2</v>
+      </c>
+      <c r="AB138">
+        <v>5.5</v>
+      </c>
+      <c r="AC138">
+        <v>1.03</v>
+      </c>
+      <c r="AD138">
+        <v>15</v>
+      </c>
+      <c r="AE138">
+        <v>1.18</v>
+      </c>
+      <c r="AF138">
+        <v>4.75</v>
+      </c>
+      <c r="AG138">
+        <v>1.53</v>
+      </c>
+      <c r="AH138">
+        <v>2.25</v>
+      </c>
+      <c r="AI138">
+        <v>1.62</v>
+      </c>
+      <c r="AJ138">
+        <v>2.2</v>
+      </c>
+      <c r="AK138">
+        <v>1.16</v>
+      </c>
+      <c r="AL138">
+        <v>1.21</v>
+      </c>
+      <c r="AM138">
+        <v>2.35</v>
+      </c>
+      <c r="AN138">
+        <v>1.82</v>
+      </c>
+      <c r="AO138">
+        <v>0.36</v>
+      </c>
+      <c r="AP138">
+        <v>1.92</v>
+      </c>
+      <c r="AQ138">
+        <v>0.33</v>
+      </c>
+      <c r="AR138">
+        <v>1.66</v>
+      </c>
+      <c r="AS138">
+        <v>1.18</v>
+      </c>
+      <c r="AT138">
+        <v>2.84</v>
+      </c>
+      <c r="AU138">
+        <v>12</v>
+      </c>
+      <c r="AV138">
+        <v>6</v>
+      </c>
+      <c r="AW138">
+        <v>13</v>
+      </c>
+      <c r="AX138">
+        <v>8</v>
+      </c>
+      <c r="AY138">
+        <v>35</v>
+      </c>
+      <c r="AZ138">
+        <v>16</v>
+      </c>
+      <c r="BA138">
+        <v>2</v>
+      </c>
+      <c r="BB138">
+        <v>4</v>
+      </c>
+      <c r="BC138">
+        <v>6</v>
+      </c>
+      <c r="BD138">
+        <v>1.3</v>
+      </c>
+      <c r="BE138">
+        <v>10.25</v>
+      </c>
+      <c r="BF138">
+        <v>4.4</v>
+      </c>
+      <c r="BG138">
+        <v>1.14</v>
+      </c>
+      <c r="BH138">
+        <v>4.4</v>
+      </c>
+      <c r="BI138">
+        <v>1.29</v>
+      </c>
+      <c r="BJ138">
+        <v>3.04</v>
+      </c>
+      <c r="BK138">
+        <v>1.55</v>
+      </c>
+      <c r="BL138">
+        <v>2.23</v>
+      </c>
+      <c r="BM138">
+        <v>1.93</v>
+      </c>
+      <c r="BN138">
+        <v>1.78</v>
+      </c>
+      <c r="BO138">
+        <v>2.48</v>
+      </c>
+      <c r="BP138">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7784920</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45697.52083333334</v>
+      </c>
+      <c r="F139">
+        <v>23</v>
+      </c>
+      <c r="G139" t="s">
+        <v>81</v>
+      </c>
+      <c r="H139" t="s">
+        <v>80</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>2</v>
+      </c>
+      <c r="N139">
+        <v>3</v>
+      </c>
+      <c r="O139" t="s">
+        <v>187</v>
+      </c>
+      <c r="P139" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q139">
+        <v>2.8</v>
+      </c>
+      <c r="R139">
+        <v>2.25</v>
+      </c>
+      <c r="S139">
+        <v>3.1</v>
+      </c>
+      <c r="T139">
+        <v>1.29</v>
+      </c>
+      <c r="U139">
+        <v>3.25</v>
+      </c>
+      <c r="V139">
+        <v>2.3</v>
+      </c>
+      <c r="W139">
+        <v>1.53</v>
+      </c>
+      <c r="X139">
+        <v>5.25</v>
+      </c>
+      <c r="Y139">
+        <v>1.13</v>
+      </c>
+      <c r="Z139">
+        <v>2.26</v>
+      </c>
+      <c r="AA139">
+        <v>3.6</v>
+      </c>
+      <c r="AB139">
+        <v>2.86</v>
+      </c>
+      <c r="AC139">
+        <v>1.04</v>
+      </c>
+      <c r="AD139">
+        <v>10</v>
+      </c>
+      <c r="AE139">
+        <v>1.22</v>
+      </c>
+      <c r="AF139">
+        <v>4.2</v>
+      </c>
+      <c r="AG139">
+        <v>1.57</v>
+      </c>
+      <c r="AH139">
+        <v>2.15</v>
+      </c>
+      <c r="AI139">
+        <v>1.53</v>
+      </c>
+      <c r="AJ139">
+        <v>2.38</v>
+      </c>
+      <c r="AK139">
+        <v>1.44</v>
+      </c>
+      <c r="AL139">
+        <v>1.28</v>
+      </c>
+      <c r="AM139">
+        <v>1.55</v>
+      </c>
+      <c r="AN139">
+        <v>1.45</v>
+      </c>
+      <c r="AO139">
+        <v>1.09</v>
+      </c>
+      <c r="AP139">
+        <v>1.33</v>
+      </c>
+      <c r="AQ139">
+        <v>1.25</v>
+      </c>
+      <c r="AR139">
+        <v>1.48</v>
+      </c>
+      <c r="AS139">
+        <v>1.41</v>
+      </c>
+      <c r="AT139">
+        <v>2.89</v>
+      </c>
+      <c r="AU139">
+        <v>3</v>
+      </c>
+      <c r="AV139">
+        <v>9</v>
+      </c>
+      <c r="AW139">
+        <v>16</v>
+      </c>
+      <c r="AX139">
+        <v>6</v>
+      </c>
+      <c r="AY139">
+        <v>29</v>
+      </c>
+      <c r="AZ139">
+        <v>17</v>
+      </c>
+      <c r="BA139">
+        <v>8</v>
+      </c>
+      <c r="BB139">
+        <v>4</v>
+      </c>
+      <c r="BC139">
+        <v>12</v>
+      </c>
+      <c r="BD139">
+        <v>2.07</v>
+      </c>
+      <c r="BE139">
+        <v>6.6</v>
+      </c>
+      <c r="BF139">
+        <v>2.18</v>
+      </c>
+      <c r="BG139">
+        <v>1.16</v>
+      </c>
+      <c r="BH139">
+        <v>4.05</v>
+      </c>
+      <c r="BI139">
+        <v>1.34</v>
+      </c>
+      <c r="BJ139">
+        <v>2.78</v>
+      </c>
+      <c r="BK139">
+        <v>1.62</v>
+      </c>
+      <c r="BL139">
+        <v>2.1</v>
+      </c>
+      <c r="BM139">
+        <v>2.06</v>
+      </c>
+      <c r="BN139">
+        <v>1.68</v>
+      </c>
+      <c r="BO139">
+        <v>2.67</v>
+      </c>
+      <c r="BP139">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -29559,13 +29559,13 @@
         <v>16</v>
       </c>
       <c r="BA138">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB138">
         <v>4</v>
       </c>
       <c r="BC138">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD138">
         <v>1.3</v>
@@ -29768,10 +29768,10 @@
         <v>8</v>
       </c>
       <c r="BB139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC139">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD139">
         <v>2.07</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -578,6 +578,12 @@
   </si>
   <si>
     <t>['19']</t>
+  </si>
+  <si>
+    <t>['67', '89']</t>
+  </si>
+  <si>
+    <t>['18', '39']</t>
   </si>
   <si>
     <t>['25']</t>
@@ -1176,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1432,7 +1438,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1510,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1638,7 +1644,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1716,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ3">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1922,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2050,7 +2056,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2128,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ5">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2256,7 +2262,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2334,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2462,7 +2468,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2540,10 +2546,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ7">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2668,7 +2674,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2740,25 +2746,25 @@
         <v>1.73</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2946,25 +2952,25 @@
         <v>1.52</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP9">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU9">
         <v>12</v>
@@ -3080,7 +3086,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3158,19 +3164,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ10">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3286,7 +3292,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3361,22 +3367,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ11">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU11">
         <v>9</v>
@@ -3492,7 +3498,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3570,19 +3576,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR12">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AT12">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="AU12">
         <v>7</v>
@@ -3776,19 +3782,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
+        <v>1.52</v>
+      </c>
+      <c r="AQ13">
+        <v>1.42</v>
+      </c>
+      <c r="AR13">
+        <v>2.01</v>
+      </c>
+      <c r="AS13">
         <v>1.82</v>
       </c>
-      <c r="AQ13">
-        <v>0.91</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>1.79</v>
-      </c>
       <c r="AT13">
-        <v>1.79</v>
+        <v>3.83</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3904,7 +3910,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -3976,25 +3982,25 @@
         <v>2.3</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU14">
         <v>15</v>
@@ -4110,7 +4116,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4182,25 +4188,25 @@
         <v>1.52</v>
       </c>
       <c r="AN15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ15">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR15">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AS15">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="AT15">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="AU15">
         <v>2</v>
@@ -4394,19 +4400,19 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ16">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR16">
-        <v>2.11</v>
+        <v>1.59</v>
       </c>
       <c r="AS16">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AT16">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="AU16">
         <v>8</v>
@@ -4594,25 +4600,25 @@
         <v>1.65</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AS17">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AT17">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4728,7 +4734,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4800,25 +4806,25 @@
         <v>1.45</v>
       </c>
       <c r="AN18">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP18">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ18">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR18">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="AS18">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AT18">
-        <v>3.46</v>
+        <v>3.15</v>
       </c>
       <c r="AU18">
         <v>9</v>
@@ -4934,7 +4940,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5012,19 +5018,19 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AS19">
-        <v>1.76</v>
+        <v>2.59</v>
       </c>
       <c r="AT19">
-        <v>3.61</v>
+        <v>4.39</v>
       </c>
       <c r="AU19">
         <v>3</v>
@@ -5212,25 +5218,25 @@
         <v>1.88</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
         <v>0</v>
       </c>
       <c r="AP20">
+        <v>0.71</v>
+      </c>
+      <c r="AQ20">
         <v>0.91</v>
       </c>
-      <c r="AQ20">
-        <v>0.58</v>
-      </c>
       <c r="AR20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AS20">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="AT20">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5418,25 +5424,25 @@
         <v>1.85</v>
       </c>
       <c r="AN21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP21">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ21">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR21">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AS21">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AT21">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5552,7 +5558,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5624,25 +5630,25 @@
         <v>1.2</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP22">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ22">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR22">
-        <v>0.55</v>
+        <v>1.15</v>
       </c>
       <c r="AS22">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AT22">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5830,25 +5836,25 @@
         <v>2.15</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP23">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR23">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AS23">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AT23">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -5964,7 +5970,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6039,22 +6045,22 @@
         <v>3</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR24">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AS24">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT24">
-        <v>3.53</v>
+        <v>3.09</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6242,25 +6248,25 @@
         <v>1.85</v>
       </c>
       <c r="AN25">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR25">
-        <v>3.42</v>
+        <v>2.37</v>
       </c>
       <c r="AS25">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="AT25">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6376,7 +6382,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6448,22 +6454,22 @@
         <v>2.05</v>
       </c>
       <c r="AN26">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO26">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ26">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR26">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AS26">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AT26">
         <v>3.14</v>
@@ -6654,25 +6660,25 @@
         <v>2.3</v>
       </c>
       <c r="AN27">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ27">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR27">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AS27">
-        <v>0.89</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="AU27">
         <v>5</v>
@@ -6788,7 +6794,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6860,25 +6866,25 @@
         <v>1.35</v>
       </c>
       <c r="AN28">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO28">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ28">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AS28">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AT28">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AU28">
         <v>9</v>
@@ -7066,25 +7072,25 @@
         <v>2.4</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO29">
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ29">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR29">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="AS29">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT29">
-        <v>3.49</v>
+        <v>3.08</v>
       </c>
       <c r="AU29">
         <v>9</v>
@@ -7200,7 +7206,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7272,25 +7278,25 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP30">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR30">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="AS30">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AT30">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7406,7 +7412,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -7478,25 +7484,25 @@
         <v>0</v>
       </c>
       <c r="AN31">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AP31">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR31">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS31">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AT31">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AU31">
         <v>4</v>
@@ -7684,25 +7690,25 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ32">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR32">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AS32">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AT32">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AU32">
         <v>2</v>
@@ -7890,25 +7896,25 @@
         <v>1.3</v>
       </c>
       <c r="AN33">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP33">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ33">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR33">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AS33">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="AT33">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8096,25 +8102,25 @@
         <v>1.91</v>
       </c>
       <c r="AN34">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO34">
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR34">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="AS34">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT34">
-        <v>3.86</v>
+        <v>3.54</v>
       </c>
       <c r="AU34">
         <v>2</v>
@@ -8302,25 +8308,25 @@
         <v>1.62</v>
       </c>
       <c r="AN35">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO35">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ35">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR35">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AS35">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AT35">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="AU35">
         <v>7</v>
@@ -8436,7 +8442,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8508,25 +8514,25 @@
         <v>1.55</v>
       </c>
       <c r="AN36">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP36">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR36">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AS36">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AT36">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8642,7 +8648,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8714,25 +8720,25 @@
         <v>1.87</v>
       </c>
       <c r="AN37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO37">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AP37">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR37">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AS37">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AT37">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="AU37">
         <v>4</v>
@@ -8848,7 +8854,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8920,25 +8926,25 @@
         <v>1.3</v>
       </c>
       <c r="AN38">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO38">
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ38">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR38">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AS38">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AT38">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="AU38">
         <v>9</v>
@@ -9054,7 +9060,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9126,25 +9132,25 @@
         <v>1.75</v>
       </c>
       <c r="AN39">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO39">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ39">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AS39">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AT39">
-        <v>4.01</v>
+        <v>3.67</v>
       </c>
       <c r="AU39">
         <v>2</v>
@@ -9260,7 +9266,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9332,25 +9338,25 @@
         <v>2.3</v>
       </c>
       <c r="AN40">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO40">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP40">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ40">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR40">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AS40">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AT40">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9538,25 +9544,25 @@
         <v>1.43</v>
       </c>
       <c r="AN41">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO41">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AP41">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR41">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AS41">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="AT41">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="AU41">
         <v>2</v>
@@ -9672,7 +9678,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9744,25 +9750,25 @@
         <v>1.17</v>
       </c>
       <c r="AN42">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO42">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ42">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR42">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AS42">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AT42">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9878,7 +9884,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -9950,25 +9956,25 @@
         <v>1.77</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO43">
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ43">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
       </c>
       <c r="AS43">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AT43">
-        <v>3.22</v>
+        <v>3.39</v>
       </c>
       <c r="AU43">
         <v>8</v>
@@ -10156,25 +10162,25 @@
         <v>1.22</v>
       </c>
       <c r="AN44">
-        <v>1.33</v>
+        <v>0.71</v>
       </c>
       <c r="AO44">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ44">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR44">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AS44">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AT44">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="AU44">
         <v>2</v>
@@ -10362,25 +10368,25 @@
         <v>1.9</v>
       </c>
       <c r="AN45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AO45">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ45">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR45">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AS45">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AT45">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10496,7 +10502,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10568,25 +10574,25 @@
         <v>2.45</v>
       </c>
       <c r="AN46">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AO46">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR46">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AS46">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AT46">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10774,25 +10780,25 @@
         <v>2.11</v>
       </c>
       <c r="AN47">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AP47">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ47">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR47">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AS47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT47">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="AU47">
         <v>3</v>
@@ -10983,22 +10989,22 @@
         <v>2</v>
       </c>
       <c r="AO48">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AP48">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR48">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AS48">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AT48">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="AU48">
         <v>11</v>
@@ -11114,7 +11120,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11186,25 +11192,25 @@
         <v>2.42</v>
       </c>
       <c r="AN49">
+        <v>2</v>
+      </c>
+      <c r="AO49">
+        <v>0.57</v>
+      </c>
+      <c r="AP49">
         <v>1.75</v>
       </c>
-      <c r="AO49">
-        <v>0</v>
-      </c>
-      <c r="AP49">
-        <v>2</v>
-      </c>
       <c r="AQ49">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR49">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AS49">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT49">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="AU49">
         <v>8</v>
@@ -11320,7 +11326,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11392,25 +11398,25 @@
         <v>2.3</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AO50">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ50">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR50">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AS50">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AT50">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11526,7 +11532,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11598,25 +11604,25 @@
         <v>1.65</v>
       </c>
       <c r="AN51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AO51">
-        <v>0.25</v>
+        <v>0.88</v>
       </c>
       <c r="AP51">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ51">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR51">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS51">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AT51">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11804,25 +11810,25 @@
         <v>1.38</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO52">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP52">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR52">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AS52">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AT52">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="AU52">
         <v>7</v>
@@ -12010,25 +12016,25 @@
         <v>1.62</v>
       </c>
       <c r="AN53">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AO53">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="AP53">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ53">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR53">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS53">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AT53">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12216,25 +12222,25 @@
         <v>1.5</v>
       </c>
       <c r="AN54">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO54">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ54">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR54">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AS54">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AT54">
-        <v>3.66</v>
+        <v>3.32</v>
       </c>
       <c r="AU54">
         <v>7</v>
@@ -12350,7 +12356,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12422,25 +12428,25 @@
         <v>1.65</v>
       </c>
       <c r="AN55">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO55">
+        <v>2</v>
+      </c>
+      <c r="AP55">
+        <v>1.52</v>
+      </c>
+      <c r="AQ55">
+        <v>1.57</v>
+      </c>
+      <c r="AR55">
+        <v>1.64</v>
+      </c>
+      <c r="AS55">
         <v>1.75</v>
       </c>
-      <c r="AP55">
-        <v>1.82</v>
-      </c>
-      <c r="AQ55">
-        <v>1.18</v>
-      </c>
-      <c r="AR55">
-        <v>1.62</v>
-      </c>
-      <c r="AS55">
-        <v>1.54</v>
-      </c>
       <c r="AT55">
-        <v>3.16</v>
+        <v>3.39</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12556,7 +12562,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12628,25 +12634,25 @@
         <v>1.42</v>
       </c>
       <c r="AN56">
-        <v>1.25</v>
+        <v>0.89</v>
       </c>
       <c r="AO56">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP56">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ56">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR56">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AS56">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AT56">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AU56">
         <v>4</v>
@@ -12834,25 +12840,25 @@
         <v>1.83</v>
       </c>
       <c r="AN57">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO57">
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ57">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR57">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AS57">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AT57">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="AU57">
         <v>6</v>
@@ -13040,25 +13046,25 @@
         <v>1.95</v>
       </c>
       <c r="AN58">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AO58">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ58">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR58">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AS58">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AT58">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="AU58">
         <v>7</v>
@@ -13174,7 +13180,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13246,25 +13252,25 @@
         <v>1.7</v>
       </c>
       <c r="AN59">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR59">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AS59">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AT59">
-        <v>3.41</v>
+        <v>3.24</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13452,25 +13458,25 @@
         <v>2.5</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="AO60">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AP60">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ60">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR60">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AS60">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT60">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13658,25 +13664,25 @@
         <v>1.1</v>
       </c>
       <c r="AN61">
+        <v>1</v>
+      </c>
+      <c r="AO61">
+        <v>2</v>
+      </c>
+      <c r="AP61">
+        <v>0.91</v>
+      </c>
+      <c r="AQ61">
         <v>1.75</v>
       </c>
-      <c r="AO61">
-        <v>2</v>
-      </c>
-      <c r="AP61">
-        <v>1.27</v>
-      </c>
-      <c r="AQ61">
-        <v>1.36</v>
-      </c>
       <c r="AR61">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS61">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AT61">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="AU61">
         <v>5</v>
@@ -13864,25 +13870,25 @@
         <v>1.83</v>
       </c>
       <c r="AN62">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AO62">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AP62">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR62">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AS62">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT62">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="AU62">
         <v>9</v>
@@ -13998,7 +14004,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14070,25 +14076,25 @@
         <v>1.22</v>
       </c>
       <c r="AN63">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="AO63">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AP63">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR63">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS63">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AT63">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14204,7 +14210,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14276,25 +14282,25 @@
         <v>2.7</v>
       </c>
       <c r="AN64">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO64">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="AP64">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ64">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR64">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AS64">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AT64">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AU64">
         <v>10</v>
@@ -14410,7 +14416,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14482,25 +14488,25 @@
         <v>1.6</v>
       </c>
       <c r="AN65">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AO65">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR65">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AS65">
         <v>1.59</v>
       </c>
       <c r="AT65">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14688,25 +14694,25 @@
         <v>1.62</v>
       </c>
       <c r="AN66">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO66">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ66">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR66">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AS66">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AT66">
-        <v>3.59</v>
+        <v>3.43</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14822,7 +14828,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14894,25 +14900,25 @@
         <v>1.53</v>
       </c>
       <c r="AN67">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AO67">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ67">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR67">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AS67">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AT67">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -15028,7 +15034,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15100,25 +15106,25 @@
         <v>1.2</v>
       </c>
       <c r="AN68">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO68">
-        <v>0.4</v>
+        <v>1.27</v>
       </c>
       <c r="AP68">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ68">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR68">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AS68">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AT68">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="AU68">
         <v>2</v>
@@ -15234,7 +15240,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15306,25 +15312,25 @@
         <v>1.55</v>
       </c>
       <c r="AN69">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AO69">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AP69">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ69">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR69">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS69">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AT69">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15440,7 +15446,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15512,25 +15518,25 @@
         <v>2.8</v>
       </c>
       <c r="AN70">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AP70">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ70">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR70">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AS70">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AT70">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15646,7 +15652,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15718,25 +15724,25 @@
         <v>1.75</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AO71">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR71">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AS71">
         <v>1.68</v>
       </c>
       <c r="AT71">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15924,25 +15930,25 @@
         <v>1.35</v>
       </c>
       <c r="AN72">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO72">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AP72">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ72">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR72">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AS72">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AT72">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16058,7 +16064,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16130,25 +16136,25 @@
         <v>1.9</v>
       </c>
       <c r="AN73">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AO73">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP73">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ73">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR73">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AS73">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AT73">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16336,25 +16342,25 @@
         <v>1.55</v>
       </c>
       <c r="AN74">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO74">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ74">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR74">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AS74">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AT74">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16542,25 +16548,25 @@
         <v>2.85</v>
       </c>
       <c r="AN75">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AO75">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ75">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
       </c>
       <c r="AS75">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AT75">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="AU75">
         <v>10</v>
@@ -16676,7 +16682,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16748,25 +16754,25 @@
         <v>1.72</v>
       </c>
       <c r="AN76">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO76">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="AP76">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ76">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR76">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AS76">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT76">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16954,25 +16960,25 @@
         <v>1.45</v>
       </c>
       <c r="AN77">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AO77">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AP77">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ77">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR77">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AS77">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AT77">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="AU77">
         <v>4</v>
@@ -17160,25 +17166,25 @@
         <v>3</v>
       </c>
       <c r="AN78">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AO78">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR78">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AS78">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17366,25 +17372,25 @@
         <v>1.87</v>
       </c>
       <c r="AN79">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AO79">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP79">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR79">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AS79">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AT79">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="AU79">
         <v>7</v>
@@ -17572,25 +17578,25 @@
         <v>1.22</v>
       </c>
       <c r="AN80">
-        <v>1.17</v>
+        <v>0.62</v>
       </c>
       <c r="AO80">
-        <v>0.83</v>
+        <v>1.54</v>
       </c>
       <c r="AP80">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ80">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR80">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS80">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AT80">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17706,7 +17712,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17778,25 +17784,25 @@
         <v>1.17</v>
       </c>
       <c r="AN81">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AO81">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="AP81">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR81">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="AS81">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AT81">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17912,7 +17918,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -17984,25 +17990,25 @@
         <v>1.8</v>
       </c>
       <c r="AN82">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AO82">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AP82">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ82">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR82">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AS82">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AT82">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18118,7 +18124,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18190,25 +18196,25 @@
         <v>1.65</v>
       </c>
       <c r="AN83">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="AO83">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AP83">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ83">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AS83">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AT83">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="AU83">
         <v>11</v>
@@ -18324,7 +18330,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18396,25 +18402,25 @@
         <v>1.45</v>
       </c>
       <c r="AN84">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO84">
-        <v>0.83</v>
+        <v>1.31</v>
       </c>
       <c r="AP84">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ84">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR84">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS84">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AT84">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="AU84">
         <v>6</v>
@@ -18530,7 +18536,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18602,25 +18608,25 @@
         <v>1.67</v>
       </c>
       <c r="AN85">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ85">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR85">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AS85">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AT85">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18736,7 +18742,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18808,25 +18814,25 @@
         <v>1.55</v>
       </c>
       <c r="AN86">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AO86">
-        <v>0.71</v>
+        <v>1.14</v>
       </c>
       <c r="AP86">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ86">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR86">
+        <v>1.59</v>
+      </c>
+      <c r="AS86">
         <v>1.7</v>
       </c>
-      <c r="AS86">
-        <v>1.68</v>
-      </c>
       <c r="AT86">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -18942,7 +18948,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19014,25 +19020,25 @@
         <v>2.3</v>
       </c>
       <c r="AN87">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="AO87">
-        <v>0.14</v>
+        <v>0.79</v>
       </c>
       <c r="AP87">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ87">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR87">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS87">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AT87">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AU87">
         <v>6</v>
@@ -19220,25 +19226,25 @@
         <v>1.95</v>
       </c>
       <c r="AN88">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="AO88">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AP88">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ88">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR88">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AS88">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AT88">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="AU88">
         <v>-1</v>
@@ -19426,25 +19432,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>2.29</v>
+        <v>1.79</v>
       </c>
       <c r="AO89">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ89">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR89">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AS89">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AT89">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="AU89">
         <v>12</v>
@@ -19632,25 +19638,25 @@
         <v>2.7</v>
       </c>
       <c r="AN90">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AO90">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="AP90">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ90">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR90">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AS90">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT90">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AU90">
         <v>8</v>
@@ -19838,25 +19844,25 @@
         <v>1.7</v>
       </c>
       <c r="AN91">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AO91">
+        <v>1.79</v>
+      </c>
+      <c r="AP91">
+        <v>1.74</v>
+      </c>
+      <c r="AQ91">
         <v>1.57</v>
       </c>
-      <c r="AP91">
-        <v>2</v>
-      </c>
-      <c r="AQ91">
-        <v>1.18</v>
-      </c>
       <c r="AR91">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS91">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AT91">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AU91">
         <v>8</v>
@@ -20044,25 +20050,25 @@
         <v>1.85</v>
       </c>
       <c r="AN92">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AO92">
-        <v>0.71</v>
+        <v>1.53</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ92">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR92">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AS92">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AT92">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20250,25 +20256,25 @@
         <v>1.22</v>
       </c>
       <c r="AN93">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="AO93">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AP93">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ93">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR93">
-        <v>0.95</v>
+        <v>1.07</v>
       </c>
       <c r="AS93">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AT93">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20384,7 +20390,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20456,25 +20462,25 @@
         <v>1.93</v>
       </c>
       <c r="AN94">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AO94">
-        <v>0.43</v>
+        <v>0.67</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR94">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AS94">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AT94">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20590,7 +20596,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20662,25 +20668,25 @@
         <v>1.22</v>
       </c>
       <c r="AN95">
-        <v>1.43</v>
+        <v>0.8</v>
       </c>
       <c r="AO95">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="AP95">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ95">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR95">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AS95">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AT95">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20868,25 +20874,25 @@
         <v>1.75</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO96">
-        <v>1.29</v>
+        <v>1.87</v>
       </c>
       <c r="AP96">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR96">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AS96">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AT96">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="AU96">
         <v>11</v>
@@ -21002,7 +21008,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21074,25 +21080,25 @@
         <v>1.95</v>
       </c>
       <c r="AN97">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AO97">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ97">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR97">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AS97">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AT97">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="AU97">
         <v>13</v>
@@ -21208,7 +21214,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21280,25 +21286,25 @@
         <v>2.25</v>
       </c>
       <c r="AN98">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO98">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP98">
+        <v>0.96</v>
+      </c>
+      <c r="AQ98">
         <v>0.91</v>
       </c>
-      <c r="AQ98">
-        <v>0.58</v>
-      </c>
       <c r="AR98">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS98">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT98">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21414,7 +21420,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21486,25 +21492,25 @@
         <v>1.42</v>
       </c>
       <c r="AN99">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AO99">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AP99">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ99">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR99">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AS99">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AT99">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21620,7 +21626,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21692,25 +21698,25 @@
         <v>1.45</v>
       </c>
       <c r="AN100">
+        <v>1.63</v>
+      </c>
+      <c r="AO100">
         <v>1.75</v>
       </c>
-      <c r="AO100">
-        <v>1.13</v>
-      </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ100">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR100">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AS100">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AT100">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21898,25 +21904,25 @@
         <v>1.75</v>
       </c>
       <c r="AN101">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO101">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AP101">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ101">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR101">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AS101">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT101">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="AU101">
         <v>6</v>
@@ -22032,7 +22038,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22104,25 +22110,25 @@
         <v>3.3</v>
       </c>
       <c r="AN102">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO102">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ102">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR102">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AS102">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AT102">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22238,7 +22244,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22310,25 +22316,25 @@
         <v>1.45</v>
       </c>
       <c r="AN103">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="AO103">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AP103">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ103">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR103">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AS103">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AT103">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22444,7 +22450,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22516,25 +22522,25 @@
         <v>1.3</v>
       </c>
       <c r="AN104">
-        <v>1.25</v>
+        <v>0.76</v>
       </c>
       <c r="AO104">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP104">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ104">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR104">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AS104">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AT104">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22650,7 +22656,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22722,25 +22728,25 @@
         <v>1.2</v>
       </c>
       <c r="AN105">
+        <v>1</v>
+      </c>
+      <c r="AO105">
+        <v>1.35</v>
+      </c>
+      <c r="AP105">
+        <v>0.91</v>
+      </c>
+      <c r="AQ105">
         <v>1.25</v>
       </c>
-      <c r="AO105">
-        <v>0.88</v>
-      </c>
-      <c r="AP105">
-        <v>1.27</v>
-      </c>
-      <c r="AQ105">
-        <v>0.83</v>
-      </c>
       <c r="AR105">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="AS105">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AT105">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22928,25 +22934,25 @@
         <v>2.2</v>
       </c>
       <c r="AN106">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO106">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR106">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AS106">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AT106">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="AU106">
         <v>7</v>
@@ -23062,7 +23068,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23134,25 +23140,25 @@
         <v>1.62</v>
       </c>
       <c r="AN107">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AO107">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ107">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR107">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AS107">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AT107">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="AU107">
         <v>9</v>
@@ -23268,7 +23274,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23340,25 +23346,25 @@
         <v>1.75</v>
       </c>
       <c r="AN108">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="AO108">
-        <v>0.75</v>
+        <v>1.59</v>
       </c>
       <c r="AP108">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ108">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR108">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AS108">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AT108">
-        <v>3.49</v>
+        <v>3.39</v>
       </c>
       <c r="AU108">
         <v>6</v>
@@ -23474,7 +23480,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23546,25 +23552,25 @@
         <v>1.62</v>
       </c>
       <c r="AN109">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AO109">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ109">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR109">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AS109">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AT109">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23752,25 +23758,25 @@
         <v>3.3</v>
       </c>
       <c r="AN110">
-        <v>1.89</v>
+        <v>1.28</v>
       </c>
       <c r="AO110">
-        <v>0.33</v>
+        <v>0.72</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR110">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AS110">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AT110">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AU110">
         <v>9</v>
@@ -23886,7 +23892,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -23958,25 +23964,25 @@
         <v>1.77</v>
       </c>
       <c r="AN111">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AO111">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AP111">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR111">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AS111">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AT111">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24164,25 +24170,25 @@
         <v>2.05</v>
       </c>
       <c r="AN112">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AO112">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AP112">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ112">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR112">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AS112">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AT112">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24370,25 +24376,25 @@
         <v>2.65</v>
       </c>
       <c r="AN113">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO113">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP113">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ113">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR113">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AS113">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT113">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AU113">
         <v>4</v>
@@ -24504,7 +24510,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24576,25 +24582,25 @@
         <v>1.57</v>
       </c>
       <c r="AN114">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AO114">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR114">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AS114">
         <v>1.76</v>
       </c>
       <c r="AT114">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="AU114">
         <v>6</v>
@@ -24782,25 +24788,25 @@
         <v>1.85</v>
       </c>
       <c r="AN115">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO115">
+        <v>1.61</v>
+      </c>
+      <c r="AP115">
+        <v>1.52</v>
+      </c>
+      <c r="AQ115">
+        <v>1.63</v>
+      </c>
+      <c r="AR115">
+        <v>1.68</v>
+      </c>
+      <c r="AS115">
         <v>1.67</v>
       </c>
-      <c r="AP115">
-        <v>2.08</v>
-      </c>
-      <c r="AQ115">
-        <v>1.45</v>
-      </c>
-      <c r="AR115">
-        <v>1.76</v>
-      </c>
-      <c r="AS115">
-        <v>1.68</v>
-      </c>
       <c r="AT115">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24988,25 +24994,25 @@
         <v>1.36</v>
       </c>
       <c r="AN116">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AO116">
-        <v>0.67</v>
+        <v>1.26</v>
       </c>
       <c r="AP116">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ116">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR116">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS116">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AT116">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="AU116">
         <v>7</v>
@@ -25194,25 +25200,25 @@
         <v>1.09</v>
       </c>
       <c r="AN117">
+        <v>0.89</v>
+      </c>
+      <c r="AO117">
+        <v>1.58</v>
+      </c>
+      <c r="AP117">
+        <v>0.91</v>
+      </c>
+      <c r="AQ117">
+        <v>1.57</v>
+      </c>
+      <c r="AR117">
         <v>1.11</v>
       </c>
-      <c r="AO117">
-        <v>1.22</v>
-      </c>
-      <c r="AP117">
-        <v>1.27</v>
-      </c>
-      <c r="AQ117">
-        <v>1.18</v>
-      </c>
-      <c r="AR117">
-        <v>1</v>
-      </c>
       <c r="AS117">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AT117">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="AU117">
         <v>3</v>
@@ -25328,7 +25334,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25400,25 +25406,25 @@
         <v>1.22</v>
       </c>
       <c r="AN118">
-        <v>1.11</v>
+        <v>0.74</v>
       </c>
       <c r="AO118">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AP118">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ118">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR118">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AS118">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AT118">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25534,7 +25540,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25606,25 +25612,25 @@
         <v>1.5</v>
       </c>
       <c r="AN119">
+        <v>1.37</v>
+      </c>
+      <c r="AO119">
+        <v>1.63</v>
+      </c>
+      <c r="AP119">
+        <v>1.52</v>
+      </c>
+      <c r="AQ119">
+        <v>1.52</v>
+      </c>
+      <c r="AR119">
         <v>1.56</v>
       </c>
-      <c r="AO119">
-        <v>1</v>
-      </c>
-      <c r="AP119">
-        <v>1.82</v>
-      </c>
-      <c r="AQ119">
-        <v>0.91</v>
-      </c>
-      <c r="AR119">
-        <v>1.76</v>
-      </c>
       <c r="AS119">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AT119">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="AU119">
         <v>12</v>
@@ -25740,7 +25746,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25812,25 +25818,25 @@
         <v>2.1</v>
       </c>
       <c r="AN120">
+        <v>1.63</v>
+      </c>
+      <c r="AO120">
+        <v>1.37</v>
+      </c>
+      <c r="AP120">
+        <v>1.74</v>
+      </c>
+      <c r="AQ120">
+        <v>1.25</v>
+      </c>
+      <c r="AR120">
         <v>1.78</v>
       </c>
-      <c r="AO120">
-        <v>1.11</v>
-      </c>
-      <c r="AP120">
-        <v>2</v>
-      </c>
-      <c r="AQ120">
-        <v>0.83</v>
-      </c>
-      <c r="AR120">
-        <v>1.76</v>
-      </c>
       <c r="AS120">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AT120">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26018,25 +26024,25 @@
         <v>1.67</v>
       </c>
       <c r="AN121">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AO121">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AP121">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ121">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR121">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS121">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AT121">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26152,7 +26158,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26224,25 +26230,25 @@
         <v>1.55</v>
       </c>
       <c r="AN122">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AO122">
-        <v>0.7</v>
+        <v>1.25</v>
       </c>
       <c r="AP122">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ122">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR122">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AS122">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AT122">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26358,7 +26364,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26430,25 +26436,25 @@
         <v>1.93</v>
       </c>
       <c r="AN123">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO123">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ123">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR123">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS123">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AT123">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="AU123">
         <v>6</v>
@@ -26636,25 +26642,25 @@
         <v>2.25</v>
       </c>
       <c r="AN124">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AO124">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AP124">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR124">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AS124">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT124">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26842,25 +26848,25 @@
         <v>1.67</v>
       </c>
       <c r="AN125">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AO125">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AP125">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ125">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR125">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AS125">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AT125">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="AU125">
         <v>8</v>
@@ -26976,7 +26982,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27048,25 +27054,25 @@
         <v>1.3</v>
       </c>
       <c r="AN126">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO126">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AP126">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR126">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AS126">
         <v>1.8</v>
       </c>
       <c r="AT126">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27254,25 +27260,25 @@
         <v>1.55</v>
       </c>
       <c r="AN127">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AO127">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AP127">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AQ127">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR127">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS127">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AT127">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AU127">
         <v>4</v>
@@ -27388,7 +27394,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27460,22 +27466,22 @@
         <v>1.36</v>
       </c>
       <c r="AN128">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AO128">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="AP128">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AQ128">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AR128">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AS128">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AT128">
         <v>3.11</v>
@@ -27594,7 +27600,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27666,25 +27672,25 @@
         <v>1.35</v>
       </c>
       <c r="AN129">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AO129">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AP129">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ129">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AR129">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AS129">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AT129">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="AU129">
         <v>8</v>
@@ -27800,7 +27806,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27872,25 +27878,25 @@
         <v>1.52</v>
       </c>
       <c r="AN130">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AP130">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AQ130">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AR130">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AS130">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AT130">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28006,7 +28012,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28078,25 +28084,25 @@
         <v>3.3</v>
       </c>
       <c r="AN131">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AO131">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AQ131">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR131">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AS131">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AT131">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="AU131">
         <v>11</v>
@@ -28284,25 +28290,25 @@
         <v>2.15</v>
       </c>
       <c r="AN132">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AO132">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AQ132">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
       </c>
       <c r="AS132">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AT132">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28418,7 +28424,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28490,25 +28496,25 @@
         <v>1.31</v>
       </c>
       <c r="AN133">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO133">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AP133">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AQ133">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR133">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS133">
         <v>1.48</v>
       </c>
       <c r="AT133">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28624,7 +28630,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28696,25 +28702,25 @@
         <v>2.95</v>
       </c>
       <c r="AN134">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AO134">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="AP134">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AQ134">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="AR134">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AS134">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AT134">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -28830,7 +28836,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -28902,25 +28908,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AO135">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AP135">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR135">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AS135">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AT135">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="AU135">
         <v>12</v>
@@ -29036,7 +29042,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29108,25 +29114,25 @@
         <v>2.1</v>
       </c>
       <c r="AN136">
+        <v>1.41</v>
+      </c>
+      <c r="AO136">
+        <v>1.23</v>
+      </c>
+      <c r="AP136">
+        <v>1.42</v>
+      </c>
+      <c r="AQ136">
+        <v>1.25</v>
+      </c>
+      <c r="AR136">
         <v>1.91</v>
       </c>
-      <c r="AO136">
-        <v>0.91</v>
-      </c>
-      <c r="AP136">
-        <v>2</v>
-      </c>
-      <c r="AQ136">
-        <v>0.83</v>
-      </c>
-      <c r="AR136">
-        <v>2.08</v>
-      </c>
       <c r="AS136">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AT136">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="AU136">
         <v>9</v>
@@ -29242,7 +29248,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29314,25 +29320,25 @@
         <v>1.62</v>
       </c>
       <c r="AN137">
+        <v>1.5</v>
+      </c>
+      <c r="AO137">
         <v>1.82</v>
       </c>
-      <c r="AO137">
-        <v>1.64</v>
-      </c>
       <c r="AP137">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AQ137">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR137">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AS137">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AT137">
-        <v>3.78</v>
+        <v>3.61</v>
       </c>
       <c r="AU137">
         <v>4</v>
@@ -29448,7 +29454,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29520,25 +29526,25 @@
         <v>2.35</v>
       </c>
       <c r="AN138">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AO138">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="AP138">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AQ138">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR138">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AS138">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AT138">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AU138">
         <v>12</v>
@@ -29654,7 +29660,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29726,25 +29732,25 @@
         <v>1.55</v>
       </c>
       <c r="AN139">
+        <v>1.5</v>
+      </c>
+      <c r="AO139">
         <v>1.45</v>
       </c>
-      <c r="AO139">
-        <v>1.09</v>
-      </c>
       <c r="AP139">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AQ139">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AR139">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AS139">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AT139">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="AU139">
         <v>3</v>
@@ -29811,6 +29817,624 @@
       </c>
       <c r="BP139">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7784921</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45703.58333333334</v>
+      </c>
+      <c r="F140">
+        <v>24</v>
+      </c>
+      <c r="G140" t="s">
+        <v>70</v>
+      </c>
+      <c r="H140" t="s">
+        <v>75</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>2</v>
+      </c>
+      <c r="O140" t="s">
+        <v>188</v>
+      </c>
+      <c r="P140" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q140">
+        <v>2.45</v>
+      </c>
+      <c r="R140">
+        <v>2.2</v>
+      </c>
+      <c r="S140">
+        <v>3.9</v>
+      </c>
+      <c r="T140">
+        <v>1.33</v>
+      </c>
+      <c r="U140">
+        <v>3.1</v>
+      </c>
+      <c r="V140">
+        <v>2.4</v>
+      </c>
+      <c r="W140">
+        <v>1.5</v>
+      </c>
+      <c r="X140">
+        <v>6.3</v>
+      </c>
+      <c r="Y140">
+        <v>1.06</v>
+      </c>
+      <c r="Z140">
+        <v>1.93</v>
+      </c>
+      <c r="AA140">
+        <v>3.68</v>
+      </c>
+      <c r="AB140">
+        <v>3.56</v>
+      </c>
+      <c r="AC140">
+        <v>1.04</v>
+      </c>
+      <c r="AD140">
+        <v>10</v>
+      </c>
+      <c r="AE140">
+        <v>1.22</v>
+      </c>
+      <c r="AF140">
+        <v>4</v>
+      </c>
+      <c r="AG140">
+        <v>1.67</v>
+      </c>
+      <c r="AH140">
+        <v>2</v>
+      </c>
+      <c r="AI140">
+        <v>1.57</v>
+      </c>
+      <c r="AJ140">
+        <v>2.2</v>
+      </c>
+      <c r="AK140">
+        <v>1.28</v>
+      </c>
+      <c r="AL140">
+        <v>1.22</v>
+      </c>
+      <c r="AM140">
+        <v>1.8</v>
+      </c>
+      <c r="AN140">
+        <v>1.7</v>
+      </c>
+      <c r="AO140">
+        <v>1.7</v>
+      </c>
+      <c r="AP140">
+        <v>1.75</v>
+      </c>
+      <c r="AQ140">
+        <v>1.63</v>
+      </c>
+      <c r="AR140">
+        <v>1.78</v>
+      </c>
+      <c r="AS140">
+        <v>1.74</v>
+      </c>
+      <c r="AT140">
+        <v>3.52</v>
+      </c>
+      <c r="AU140">
+        <v>8</v>
+      </c>
+      <c r="AV140">
+        <v>7</v>
+      </c>
+      <c r="AW140">
+        <v>12</v>
+      </c>
+      <c r="AX140">
+        <v>9</v>
+      </c>
+      <c r="AY140">
+        <v>24</v>
+      </c>
+      <c r="AZ140">
+        <v>17</v>
+      </c>
+      <c r="BA140">
+        <v>5</v>
+      </c>
+      <c r="BB140">
+        <v>3</v>
+      </c>
+      <c r="BC140">
+        <v>8</v>
+      </c>
+      <c r="BD140">
+        <v>1.71</v>
+      </c>
+      <c r="BE140">
+        <v>6.4</v>
+      </c>
+      <c r="BF140">
+        <v>2.4</v>
+      </c>
+      <c r="BG140">
+        <v>1.34</v>
+      </c>
+      <c r="BH140">
+        <v>2.9</v>
+      </c>
+      <c r="BI140">
+        <v>1.58</v>
+      </c>
+      <c r="BJ140">
+        <v>2.18</v>
+      </c>
+      <c r="BK140">
+        <v>1.93</v>
+      </c>
+      <c r="BL140">
+        <v>1.74</v>
+      </c>
+      <c r="BM140">
+        <v>2.48</v>
+      </c>
+      <c r="BN140">
+        <v>1.45</v>
+      </c>
+      <c r="BO140">
+        <v>3.2</v>
+      </c>
+      <c r="BP140">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7784922</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45703.58333333334</v>
+      </c>
+      <c r="F141">
+        <v>24</v>
+      </c>
+      <c r="G141" t="s">
+        <v>77</v>
+      </c>
+      <c r="H141" t="s">
+        <v>81</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141">
+        <v>3</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>3</v>
+      </c>
+      <c r="O141" t="s">
+        <v>189</v>
+      </c>
+      <c r="P141" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q141">
+        <v>2.8</v>
+      </c>
+      <c r="R141">
+        <v>2.1</v>
+      </c>
+      <c r="S141">
+        <v>3.5</v>
+      </c>
+      <c r="T141">
+        <v>1.38</v>
+      </c>
+      <c r="U141">
+        <v>2.8</v>
+      </c>
+      <c r="V141">
+        <v>2.75</v>
+      </c>
+      <c r="W141">
+        <v>1.4</v>
+      </c>
+      <c r="X141">
+        <v>6.4</v>
+      </c>
+      <c r="Y141">
+        <v>1.05</v>
+      </c>
+      <c r="Z141">
+        <v>2.25</v>
+      </c>
+      <c r="AA141">
+        <v>3.3</v>
+      </c>
+      <c r="AB141">
+        <v>3.09</v>
+      </c>
+      <c r="AC141">
+        <v>1.05</v>
+      </c>
+      <c r="AD141">
+        <v>9</v>
+      </c>
+      <c r="AE141">
+        <v>1.3</v>
+      </c>
+      <c r="AF141">
+        <v>3.4</v>
+      </c>
+      <c r="AG141">
+        <v>1.89</v>
+      </c>
+      <c r="AH141">
+        <v>1.85</v>
+      </c>
+      <c r="AI141">
+        <v>1.7</v>
+      </c>
+      <c r="AJ141">
+        <v>2</v>
+      </c>
+      <c r="AK141">
+        <v>1.36</v>
+      </c>
+      <c r="AL141">
+        <v>1.25</v>
+      </c>
+      <c r="AM141">
+        <v>1.6</v>
+      </c>
+      <c r="AN141">
+        <v>1.17</v>
+      </c>
+      <c r="AO141">
+        <v>1.43</v>
+      </c>
+      <c r="AP141">
+        <v>1.25</v>
+      </c>
+      <c r="AQ141">
+        <v>1.38</v>
+      </c>
+      <c r="AR141">
+        <v>1.56</v>
+      </c>
+      <c r="AS141">
+        <v>1.54</v>
+      </c>
+      <c r="AT141">
+        <v>3.1</v>
+      </c>
+      <c r="AU141">
+        <v>6</v>
+      </c>
+      <c r="AV141">
+        <v>5</v>
+      </c>
+      <c r="AW141">
+        <v>2</v>
+      </c>
+      <c r="AX141">
+        <v>9</v>
+      </c>
+      <c r="AY141">
+        <v>9</v>
+      </c>
+      <c r="AZ141">
+        <v>19</v>
+      </c>
+      <c r="BA141">
+        <v>1</v>
+      </c>
+      <c r="BB141">
+        <v>9</v>
+      </c>
+      <c r="BC141">
+        <v>10</v>
+      </c>
+      <c r="BD141">
+        <v>1.83</v>
+      </c>
+      <c r="BE141">
+        <v>6.25</v>
+      </c>
+      <c r="BF141">
+        <v>2.18</v>
+      </c>
+      <c r="BG141">
+        <v>1.4</v>
+      </c>
+      <c r="BH141">
+        <v>2.65</v>
+      </c>
+      <c r="BI141">
+        <v>1.68</v>
+      </c>
+      <c r="BJ141">
+        <v>2.02</v>
+      </c>
+      <c r="BK141">
+        <v>2.08</v>
+      </c>
+      <c r="BL141">
+        <v>1.63</v>
+      </c>
+      <c r="BM141">
+        <v>2.7</v>
+      </c>
+      <c r="BN141">
+        <v>1.38</v>
+      </c>
+      <c r="BO141">
+        <v>3.55</v>
+      </c>
+      <c r="BP141">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7784923</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45703.6875</v>
+      </c>
+      <c r="F142">
+        <v>24</v>
+      </c>
+      <c r="G142" t="s">
+        <v>72</v>
+      </c>
+      <c r="H142" t="s">
+        <v>73</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="O142" t="s">
+        <v>150</v>
+      </c>
+      <c r="P142" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q142">
+        <v>4.75</v>
+      </c>
+      <c r="R142">
+        <v>2.5</v>
+      </c>
+      <c r="S142">
+        <v>1.95</v>
+      </c>
+      <c r="T142">
+        <v>1.25</v>
+      </c>
+      <c r="U142">
+        <v>3.65</v>
+      </c>
+      <c r="V142">
+        <v>2.15</v>
+      </c>
+      <c r="W142">
+        <v>1.62</v>
+      </c>
+      <c r="X142">
+        <v>4.7</v>
+      </c>
+      <c r="Y142">
+        <v>1.13</v>
+      </c>
+      <c r="Z142">
+        <v>4.9</v>
+      </c>
+      <c r="AA142">
+        <v>4.4</v>
+      </c>
+      <c r="AB142">
+        <v>1.57</v>
+      </c>
+      <c r="AC142">
+        <v>1.02</v>
+      </c>
+      <c r="AD142">
+        <v>13</v>
+      </c>
+      <c r="AE142">
+        <v>1.15</v>
+      </c>
+      <c r="AF142">
+        <v>5.25</v>
+      </c>
+      <c r="AG142">
+        <v>1.53</v>
+      </c>
+      <c r="AH142">
+        <v>2.4</v>
+      </c>
+      <c r="AI142">
+        <v>1.57</v>
+      </c>
+      <c r="AJ142">
+        <v>2.2</v>
+      </c>
+      <c r="AK142">
+        <v>2.4</v>
+      </c>
+      <c r="AL142">
+        <v>1.15</v>
+      </c>
+      <c r="AM142">
+        <v>1.15</v>
+      </c>
+      <c r="AN142">
+        <v>0.61</v>
+      </c>
+      <c r="AO142">
+        <v>1.48</v>
+      </c>
+      <c r="AP142">
+        <v>0.71</v>
+      </c>
+      <c r="AQ142">
+        <v>1.42</v>
+      </c>
+      <c r="AR142">
+        <v>1.24</v>
+      </c>
+      <c r="AS142">
+        <v>1.93</v>
+      </c>
+      <c r="AT142">
+        <v>3.17</v>
+      </c>
+      <c r="AU142">
+        <v>5</v>
+      </c>
+      <c r="AV142">
+        <v>8</v>
+      </c>
+      <c r="AW142">
+        <v>9</v>
+      </c>
+      <c r="AX142">
+        <v>12</v>
+      </c>
+      <c r="AY142">
+        <v>19</v>
+      </c>
+      <c r="AZ142">
+        <v>22</v>
+      </c>
+      <c r="BA142">
+        <v>4</v>
+      </c>
+      <c r="BB142">
+        <v>6</v>
+      </c>
+      <c r="BC142">
+        <v>10</v>
+      </c>
+      <c r="BD142">
+        <v>3.15</v>
+      </c>
+      <c r="BE142">
+        <v>7</v>
+      </c>
+      <c r="BF142">
+        <v>1.43</v>
+      </c>
+      <c r="BG142">
+        <v>1.16</v>
+      </c>
+      <c r="BH142">
+        <v>4.3</v>
+      </c>
+      <c r="BI142">
+        <v>1.3</v>
+      </c>
+      <c r="BJ142">
+        <v>3.05</v>
+      </c>
+      <c r="BK142">
+        <v>1.52</v>
+      </c>
+      <c r="BL142">
+        <v>2.3</v>
+      </c>
+      <c r="BM142">
+        <v>1.82</v>
+      </c>
+      <c r="BN142">
+        <v>1.84</v>
+      </c>
+      <c r="BO142">
+        <v>2.25</v>
+      </c>
+      <c r="BP142">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ2">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1722,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1928,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ4">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2340,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2546,10 +2546,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ7">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2746,25 +2746,25 @@
         <v>1.73</v>
       </c>
       <c r="AN8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ8">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR8">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2952,25 +2952,25 @@
         <v>1.52</v>
       </c>
       <c r="AN9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>12</v>
@@ -3164,19 +3164,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ10">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3367,22 +3367,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR11">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>9</v>
@@ -3576,19 +3576,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR12">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="AS12">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="AU12">
         <v>7</v>
@@ -3782,19 +3782,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR13">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AT13">
-        <v>3.83</v>
+        <v>1.79</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3982,25 +3982,25 @@
         <v>2.3</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR14">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>15</v>
@@ -4188,25 +4188,25 @@
         <v>1.52</v>
       </c>
       <c r="AN15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ15">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR15">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AS15">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="AT15">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AU15">
         <v>2</v>
@@ -4400,19 +4400,19 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR16">
-        <v>1.59</v>
+        <v>2.11</v>
       </c>
       <c r="AS16">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AT16">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="AU16">
         <v>8</v>
@@ -4600,25 +4600,25 @@
         <v>1.65</v>
       </c>
       <c r="AN17">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AS17">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT17">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4806,25 +4806,25 @@
         <v>1.45</v>
       </c>
       <c r="AN18">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ18">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AS18">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AT18">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="AU18">
         <v>9</v>
@@ -5018,19 +5018,19 @@
         <v>3</v>
       </c>
       <c r="AP19">
+        <v>2</v>
+      </c>
+      <c r="AQ19">
         <v>1.42</v>
       </c>
-      <c r="AQ19">
-        <v>1.38</v>
-      </c>
       <c r="AR19">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AS19">
-        <v>2.59</v>
+        <v>1.76</v>
       </c>
       <c r="AT19">
-        <v>4.39</v>
+        <v>3.61</v>
       </c>
       <c r="AU19">
         <v>3</v>
@@ -5218,25 +5218,25 @@
         <v>1.88</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO20">
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ20">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR20">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AS20">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="AT20">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5424,25 +5424,25 @@
         <v>1.85</v>
       </c>
       <c r="AN21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR21">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AS21">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AT21">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5630,25 +5630,25 @@
         <v>1.2</v>
       </c>
       <c r="AN22">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ22">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR22">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="AS22">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AT22">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5836,25 +5836,25 @@
         <v>2.15</v>
       </c>
       <c r="AN23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ23">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR23">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AS23">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AT23">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -6045,22 +6045,22 @@
         <v>3</v>
       </c>
       <c r="AO24">
+        <v>1</v>
+      </c>
+      <c r="AP24">
+        <v>2.08</v>
+      </c>
+      <c r="AQ24">
         <v>1.33</v>
       </c>
-      <c r="AP24">
-        <v>1.75</v>
-      </c>
-      <c r="AQ24">
-        <v>1.63</v>
-      </c>
       <c r="AR24">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AS24">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT24">
-        <v>3.09</v>
+        <v>3.53</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6248,25 +6248,25 @@
         <v>1.85</v>
       </c>
       <c r="AN25">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR25">
-        <v>2.37</v>
+        <v>3.42</v>
       </c>
       <c r="AS25">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="AT25">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6454,22 +6454,22 @@
         <v>2.05</v>
       </c>
       <c r="AN26">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR26">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AS26">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AT26">
         <v>3.14</v>
@@ -6660,25 +6660,25 @@
         <v>2.3</v>
       </c>
       <c r="AN27">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ27">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR27">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AT27">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="AU27">
         <v>5</v>
@@ -6866,25 +6866,25 @@
         <v>1.35</v>
       </c>
       <c r="AN28">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO28">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AS28">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT28">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AU28">
         <v>9</v>
@@ -7072,25 +7072,25 @@
         <v>2.4</v>
       </c>
       <c r="AN29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR29">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="AS29">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT29">
-        <v>3.08</v>
+        <v>3.49</v>
       </c>
       <c r="AU29">
         <v>9</v>
@@ -7278,25 +7278,25 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AS30">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AT30">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7484,25 +7484,25 @@
         <v>0</v>
       </c>
       <c r="AN31">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO31">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR31">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS31">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AT31">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="AU31">
         <v>4</v>
@@ -7690,25 +7690,25 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO32">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR32">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AS32">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AT32">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AU32">
         <v>2</v>
@@ -7896,25 +7896,25 @@
         <v>1.3</v>
       </c>
       <c r="AN33">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AO33">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ33">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR33">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AS33">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="AT33">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8102,25 +8102,25 @@
         <v>1.91</v>
       </c>
       <c r="AN34">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO34">
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="AS34">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AT34">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="AU34">
         <v>2</v>
@@ -8308,25 +8308,25 @@
         <v>1.62</v>
       </c>
       <c r="AN35">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO35">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ35">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR35">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AS35">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AT35">
-        <v>3.39</v>
+        <v>3.52</v>
       </c>
       <c r="AU35">
         <v>7</v>
@@ -8514,25 +8514,25 @@
         <v>1.55</v>
       </c>
       <c r="AN36">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ36">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AS36">
-        <v>1.7</v>
+        <v>1.08</v>
       </c>
       <c r="AT36">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8720,25 +8720,25 @@
         <v>1.87</v>
       </c>
       <c r="AN37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ37">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AS37">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT37">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="AU37">
         <v>4</v>
@@ -8926,25 +8926,25 @@
         <v>1.3</v>
       </c>
       <c r="AN38">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="AO38">
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ38">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR38">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AS38">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AT38">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AU38">
         <v>9</v>
@@ -9132,25 +9132,25 @@
         <v>1.75</v>
       </c>
       <c r="AN39">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO39">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR39">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="AS39">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AT39">
-        <v>3.67</v>
+        <v>4.01</v>
       </c>
       <c r="AU39">
         <v>2</v>
@@ -9338,25 +9338,25 @@
         <v>2.3</v>
       </c>
       <c r="AN40">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO40">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ40">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR40">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AS40">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AT40">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9544,25 +9544,25 @@
         <v>1.43</v>
       </c>
       <c r="AN41">
+        <v>2.33</v>
+      </c>
+      <c r="AO41">
+        <v>3</v>
+      </c>
+      <c r="AP41">
         <v>1.67</v>
       </c>
-      <c r="AO41">
-        <v>2.17</v>
-      </c>
-      <c r="AP41">
-        <v>1.25</v>
-      </c>
       <c r="AQ41">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR41">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AS41">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AT41">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="AU41">
         <v>2</v>
@@ -9750,25 +9750,25 @@
         <v>1.17</v>
       </c>
       <c r="AN42">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="AO42">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ42">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR42">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AS42">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AT42">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9956,25 +9956,25 @@
         <v>1.77</v>
       </c>
       <c r="AN43">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO43">
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
       </c>
       <c r="AS43">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AT43">
-        <v>3.39</v>
+        <v>3.22</v>
       </c>
       <c r="AU43">
         <v>8</v>
@@ -10162,25 +10162,25 @@
         <v>1.22</v>
       </c>
       <c r="AN44">
-        <v>0.71</v>
+        <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AP44">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR44">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AS44">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AT44">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="AU44">
         <v>2</v>
@@ -10368,25 +10368,25 @@
         <v>1.9</v>
       </c>
       <c r="AN45">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AO45">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR45">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AS45">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AT45">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10574,25 +10574,25 @@
         <v>2.45</v>
       </c>
       <c r="AN46">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AO46">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AP46">
+        <v>2</v>
+      </c>
+      <c r="AQ46">
+        <v>1</v>
+      </c>
+      <c r="AR46">
         <v>1.42</v>
       </c>
-      <c r="AQ46">
-        <v>0.96</v>
-      </c>
-      <c r="AR46">
-        <v>1.71</v>
-      </c>
       <c r="AS46">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AT46">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10780,25 +10780,25 @@
         <v>2.11</v>
       </c>
       <c r="AN47">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO47">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ47">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR47">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AS47">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT47">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="AU47">
         <v>3</v>
@@ -10989,22 +10989,22 @@
         <v>2</v>
       </c>
       <c r="AO48">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AP48">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ48">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AS48">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AT48">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="AU48">
         <v>11</v>
@@ -11192,25 +11192,25 @@
         <v>2.42</v>
       </c>
       <c r="AN49">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO49">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ49">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR49">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="AS49">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AT49">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="AU49">
         <v>8</v>
@@ -11398,25 +11398,25 @@
         <v>2.3</v>
       </c>
       <c r="AN50">
+        <v>2</v>
+      </c>
+      <c r="AO50">
+        <v>0.25</v>
+      </c>
+      <c r="AP50">
+        <v>1.67</v>
+      </c>
+      <c r="AQ50">
+        <v>0.58</v>
+      </c>
+      <c r="AR50">
         <v>1.38</v>
       </c>
-      <c r="AO50">
-        <v>1</v>
-      </c>
-      <c r="AP50">
-        <v>1.25</v>
-      </c>
-      <c r="AQ50">
-        <v>0.91</v>
-      </c>
-      <c r="AR50">
-        <v>1.4</v>
-      </c>
       <c r="AS50">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AT50">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11604,25 +11604,25 @@
         <v>1.65</v>
       </c>
       <c r="AN51">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AO51">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ51">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR51">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS51">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AT51">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11810,25 +11810,25 @@
         <v>1.38</v>
       </c>
       <c r="AN52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP52">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ52">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR52">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AS52">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AT52">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="AU52">
         <v>7</v>
@@ -12016,25 +12016,25 @@
         <v>1.62</v>
       </c>
       <c r="AN53">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AO53">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ53">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR53">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AS53">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AT53">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12222,25 +12222,25 @@
         <v>1.5</v>
       </c>
       <c r="AN54">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO54">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP54">
+        <v>2</v>
+      </c>
+      <c r="AQ54">
+        <v>0.83</v>
+      </c>
+      <c r="AR54">
         <v>1.74</v>
       </c>
-      <c r="AQ54">
-        <v>1.42</v>
-      </c>
-      <c r="AR54">
-        <v>1.6</v>
-      </c>
       <c r="AS54">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AT54">
-        <v>3.32</v>
+        <v>3.66</v>
       </c>
       <c r="AU54">
         <v>7</v>
@@ -12428,25 +12428,25 @@
         <v>1.65</v>
       </c>
       <c r="AN55">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AO55">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ55">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR55">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AS55">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AT55">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12634,25 +12634,25 @@
         <v>1.42</v>
       </c>
       <c r="AN56">
-        <v>0.89</v>
+        <v>1.25</v>
       </c>
       <c r="AO56">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR56">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AS56">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AT56">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AU56">
         <v>4</v>
@@ -12840,25 +12840,25 @@
         <v>1.83</v>
       </c>
       <c r="AN57">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO57">
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AS57">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AT57">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="AU57">
         <v>6</v>
@@ -13046,25 +13046,25 @@
         <v>1.95</v>
       </c>
       <c r="AN58">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AO58">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ58">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR58">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AS58">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AT58">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="AU58">
         <v>7</v>
@@ -13252,25 +13252,25 @@
         <v>1.7</v>
       </c>
       <c r="AN59">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO59">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AS59">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AT59">
-        <v>3.24</v>
+        <v>3.41</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13458,25 +13458,25 @@
         <v>2.5</v>
       </c>
       <c r="AN60">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR60">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AS60">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT60">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13664,25 +13664,25 @@
         <v>1.1</v>
       </c>
       <c r="AN61">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AO61">
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ61">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR61">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AS61">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AT61">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="AU61">
         <v>5</v>
@@ -13870,25 +13870,25 @@
         <v>1.83</v>
       </c>
       <c r="AN62">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AO62">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ62">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR62">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AS62">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AT62">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="AU62">
         <v>9</v>
@@ -14076,25 +14076,25 @@
         <v>1.22</v>
       </c>
       <c r="AN63">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="AO63">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ63">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AS63">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AT63">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14282,25 +14282,25 @@
         <v>2.7</v>
       </c>
       <c r="AN64">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO64">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="AP64">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ64">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR64">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AS64">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT64">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AU64">
         <v>10</v>
@@ -14488,25 +14488,25 @@
         <v>1.6</v>
       </c>
       <c r="AN65">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO65">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP65">
+        <v>1.67</v>
+      </c>
+      <c r="AQ65">
         <v>1.25</v>
       </c>
-      <c r="AQ65">
-        <v>1.52</v>
-      </c>
       <c r="AR65">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AS65">
         <v>1.59</v>
       </c>
       <c r="AT65">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14694,25 +14694,25 @@
         <v>1.62</v>
       </c>
       <c r="AN66">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO66">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ66">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR66">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AS66">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AT66">
-        <v>3.43</v>
+        <v>3.59</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14900,25 +14900,25 @@
         <v>1.53</v>
       </c>
       <c r="AN67">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AO67">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ67">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR67">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS67">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AT67">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -15106,25 +15106,25 @@
         <v>1.2</v>
       </c>
       <c r="AN68">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AO68">
+        <v>0.4</v>
+      </c>
+      <c r="AP68">
         <v>1.27</v>
       </c>
-      <c r="AP68">
+      <c r="AQ68">
         <v>0.91</v>
       </c>
-      <c r="AQ68">
-        <v>1.52</v>
-      </c>
       <c r="AR68">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AS68">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AT68">
-        <v>2.79</v>
+        <v>2.48</v>
       </c>
       <c r="AU68">
         <v>2</v>
@@ -15312,25 +15312,25 @@
         <v>1.55</v>
       </c>
       <c r="AN69">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AO69">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR69">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS69">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AT69">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15518,25 +15518,25 @@
         <v>2.8</v>
       </c>
       <c r="AN70">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AO70">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ70">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR70">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AS70">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AT70">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15724,25 +15724,25 @@
         <v>1.75</v>
       </c>
       <c r="AN71">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AS71">
         <v>1.68</v>
       </c>
       <c r="AT71">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15930,25 +15930,25 @@
         <v>1.35</v>
       </c>
       <c r="AN72">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO72">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ72">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR72">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AS72">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AT72">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16136,25 +16136,25 @@
         <v>1.9</v>
       </c>
       <c r="AN73">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AO73">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ73">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR73">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AS73">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT73">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16342,25 +16342,25 @@
         <v>1.55</v>
       </c>
       <c r="AN74">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO74">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR74">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AS74">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AT74">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16548,25 +16548,25 @@
         <v>2.85</v>
       </c>
       <c r="AN75">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AO75">
-        <v>0.67</v>
+        <v>0.17</v>
       </c>
       <c r="AP75">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
       </c>
       <c r="AS75">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT75">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="AU75">
         <v>10</v>
@@ -16754,25 +16754,25 @@
         <v>1.72</v>
       </c>
       <c r="AN76">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AO76">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ76">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR76">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AS76">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT76">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16960,25 +16960,25 @@
         <v>1.45</v>
       </c>
       <c r="AN77">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AO77">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ77">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR77">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AS77">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AT77">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="AU77">
         <v>4</v>
@@ -17166,25 +17166,25 @@
         <v>3</v>
       </c>
       <c r="AN78">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AO78">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ78">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR78">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AS78">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AT78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17372,25 +17372,25 @@
         <v>1.87</v>
       </c>
       <c r="AN79">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AO79">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ79">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR79">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AS79">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AT79">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AU79">
         <v>7</v>
@@ -17578,25 +17578,25 @@
         <v>1.22</v>
       </c>
       <c r="AN80">
-        <v>0.62</v>
+        <v>1.17</v>
       </c>
       <c r="AO80">
-        <v>1.54</v>
+        <v>0.83</v>
       </c>
       <c r="AP80">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ80">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR80">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AS80">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AT80">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17784,25 +17784,25 @@
         <v>1.17</v>
       </c>
       <c r="AN81">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="AO81">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AP81">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="AS81">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AT81">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17990,25 +17990,25 @@
         <v>1.8</v>
       </c>
       <c r="AN82">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AO82">
+        <v>2.17</v>
+      </c>
+      <c r="AP82">
         <v>1.92</v>
       </c>
-      <c r="AP82">
-        <v>1.57</v>
-      </c>
       <c r="AQ82">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR82">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AS82">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AT82">
-        <v>3.27</v>
+        <v>3.53</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18196,25 +18196,25 @@
         <v>1.65</v>
       </c>
       <c r="AN83">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="AO83">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ83">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AS83">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AT83">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="AU83">
         <v>11</v>
@@ -18402,25 +18402,25 @@
         <v>1.45</v>
       </c>
       <c r="AN84">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="AO84">
-        <v>1.31</v>
+        <v>0.83</v>
       </c>
       <c r="AP84">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ84">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS84">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AT84">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="AU84">
         <v>6</v>
@@ -18608,25 +18608,25 @@
         <v>1.67</v>
       </c>
       <c r="AN85">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO85">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR85">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AS85">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AT85">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18814,25 +18814,25 @@
         <v>1.55</v>
       </c>
       <c r="AN86">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AO86">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ86">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR86">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AS86">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AT86">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -19020,25 +19020,25 @@
         <v>2.3</v>
       </c>
       <c r="AN87">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="AO87">
-        <v>0.79</v>
+        <v>0.14</v>
       </c>
       <c r="AP87">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ87">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR87">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AS87">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AT87">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AU87">
         <v>6</v>
@@ -19226,25 +19226,25 @@
         <v>1.95</v>
       </c>
       <c r="AN88">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="AO88">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ88">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR88">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AS88">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT88">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="AU88">
         <v>-1</v>
@@ -19432,25 +19432,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="AO89">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP89">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR89">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AS89">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AT89">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="AU89">
         <v>12</v>
@@ -19638,25 +19638,25 @@
         <v>2.7</v>
       </c>
       <c r="AN90">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AO90">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="AP90">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ90">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR90">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AS90">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AT90">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AU90">
         <v>8</v>
@@ -19844,25 +19844,25 @@
         <v>1.7</v>
       </c>
       <c r="AN91">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AO91">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AP91">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ91">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR91">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AS91">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AT91">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AU91">
         <v>8</v>
@@ -20050,25 +20050,25 @@
         <v>1.85</v>
       </c>
       <c r="AN92">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AO92">
-        <v>1.53</v>
+        <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR92">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AS92">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AT92">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20256,25 +20256,25 @@
         <v>1.22</v>
       </c>
       <c r="AN93">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="AO93">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ93">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="AS93">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT93">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20462,25 +20462,25 @@
         <v>1.93</v>
       </c>
       <c r="AN94">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AO94">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR94">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AS94">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AT94">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20668,25 +20668,25 @@
         <v>1.22</v>
       </c>
       <c r="AN95">
-        <v>0.8</v>
+        <v>1.43</v>
       </c>
       <c r="AO95">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR95">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AS95">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT95">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20874,25 +20874,25 @@
         <v>1.75</v>
       </c>
       <c r="AN96">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO96">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AS96">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AT96">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="AU96">
         <v>11</v>
@@ -21080,25 +21080,25 @@
         <v>1.95</v>
       </c>
       <c r="AN97">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AO97">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR97">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AS97">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AT97">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AU97">
         <v>13</v>
@@ -21286,25 +21286,25 @@
         <v>2.25</v>
       </c>
       <c r="AN98">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AO98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ98">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR98">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS98">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AT98">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21492,25 +21492,25 @@
         <v>1.42</v>
       </c>
       <c r="AN99">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO99">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR99">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AS99">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AT99">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21698,25 +21698,25 @@
         <v>1.45</v>
       </c>
       <c r="AN100">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO100">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AS100">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AT100">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21904,25 +21904,25 @@
         <v>1.75</v>
       </c>
       <c r="AN101">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AO101">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ101">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR101">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AS101">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT101">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="AU101">
         <v>6</v>
@@ -22110,25 +22110,25 @@
         <v>3.3</v>
       </c>
       <c r="AN102">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO102">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ102">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR102">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AS102">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AT102">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22316,25 +22316,25 @@
         <v>1.45</v>
       </c>
       <c r="AN103">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AO103">
+        <v>1.63</v>
+      </c>
+      <c r="AP103">
+        <v>1.82</v>
+      </c>
+      <c r="AQ103">
+        <v>1.5</v>
+      </c>
+      <c r="AR103">
         <v>1.81</v>
       </c>
-      <c r="AP103">
-        <v>1.52</v>
-      </c>
-      <c r="AQ103">
-        <v>1.74</v>
-      </c>
-      <c r="AR103">
-        <v>1.64</v>
-      </c>
       <c r="AS103">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AT103">
-        <v>3.39</v>
+        <v>3.58</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22522,25 +22522,25 @@
         <v>1.3</v>
       </c>
       <c r="AN104">
-        <v>0.76</v>
+        <v>1.25</v>
       </c>
       <c r="AO104">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ104">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AS104">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AT104">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22728,25 +22728,25 @@
         <v>1.2</v>
       </c>
       <c r="AN105">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO105">
-        <v>1.35</v>
+        <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR105">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="AS105">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AT105">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22934,25 +22934,25 @@
         <v>2.2</v>
       </c>
       <c r="AN106">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AO106">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR106">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS106">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AT106">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="AU106">
         <v>7</v>
@@ -23140,25 +23140,25 @@
         <v>1.62</v>
       </c>
       <c r="AN107">
+        <v>1.75</v>
+      </c>
+      <c r="AO107">
+        <v>1.38</v>
+      </c>
+      <c r="AP107">
+        <v>2</v>
+      </c>
+      <c r="AQ107">
         <v>1.18</v>
       </c>
-      <c r="AO107">
-        <v>1.71</v>
-      </c>
-      <c r="AP107">
-        <v>1.42</v>
-      </c>
-      <c r="AQ107">
+      <c r="AR107">
+        <v>1.85</v>
+      </c>
+      <c r="AS107">
         <v>1.57</v>
       </c>
-      <c r="AR107">
-        <v>1.76</v>
-      </c>
-      <c r="AS107">
-        <v>1.71</v>
-      </c>
       <c r="AT107">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="AU107">
         <v>9</v>
@@ -23346,25 +23346,25 @@
         <v>1.75</v>
       </c>
       <c r="AN108">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="AO108">
-        <v>1.59</v>
+        <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ108">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR108">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AS108">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AT108">
-        <v>3.39</v>
+        <v>3.49</v>
       </c>
       <c r="AU108">
         <v>6</v>
@@ -23552,25 +23552,25 @@
         <v>1.62</v>
       </c>
       <c r="AN109">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AO109">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR109">
+        <v>1.41</v>
+      </c>
+      <c r="AS109">
         <v>1.46</v>
       </c>
-      <c r="AS109">
-        <v>1.62</v>
-      </c>
       <c r="AT109">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23758,25 +23758,25 @@
         <v>3.3</v>
       </c>
       <c r="AN110">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="AO110">
-        <v>0.72</v>
+        <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR110">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AS110">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AT110">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AU110">
         <v>9</v>
@@ -23964,25 +23964,25 @@
         <v>1.77</v>
       </c>
       <c r="AN111">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AO111">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ111">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR111">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AS111">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AT111">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24170,25 +24170,25 @@
         <v>2.05</v>
       </c>
       <c r="AN112">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AO112">
+        <v>1.22</v>
+      </c>
+      <c r="AP112">
+        <v>1.92</v>
+      </c>
+      <c r="AQ112">
+        <v>1.25</v>
+      </c>
+      <c r="AR112">
+        <v>1.84</v>
+      </c>
+      <c r="AS112">
         <v>1.39</v>
       </c>
-      <c r="AP112">
-        <v>1.57</v>
-      </c>
-      <c r="AQ112">
-        <v>1.52</v>
-      </c>
-      <c r="AR112">
-        <v>1.68</v>
-      </c>
-      <c r="AS112">
-        <v>1.58</v>
-      </c>
       <c r="AT112">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24376,25 +24376,25 @@
         <v>2.65</v>
       </c>
       <c r="AN113">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AO113">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ113">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR113">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AS113">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AT113">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AU113">
         <v>4</v>
@@ -24582,25 +24582,25 @@
         <v>1.57</v>
       </c>
       <c r="AN114">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AO114">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AP114">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ114">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR114">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AS114">
         <v>1.76</v>
       </c>
       <c r="AT114">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
       <c r="AU114">
         <v>6</v>
@@ -24788,25 +24788,25 @@
         <v>1.85</v>
       </c>
       <c r="AN115">
+        <v>2.33</v>
+      </c>
+      <c r="AO115">
         <v>1.67</v>
       </c>
-      <c r="AO115">
-        <v>1.61</v>
-      </c>
       <c r="AP115">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ115">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
+        <v>1.76</v>
+      </c>
+      <c r="AS115">
         <v>1.68</v>
       </c>
-      <c r="AS115">
-        <v>1.67</v>
-      </c>
       <c r="AT115">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24994,25 +24994,25 @@
         <v>1.36</v>
       </c>
       <c r="AN116">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AO116">
-        <v>1.26</v>
+        <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ116">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR116">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AS116">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AT116">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="AU116">
         <v>7</v>
@@ -25200,25 +25200,25 @@
         <v>1.09</v>
       </c>
       <c r="AN117">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AO117">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AP117">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ117">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR117">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AS117">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AT117">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="AU117">
         <v>3</v>
@@ -25406,25 +25406,25 @@
         <v>1.22</v>
       </c>
       <c r="AN118">
-        <v>0.74</v>
+        <v>1.11</v>
       </c>
       <c r="AO118">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ118">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR118">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AS118">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AT118">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25612,25 +25612,25 @@
         <v>1.5</v>
       </c>
       <c r="AN119">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AO119">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ119">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR119">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AS119">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AT119">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="AU119">
         <v>12</v>
@@ -25818,25 +25818,25 @@
         <v>2.1</v>
       </c>
       <c r="AN120">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AO120">
+        <v>1.11</v>
+      </c>
+      <c r="AP120">
+        <v>2</v>
+      </c>
+      <c r="AQ120">
+        <v>0.83</v>
+      </c>
+      <c r="AR120">
+        <v>1.76</v>
+      </c>
+      <c r="AS120">
         <v>1.37</v>
       </c>
-      <c r="AP120">
-        <v>1.74</v>
-      </c>
-      <c r="AQ120">
-        <v>1.25</v>
-      </c>
-      <c r="AR120">
-        <v>1.78</v>
-      </c>
-      <c r="AS120">
-        <v>1.56</v>
-      </c>
       <c r="AT120">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26024,25 +26024,25 @@
         <v>1.67</v>
       </c>
       <c r="AN121">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AO121">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AP121">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ121">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR121">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AS121">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AT121">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26230,25 +26230,25 @@
         <v>1.55</v>
       </c>
       <c r="AN122">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AO122">
-        <v>1.25</v>
+        <v>0.7</v>
       </c>
       <c r="AP122">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ122">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR122">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AS122">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AT122">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26436,25 +26436,25 @@
         <v>1.93</v>
       </c>
       <c r="AN123">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO123">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ123">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR123">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AS123">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT123">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="AU123">
         <v>6</v>
@@ -26642,25 +26642,25 @@
         <v>2.25</v>
       </c>
       <c r="AN124">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AO124">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AQ124">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR124">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AS124">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT124">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26848,25 +26848,25 @@
         <v>1.67</v>
       </c>
       <c r="AN125">
+        <v>1.7</v>
+      </c>
+      <c r="AO125">
+        <v>1.2</v>
+      </c>
+      <c r="AP125">
+        <v>1.92</v>
+      </c>
+      <c r="AQ125">
+        <v>1.25</v>
+      </c>
+      <c r="AR125">
         <v>1.65</v>
       </c>
-      <c r="AO125">
-        <v>1.45</v>
-      </c>
-      <c r="AP125">
-        <v>1.63</v>
-      </c>
-      <c r="AQ125">
-        <v>1.52</v>
-      </c>
-      <c r="AR125">
-        <v>1.62</v>
-      </c>
       <c r="AS125">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AT125">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="AU125">
         <v>8</v>
@@ -27054,25 +27054,25 @@
         <v>1.3</v>
       </c>
       <c r="AN126">
+        <v>1.6</v>
+      </c>
+      <c r="AO126">
         <v>1.5</v>
       </c>
-      <c r="AO126">
-        <v>1.7</v>
-      </c>
       <c r="AP126">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ126">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AR126">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AS126">
         <v>1.8</v>
       </c>
       <c r="AT126">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27260,25 +27260,25 @@
         <v>1.55</v>
       </c>
       <c r="AN127">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AO127">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AP127">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AQ127">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR127">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AS127">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AT127">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AU127">
         <v>4</v>
@@ -27466,22 +27466,22 @@
         <v>1.36</v>
       </c>
       <c r="AN128">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AO128">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AQ128">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AR128">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AS128">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AT128">
         <v>3.11</v>
@@ -27672,25 +27672,25 @@
         <v>1.35</v>
       </c>
       <c r="AN129">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AO129">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AR129">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AS129">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AT129">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="AU129">
         <v>8</v>
@@ -27878,25 +27878,25 @@
         <v>1.52</v>
       </c>
       <c r="AN130">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AO130">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AP130">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AQ130">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AR130">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AS130">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AT130">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28084,25 +28084,25 @@
         <v>3.3</v>
       </c>
       <c r="AN131">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AO131">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP131">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR131">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AS131">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AT131">
-        <v>2.94</v>
+        <v>3.16</v>
       </c>
       <c r="AU131">
         <v>11</v>
@@ -28290,25 +28290,25 @@
         <v>2.15</v>
       </c>
       <c r="AN132">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AO132">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
       </c>
       <c r="AS132">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AT132">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28496,25 +28496,25 @@
         <v>1.31</v>
       </c>
       <c r="AN133">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO133">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AP133">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR133">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS133">
         <v>1.48</v>
       </c>
       <c r="AT133">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28702,25 +28702,25 @@
         <v>2.95</v>
       </c>
       <c r="AN134">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AO134">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="AP134">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="AQ134">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="AR134">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AS134">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AT134">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -28908,25 +28908,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AO135">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ135">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR135">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AS135">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AT135">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="AU135">
         <v>12</v>
@@ -29114,25 +29114,25 @@
         <v>2.1</v>
       </c>
       <c r="AN136">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AO136">
-        <v>1.23</v>
+        <v>0.91</v>
       </c>
       <c r="AP136">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR136">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AS136">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AT136">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="AU136">
         <v>9</v>
@@ -29320,25 +29320,25 @@
         <v>1.62</v>
       </c>
       <c r="AN137">
+        <v>1.82</v>
+      </c>
+      <c r="AO137">
+        <v>1.64</v>
+      </c>
+      <c r="AP137">
+        <v>1.92</v>
+      </c>
+      <c r="AQ137">
         <v>1.5</v>
       </c>
-      <c r="AO137">
-        <v>1.82</v>
-      </c>
-      <c r="AP137">
-        <v>1.57</v>
-      </c>
-      <c r="AQ137">
-        <v>1.74</v>
-      </c>
       <c r="AR137">
+        <v>1.97</v>
+      </c>
+      <c r="AS137">
         <v>1.81</v>
       </c>
-      <c r="AS137">
-        <v>1.8</v>
-      </c>
       <c r="AT137">
-        <v>3.61</v>
+        <v>3.78</v>
       </c>
       <c r="AU137">
         <v>4</v>
@@ -29526,25 +29526,25 @@
         <v>2.35</v>
       </c>
       <c r="AN138">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AO138">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="AP138">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AQ138">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AR138">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS138">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AT138">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AU138">
         <v>12</v>
@@ -29732,25 +29732,25 @@
         <v>1.55</v>
       </c>
       <c r="AN139">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AO139">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AP139">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ139">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR139">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS139">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AT139">
-        <v>3.17</v>
+        <v>2.89</v>
       </c>
       <c r="AU139">
         <v>3</v>
@@ -29938,25 +29938,25 @@
         <v>1.8</v>
       </c>
       <c r="AN140">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AO140">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AP140">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AQ140">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AR140">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AS140">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AT140">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30144,25 +30144,25 @@
         <v>1.6</v>
       </c>
       <c r="AN141">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="AO141">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AP141">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ141">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR141">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AS141">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AT141">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30350,25 +30350,25 @@
         <v>1.15</v>
       </c>
       <c r="AN142">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="AO142">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="AP142">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AQ142">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="AR142">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AS142">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AT142">
-        <v>3.17</v>
+        <v>2.98</v>
       </c>
       <c r="AU142">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="272">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -586,6 +586,12 @@
     <t>['18', '39']</t>
   </si>
   <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -638,9 +644,6 @@
   </si>
   <si>
     <t>['5']</t>
-  </si>
-  <si>
-    <t>['3']</t>
   </si>
   <si>
     <t>['39', '77']</t>
@@ -821,6 +824,12 @@
   </si>
   <si>
     <t>['70', '76']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['76', '79']</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP142"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,7 +1447,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1644,7 +1653,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1722,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ3">
         <v>1.42</v>
@@ -1931,7 +1940,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2056,7 +2065,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2262,7 +2271,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2468,7 +2477,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2549,7 +2558,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ7">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2674,7 +2683,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2961,7 +2970,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3086,7 +3095,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3164,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3292,7 +3301,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3370,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ11">
         <v>1.36</v>
@@ -3498,7 +3507,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3910,7 +3919,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4116,7 +4125,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4194,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ15">
         <v>1.5</v>
@@ -4403,7 +4412,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ16">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
         <v>2.11</v>
@@ -4734,7 +4743,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4815,7 +4824,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ18">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR18">
         <v>1.45</v>
@@ -4940,7 +4949,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5558,7 +5567,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5636,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22">
         <v>0.83</v>
@@ -5970,7 +5979,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6257,7 +6266,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR25">
         <v>3.42</v>
@@ -6382,7 +6391,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6794,7 +6803,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6872,7 +6881,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ28">
         <v>0.83</v>
@@ -7078,7 +7087,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ29">
         <v>0.58</v>
@@ -7206,7 +7215,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7412,7 +7421,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -7490,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7699,7 +7708,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR32">
         <v>1.68</v>
@@ -7905,7 +7914,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ33">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR33">
         <v>1.17</v>
@@ -8317,7 +8326,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ35">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR35">
         <v>1.92</v>
@@ -8442,7 +8451,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8648,7 +8657,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8854,7 +8863,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8932,10 +8941,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ38">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>1.38</v>
@@ -9060,7 +9069,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9138,7 +9147,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ39">
         <v>1.42</v>
@@ -9266,7 +9275,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9678,7 +9687,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9884,7 +9893,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10168,10 +10177,10 @@
         <v>1.33</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10377,7 +10386,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ45">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR45">
         <v>2.03</v>
@@ -10502,7 +10511,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -11120,7 +11129,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11326,7 +11335,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11532,7 +11541,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11613,7 +11622,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ51">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
         <v>1.66</v>
@@ -12228,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ54">
         <v>0.83</v>
@@ -12356,7 +12365,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12437,7 +12446,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ55">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
         <v>1.62</v>
@@ -12562,7 +12571,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12640,7 +12649,7 @@
         <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ56">
         <v>1.42</v>
@@ -13180,7 +13189,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13258,10 +13267,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR59">
         <v>1.76</v>
@@ -13670,7 +13679,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ61">
         <v>1.36</v>
@@ -14004,7 +14013,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14210,7 +14219,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14416,7 +14425,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14497,7 +14506,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14828,7 +14837,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14909,7 +14918,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ67">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR67">
         <v>1.55</v>
@@ -15034,7 +15043,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15112,10 +15121,10 @@
         <v>0.4</v>
       </c>
       <c r="AP68">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ68">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR68">
         <v>1.02</v>
@@ -15240,7 +15249,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15446,7 +15455,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15652,7 +15661,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15936,7 +15945,7 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ72">
         <v>1.36</v>
@@ -16064,7 +16073,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16554,7 +16563,7 @@
         <v>0.17</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ75">
         <v>0.33</v>
@@ -16682,7 +16691,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16969,7 +16978,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ77">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR77">
         <v>1.84</v>
@@ -17587,7 +17596,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ80">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR80">
         <v>1.35</v>
@@ -17712,7 +17721,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17790,7 +17799,7 @@
         <v>1.43</v>
       </c>
       <c r="AP81">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ81">
         <v>1.5</v>
@@ -17918,7 +17927,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18124,7 +18133,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18330,7 +18339,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18408,10 +18417,10 @@
         <v>0.83</v>
       </c>
       <c r="AP84">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ84">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR84">
         <v>1.54</v>
@@ -18536,7 +18545,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18742,7 +18751,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18948,7 +18957,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19026,7 +19035,7 @@
         <v>0.14</v>
       </c>
       <c r="AP87">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ87">
         <v>0.33</v>
@@ -19850,10 +19859,10 @@
         <v>1.57</v>
       </c>
       <c r="AP91">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ91">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR91">
         <v>1.8</v>
@@ -20056,10 +20065,10 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ92">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR92">
         <v>1.84</v>
@@ -20262,7 +20271,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20390,7 +20399,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20596,7 +20605,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21008,7 +21017,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21089,7 +21098,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21214,7 +21223,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21292,7 +21301,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ98">
         <v>0.58</v>
@@ -21420,7 +21429,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21626,7 +21635,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22038,7 +22047,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22244,7 +22253,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22450,7 +22459,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22656,7 +22665,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22734,7 +22743,7 @@
         <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ105">
         <v>0.83</v>
@@ -22940,7 +22949,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23068,7 +23077,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23149,7 +23158,7 @@
         <v>2</v>
       </c>
       <c r="AQ107">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23274,7 +23283,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23355,7 +23364,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ108">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23480,7 +23489,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23561,7 +23570,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR109">
         <v>1.41</v>
@@ -23892,7 +23901,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24179,7 +24188,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ112">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR112">
         <v>1.84</v>
@@ -24510,7 +24519,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -25000,7 +25009,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ116">
         <v>0.83</v>
@@ -25206,10 +25215,10 @@
         <v>1.22</v>
       </c>
       <c r="AP117">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ117">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR117">
         <v>1</v>
@@ -25334,7 +25343,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25540,7 +25549,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25621,7 +25630,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ119">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR119">
         <v>1.76</v>
@@ -25746,7 +25755,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25824,7 +25833,7 @@
         <v>1.11</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ120">
         <v>0.83</v>
@@ -26158,7 +26167,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26364,7 +26373,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26857,7 +26866,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ125">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR125">
         <v>1.65</v>
@@ -26982,7 +26991,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27266,7 +27275,7 @@
         <v>0.4</v>
       </c>
       <c r="AP127">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ127">
         <v>0.33</v>
@@ -27394,7 +27403,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27472,10 +27481,10 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ128">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR128">
         <v>1.49</v>
@@ -27600,7 +27609,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27681,7 +27690,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ129">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR129">
         <v>1.71</v>
@@ -27806,7 +27815,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28012,7 +28021,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28296,7 +28305,7 @@
         <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ132">
         <v>1.33</v>
@@ -28424,7 +28433,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28630,7 +28639,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28836,7 +28845,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29042,7 +29051,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29248,7 +29257,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29454,7 +29463,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29660,7 +29669,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29741,7 +29750,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ139">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR139">
         <v>1.48</v>
@@ -30435,6 +30444,624 @@
       </c>
       <c r="BP142">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7784924</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45704.42708333334</v>
+      </c>
+      <c r="F143">
+        <v>24</v>
+      </c>
+      <c r="G143" t="s">
+        <v>71</v>
+      </c>
+      <c r="H143" t="s">
+        <v>80</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
+        <v>87</v>
+      </c>
+      <c r="P143" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q143">
+        <v>4.6</v>
+      </c>
+      <c r="R143">
+        <v>2.39</v>
+      </c>
+      <c r="S143">
+        <v>2.22</v>
+      </c>
+      <c r="T143">
+        <v>1.3</v>
+      </c>
+      <c r="U143">
+        <v>3.2</v>
+      </c>
+      <c r="V143">
+        <v>2.37</v>
+      </c>
+      <c r="W143">
+        <v>1.53</v>
+      </c>
+      <c r="X143">
+        <v>5.35</v>
+      </c>
+      <c r="Y143">
+        <v>1.12</v>
+      </c>
+      <c r="Z143">
+        <v>4.4</v>
+      </c>
+      <c r="AA143">
+        <v>3.94</v>
+      </c>
+      <c r="AB143">
+        <v>1.7</v>
+      </c>
+      <c r="AC143">
+        <v>1.04</v>
+      </c>
+      <c r="AD143">
+        <v>10</v>
+      </c>
+      <c r="AE143">
+        <v>1.2</v>
+      </c>
+      <c r="AF143">
+        <v>4.1</v>
+      </c>
+      <c r="AG143">
+        <v>1.55</v>
+      </c>
+      <c r="AH143">
+        <v>2.2</v>
+      </c>
+      <c r="AI143">
+        <v>1.63</v>
+      </c>
+      <c r="AJ143">
+        <v>2.15</v>
+      </c>
+      <c r="AK143">
+        <v>2</v>
+      </c>
+      <c r="AL143">
+        <v>1.23</v>
+      </c>
+      <c r="AM143">
+        <v>1.21</v>
+      </c>
+      <c r="AN143">
+        <v>1.27</v>
+      </c>
+      <c r="AO143">
+        <v>1.25</v>
+      </c>
+      <c r="AP143">
+        <v>1.42</v>
+      </c>
+      <c r="AQ143">
+        <v>1.15</v>
+      </c>
+      <c r="AR143">
+        <v>1.03</v>
+      </c>
+      <c r="AS143">
+        <v>1.45</v>
+      </c>
+      <c r="AT143">
+        <v>2.48</v>
+      </c>
+      <c r="AU143">
+        <v>9</v>
+      </c>
+      <c r="AV143">
+        <v>4</v>
+      </c>
+      <c r="AW143">
+        <v>13</v>
+      </c>
+      <c r="AX143">
+        <v>6</v>
+      </c>
+      <c r="AY143">
+        <v>22</v>
+      </c>
+      <c r="AZ143">
+        <v>11</v>
+      </c>
+      <c r="BA143">
+        <v>2</v>
+      </c>
+      <c r="BB143">
+        <v>3</v>
+      </c>
+      <c r="BC143">
+        <v>5</v>
+      </c>
+      <c r="BD143">
+        <v>2.7</v>
+      </c>
+      <c r="BE143">
+        <v>6.75</v>
+      </c>
+      <c r="BF143">
+        <v>1.53</v>
+      </c>
+      <c r="BG143">
+        <v>1.22</v>
+      </c>
+      <c r="BH143">
+        <v>3.55</v>
+      </c>
+      <c r="BI143">
+        <v>1.41</v>
+      </c>
+      <c r="BJ143">
+        <v>2.63</v>
+      </c>
+      <c r="BK143">
+        <v>1.66</v>
+      </c>
+      <c r="BL143">
+        <v>2.04</v>
+      </c>
+      <c r="BM143">
+        <v>2.04</v>
+      </c>
+      <c r="BN143">
+        <v>1.66</v>
+      </c>
+      <c r="BO143">
+        <v>2.55</v>
+      </c>
+      <c r="BP143">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7784925</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45704.52083333334</v>
+      </c>
+      <c r="F144">
+        <v>24</v>
+      </c>
+      <c r="G144" t="s">
+        <v>79</v>
+      </c>
+      <c r="H144" t="s">
+        <v>74</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>2</v>
+      </c>
+      <c r="O144" t="s">
+        <v>190</v>
+      </c>
+      <c r="P144" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q144">
+        <v>2.5</v>
+      </c>
+      <c r="R144">
+        <v>2.35</v>
+      </c>
+      <c r="S144">
+        <v>3.8</v>
+      </c>
+      <c r="T144">
+        <v>1.31</v>
+      </c>
+      <c r="U144">
+        <v>3.2</v>
+      </c>
+      <c r="V144">
+        <v>2.37</v>
+      </c>
+      <c r="W144">
+        <v>1.53</v>
+      </c>
+      <c r="X144">
+        <v>5.3</v>
+      </c>
+      <c r="Y144">
+        <v>1.13</v>
+      </c>
+      <c r="Z144">
+        <v>2</v>
+      </c>
+      <c r="AA144">
+        <v>3.59</v>
+      </c>
+      <c r="AB144">
+        <v>3.45</v>
+      </c>
+      <c r="AC144">
+        <v>1.04</v>
+      </c>
+      <c r="AD144">
+        <v>10</v>
+      </c>
+      <c r="AE144">
+        <v>1.2</v>
+      </c>
+      <c r="AF144">
+        <v>4.1</v>
+      </c>
+      <c r="AG144">
+        <v>1.61</v>
+      </c>
+      <c r="AH144">
+        <v>2.1</v>
+      </c>
+      <c r="AI144">
+        <v>1.56</v>
+      </c>
+      <c r="AJ144">
+        <v>2.28</v>
+      </c>
+      <c r="AK144">
+        <v>1.3</v>
+      </c>
+      <c r="AL144">
+        <v>1.26</v>
+      </c>
+      <c r="AM144">
+        <v>1.74</v>
+      </c>
+      <c r="AN144">
+        <v>2</v>
+      </c>
+      <c r="AO144">
+        <v>0.91</v>
+      </c>
+      <c r="AP144">
+        <v>1.92</v>
+      </c>
+      <c r="AQ144">
+        <v>0.92</v>
+      </c>
+      <c r="AR144">
+        <v>1.79</v>
+      </c>
+      <c r="AS144">
+        <v>1.65</v>
+      </c>
+      <c r="AT144">
+        <v>3.44</v>
+      </c>
+      <c r="AU144">
+        <v>10</v>
+      </c>
+      <c r="AV144">
+        <v>7</v>
+      </c>
+      <c r="AW144">
+        <v>13</v>
+      </c>
+      <c r="AX144">
+        <v>9</v>
+      </c>
+      <c r="AY144">
+        <v>24</v>
+      </c>
+      <c r="AZ144">
+        <v>20</v>
+      </c>
+      <c r="BA144">
+        <v>9</v>
+      </c>
+      <c r="BB144">
+        <v>6</v>
+      </c>
+      <c r="BC144">
+        <v>15</v>
+      </c>
+      <c r="BD144">
+        <v>1.73</v>
+      </c>
+      <c r="BE144">
+        <v>6.5</v>
+      </c>
+      <c r="BF144">
+        <v>2.33</v>
+      </c>
+      <c r="BG144">
+        <v>1.23</v>
+      </c>
+      <c r="BH144">
+        <v>3.55</v>
+      </c>
+      <c r="BI144">
+        <v>1.42</v>
+      </c>
+      <c r="BJ144">
+        <v>2.55</v>
+      </c>
+      <c r="BK144">
+        <v>1.7</v>
+      </c>
+      <c r="BL144">
+        <v>2</v>
+      </c>
+      <c r="BM144">
+        <v>2.1</v>
+      </c>
+      <c r="BN144">
+        <v>1.62</v>
+      </c>
+      <c r="BO144">
+        <v>2.65</v>
+      </c>
+      <c r="BP144">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7784926</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45704.52083333334</v>
+      </c>
+      <c r="F145">
+        <v>24</v>
+      </c>
+      <c r="G145" t="s">
+        <v>78</v>
+      </c>
+      <c r="H145" t="s">
+        <v>76</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>2</v>
+      </c>
+      <c r="N145">
+        <v>3</v>
+      </c>
+      <c r="O145" t="s">
+        <v>191</v>
+      </c>
+      <c r="P145" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q145">
+        <v>3.7</v>
+      </c>
+      <c r="R145">
+        <v>2.24</v>
+      </c>
+      <c r="S145">
+        <v>2.7</v>
+      </c>
+      <c r="T145">
+        <v>1.36</v>
+      </c>
+      <c r="U145">
+        <v>2.95</v>
+      </c>
+      <c r="V145">
+        <v>2.55</v>
+      </c>
+      <c r="W145">
+        <v>1.46</v>
+      </c>
+      <c r="X145">
+        <v>5.95</v>
+      </c>
+      <c r="Y145">
+        <v>1.1</v>
+      </c>
+      <c r="Z145">
+        <v>3.28</v>
+      </c>
+      <c r="AA145">
+        <v>3.47</v>
+      </c>
+      <c r="AB145">
+        <v>2.09</v>
+      </c>
+      <c r="AC145">
+        <v>1.04</v>
+      </c>
+      <c r="AD145">
+        <v>10</v>
+      </c>
+      <c r="AE145">
+        <v>1.25</v>
+      </c>
+      <c r="AF145">
+        <v>3.65</v>
+      </c>
+      <c r="AG145">
+        <v>1.77</v>
+      </c>
+      <c r="AH145">
+        <v>1.98</v>
+      </c>
+      <c r="AI145">
+        <v>1.64</v>
+      </c>
+      <c r="AJ145">
+        <v>2.13</v>
+      </c>
+      <c r="AK145">
+        <v>1.66</v>
+      </c>
+      <c r="AL145">
+        <v>1.27</v>
+      </c>
+      <c r="AM145">
+        <v>1.34</v>
+      </c>
+      <c r="AN145">
+        <v>0.91</v>
+      </c>
+      <c r="AO145">
+        <v>1.18</v>
+      </c>
+      <c r="AP145">
+        <v>0.83</v>
+      </c>
+      <c r="AQ145">
+        <v>1.33</v>
+      </c>
+      <c r="AR145">
+        <v>1.53</v>
+      </c>
+      <c r="AS145">
+        <v>1.66</v>
+      </c>
+      <c r="AT145">
+        <v>3.19</v>
+      </c>
+      <c r="AU145">
+        <v>6</v>
+      </c>
+      <c r="AV145">
+        <v>4</v>
+      </c>
+      <c r="AW145">
+        <v>11</v>
+      </c>
+      <c r="AX145">
+        <v>4</v>
+      </c>
+      <c r="AY145">
+        <v>21</v>
+      </c>
+      <c r="AZ145">
+        <v>9</v>
+      </c>
+      <c r="BA145">
+        <v>5</v>
+      </c>
+      <c r="BB145">
+        <v>6</v>
+      </c>
+      <c r="BC145">
+        <v>11</v>
+      </c>
+      <c r="BD145">
+        <v>2.25</v>
+      </c>
+      <c r="BE145">
+        <v>6.75</v>
+      </c>
+      <c r="BF145">
+        <v>1.76</v>
+      </c>
+      <c r="BG145">
+        <v>1.25</v>
+      </c>
+      <c r="BH145">
+        <v>3.4</v>
+      </c>
+      <c r="BI145">
+        <v>1.45</v>
+      </c>
+      <c r="BJ145">
+        <v>2.48</v>
+      </c>
+      <c r="BK145">
+        <v>1.74</v>
+      </c>
+      <c r="BL145">
+        <v>1.93</v>
+      </c>
+      <c r="BM145">
+        <v>2.16</v>
+      </c>
+      <c r="BN145">
+        <v>1.58</v>
+      </c>
+      <c r="BO145">
+        <v>2.75</v>
+      </c>
+      <c r="BP145">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,15 @@
     <t>['28']</t>
   </si>
   <si>
+    <t>['13', '90+6']</t>
+  </si>
+  <si>
+    <t>['9', '74']</t>
+  </si>
+  <si>
+    <t>['78', '87']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -830,6 +839,12 @@
   </si>
   <si>
     <t>['76', '79']</t>
+  </si>
+  <si>
+    <t>['55', '60']</t>
+  </si>
+  <si>
+    <t>['10', '71']</t>
   </si>
 </sst>
 </file>
@@ -1191,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1447,7 +1462,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1653,7 +1668,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2065,7 +2080,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2271,7 +2286,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2349,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2477,7 +2492,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2683,7 +2698,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3095,7 +3110,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3301,7 +3316,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3507,7 +3522,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3588,7 +3603,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ12">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR12">
         <v>2.07</v>
@@ -3791,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13">
         <v>0.83</v>
@@ -3919,7 +3934,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -3997,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ14">
         <v>0.33</v>
@@ -4125,7 +4140,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4206,7 +4221,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ15">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR15">
         <v>1.44</v>
@@ -4743,7 +4758,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4821,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
         <v>1.15</v>
@@ -4949,7 +4964,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5236,7 +5251,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ20">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR20">
         <v>1.02</v>
@@ -5567,7 +5582,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5851,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -5979,7 +5994,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6263,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ25">
         <v>0.92</v>
@@ -6391,7 +6406,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6472,7 +6487,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR26">
         <v>1.85</v>
@@ -6803,7 +6818,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7090,7 +7105,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ29">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7215,7 +7230,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7296,7 +7311,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -8117,7 +8132,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8451,7 +8466,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8529,7 +8544,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.36</v>
@@ -8657,7 +8672,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8735,7 +8750,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -8863,7 +8878,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9069,7 +9084,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9275,7 +9290,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9353,10 +9368,10 @@
         <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR40">
         <v>1.54</v>
@@ -9687,7 +9702,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9893,7 +9908,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -9971,7 +9986,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
         <v>1.42</v>
@@ -10511,7 +10526,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10795,7 +10810,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ47">
         <v>0.83</v>
@@ -11004,7 +11019,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR48">
         <v>1.38</v>
@@ -11129,7 +11144,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11335,7 +11350,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11416,7 +11431,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ50">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR50">
         <v>1.38</v>
@@ -11541,7 +11556,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -12031,7 +12046,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ53">
         <v>1.36</v>
@@ -12365,7 +12380,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12443,7 +12458,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ55">
         <v>1.33</v>
@@ -12571,7 +12586,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -13189,7 +13204,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13473,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>0.33</v>
@@ -13885,7 +13900,7 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14013,7 +14028,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14094,7 +14109,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14219,7 +14234,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14300,7 +14315,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ64">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14425,7 +14440,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14837,7 +14852,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14915,7 +14930,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ67">
         <v>1.33</v>
@@ -15043,7 +15058,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15249,7 +15264,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15455,7 +15470,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15533,7 +15548,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ70">
         <v>0.33</v>
@@ -15661,7 +15676,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15742,7 +15757,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR71">
         <v>1.55</v>
@@ -16073,7 +16088,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16357,7 +16372,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
         <v>0.83</v>
@@ -16691,7 +16706,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16769,7 +16784,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ76">
         <v>0.83</v>
@@ -16975,7 +16990,7 @@
         <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>1.33</v>
@@ -17184,7 +17199,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ78">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -17721,7 +17736,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17802,7 +17817,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR81">
         <v>0.99</v>
@@ -17927,7 +17942,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18133,7 +18148,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18339,7 +18354,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18545,7 +18560,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18751,7 +18766,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18957,7 +18972,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19241,7 +19256,7 @@
         <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>0.83</v>
@@ -19653,10 +19668,10 @@
         <v>0.71</v>
       </c>
       <c r="AP90">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ90">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -20399,7 +20414,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20477,7 +20492,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20605,7 +20620,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21017,7 +21032,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21223,7 +21238,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21304,7 +21319,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ98">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21429,7 +21444,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21635,7 +21650,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21919,7 +21934,7 @@
         <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
         <v>1.42</v>
@@ -22047,7 +22062,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22253,7 +22268,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22331,10 +22346,10 @@
         <v>1.63</v>
       </c>
       <c r="AP103">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ103">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR103">
         <v>1.81</v>
@@ -22459,7 +22474,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22665,7 +22680,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23077,7 +23092,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23283,7 +23298,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23489,7 +23504,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23567,7 +23582,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ109">
         <v>1.15</v>
@@ -23901,7 +23916,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24391,10 +24406,10 @@
         <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ113">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR113">
         <v>1.39</v>
@@ -24519,7 +24534,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24600,7 +24615,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR114">
         <v>1.86</v>
@@ -24803,7 +24818,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -25343,7 +25358,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25549,7 +25564,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25627,7 +25642,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
         <v>0.92</v>
@@ -25755,7 +25770,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26167,7 +26182,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26245,7 +26260,7 @@
         <v>0.7</v>
       </c>
       <c r="AP122">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ122">
         <v>0.83</v>
@@ -26373,7 +26388,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26991,7 +27006,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27069,10 +27084,10 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27403,7 +27418,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27609,7 +27624,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27815,7 +27830,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27893,7 +27908,7 @@
         <v>1.5</v>
       </c>
       <c r="AP130">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ130">
         <v>1.36</v>
@@ -28021,7 +28036,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28102,7 +28117,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR131">
         <v>1.95</v>
@@ -28433,7 +28448,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28639,7 +28654,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28717,10 +28732,10 @@
         <v>0.64</v>
       </c>
       <c r="AP134">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR134">
         <v>1.83</v>
@@ -28845,7 +28860,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29051,7 +29066,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29257,7 +29272,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29338,7 +29353,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ137">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
         <v>1.97</v>
@@ -29463,7 +29478,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29669,7 +29684,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29747,7 +29762,7 @@
         <v>1.09</v>
       </c>
       <c r="AP139">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ139">
         <v>1.15</v>
@@ -30699,7 +30714,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30905,7 +30920,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31062,6 +31077,624 @@
       </c>
       <c r="BP145">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7784927</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45710.58333333334</v>
+      </c>
+      <c r="F146">
+        <v>25</v>
+      </c>
+      <c r="G146" t="s">
+        <v>74</v>
+      </c>
+      <c r="H146" t="s">
+        <v>78</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="L146">
+        <v>2</v>
+      </c>
+      <c r="M146">
+        <v>2</v>
+      </c>
+      <c r="N146">
+        <v>4</v>
+      </c>
+      <c r="O146" t="s">
+        <v>192</v>
+      </c>
+      <c r="P146" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q146">
+        <v>2.18</v>
+      </c>
+      <c r="R146">
+        <v>2.32</v>
+      </c>
+      <c r="S146">
+        <v>5</v>
+      </c>
+      <c r="T146">
+        <v>1.35</v>
+      </c>
+      <c r="U146">
+        <v>2.95</v>
+      </c>
+      <c r="V146">
+        <v>2.5</v>
+      </c>
+      <c r="W146">
+        <v>1.47</v>
+      </c>
+      <c r="X146">
+        <v>5.95</v>
+      </c>
+      <c r="Y146">
+        <v>1.1</v>
+      </c>
+      <c r="Z146">
+        <v>1.76</v>
+      </c>
+      <c r="AA146">
+        <v>3.77</v>
+      </c>
+      <c r="AB146">
+        <v>4.2</v>
+      </c>
+      <c r="AC146">
+        <v>1.05</v>
+      </c>
+      <c r="AD146">
+        <v>9.5</v>
+      </c>
+      <c r="AE146">
+        <v>1.25</v>
+      </c>
+      <c r="AF146">
+        <v>3.6</v>
+      </c>
+      <c r="AG146">
+        <v>1.83</v>
+      </c>
+      <c r="AH146">
+        <v>1.91</v>
+      </c>
+      <c r="AI146">
+        <v>1.77</v>
+      </c>
+      <c r="AJ146">
+        <v>1.94</v>
+      </c>
+      <c r="AK146">
+        <v>1.18</v>
+      </c>
+      <c r="AL146">
+        <v>1.23</v>
+      </c>
+      <c r="AM146">
+        <v>2.1</v>
+      </c>
+      <c r="AN146">
+        <v>2.08</v>
+      </c>
+      <c r="AO146">
+        <v>1</v>
+      </c>
+      <c r="AP146">
+        <v>2</v>
+      </c>
+      <c r="AQ146">
+        <v>1</v>
+      </c>
+      <c r="AR146">
+        <v>1.86</v>
+      </c>
+      <c r="AS146">
+        <v>1.28</v>
+      </c>
+      <c r="AT146">
+        <v>3.14</v>
+      </c>
+      <c r="AU146">
+        <v>6</v>
+      </c>
+      <c r="AV146">
+        <v>3</v>
+      </c>
+      <c r="AW146">
+        <v>9</v>
+      </c>
+      <c r="AX146">
+        <v>9</v>
+      </c>
+      <c r="AY146">
+        <v>15</v>
+      </c>
+      <c r="AZ146">
+        <v>15</v>
+      </c>
+      <c r="BA146">
+        <v>7</v>
+      </c>
+      <c r="BB146">
+        <v>5</v>
+      </c>
+      <c r="BC146">
+        <v>12</v>
+      </c>
+      <c r="BD146">
+        <v>1.5</v>
+      </c>
+      <c r="BE146">
+        <v>7</v>
+      </c>
+      <c r="BF146">
+        <v>2.8</v>
+      </c>
+      <c r="BG146">
+        <v>1.25</v>
+      </c>
+      <c r="BH146">
+        <v>3.45</v>
+      </c>
+      <c r="BI146">
+        <v>1.43</v>
+      </c>
+      <c r="BJ146">
+        <v>2.55</v>
+      </c>
+      <c r="BK146">
+        <v>1.68</v>
+      </c>
+      <c r="BL146">
+        <v>2.02</v>
+      </c>
+      <c r="BM146">
+        <v>2.06</v>
+      </c>
+      <c r="BN146">
+        <v>1.64</v>
+      </c>
+      <c r="BO146">
+        <v>2.63</v>
+      </c>
+      <c r="BP146">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7784928</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45710.58333333334</v>
+      </c>
+      <c r="F147">
+        <v>25</v>
+      </c>
+      <c r="G147" t="s">
+        <v>81</v>
+      </c>
+      <c r="H147" t="s">
+        <v>71</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147">
+        <v>2</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>3</v>
+      </c>
+      <c r="O147" t="s">
+        <v>193</v>
+      </c>
+      <c r="P147" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q147">
+        <v>2</v>
+      </c>
+      <c r="R147">
+        <v>2.35</v>
+      </c>
+      <c r="S147">
+        <v>5</v>
+      </c>
+      <c r="T147">
+        <v>1.3</v>
+      </c>
+      <c r="U147">
+        <v>3.2</v>
+      </c>
+      <c r="V147">
+        <v>2.45</v>
+      </c>
+      <c r="W147">
+        <v>1.48</v>
+      </c>
+      <c r="X147">
+        <v>6.25</v>
+      </c>
+      <c r="Y147">
+        <v>1.06</v>
+      </c>
+      <c r="Z147">
+        <v>1.56</v>
+      </c>
+      <c r="AA147">
+        <v>4.2</v>
+      </c>
+      <c r="AB147">
+        <v>5.2</v>
+      </c>
+      <c r="AC147">
+        <v>1.04</v>
+      </c>
+      <c r="AD147">
+        <v>10</v>
+      </c>
+      <c r="AE147">
+        <v>1.22</v>
+      </c>
+      <c r="AF147">
+        <v>4.2</v>
+      </c>
+      <c r="AG147">
+        <v>1.6</v>
+      </c>
+      <c r="AH147">
+        <v>2.1</v>
+      </c>
+      <c r="AI147">
+        <v>1.75</v>
+      </c>
+      <c r="AJ147">
+        <v>1.93</v>
+      </c>
+      <c r="AK147">
+        <v>1.14</v>
+      </c>
+      <c r="AL147">
+        <v>1.18</v>
+      </c>
+      <c r="AM147">
+        <v>2.3</v>
+      </c>
+      <c r="AN147">
+        <v>1.33</v>
+      </c>
+      <c r="AO147">
+        <v>0.58</v>
+      </c>
+      <c r="AP147">
+        <v>1.46</v>
+      </c>
+      <c r="AQ147">
+        <v>0.54</v>
+      </c>
+      <c r="AR147">
+        <v>1.5</v>
+      </c>
+      <c r="AS147">
+        <v>1.18</v>
+      </c>
+      <c r="AT147">
+        <v>2.68</v>
+      </c>
+      <c r="AU147">
+        <v>8</v>
+      </c>
+      <c r="AV147">
+        <v>6</v>
+      </c>
+      <c r="AW147">
+        <v>7</v>
+      </c>
+      <c r="AX147">
+        <v>5</v>
+      </c>
+      <c r="AY147">
+        <v>18</v>
+      </c>
+      <c r="AZ147">
+        <v>11</v>
+      </c>
+      <c r="BA147">
+        <v>9</v>
+      </c>
+      <c r="BB147">
+        <v>7</v>
+      </c>
+      <c r="BC147">
+        <v>16</v>
+      </c>
+      <c r="BD147">
+        <v>1.49</v>
+      </c>
+      <c r="BE147">
+        <v>6.5</v>
+      </c>
+      <c r="BF147">
+        <v>2.9</v>
+      </c>
+      <c r="BG147">
+        <v>1.36</v>
+      </c>
+      <c r="BH147">
+        <v>2.8</v>
+      </c>
+      <c r="BI147">
+        <v>1.6</v>
+      </c>
+      <c r="BJ147">
+        <v>2.15</v>
+      </c>
+      <c r="BK147">
+        <v>1.96</v>
+      </c>
+      <c r="BL147">
+        <v>1.72</v>
+      </c>
+      <c r="BM147">
+        <v>2.48</v>
+      </c>
+      <c r="BN147">
+        <v>1.45</v>
+      </c>
+      <c r="BO147">
+        <v>3.3</v>
+      </c>
+      <c r="BP147">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7784929</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45710.6875</v>
+      </c>
+      <c r="F148">
+        <v>25</v>
+      </c>
+      <c r="G148" t="s">
+        <v>80</v>
+      </c>
+      <c r="H148" t="s">
+        <v>79</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>2</v>
+      </c>
+      <c r="M148">
+        <v>2</v>
+      </c>
+      <c r="N148">
+        <v>4</v>
+      </c>
+      <c r="O148" t="s">
+        <v>194</v>
+      </c>
+      <c r="P148" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q148">
+        <v>3</v>
+      </c>
+      <c r="R148">
+        <v>2.25</v>
+      </c>
+      <c r="S148">
+        <v>2.9</v>
+      </c>
+      <c r="T148">
+        <v>1.28</v>
+      </c>
+      <c r="U148">
+        <v>3.35</v>
+      </c>
+      <c r="V148">
+        <v>2.25</v>
+      </c>
+      <c r="W148">
+        <v>1.57</v>
+      </c>
+      <c r="X148">
+        <v>5</v>
+      </c>
+      <c r="Y148">
+        <v>1.11</v>
+      </c>
+      <c r="Z148">
+        <v>2.71</v>
+      </c>
+      <c r="AA148">
+        <v>3.65</v>
+      </c>
+      <c r="AB148">
+        <v>2.34</v>
+      </c>
+      <c r="AC148">
+        <v>1.04</v>
+      </c>
+      <c r="AD148">
+        <v>10</v>
+      </c>
+      <c r="AE148">
+        <v>1.18</v>
+      </c>
+      <c r="AF148">
+        <v>4.75</v>
+      </c>
+      <c r="AG148">
+        <v>1.53</v>
+      </c>
+      <c r="AH148">
+        <v>2.4</v>
+      </c>
+      <c r="AI148">
+        <v>1.45</v>
+      </c>
+      <c r="AJ148">
+        <v>2.5</v>
+      </c>
+      <c r="AK148">
+        <v>1.5</v>
+      </c>
+      <c r="AL148">
+        <v>1.22</v>
+      </c>
+      <c r="AM148">
+        <v>1.48</v>
+      </c>
+      <c r="AN148">
+        <v>1.82</v>
+      </c>
+      <c r="AO148">
+        <v>1.5</v>
+      </c>
+      <c r="AP148">
+        <v>1.75</v>
+      </c>
+      <c r="AQ148">
+        <v>1.46</v>
+      </c>
+      <c r="AR148">
+        <v>1.86</v>
+      </c>
+      <c r="AS148">
+        <v>1.82</v>
+      </c>
+      <c r="AT148">
+        <v>3.68</v>
+      </c>
+      <c r="AU148">
+        <v>8</v>
+      </c>
+      <c r="AV148">
+        <v>7</v>
+      </c>
+      <c r="AW148">
+        <v>11</v>
+      </c>
+      <c r="AX148">
+        <v>8</v>
+      </c>
+      <c r="AY148">
+        <v>26</v>
+      </c>
+      <c r="AZ148">
+        <v>15</v>
+      </c>
+      <c r="BA148">
+        <v>9</v>
+      </c>
+      <c r="BB148">
+        <v>4</v>
+      </c>
+      <c r="BC148">
+        <v>13</v>
+      </c>
+      <c r="BD148">
+        <v>2.08</v>
+      </c>
+      <c r="BE148">
+        <v>6.5</v>
+      </c>
+      <c r="BF148">
+        <v>1.92</v>
+      </c>
+      <c r="BG148">
+        <v>1.17</v>
+      </c>
+      <c r="BH148">
+        <v>4.1</v>
+      </c>
+      <c r="BI148">
+        <v>1.34</v>
+      </c>
+      <c r="BJ148">
+        <v>2.9</v>
+      </c>
+      <c r="BK148">
+        <v>1.55</v>
+      </c>
+      <c r="BL148">
+        <v>2.25</v>
+      </c>
+      <c r="BM148">
+        <v>1.85</v>
+      </c>
+      <c r="BN148">
+        <v>1.81</v>
+      </c>
+      <c r="BO148">
+        <v>2.3</v>
+      </c>
+      <c r="BP148">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -601,6 +601,12 @@
     <t>['78', '87']</t>
   </si>
   <si>
+    <t>['6', '58']</t>
+  </si>
+  <si>
+    <t>['69', '89', '90+5']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -845,6 +851,12 @@
   </si>
   <si>
     <t>['10', '71']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['63']</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1462,7 +1474,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1668,7 +1680,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2080,7 +2092,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2158,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ5">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2286,7 +2298,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2492,7 +2504,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2570,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -2698,7 +2710,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2776,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>0.83</v>
@@ -3110,7 +3122,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3316,7 +3328,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3397,7 +3409,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ11">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3522,7 +3534,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3600,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>0.54</v>
@@ -3934,7 +3946,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4015,7 +4027,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ14">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4140,7 +4152,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4630,10 +4642,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR17">
         <v>1.15</v>
@@ -4758,7 +4770,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4964,7 +4976,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5042,7 +5054,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ19">
         <v>1.42</v>
@@ -5457,7 +5469,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR21">
         <v>1.73</v>
@@ -5582,7 +5594,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5994,7 +6006,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6406,7 +6418,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6484,7 +6496,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.46</v>
@@ -6690,10 +6702,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -6818,7 +6830,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6899,7 +6911,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ28">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR28">
         <v>1.22</v>
@@ -7230,7 +7242,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7720,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ32">
         <v>0.92</v>
@@ -8466,7 +8478,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8547,7 +8559,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR36">
         <v>1.64</v>
@@ -8672,7 +8684,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8878,7 +8890,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9084,7 +9096,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9290,7 +9302,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9577,7 +9589,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR41">
         <v>1.53</v>
@@ -9702,7 +9714,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9908,7 +9920,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10398,7 +10410,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>0.92</v>
@@ -10526,7 +10538,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10604,7 +10616,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -10813,7 +10825,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ47">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR47">
         <v>1.94</v>
@@ -11016,7 +11028,7 @@
         <v>1.75</v>
       </c>
       <c r="AP48">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>1.46</v>
@@ -11144,7 +11156,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11225,7 +11237,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ49">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR49">
         <v>1.86</v>
@@ -11350,7 +11362,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11556,7 +11568,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11634,7 +11646,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>0.92</v>
@@ -12049,7 +12061,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ53">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR53">
         <v>1.68</v>
@@ -12380,7 +12392,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12586,7 +12598,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12870,7 +12882,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -13076,10 +13088,10 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13204,7 +13216,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13491,7 +13503,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13697,7 +13709,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ61">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR61">
         <v>1.01</v>
@@ -14028,7 +14040,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14234,7 +14246,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14312,7 +14324,7 @@
         <v>0.4</v>
       </c>
       <c r="AP64">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>0.54</v>
@@ -14440,7 +14452,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14852,7 +14864,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15058,7 +15070,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15264,7 +15276,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15470,7 +15482,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15551,7 +15563,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ70">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15676,7 +15688,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15754,7 +15766,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ71">
         <v>1.46</v>
@@ -15963,7 +15975,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ72">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16088,7 +16100,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16166,7 +16178,7 @@
         <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
         <v>1.33</v>
@@ -16581,7 +16593,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ75">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -16706,7 +16718,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16787,7 +16799,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ76">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -17402,7 +17414,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17736,7 +17748,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17942,7 +17954,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18020,7 +18032,7 @@
         <v>2.17</v>
       </c>
       <c r="AP82">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>1.42</v>
@@ -18148,7 +18160,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18354,7 +18366,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18560,7 +18572,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18638,10 +18650,10 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ85">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR85">
         <v>1.7</v>
@@ -18766,7 +18778,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18844,7 +18856,7 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ86">
         <v>0.83</v>
@@ -18972,7 +18984,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19053,7 +19065,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ87">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR87">
         <v>1.52</v>
@@ -19259,7 +19271,7 @@
         <v>2</v>
       </c>
       <c r="AQ88">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -20414,7 +20426,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20620,7 +20632,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20701,7 +20713,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR95">
         <v>1.3</v>
@@ -20904,10 +20916,10 @@
         <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21032,7 +21044,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21110,7 +21122,7 @@
         <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ97">
         <v>1.15</v>
@@ -21238,7 +21250,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21444,7 +21456,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21650,7 +21662,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21728,10 +21740,10 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -22062,7 +22074,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22140,10 +22152,10 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ102">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR102">
         <v>1.93</v>
@@ -22268,7 +22280,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22474,7 +22486,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22680,7 +22692,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22761,7 +22773,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ105">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR105">
         <v>0.93</v>
@@ -23092,7 +23104,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23170,7 +23182,7 @@
         <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ107">
         <v>1.33</v>
@@ -23298,7 +23310,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23504,7 +23516,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23788,10 +23800,10 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ110">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -23916,7 +23928,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24200,7 +24212,7 @@
         <v>1.22</v>
       </c>
       <c r="AP112">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ112">
         <v>1.15</v>
@@ -24534,7 +24546,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -25358,7 +25370,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25439,7 +25451,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ118">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25564,7 +25576,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25770,7 +25782,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25851,7 +25863,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ120">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR120">
         <v>1.76</v>
@@ -26054,7 +26066,7 @@
         <v>1.56</v>
       </c>
       <c r="AP121">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1.42</v>
@@ -26182,7 +26194,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26388,7 +26400,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26469,7 +26481,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ123">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR123">
         <v>1.87</v>
@@ -26672,7 +26684,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26878,7 +26890,7 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>1.15</v>
@@ -27006,7 +27018,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27293,7 +27305,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ127">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR127">
         <v>1.01</v>
@@ -27418,7 +27430,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27624,7 +27636,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27830,7 +27842,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27911,7 +27923,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ130">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR130">
         <v>1.84</v>
@@ -28036,7 +28048,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28114,7 +28126,7 @@
         <v>0.7</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ131">
         <v>0.54</v>
@@ -28448,7 +28460,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28654,7 +28666,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28860,7 +28872,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29066,7 +29078,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29144,10 +29156,10 @@
         <v>0.91</v>
       </c>
       <c r="AP136">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ136">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR136">
         <v>2.08</v>
@@ -29272,7 +29284,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29350,7 +29362,7 @@
         <v>1.64</v>
       </c>
       <c r="AP137">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ137">
         <v>1.46</v>
@@ -29478,7 +29490,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29556,10 +29568,10 @@
         <v>0.36</v>
       </c>
       <c r="AP138">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -29684,7 +29696,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -30714,7 +30726,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30920,7 +30932,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31126,7 +31138,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31332,7 +31344,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31538,7 +31550,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31695,6 +31707,624 @@
       </c>
       <c r="BP148">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7784930</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45711.42708333334</v>
+      </c>
+      <c r="F149">
+        <v>25</v>
+      </c>
+      <c r="G149" t="s">
+        <v>75</v>
+      </c>
+      <c r="H149" t="s">
+        <v>77</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="L149">
+        <v>2</v>
+      </c>
+      <c r="M149">
+        <v>1</v>
+      </c>
+      <c r="N149">
+        <v>3</v>
+      </c>
+      <c r="O149" t="s">
+        <v>195</v>
+      </c>
+      <c r="P149" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q149">
+        <v>2.55</v>
+      </c>
+      <c r="R149">
+        <v>2.27</v>
+      </c>
+      <c r="S149">
+        <v>3.95</v>
+      </c>
+      <c r="T149">
+        <v>1.35</v>
+      </c>
+      <c r="U149">
+        <v>2.95</v>
+      </c>
+      <c r="V149">
+        <v>2.5</v>
+      </c>
+      <c r="W149">
+        <v>1.47</v>
+      </c>
+      <c r="X149">
+        <v>5.95</v>
+      </c>
+      <c r="Y149">
+        <v>1.1</v>
+      </c>
+      <c r="Z149">
+        <v>2.05</v>
+      </c>
+      <c r="AA149">
+        <v>3.52</v>
+      </c>
+      <c r="AB149">
+        <v>3.37</v>
+      </c>
+      <c r="AC149">
+        <v>1.05</v>
+      </c>
+      <c r="AD149">
+        <v>9.5</v>
+      </c>
+      <c r="AE149">
+        <v>1.24</v>
+      </c>
+      <c r="AF149">
+        <v>3.65</v>
+      </c>
+      <c r="AG149">
+        <v>1.8</v>
+      </c>
+      <c r="AH149">
+        <v>1.94</v>
+      </c>
+      <c r="AI149">
+        <v>1.64</v>
+      </c>
+      <c r="AJ149">
+        <v>2.14</v>
+      </c>
+      <c r="AK149">
+        <v>1.29</v>
+      </c>
+      <c r="AL149">
+        <v>1.28</v>
+      </c>
+      <c r="AM149">
+        <v>1.71</v>
+      </c>
+      <c r="AN149">
+        <v>1.92</v>
+      </c>
+      <c r="AO149">
+        <v>0.83</v>
+      </c>
+      <c r="AP149">
+        <v>2</v>
+      </c>
+      <c r="AQ149">
+        <v>0.77</v>
+      </c>
+      <c r="AR149">
+        <v>1.79</v>
+      </c>
+      <c r="AS149">
+        <v>1.38</v>
+      </c>
+      <c r="AT149">
+        <v>3.17</v>
+      </c>
+      <c r="AU149">
+        <v>3</v>
+      </c>
+      <c r="AV149">
+        <v>5</v>
+      </c>
+      <c r="AW149">
+        <v>7</v>
+      </c>
+      <c r="AX149">
+        <v>19</v>
+      </c>
+      <c r="AY149">
+        <v>15</v>
+      </c>
+      <c r="AZ149">
+        <v>29</v>
+      </c>
+      <c r="BA149">
+        <v>1</v>
+      </c>
+      <c r="BB149">
+        <v>5</v>
+      </c>
+      <c r="BC149">
+        <v>6</v>
+      </c>
+      <c r="BD149">
+        <v>1.71</v>
+      </c>
+      <c r="BE149">
+        <v>6.75</v>
+      </c>
+      <c r="BF149">
+        <v>2.35</v>
+      </c>
+      <c r="BG149">
+        <v>1.21</v>
+      </c>
+      <c r="BH149">
+        <v>3.7</v>
+      </c>
+      <c r="BI149">
+        <v>1.4</v>
+      </c>
+      <c r="BJ149">
+        <v>2.65</v>
+      </c>
+      <c r="BK149">
+        <v>1.64</v>
+      </c>
+      <c r="BL149">
+        <v>2.08</v>
+      </c>
+      <c r="BM149">
+        <v>2.02</v>
+      </c>
+      <c r="BN149">
+        <v>1.68</v>
+      </c>
+      <c r="BO149">
+        <v>2.55</v>
+      </c>
+      <c r="BP149">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7784932</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45711.52083333334</v>
+      </c>
+      <c r="F150">
+        <v>25</v>
+      </c>
+      <c r="G150" t="s">
+        <v>73</v>
+      </c>
+      <c r="H150" t="s">
+        <v>70</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>150</v>
+      </c>
+      <c r="P150" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q150">
+        <v>2.42</v>
+      </c>
+      <c r="R150">
+        <v>2.4</v>
+      </c>
+      <c r="S150">
+        <v>3.9</v>
+      </c>
+      <c r="T150">
+        <v>1.29</v>
+      </c>
+      <c r="U150">
+        <v>3.3</v>
+      </c>
+      <c r="V150">
+        <v>2.28</v>
+      </c>
+      <c r="W150">
+        <v>1.57</v>
+      </c>
+      <c r="X150">
+        <v>4.95</v>
+      </c>
+      <c r="Y150">
+        <v>1.14</v>
+      </c>
+      <c r="Z150">
+        <v>1.9</v>
+      </c>
+      <c r="AA150">
+        <v>3.87</v>
+      </c>
+      <c r="AB150">
+        <v>3.51</v>
+      </c>
+      <c r="AC150">
+        <v>1.04</v>
+      </c>
+      <c r="AD150">
+        <v>10</v>
+      </c>
+      <c r="AE150">
+        <v>1.18</v>
+      </c>
+      <c r="AF150">
+        <v>4.4</v>
+      </c>
+      <c r="AG150">
+        <v>1.57</v>
+      </c>
+      <c r="AH150">
+        <v>2.15</v>
+      </c>
+      <c r="AI150">
+        <v>1.52</v>
+      </c>
+      <c r="AJ150">
+        <v>2.36</v>
+      </c>
+      <c r="AK150">
+        <v>1.29</v>
+      </c>
+      <c r="AL150">
+        <v>1.25</v>
+      </c>
+      <c r="AM150">
+        <v>1.79</v>
+      </c>
+      <c r="AN150">
+        <v>2</v>
+      </c>
+      <c r="AO150">
+        <v>1.36</v>
+      </c>
+      <c r="AP150">
+        <v>2.08</v>
+      </c>
+      <c r="AQ150">
+        <v>1.25</v>
+      </c>
+      <c r="AR150">
+        <v>2.1</v>
+      </c>
+      <c r="AS150">
+        <v>1.54</v>
+      </c>
+      <c r="AT150">
+        <v>3.64</v>
+      </c>
+      <c r="AU150">
+        <v>5</v>
+      </c>
+      <c r="AV150">
+        <v>4</v>
+      </c>
+      <c r="AW150">
+        <v>8</v>
+      </c>
+      <c r="AX150">
+        <v>10</v>
+      </c>
+      <c r="AY150">
+        <v>14</v>
+      </c>
+      <c r="AZ150">
+        <v>17</v>
+      </c>
+      <c r="BA150">
+        <v>3</v>
+      </c>
+      <c r="BB150">
+        <v>3</v>
+      </c>
+      <c r="BC150">
+        <v>6</v>
+      </c>
+      <c r="BD150">
+        <v>1.73</v>
+      </c>
+      <c r="BE150">
+        <v>6.4</v>
+      </c>
+      <c r="BF150">
+        <v>2.35</v>
+      </c>
+      <c r="BG150">
+        <v>1.3</v>
+      </c>
+      <c r="BH150">
+        <v>3.05</v>
+      </c>
+      <c r="BI150">
+        <v>1.53</v>
+      </c>
+      <c r="BJ150">
+        <v>2.28</v>
+      </c>
+      <c r="BK150">
+        <v>1.88</v>
+      </c>
+      <c r="BL150">
+        <v>1.78</v>
+      </c>
+      <c r="BM150">
+        <v>2.38</v>
+      </c>
+      <c r="BN150">
+        <v>1.49</v>
+      </c>
+      <c r="BO150">
+        <v>3.05</v>
+      </c>
+      <c r="BP150">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7784931</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45711.52083333334</v>
+      </c>
+      <c r="F151">
+        <v>25</v>
+      </c>
+      <c r="G151" t="s">
+        <v>76</v>
+      </c>
+      <c r="H151" t="s">
+        <v>72</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>3</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>4</v>
+      </c>
+      <c r="O151" t="s">
+        <v>196</v>
+      </c>
+      <c r="P151" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q151">
+        <v>1.71</v>
+      </c>
+      <c r="R151">
+        <v>2.85</v>
+      </c>
+      <c r="S151">
+        <v>6.6</v>
+      </c>
+      <c r="T151">
+        <v>1.2</v>
+      </c>
+      <c r="U151">
+        <v>4.05</v>
+      </c>
+      <c r="V151">
+        <v>1.99</v>
+      </c>
+      <c r="W151">
+        <v>1.74</v>
+      </c>
+      <c r="X151">
+        <v>4.05</v>
+      </c>
+      <c r="Y151">
+        <v>1.2</v>
+      </c>
+      <c r="Z151">
+        <v>1.34</v>
+      </c>
+      <c r="AA151">
+        <v>5.2</v>
+      </c>
+      <c r="AB151">
+        <v>7.5</v>
+      </c>
+      <c r="AC151">
+        <v>1.02</v>
+      </c>
+      <c r="AD151">
+        <v>21</v>
+      </c>
+      <c r="AE151">
+        <v>1.12</v>
+      </c>
+      <c r="AF151">
+        <v>5.6</v>
+      </c>
+      <c r="AG151">
+        <v>1.44</v>
+      </c>
+      <c r="AH151">
+        <v>2.67</v>
+      </c>
+      <c r="AI151">
+        <v>1.66</v>
+      </c>
+      <c r="AJ151">
+        <v>2.09</v>
+      </c>
+      <c r="AK151">
+        <v>1.09</v>
+      </c>
+      <c r="AL151">
+        <v>1.13</v>
+      </c>
+      <c r="AM151">
+        <v>3</v>
+      </c>
+      <c r="AN151">
+        <v>1.92</v>
+      </c>
+      <c r="AO151">
+        <v>0.33</v>
+      </c>
+      <c r="AP151">
+        <v>2</v>
+      </c>
+      <c r="AQ151">
+        <v>0.31</v>
+      </c>
+      <c r="AR151">
+        <v>1.93</v>
+      </c>
+      <c r="AS151">
+        <v>1.21</v>
+      </c>
+      <c r="AT151">
+        <v>3.14</v>
+      </c>
+      <c r="AU151">
+        <v>12</v>
+      </c>
+      <c r="AV151">
+        <v>6</v>
+      </c>
+      <c r="AW151">
+        <v>9</v>
+      </c>
+      <c r="AX151">
+        <v>3</v>
+      </c>
+      <c r="AY151">
+        <v>22</v>
+      </c>
+      <c r="AZ151">
+        <v>9</v>
+      </c>
+      <c r="BA151">
+        <v>6</v>
+      </c>
+      <c r="BB151">
+        <v>3</v>
+      </c>
+      <c r="BC151">
+        <v>9</v>
+      </c>
+      <c r="BD151">
+        <v>1.35</v>
+      </c>
+      <c r="BE151">
+        <v>7</v>
+      </c>
+      <c r="BF151">
+        <v>3.55</v>
+      </c>
+      <c r="BG151">
+        <v>1.27</v>
+      </c>
+      <c r="BH151">
+        <v>3.3</v>
+      </c>
+      <c r="BI151">
+        <v>1.47</v>
+      </c>
+      <c r="BJ151">
+        <v>2.43</v>
+      </c>
+      <c r="BK151">
+        <v>1.78</v>
+      </c>
+      <c r="BL151">
+        <v>1.88</v>
+      </c>
+      <c r="BM151">
+        <v>2.2</v>
+      </c>
+      <c r="BN151">
+        <v>1.57</v>
+      </c>
+      <c r="BO151">
+        <v>2.8</v>
+      </c>
+      <c r="BP151">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -1552,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1758,10 +1758,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1964,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ4">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2170,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ5">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2782,25 +2782,25 @@
         <v>1.73</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ8">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2988,25 +2988,25 @@
         <v>1.52</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ9">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU9">
         <v>12</v>
@@ -3200,19 +3200,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3403,22 +3403,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ11">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU11">
         <v>9</v>
@@ -3612,19 +3612,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ12">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR12">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AT12">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="AU12">
         <v>7</v>
@@ -3818,19 +3818,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ13">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS13">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AT13">
-        <v>1.79</v>
+        <v>3.83</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -4018,25 +4018,25 @@
         <v>2.3</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ14">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU14">
         <v>15</v>
@@ -4224,25 +4224,25 @@
         <v>1.52</v>
       </c>
       <c r="AN15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ15">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR15">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AS15">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="AT15">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="AU15">
         <v>2</v>
@@ -4436,19 +4436,19 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR16">
-        <v>2.11</v>
+        <v>1.59</v>
       </c>
       <c r="AS16">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AT16">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="AU16">
         <v>8</v>
@@ -4636,25 +4636,25 @@
         <v>1.65</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ17">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR17">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AS17">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AT17">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4842,25 +4842,25 @@
         <v>1.45</v>
       </c>
       <c r="AN18">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ18">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR18">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="AS18">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AT18">
-        <v>3.46</v>
+        <v>3.15</v>
       </c>
       <c r="AU18">
         <v>9</v>
@@ -5054,19 +5054,19 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ19">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR19">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AS19">
-        <v>1.76</v>
+        <v>2.59</v>
       </c>
       <c r="AT19">
-        <v>3.61</v>
+        <v>4.39</v>
       </c>
       <c r="AU19">
         <v>3</v>
@@ -5254,25 +5254,25 @@
         <v>1.88</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ20">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AS20">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="AT20">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5460,25 +5460,25 @@
         <v>1.85</v>
       </c>
       <c r="AN21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR21">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AS21">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AT21">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5666,25 +5666,25 @@
         <v>1.2</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP22">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ22">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR22">
-        <v>0.55</v>
+        <v>1.15</v>
       </c>
       <c r="AS22">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AT22">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5872,25 +5872,25 @@
         <v>2.15</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP23">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR23">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AS23">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AT23">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -6081,22 +6081,22 @@
         <v>3</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR24">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AS24">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT24">
-        <v>3.53</v>
+        <v>3.09</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6284,25 +6284,25 @@
         <v>1.85</v>
       </c>
       <c r="AN25">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR25">
-        <v>3.42</v>
+        <v>2.37</v>
       </c>
       <c r="AS25">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="AT25">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6490,22 +6490,22 @@
         <v>2.05</v>
       </c>
       <c r="AN26">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO26">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ26">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR26">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AS26">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AT26">
         <v>3.14</v>
@@ -6696,25 +6696,25 @@
         <v>2.3</v>
       </c>
       <c r="AN27">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ27">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR27">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AS27">
-        <v>0.89</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="AU27">
         <v>5</v>
@@ -6902,25 +6902,25 @@
         <v>1.35</v>
       </c>
       <c r="AN28">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO28">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AP28">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ28">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AS28">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AT28">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AU28">
         <v>9</v>
@@ -7108,25 +7108,25 @@
         <v>2.4</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO29">
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ29">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR29">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="AS29">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT29">
-        <v>3.49</v>
+        <v>3.08</v>
       </c>
       <c r="AU29">
         <v>9</v>
@@ -7314,25 +7314,25 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP30">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR30">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="AS30">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AT30">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7520,25 +7520,25 @@
         <v>0</v>
       </c>
       <c r="AN31">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AP31">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR31">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS31">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AT31">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AU31">
         <v>4</v>
@@ -7726,25 +7726,25 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP32">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ32">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR32">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AS32">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AT32">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AU32">
         <v>2</v>
@@ -7932,25 +7932,25 @@
         <v>1.3</v>
       </c>
       <c r="AN33">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP33">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ33">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR33">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AS33">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="AT33">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8138,25 +8138,25 @@
         <v>1.91</v>
       </c>
       <c r="AN34">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO34">
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR34">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="AS34">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT34">
-        <v>3.86</v>
+        <v>3.54</v>
       </c>
       <c r="AU34">
         <v>2</v>
@@ -8344,25 +8344,25 @@
         <v>1.62</v>
       </c>
       <c r="AN35">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO35">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AP35">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ35">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR35">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AS35">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AT35">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="AU35">
         <v>7</v>
@@ -8550,25 +8550,25 @@
         <v>1.55</v>
       </c>
       <c r="AN36">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ36">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR36">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AS36">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AT36">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8756,25 +8756,25 @@
         <v>1.87</v>
       </c>
       <c r="AN37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO37">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AP37">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR37">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AS37">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AT37">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="AU37">
         <v>4</v>
@@ -8962,25 +8962,25 @@
         <v>1.3</v>
       </c>
       <c r="AN38">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO38">
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR38">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AS38">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AT38">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="AU38">
         <v>9</v>
@@ -9168,25 +9168,25 @@
         <v>1.75</v>
       </c>
       <c r="AN39">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO39">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP39">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ39">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR39">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AS39">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AT39">
-        <v>4.01</v>
+        <v>3.67</v>
       </c>
       <c r="AU39">
         <v>2</v>
@@ -9374,25 +9374,25 @@
         <v>2.3</v>
       </c>
       <c r="AN40">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO40">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ40">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR40">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AS40">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AT40">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9580,25 +9580,25 @@
         <v>1.43</v>
       </c>
       <c r="AN41">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO41">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR41">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AS41">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="AT41">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="AU41">
         <v>2</v>
@@ -9786,25 +9786,25 @@
         <v>1.17</v>
       </c>
       <c r="AN42">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO42">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ42">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR42">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AS42">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AT42">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9992,25 +9992,25 @@
         <v>1.77</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO43">
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ43">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
       </c>
       <c r="AS43">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AT43">
-        <v>3.22</v>
+        <v>3.39</v>
       </c>
       <c r="AU43">
         <v>8</v>
@@ -10198,25 +10198,25 @@
         <v>1.22</v>
       </c>
       <c r="AN44">
-        <v>1.33</v>
+        <v>0.71</v>
       </c>
       <c r="AO44">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AP44">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ44">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR44">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AS44">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AT44">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="AU44">
         <v>2</v>
@@ -10404,25 +10404,25 @@
         <v>1.9</v>
       </c>
       <c r="AN45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AO45">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ45">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR45">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AS45">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AT45">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10610,25 +10610,25 @@
         <v>2.45</v>
       </c>
       <c r="AN46">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AO46">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR46">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AS46">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AT46">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10816,25 +10816,25 @@
         <v>2.11</v>
       </c>
       <c r="AN47">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AP47">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ47">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR47">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AS47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT47">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="AU47">
         <v>3</v>
@@ -11025,22 +11025,22 @@
         <v>2</v>
       </c>
       <c r="AO48">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ48">
+        <v>1.68</v>
+      </c>
+      <c r="AR48">
         <v>1.46</v>
       </c>
-      <c r="AR48">
-        <v>1.38</v>
-      </c>
       <c r="AS48">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AT48">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="AU48">
         <v>11</v>
@@ -11228,25 +11228,25 @@
         <v>2.42</v>
       </c>
       <c r="AN49">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO49">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AP49">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ49">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR49">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AS49">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT49">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="AU49">
         <v>8</v>
@@ -11434,25 +11434,25 @@
         <v>2.3</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AO50">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR50">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AS50">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AT50">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11640,25 +11640,25 @@
         <v>1.65</v>
       </c>
       <c r="AN51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AO51">
-        <v>0.25</v>
+        <v>0.88</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ51">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR51">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS51">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AT51">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11846,25 +11846,25 @@
         <v>1.38</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO52">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR52">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AS52">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AT52">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="AU52">
         <v>7</v>
@@ -12052,25 +12052,25 @@
         <v>1.62</v>
       </c>
       <c r="AN53">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AO53">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="AP53">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ53">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR53">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS53">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AT53">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12258,25 +12258,25 @@
         <v>1.5</v>
       </c>
       <c r="AN54">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO54">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP54">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ54">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR54">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AS54">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AT54">
-        <v>3.66</v>
+        <v>3.32</v>
       </c>
       <c r="AU54">
         <v>7</v>
@@ -12464,25 +12464,25 @@
         <v>1.65</v>
       </c>
       <c r="AN55">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO55">
+        <v>2</v>
+      </c>
+      <c r="AP55">
+        <v>1.44</v>
+      </c>
+      <c r="AQ55">
+        <v>1.68</v>
+      </c>
+      <c r="AR55">
+        <v>1.64</v>
+      </c>
+      <c r="AS55">
         <v>1.75</v>
       </c>
-      <c r="AP55">
-        <v>1.75</v>
-      </c>
-      <c r="AQ55">
-        <v>1.33</v>
-      </c>
-      <c r="AR55">
-        <v>1.62</v>
-      </c>
-      <c r="AS55">
-        <v>1.54</v>
-      </c>
       <c r="AT55">
-        <v>3.16</v>
+        <v>3.39</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12670,25 +12670,25 @@
         <v>1.42</v>
       </c>
       <c r="AN56">
-        <v>1.25</v>
+        <v>0.89</v>
       </c>
       <c r="AO56">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP56">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ56">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR56">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AS56">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AT56">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AU56">
         <v>4</v>
@@ -12876,25 +12876,25 @@
         <v>1.83</v>
       </c>
       <c r="AN57">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO57">
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR57">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AS57">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AT57">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="AU57">
         <v>6</v>
@@ -13082,25 +13082,25 @@
         <v>1.95</v>
       </c>
       <c r="AN58">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AO58">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ58">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR58">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AS58">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AT58">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="AU58">
         <v>7</v>
@@ -13288,25 +13288,25 @@
         <v>1.7</v>
       </c>
       <c r="AN59">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP59">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ59">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR59">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AS59">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AT59">
-        <v>3.41</v>
+        <v>3.24</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13494,25 +13494,25 @@
         <v>2.5</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="AO60">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ60">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR60">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AS60">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT60">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13700,25 +13700,25 @@
         <v>1.1</v>
       </c>
       <c r="AN61">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AO61">
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ61">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR61">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS61">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AT61">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="AU61">
         <v>5</v>
@@ -13906,25 +13906,25 @@
         <v>1.83</v>
       </c>
       <c r="AN62">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AO62">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR62">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AS62">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT62">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="AU62">
         <v>9</v>
@@ -14112,25 +14112,25 @@
         <v>1.22</v>
       </c>
       <c r="AN63">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="AO63">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AP63">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ63">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR63">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS63">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AT63">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14318,25 +14318,25 @@
         <v>2.7</v>
       </c>
       <c r="AN64">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO64">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ64">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR64">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AS64">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AT64">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AU64">
         <v>10</v>
@@ -14524,25 +14524,25 @@
         <v>1.6</v>
       </c>
       <c r="AN65">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AO65">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR65">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AS65">
         <v>1.59</v>
       </c>
       <c r="AT65">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14730,25 +14730,25 @@
         <v>1.62</v>
       </c>
       <c r="AN66">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO66">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AP66">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ66">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR66">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AS66">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AT66">
-        <v>3.59</v>
+        <v>3.43</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14936,25 +14936,25 @@
         <v>1.53</v>
       </c>
       <c r="AN67">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AO67">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ67">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR67">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AS67">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AT67">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -15142,25 +15142,25 @@
         <v>1.2</v>
       </c>
       <c r="AN68">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO68">
-        <v>0.4</v>
+        <v>1.27</v>
       </c>
       <c r="AP68">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ68">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR68">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AS68">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AT68">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="AU68">
         <v>2</v>
@@ -15348,25 +15348,25 @@
         <v>1.55</v>
       </c>
       <c r="AN69">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AO69">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ69">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR69">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS69">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AT69">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15554,25 +15554,25 @@
         <v>2.8</v>
       </c>
       <c r="AN70">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AP70">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ70">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR70">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AS70">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AT70">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15760,25 +15760,25 @@
         <v>1.75</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AO71">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AP71">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ71">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR71">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AS71">
         <v>1.68</v>
       </c>
       <c r="AT71">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15966,25 +15966,25 @@
         <v>1.35</v>
       </c>
       <c r="AN72">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO72">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AP72">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR72">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AS72">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AT72">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16172,25 +16172,25 @@
         <v>1.9</v>
       </c>
       <c r="AN73">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AO73">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR73">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AS73">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AT73">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16378,25 +16378,25 @@
         <v>1.55</v>
       </c>
       <c r="AN74">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO74">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR74">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AS74">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AT74">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16584,25 +16584,25 @@
         <v>2.85</v>
       </c>
       <c r="AN75">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AO75">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ75">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
       </c>
       <c r="AS75">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AT75">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="AU75">
         <v>10</v>
@@ -16790,25 +16790,25 @@
         <v>1.72</v>
       </c>
       <c r="AN76">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO76">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="AP76">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ76">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR76">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AS76">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT76">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16996,25 +16996,25 @@
         <v>1.45</v>
       </c>
       <c r="AN77">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AO77">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR77">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AS77">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AT77">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="AU77">
         <v>4</v>
@@ -17202,25 +17202,25 @@
         <v>3</v>
       </c>
       <c r="AN78">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AO78">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AP78">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ78">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR78">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AS78">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT78">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17408,25 +17408,25 @@
         <v>1.87</v>
       </c>
       <c r="AN79">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AO79">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR79">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AS79">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AT79">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="AU79">
         <v>7</v>
@@ -17614,25 +17614,25 @@
         <v>1.22</v>
       </c>
       <c r="AN80">
-        <v>1.17</v>
+        <v>0.62</v>
       </c>
       <c r="AO80">
-        <v>0.83</v>
+        <v>1.54</v>
       </c>
       <c r="AP80">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ80">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR80">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS80">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AT80">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17820,25 +17820,25 @@
         <v>1.17</v>
       </c>
       <c r="AN81">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AO81">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="AP81">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ81">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR81">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="AS81">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AT81">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -18026,25 +18026,25 @@
         <v>1.8</v>
       </c>
       <c r="AN82">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AO82">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ82">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR82">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AS82">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AT82">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18232,25 +18232,25 @@
         <v>1.65</v>
       </c>
       <c r="AN83">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="AO83">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AS83">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AT83">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="AU83">
         <v>11</v>
@@ -18438,25 +18438,25 @@
         <v>1.45</v>
       </c>
       <c r="AN84">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO84">
-        <v>0.83</v>
+        <v>1.31</v>
       </c>
       <c r="AP84">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ84">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR84">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS84">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AT84">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="AU84">
         <v>6</v>
@@ -18644,25 +18644,25 @@
         <v>1.67</v>
       </c>
       <c r="AN85">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AP85">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ85">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR85">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AS85">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AT85">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18850,25 +18850,25 @@
         <v>1.55</v>
       </c>
       <c r="AN86">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AO86">
-        <v>0.71</v>
+        <v>1.14</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ86">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR86">
+        <v>1.59</v>
+      </c>
+      <c r="AS86">
         <v>1.7</v>
       </c>
-      <c r="AS86">
-        <v>1.68</v>
-      </c>
       <c r="AT86">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -19056,25 +19056,25 @@
         <v>2.3</v>
       </c>
       <c r="AN87">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="AO87">
-        <v>0.14</v>
+        <v>0.79</v>
       </c>
       <c r="AP87">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ87">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR87">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS87">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AT87">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AU87">
         <v>6</v>
@@ -19262,25 +19262,25 @@
         <v>1.95</v>
       </c>
       <c r="AN88">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="AO88">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ88">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR88">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AS88">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AT88">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="AU88">
         <v>-1</v>
@@ -19468,25 +19468,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>2.29</v>
+        <v>1.79</v>
       </c>
       <c r="AO89">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP89">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ89">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR89">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AS89">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AT89">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="AU89">
         <v>12</v>
@@ -19674,25 +19674,25 @@
         <v>2.7</v>
       </c>
       <c r="AN90">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AO90">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="AP90">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ90">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR90">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AS90">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT90">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AU90">
         <v>8</v>
@@ -19880,25 +19880,25 @@
         <v>1.7</v>
       </c>
       <c r="AN91">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AO91">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AP91">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ91">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR91">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS91">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AT91">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AU91">
         <v>8</v>
@@ -20086,25 +20086,25 @@
         <v>1.85</v>
       </c>
       <c r="AN92">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AO92">
-        <v>0.71</v>
+        <v>1.53</v>
       </c>
       <c r="AP92">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ92">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR92">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AS92">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AT92">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20292,25 +20292,25 @@
         <v>1.22</v>
       </c>
       <c r="AN93">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="AO93">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AP93">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR93">
-        <v>0.95</v>
+        <v>1.07</v>
       </c>
       <c r="AS93">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AT93">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20498,25 +20498,25 @@
         <v>1.93</v>
       </c>
       <c r="AN94">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AO94">
-        <v>0.43</v>
+        <v>0.67</v>
       </c>
       <c r="AP94">
+        <v>1.44</v>
+      </c>
+      <c r="AQ94">
+        <v>0.92</v>
+      </c>
+      <c r="AR94">
+        <v>1.55</v>
+      </c>
+      <c r="AS94">
         <v>1.46</v>
       </c>
-      <c r="AQ94">
-        <v>1</v>
-      </c>
-      <c r="AR94">
-        <v>1.49</v>
-      </c>
-      <c r="AS94">
-        <v>1.41</v>
-      </c>
       <c r="AT94">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20704,25 +20704,25 @@
         <v>1.22</v>
       </c>
       <c r="AN95">
-        <v>1.43</v>
+        <v>0.8</v>
       </c>
       <c r="AO95">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ95">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR95">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AS95">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AT95">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20910,25 +20910,25 @@
         <v>1.75</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO96">
-        <v>1.29</v>
+        <v>1.87</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ96">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR96">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AS96">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AT96">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="AU96">
         <v>11</v>
@@ -21116,25 +21116,25 @@
         <v>1.95</v>
       </c>
       <c r="AN97">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AO97">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ97">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR97">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AS97">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AT97">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="AU97">
         <v>13</v>
@@ -21322,25 +21322,25 @@
         <v>2.25</v>
       </c>
       <c r="AN98">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO98">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP98">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ98">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR98">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS98">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT98">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21528,25 +21528,25 @@
         <v>1.42</v>
       </c>
       <c r="AN99">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AO99">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ99">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR99">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AS99">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AT99">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21734,25 +21734,25 @@
         <v>1.45</v>
       </c>
       <c r="AN100">
+        <v>1.63</v>
+      </c>
+      <c r="AO100">
         <v>1.75</v>
       </c>
-      <c r="AO100">
-        <v>1.13</v>
-      </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ100">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR100">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AS100">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AT100">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21940,25 +21940,25 @@
         <v>1.75</v>
       </c>
       <c r="AN101">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO101">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ101">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR101">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AS101">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT101">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="AU101">
         <v>6</v>
@@ -22146,25 +22146,25 @@
         <v>3.3</v>
       </c>
       <c r="AN102">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO102">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ102">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR102">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AS102">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AT102">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22352,25 +22352,25 @@
         <v>1.45</v>
       </c>
       <c r="AN103">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="AO103">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AP103">
+        <v>1.44</v>
+      </c>
+      <c r="AQ103">
+        <v>1.68</v>
+      </c>
+      <c r="AR103">
+        <v>1.64</v>
+      </c>
+      <c r="AS103">
         <v>1.75</v>
       </c>
-      <c r="AQ103">
-        <v>1.46</v>
-      </c>
-      <c r="AR103">
-        <v>1.81</v>
-      </c>
-      <c r="AS103">
-        <v>1.77</v>
-      </c>
       <c r="AT103">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22558,25 +22558,25 @@
         <v>1.3</v>
       </c>
       <c r="AN104">
-        <v>1.25</v>
+        <v>0.76</v>
       </c>
       <c r="AO104">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP104">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR104">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AS104">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AT104">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22764,25 +22764,25 @@
         <v>1.2</v>
       </c>
       <c r="AN105">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO105">
-        <v>0.88</v>
+        <v>1.35</v>
       </c>
       <c r="AP105">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ105">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR105">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="AS105">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AT105">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22970,25 +22970,25 @@
         <v>2.2</v>
       </c>
       <c r="AN106">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO106">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP106">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR106">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AS106">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AT106">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="AU106">
         <v>7</v>
@@ -23176,25 +23176,25 @@
         <v>1.62</v>
       </c>
       <c r="AN107">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AO107">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AP107">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ107">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR107">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AS107">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AT107">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="AU107">
         <v>9</v>
@@ -23382,25 +23382,25 @@
         <v>1.75</v>
       </c>
       <c r="AN108">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="AO108">
-        <v>0.75</v>
+        <v>1.59</v>
       </c>
       <c r="AP108">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ108">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR108">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AS108">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AT108">
-        <v>3.49</v>
+        <v>3.39</v>
       </c>
       <c r="AU108">
         <v>6</v>
@@ -23588,25 +23588,25 @@
         <v>1.62</v>
       </c>
       <c r="AN109">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AO109">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP109">
+        <v>1.44</v>
+      </c>
+      <c r="AQ109">
+        <v>1.44</v>
+      </c>
+      <c r="AR109">
         <v>1.46</v>
       </c>
-      <c r="AQ109">
-        <v>1.15</v>
-      </c>
-      <c r="AR109">
-        <v>1.41</v>
-      </c>
       <c r="AS109">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AT109">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23794,25 +23794,25 @@
         <v>3.3</v>
       </c>
       <c r="AN110">
-        <v>1.89</v>
+        <v>1.28</v>
       </c>
       <c r="AO110">
-        <v>0.33</v>
+        <v>0.72</v>
       </c>
       <c r="AP110">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ110">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR110">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AS110">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AT110">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AU110">
         <v>9</v>
@@ -24000,25 +24000,25 @@
         <v>1.77</v>
       </c>
       <c r="AN111">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AO111">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AP111">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR111">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AS111">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AT111">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24206,25 +24206,25 @@
         <v>2.05</v>
       </c>
       <c r="AN112">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AO112">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ112">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR112">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AS112">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AT112">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24412,25 +24412,25 @@
         <v>2.65</v>
       </c>
       <c r="AN113">
+        <v>1.5</v>
+      </c>
+      <c r="AO113">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AP113">
         <v>1.44</v>
       </c>
-      <c r="AO113">
-        <v>0.78</v>
-      </c>
-      <c r="AP113">
-        <v>1.46</v>
-      </c>
       <c r="AQ113">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR113">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AS113">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT113">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AU113">
         <v>4</v>
@@ -24618,25 +24618,25 @@
         <v>1.57</v>
       </c>
       <c r="AN114">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AO114">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ114">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR114">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AS114">
         <v>1.76</v>
       </c>
       <c r="AT114">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="AU114">
         <v>6</v>
@@ -24824,25 +24824,25 @@
         <v>1.85</v>
       </c>
       <c r="AN115">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO115">
+        <v>1.61</v>
+      </c>
+      <c r="AP115">
+        <v>1.48</v>
+      </c>
+      <c r="AQ115">
+        <v>1.68</v>
+      </c>
+      <c r="AR115">
+        <v>1.68</v>
+      </c>
+      <c r="AS115">
         <v>1.67</v>
       </c>
-      <c r="AP115">
-        <v>2</v>
-      </c>
-      <c r="AQ115">
-        <v>1.33</v>
-      </c>
-      <c r="AR115">
-        <v>1.76</v>
-      </c>
-      <c r="AS115">
-        <v>1.68</v>
-      </c>
       <c r="AT115">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -25030,25 +25030,25 @@
         <v>1.36</v>
       </c>
       <c r="AN116">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AO116">
-        <v>0.67</v>
+        <v>1.26</v>
       </c>
       <c r="AP116">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ116">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR116">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS116">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AT116">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="AU116">
         <v>7</v>
@@ -25236,25 +25236,25 @@
         <v>1.09</v>
       </c>
       <c r="AN117">
+        <v>0.89</v>
+      </c>
+      <c r="AO117">
+        <v>1.58</v>
+      </c>
+      <c r="AP117">
+        <v>0.96</v>
+      </c>
+      <c r="AQ117">
+        <v>1.68</v>
+      </c>
+      <c r="AR117">
         <v>1.11</v>
       </c>
-      <c r="AO117">
-        <v>1.22</v>
-      </c>
-      <c r="AP117">
-        <v>1.42</v>
-      </c>
-      <c r="AQ117">
-        <v>1.33</v>
-      </c>
-      <c r="AR117">
-        <v>1</v>
-      </c>
       <c r="AS117">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AT117">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="AU117">
         <v>3</v>
@@ -25442,25 +25442,25 @@
         <v>1.22</v>
       </c>
       <c r="AN118">
-        <v>1.11</v>
+        <v>0.74</v>
       </c>
       <c r="AO118">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AP118">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ118">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR118">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AS118">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AT118">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25648,25 +25648,25 @@
         <v>1.5</v>
       </c>
       <c r="AN119">
+        <v>1.37</v>
+      </c>
+      <c r="AO119">
+        <v>1.63</v>
+      </c>
+      <c r="AP119">
+        <v>1.44</v>
+      </c>
+      <c r="AQ119">
+        <v>1.48</v>
+      </c>
+      <c r="AR119">
         <v>1.56</v>
       </c>
-      <c r="AO119">
-        <v>1</v>
-      </c>
-      <c r="AP119">
-        <v>1.75</v>
-      </c>
-      <c r="AQ119">
-        <v>0.92</v>
-      </c>
-      <c r="AR119">
-        <v>1.76</v>
-      </c>
       <c r="AS119">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AT119">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="AU119">
         <v>12</v>
@@ -25854,25 +25854,25 @@
         <v>2.1</v>
       </c>
       <c r="AN120">
+        <v>1.63</v>
+      </c>
+      <c r="AO120">
+        <v>1.37</v>
+      </c>
+      <c r="AP120">
+        <v>1.68</v>
+      </c>
+      <c r="AQ120">
+        <v>1.2</v>
+      </c>
+      <c r="AR120">
         <v>1.78</v>
       </c>
-      <c r="AO120">
-        <v>1.11</v>
-      </c>
-      <c r="AP120">
-        <v>1.92</v>
-      </c>
-      <c r="AQ120">
-        <v>0.77</v>
-      </c>
-      <c r="AR120">
-        <v>1.76</v>
-      </c>
       <c r="AS120">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AT120">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26060,25 +26060,25 @@
         <v>1.67</v>
       </c>
       <c r="AN121">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AO121">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ121">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR121">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS121">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AT121">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26266,25 +26266,25 @@
         <v>1.55</v>
       </c>
       <c r="AN122">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AO122">
-        <v>0.7</v>
+        <v>1.25</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ122">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR122">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AS122">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AT122">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26472,25 +26472,25 @@
         <v>1.93</v>
       </c>
       <c r="AN123">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO123">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AP123">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ123">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR123">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS123">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AT123">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="AU123">
         <v>6</v>
@@ -26678,25 +26678,25 @@
         <v>2.25</v>
       </c>
       <c r="AN124">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AO124">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AS124">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT124">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26884,25 +26884,25 @@
         <v>1.67</v>
       </c>
       <c r="AN125">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AO125">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ125">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR125">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AS125">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AT125">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="AU125">
         <v>8</v>
@@ -27090,25 +27090,25 @@
         <v>1.3</v>
       </c>
       <c r="AN126">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO126">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AP126">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ126">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR126">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AS126">
         <v>1.8</v>
       </c>
       <c r="AT126">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27296,25 +27296,25 @@
         <v>1.55</v>
       </c>
       <c r="AN127">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AO127">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AP127">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ127">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR127">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS127">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AT127">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AU127">
         <v>4</v>
@@ -27502,22 +27502,22 @@
         <v>1.36</v>
       </c>
       <c r="AN128">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AO128">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="AP128">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ128">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR128">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AS128">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AT128">
         <v>3.11</v>
@@ -27708,25 +27708,25 @@
         <v>1.35</v>
       </c>
       <c r="AN129">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AO129">
+        <v>1.52</v>
+      </c>
+      <c r="AP129">
         <v>1.2</v>
       </c>
-      <c r="AP129">
-        <v>1.67</v>
-      </c>
       <c r="AQ129">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR129">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AS129">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AT129">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="AU129">
         <v>8</v>
@@ -27914,25 +27914,25 @@
         <v>1.52</v>
       </c>
       <c r="AN130">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AP130">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ130">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR130">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AS130">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AT130">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28120,25 +28120,25 @@
         <v>3.3</v>
       </c>
       <c r="AN131">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AO131">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AP131">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ131">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR131">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AS131">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AT131">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="AU131">
         <v>11</v>
@@ -28326,25 +28326,25 @@
         <v>2.15</v>
       </c>
       <c r="AN132">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AO132">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AP132">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
       </c>
       <c r="AS132">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AT132">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28532,25 +28532,25 @@
         <v>1.31</v>
       </c>
       <c r="AN133">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO133">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AP133">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ133">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR133">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS133">
         <v>1.48</v>
       </c>
       <c r="AT133">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28738,25 +28738,25 @@
         <v>2.95</v>
       </c>
       <c r="AN134">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AO134">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ134">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR134">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AS134">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AT134">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -28944,25 +28944,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AO135">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AP135">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR135">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AS135">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AT135">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="AU135">
         <v>12</v>
@@ -29150,25 +29150,25 @@
         <v>2.1</v>
       </c>
       <c r="AN136">
+        <v>1.41</v>
+      </c>
+      <c r="AO136">
+        <v>1.23</v>
+      </c>
+      <c r="AP136">
+        <v>1.48</v>
+      </c>
+      <c r="AQ136">
+        <v>1.2</v>
+      </c>
+      <c r="AR136">
         <v>1.91</v>
       </c>
-      <c r="AO136">
-        <v>0.91</v>
-      </c>
-      <c r="AP136">
-        <v>2.08</v>
-      </c>
-      <c r="AQ136">
-        <v>0.77</v>
-      </c>
-      <c r="AR136">
-        <v>2.08</v>
-      </c>
       <c r="AS136">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AT136">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="AU136">
         <v>9</v>
@@ -29356,25 +29356,25 @@
         <v>1.62</v>
       </c>
       <c r="AN137">
+        <v>1.5</v>
+      </c>
+      <c r="AO137">
         <v>1.82</v>
       </c>
-      <c r="AO137">
-        <v>1.64</v>
-      </c>
       <c r="AP137">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ137">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR137">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AS137">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AT137">
-        <v>3.78</v>
+        <v>3.61</v>
       </c>
       <c r="AU137">
         <v>4</v>
@@ -29562,25 +29562,25 @@
         <v>2.35</v>
       </c>
       <c r="AN138">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AO138">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ138">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR138">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AS138">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AT138">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AU138">
         <v>12</v>
@@ -29768,25 +29768,25 @@
         <v>1.55</v>
       </c>
       <c r="AN139">
+        <v>1.5</v>
+      </c>
+      <c r="AO139">
         <v>1.45</v>
       </c>
-      <c r="AO139">
-        <v>1.09</v>
-      </c>
       <c r="AP139">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ139">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR139">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AS139">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AT139">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="AU139">
         <v>3</v>
@@ -29974,25 +29974,25 @@
         <v>1.8</v>
       </c>
       <c r="AN140">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AO140">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AP140">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR140">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AS140">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AT140">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30180,25 +30180,25 @@
         <v>1.6</v>
       </c>
       <c r="AN141">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="AO141">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AP141">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ141">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR141">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AS141">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AT141">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30386,25 +30386,25 @@
         <v>1.15</v>
       </c>
       <c r="AN142">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="AO142">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="AP142">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="AQ142">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="AR142">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AS142">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AT142">
-        <v>2.98</v>
+        <v>3.17</v>
       </c>
       <c r="AU142">
         <v>5</v>
@@ -30592,25 +30592,25 @@
         <v>1.21</v>
       </c>
       <c r="AN143">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="AO143">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AP143">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
       <c r="AQ143">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AR143">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AS143">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AT143">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="AU143">
         <v>9</v>
@@ -30798,25 +30798,25 @@
         <v>1.74</v>
       </c>
       <c r="AN144">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AO144">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AP144">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AQ144">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="AR144">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AS144">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AT144">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AU144">
         <v>10</v>
@@ -31004,25 +31004,25 @@
         <v>1.34</v>
       </c>
       <c r="AN145">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AO145">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ145">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AR145">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AS145">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AT145">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31210,25 +31210,25 @@
         <v>2.1</v>
       </c>
       <c r="AN146">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="AO146">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP146">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR146">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AS146">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AT146">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31416,25 +31416,25 @@
         <v>2.3</v>
       </c>
       <c r="AN147">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AO147">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ147">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="AR147">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS147">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AT147">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31622,25 +31622,25 @@
         <v>1.48</v>
       </c>
       <c r="AN148">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AO148">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AP148">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AQ148">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AR148">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AS148">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AT148">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="AU148">
         <v>8</v>
@@ -31828,25 +31828,25 @@
         <v>1.71</v>
       </c>
       <c r="AN149">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AO149">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AP149">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ149">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="AR149">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AS149">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AT149">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -32034,25 +32034,25 @@
         <v>1.79</v>
       </c>
       <c r="AN150">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AO150">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="AQ150">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AR150">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AS150">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AT150">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32240,25 +32240,25 @@
         <v>3</v>
       </c>
       <c r="AN151">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AO151">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ151">
-        <v>0.31</v>
+        <v>0.68</v>
       </c>
       <c r="AR151">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AS151">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AT151">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="AU151">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="283">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -605,6 +605,12 @@
   </si>
   <si>
     <t>['69', '89', '90+5']</t>
+  </si>
+  <si>
+    <t>['17', '25']</t>
+  </si>
+  <si>
+    <t>['4', '35', '40', '78']</t>
   </si>
   <si>
     <t>['25']</t>
@@ -1218,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1480,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1552,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ2">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1680,7 +1686,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1758,10 +1764,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1964,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ4">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2092,7 +2098,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2170,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2298,7 +2304,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2376,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2504,7 +2510,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2582,10 +2588,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2710,7 +2716,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2782,25 +2788,25 @@
         <v>1.73</v>
       </c>
       <c r="AN8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR8">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2988,25 +2994,25 @@
         <v>1.52</v>
       </c>
       <c r="AN9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>12</v>
@@ -3122,7 +3128,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3200,19 +3206,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ10">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3328,7 +3334,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3403,22 +3409,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR11">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>9</v>
@@ -3534,7 +3540,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3612,19 +3618,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR12">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="AS12">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="AU12">
         <v>7</v>
@@ -3818,19 +3824,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR13">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AT13">
-        <v>3.83</v>
+        <v>1.79</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3946,7 +3952,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4018,25 +4024,25 @@
         <v>2.3</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ14">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR14">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>15</v>
@@ -4152,7 +4158,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4224,25 +4230,25 @@
         <v>1.52</v>
       </c>
       <c r="AN15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ15">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR15">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AS15">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="AT15">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AU15">
         <v>2</v>
@@ -4436,19 +4442,19 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR16">
-        <v>1.59</v>
+        <v>2.11</v>
       </c>
       <c r="AS16">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AT16">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="AU16">
         <v>8</v>
@@ -4636,25 +4642,25 @@
         <v>1.65</v>
       </c>
       <c r="AN17">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR17">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AS17">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT17">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -4770,7 +4776,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4842,25 +4848,25 @@
         <v>1.45</v>
       </c>
       <c r="AN18">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR18">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AS18">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AT18">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="AU18">
         <v>9</v>
@@ -4976,7 +4982,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5054,19 +5060,19 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ19">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR19">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AS19">
-        <v>2.59</v>
+        <v>1.76</v>
       </c>
       <c r="AT19">
-        <v>4.39</v>
+        <v>3.61</v>
       </c>
       <c r="AU19">
         <v>3</v>
@@ -5254,25 +5260,25 @@
         <v>1.88</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO20">
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ20">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR20">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AS20">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="AT20">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5460,25 +5466,25 @@
         <v>1.85</v>
       </c>
       <c r="AN21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR21">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AS21">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AT21">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5594,7 +5600,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5666,25 +5672,25 @@
         <v>1.2</v>
       </c>
       <c r="AN22">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR22">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="AS22">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AT22">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5872,25 +5878,25 @@
         <v>2.15</v>
       </c>
       <c r="AN23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ23">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR23">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AS23">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AT23">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -6006,7 +6012,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6081,22 +6087,22 @@
         <v>3</v>
       </c>
       <c r="AO24">
+        <v>1</v>
+      </c>
+      <c r="AP24">
+        <v>2.08</v>
+      </c>
+      <c r="AQ24">
         <v>1.33</v>
       </c>
-      <c r="AP24">
-        <v>1.68</v>
-      </c>
-      <c r="AQ24">
-        <v>1.68</v>
-      </c>
       <c r="AR24">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AS24">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT24">
-        <v>3.09</v>
+        <v>3.53</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6284,25 +6290,25 @@
         <v>1.85</v>
       </c>
       <c r="AN25">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ25">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR25">
-        <v>2.37</v>
+        <v>3.42</v>
       </c>
       <c r="AS25">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="AT25">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6418,7 +6424,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6490,22 +6496,22 @@
         <v>2.05</v>
       </c>
       <c r="AN26">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR26">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AS26">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AT26">
         <v>3.14</v>
@@ -6696,25 +6702,25 @@
         <v>2.3</v>
       </c>
       <c r="AN27">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR27">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AT27">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="AU27">
         <v>5</v>
@@ -6830,7 +6836,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6902,25 +6908,25 @@
         <v>1.35</v>
       </c>
       <c r="AN28">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO28">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ28">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AS28">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT28">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AU28">
         <v>9</v>
@@ -7108,25 +7114,25 @@
         <v>2.4</v>
       </c>
       <c r="AN29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR29">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="AS29">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT29">
-        <v>3.08</v>
+        <v>3.49</v>
       </c>
       <c r="AU29">
         <v>9</v>
@@ -7242,7 +7248,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7314,25 +7320,25 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR30">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AS30">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AT30">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7520,25 +7526,25 @@
         <v>0</v>
       </c>
       <c r="AN31">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO31">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ31">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR31">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS31">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AT31">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="AU31">
         <v>4</v>
@@ -7726,25 +7732,25 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO32">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ32">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR32">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AS32">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AT32">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AU32">
         <v>2</v>
@@ -7932,25 +7938,25 @@
         <v>1.3</v>
       </c>
       <c r="AN33">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AO33">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ33">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR33">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AS33">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="AT33">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="AU33">
         <v>5</v>
@@ -8138,25 +8144,25 @@
         <v>1.91</v>
       </c>
       <c r="AN34">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO34">
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ34">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="AS34">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AT34">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="AU34">
         <v>2</v>
@@ -8344,25 +8350,25 @@
         <v>1.62</v>
       </c>
       <c r="AN35">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO35">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ35">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR35">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AS35">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AT35">
-        <v>3.39</v>
+        <v>3.52</v>
       </c>
       <c r="AU35">
         <v>7</v>
@@ -8478,7 +8484,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8550,25 +8556,25 @@
         <v>1.55</v>
       </c>
       <c r="AN36">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ36">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR36">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AS36">
-        <v>1.7</v>
+        <v>1.08</v>
       </c>
       <c r="AT36">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8684,7 +8690,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8756,25 +8762,25 @@
         <v>1.87</v>
       </c>
       <c r="AN37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ37">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AS37">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT37">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="AU37">
         <v>4</v>
@@ -8890,7 +8896,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8962,25 +8968,25 @@
         <v>1.3</v>
       </c>
       <c r="AN38">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="AO38">
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ38">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR38">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AS38">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AT38">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AU38">
         <v>9</v>
@@ -9096,7 +9102,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9168,25 +9174,25 @@
         <v>1.75</v>
       </c>
       <c r="AN39">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO39">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR39">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="AS39">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AT39">
-        <v>3.67</v>
+        <v>4.01</v>
       </c>
       <c r="AU39">
         <v>2</v>
@@ -9302,7 +9308,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9374,25 +9380,25 @@
         <v>2.3</v>
       </c>
       <c r="AN40">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO40">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ40">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR40">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AS40">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AT40">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9580,25 +9586,25 @@
         <v>1.43</v>
       </c>
       <c r="AN41">
+        <v>2.33</v>
+      </c>
+      <c r="AO41">
+        <v>3</v>
+      </c>
+      <c r="AP41">
         <v>1.67</v>
       </c>
-      <c r="AO41">
-        <v>2.17</v>
-      </c>
-      <c r="AP41">
-        <v>1.2</v>
-      </c>
       <c r="AQ41">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR41">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AS41">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AT41">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="AU41">
         <v>2</v>
@@ -9714,7 +9720,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9786,25 +9792,25 @@
         <v>1.17</v>
       </c>
       <c r="AN42">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="AO42">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ42">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR42">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AS42">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AT42">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9920,7 +9926,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -9992,25 +9998,25 @@
         <v>1.77</v>
       </c>
       <c r="AN43">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO43">
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
       </c>
       <c r="AS43">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AT43">
-        <v>3.39</v>
+        <v>3.22</v>
       </c>
       <c r="AU43">
         <v>8</v>
@@ -10198,25 +10204,25 @@
         <v>1.22</v>
       </c>
       <c r="AN44">
-        <v>0.71</v>
+        <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AP44">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR44">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AS44">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AT44">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="AU44">
         <v>2</v>
@@ -10404,25 +10410,25 @@
         <v>1.9</v>
       </c>
       <c r="AN45">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AO45">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
+        <v>0.92</v>
+      </c>
+      <c r="AR45">
+        <v>2.03</v>
+      </c>
+      <c r="AS45">
         <v>1.48</v>
       </c>
-      <c r="AR45">
-        <v>1.75</v>
-      </c>
-      <c r="AS45">
-        <v>1.59</v>
-      </c>
       <c r="AT45">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10538,7 +10544,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10610,25 +10616,25 @@
         <v>2.45</v>
       </c>
       <c r="AN46">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AO46">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR46">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AS46">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AT46">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AU46">
         <v>5</v>
@@ -10816,25 +10822,25 @@
         <v>2.11</v>
       </c>
       <c r="AN47">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO47">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ47">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR47">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AS47">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT47">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="AU47">
         <v>3</v>
@@ -11025,22 +11031,22 @@
         <v>2</v>
       </c>
       <c r="AO48">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AP48">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR48">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AS48">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AT48">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="AU48">
         <v>11</v>
@@ -11156,7 +11162,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11228,25 +11234,25 @@
         <v>2.42</v>
       </c>
       <c r="AN49">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO49">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ49">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR49">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="AS49">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AT49">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="AU49">
         <v>8</v>
@@ -11362,7 +11368,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11434,25 +11440,25 @@
         <v>2.3</v>
       </c>
       <c r="AN50">
+        <v>2</v>
+      </c>
+      <c r="AO50">
+        <v>0.25</v>
+      </c>
+      <c r="AP50">
+        <v>1.67</v>
+      </c>
+      <c r="AQ50">
+        <v>0.54</v>
+      </c>
+      <c r="AR50">
         <v>1.38</v>
       </c>
-      <c r="AO50">
-        <v>1</v>
-      </c>
-      <c r="AP50">
-        <v>1.2</v>
-      </c>
-      <c r="AQ50">
-        <v>0.96</v>
-      </c>
-      <c r="AR50">
-        <v>1.4</v>
-      </c>
       <c r="AS50">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AT50">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11568,7 +11574,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11640,25 +11646,25 @@
         <v>1.65</v>
       </c>
       <c r="AN51">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AO51">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS51">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AT51">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11846,25 +11852,25 @@
         <v>1.38</v>
       </c>
       <c r="AN52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP52">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR52">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AS52">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AT52">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="AU52">
         <v>7</v>
@@ -12052,25 +12058,25 @@
         <v>1.62</v>
       </c>
       <c r="AN53">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AO53">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ53">
+        <v>1.25</v>
+      </c>
+      <c r="AR53">
         <v>1.68</v>
       </c>
-      <c r="AR53">
-        <v>1.54</v>
-      </c>
       <c r="AS53">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AT53">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12258,25 +12264,25 @@
         <v>1.5</v>
       </c>
       <c r="AN54">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO54">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR54">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AS54">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AT54">
-        <v>3.32</v>
+        <v>3.66</v>
       </c>
       <c r="AU54">
         <v>7</v>
@@ -12392,7 +12398,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12464,25 +12470,25 @@
         <v>1.65</v>
       </c>
       <c r="AN55">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AO55">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ55">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR55">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AS55">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AT55">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12598,7 +12604,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12670,25 +12676,25 @@
         <v>1.42</v>
       </c>
       <c r="AN56">
-        <v>0.89</v>
+        <v>1.25</v>
       </c>
       <c r="AO56">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ56">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR56">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AS56">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AT56">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AU56">
         <v>4</v>
@@ -12876,25 +12882,25 @@
         <v>1.83</v>
       </c>
       <c r="AN57">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO57">
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ57">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AS57">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AT57">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="AU57">
         <v>6</v>
@@ -13082,25 +13088,25 @@
         <v>1.95</v>
       </c>
       <c r="AN58">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AO58">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR58">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AS58">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AT58">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="AU58">
         <v>7</v>
@@ -13216,7 +13222,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13288,25 +13294,25 @@
         <v>1.7</v>
       </c>
       <c r="AN59">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO59">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR59">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AS59">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AT59">
-        <v>3.24</v>
+        <v>3.41</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13494,25 +13500,25 @@
         <v>2.5</v>
       </c>
       <c r="AN60">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ60">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR60">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AS60">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT60">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13700,25 +13706,25 @@
         <v>1.1</v>
       </c>
       <c r="AN61">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AO61">
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ61">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR61">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AS61">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AT61">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="AU61">
         <v>5</v>
@@ -13906,25 +13912,25 @@
         <v>1.83</v>
       </c>
       <c r="AN62">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AO62">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ62">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR62">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AS62">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AT62">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="AU62">
         <v>9</v>
@@ -14040,7 +14046,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14112,25 +14118,25 @@
         <v>1.22</v>
       </c>
       <c r="AN63">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="AO63">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ63">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR63">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AS63">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AT63">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14246,7 +14252,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14318,25 +14324,25 @@
         <v>2.7</v>
       </c>
       <c r="AN64">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO64">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="AP64">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR64">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AS64">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT64">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AU64">
         <v>10</v>
@@ -14452,7 +14458,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14524,25 +14530,25 @@
         <v>1.6</v>
       </c>
       <c r="AN65">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO65">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ65">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR65">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AS65">
         <v>1.59</v>
       </c>
       <c r="AT65">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14730,25 +14736,25 @@
         <v>1.62</v>
       </c>
       <c r="AN66">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO66">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ66">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR66">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AS66">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AT66">
-        <v>3.43</v>
+        <v>3.59</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14864,7 +14870,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14936,25 +14942,25 @@
         <v>1.53</v>
       </c>
       <c r="AN67">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AO67">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ67">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR67">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS67">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AT67">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -15070,7 +15076,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15142,25 +15148,25 @@
         <v>1.2</v>
       </c>
       <c r="AN68">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AO68">
-        <v>1.27</v>
+        <v>0.4</v>
       </c>
       <c r="AP68">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ68">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR68">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AS68">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AT68">
-        <v>2.79</v>
+        <v>2.48</v>
       </c>
       <c r="AU68">
         <v>2</v>
@@ -15276,7 +15282,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15348,25 +15354,25 @@
         <v>1.55</v>
       </c>
       <c r="AN69">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AO69">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR69">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS69">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AT69">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15482,7 +15488,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15554,25 +15560,25 @@
         <v>2.8</v>
       </c>
       <c r="AN70">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AO70">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ70">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR70">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AS70">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AT70">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15688,7 +15694,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15760,25 +15766,25 @@
         <v>1.75</v>
       </c>
       <c r="AN71">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ71">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR71">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AS71">
         <v>1.68</v>
       </c>
       <c r="AT71">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15966,25 +15972,25 @@
         <v>1.35</v>
       </c>
       <c r="AN72">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO72">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ72">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AS72">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AT72">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16100,7 +16106,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16172,25 +16178,25 @@
         <v>1.9</v>
       </c>
       <c r="AN73">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AO73">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR73">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AS73">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT73">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16378,25 +16384,25 @@
         <v>1.55</v>
       </c>
       <c r="AN74">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO74">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR74">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AS74">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AT74">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16584,25 +16590,25 @@
         <v>2.85</v>
       </c>
       <c r="AN75">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AO75">
-        <v>0.67</v>
+        <v>0.17</v>
       </c>
       <c r="AP75">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
       </c>
       <c r="AS75">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT75">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="AU75">
         <v>10</v>
@@ -16718,7 +16724,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16790,25 +16796,25 @@
         <v>1.72</v>
       </c>
       <c r="AN76">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AO76">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ76">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR76">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AS76">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT76">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16996,25 +17002,25 @@
         <v>1.45</v>
       </c>
       <c r="AN77">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AO77">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ77">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR77">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AS77">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AT77">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="AU77">
         <v>4</v>
@@ -17202,25 +17208,25 @@
         <v>3</v>
       </c>
       <c r="AN78">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AO78">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ78">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR78">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AS78">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AT78">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17408,25 +17414,25 @@
         <v>1.87</v>
       </c>
       <c r="AN79">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AO79">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR79">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AS79">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AT79">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AU79">
         <v>7</v>
@@ -17614,25 +17620,25 @@
         <v>1.22</v>
       </c>
       <c r="AN80">
-        <v>0.62</v>
+        <v>1.17</v>
       </c>
       <c r="AO80">
-        <v>1.54</v>
+        <v>0.83</v>
       </c>
       <c r="AP80">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ80">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR80">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AS80">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AT80">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17748,7 +17754,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17820,25 +17826,25 @@
         <v>1.17</v>
       </c>
       <c r="AN81">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="AO81">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AP81">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ81">
+        <v>1.46</v>
+      </c>
+      <c r="AR81">
+        <v>0.99</v>
+      </c>
+      <c r="AS81">
         <v>1.68</v>
       </c>
-      <c r="AR81">
-        <v>1.09</v>
-      </c>
-      <c r="AS81">
-        <v>1.73</v>
-      </c>
       <c r="AT81">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17954,7 +17960,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18026,25 +18032,25 @@
         <v>1.8</v>
       </c>
       <c r="AN82">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AO82">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AP82">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR82">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AS82">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AT82">
-        <v>3.27</v>
+        <v>3.53</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18160,7 +18166,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18232,25 +18238,25 @@
         <v>1.65</v>
       </c>
       <c r="AN83">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="AO83">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ83">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AS83">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AT83">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="AU83">
         <v>11</v>
@@ -18366,7 +18372,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18438,25 +18444,25 @@
         <v>1.45</v>
       </c>
       <c r="AN84">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="AO84">
-        <v>1.31</v>
+        <v>0.83</v>
       </c>
       <c r="AP84">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ84">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR84">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS84">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AT84">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="AU84">
         <v>6</v>
@@ -18572,7 +18578,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18644,25 +18650,25 @@
         <v>1.67</v>
       </c>
       <c r="AN85">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO85">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ85">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR85">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AS85">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AT85">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18778,7 +18784,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18850,25 +18856,25 @@
         <v>1.55</v>
       </c>
       <c r="AN86">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AO86">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="AP86">
+        <v>2</v>
+      </c>
+      <c r="AQ86">
+        <v>0.83</v>
+      </c>
+      <c r="AR86">
+        <v>1.7</v>
+      </c>
+      <c r="AS86">
         <v>1.68</v>
       </c>
-      <c r="AQ86">
-        <v>1.48</v>
-      </c>
-      <c r="AR86">
-        <v>1.59</v>
-      </c>
-      <c r="AS86">
-        <v>1.7</v>
-      </c>
       <c r="AT86">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -18984,7 +18990,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19056,25 +19062,25 @@
         <v>2.3</v>
       </c>
       <c r="AN87">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="AO87">
-        <v>0.79</v>
+        <v>0.14</v>
       </c>
       <c r="AP87">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ87">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR87">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AS87">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AT87">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AU87">
         <v>6</v>
@@ -19262,25 +19268,25 @@
         <v>1.95</v>
       </c>
       <c r="AN88">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="AO88">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ88">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR88">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AS88">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT88">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="AU88">
         <v>-1</v>
@@ -19468,25 +19474,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="AO89">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP89">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR89">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AS89">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AT89">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="AU89">
         <v>12</v>
@@ -19674,25 +19680,25 @@
         <v>2.7</v>
       </c>
       <c r="AN90">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AO90">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="AP90">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ90">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR90">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AS90">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AT90">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AU90">
         <v>8</v>
@@ -19880,25 +19886,25 @@
         <v>1.7</v>
       </c>
       <c r="AN91">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AO91">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AP91">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ91">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR91">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AS91">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AT91">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AU91">
         <v>8</v>
@@ -20086,25 +20092,25 @@
         <v>1.85</v>
       </c>
       <c r="AN92">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AO92">
-        <v>1.53</v>
+        <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR92">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AS92">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AT92">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20292,25 +20298,25 @@
         <v>1.22</v>
       </c>
       <c r="AN93">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="AO93">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ93">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="AS93">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT93">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20426,7 +20432,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20498,25 +20504,25 @@
         <v>1.93</v>
       </c>
       <c r="AN94">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AO94">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ94">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR94">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AS94">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AT94">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AU94">
         <v>3</v>
@@ -20632,7 +20638,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20704,25 +20710,25 @@
         <v>1.22</v>
       </c>
       <c r="AN95">
-        <v>0.8</v>
+        <v>1.43</v>
       </c>
       <c r="AO95">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ95">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR95">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AS95">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT95">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20910,25 +20916,25 @@
         <v>1.75</v>
       </c>
       <c r="AN96">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO96">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR96">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AS96">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AT96">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="AU96">
         <v>11</v>
@@ -21044,7 +21050,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21116,25 +21122,25 @@
         <v>1.95</v>
       </c>
       <c r="AN97">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AO97">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ97">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR97">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AS97">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AT97">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AU97">
         <v>13</v>
@@ -21250,7 +21256,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21322,25 +21328,25 @@
         <v>2.25</v>
       </c>
       <c r="AN98">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AO98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ98">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR98">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS98">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AT98">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21456,7 +21462,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21528,25 +21534,25 @@
         <v>1.42</v>
       </c>
       <c r="AN99">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO99">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR99">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AS99">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AT99">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="AU99">
         <v>7</v>
@@ -21662,7 +21668,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21734,25 +21740,25 @@
         <v>1.45</v>
       </c>
       <c r="AN100">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO100">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR100">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AS100">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AT100">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21940,25 +21946,25 @@
         <v>1.75</v>
       </c>
       <c r="AN101">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AO101">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ101">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR101">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AS101">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT101">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="AU101">
         <v>6</v>
@@ -22074,7 +22080,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22146,25 +22152,25 @@
         <v>3.3</v>
       </c>
       <c r="AN102">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO102">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ102">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR102">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AS102">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AT102">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22280,7 +22286,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22352,25 +22358,25 @@
         <v>1.45</v>
       </c>
       <c r="AN103">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AO103">
+        <v>1.63</v>
+      </c>
+      <c r="AP103">
+        <v>1.75</v>
+      </c>
+      <c r="AQ103">
+        <v>1.46</v>
+      </c>
+      <c r="AR103">
         <v>1.81</v>
       </c>
-      <c r="AP103">
-        <v>1.44</v>
-      </c>
-      <c r="AQ103">
-        <v>1.68</v>
-      </c>
-      <c r="AR103">
-        <v>1.64</v>
-      </c>
       <c r="AS103">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AT103">
-        <v>3.39</v>
+        <v>3.58</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22486,7 +22492,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22558,25 +22564,25 @@
         <v>1.3</v>
       </c>
       <c r="AN104">
-        <v>0.76</v>
+        <v>1.25</v>
       </c>
       <c r="AO104">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ104">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AS104">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AT104">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22692,7 +22698,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22764,25 +22770,25 @@
         <v>1.2</v>
       </c>
       <c r="AN105">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO105">
-        <v>1.35</v>
+        <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ105">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR105">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="AS105">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AT105">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="AU105">
         <v>3</v>
@@ -22970,25 +22976,25 @@
         <v>2.2</v>
       </c>
       <c r="AN106">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AO106">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR106">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS106">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AT106">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="AU106">
         <v>7</v>
@@ -23104,7 +23110,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23176,25 +23182,25 @@
         <v>1.62</v>
       </c>
       <c r="AN107">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AO107">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ107">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR107">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AS107">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AT107">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="AU107">
         <v>9</v>
@@ -23310,7 +23316,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23382,25 +23388,25 @@
         <v>1.75</v>
       </c>
       <c r="AN108">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="AO108">
-        <v>1.59</v>
+        <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ108">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR108">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AS108">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AT108">
-        <v>3.39</v>
+        <v>3.49</v>
       </c>
       <c r="AU108">
         <v>6</v>
@@ -23516,7 +23522,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23588,25 +23594,25 @@
         <v>1.62</v>
       </c>
       <c r="AN109">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AO109">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ109">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR109">
+        <v>1.41</v>
+      </c>
+      <c r="AS109">
         <v>1.46</v>
       </c>
-      <c r="AS109">
-        <v>1.62</v>
-      </c>
       <c r="AT109">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23794,25 +23800,25 @@
         <v>3.3</v>
       </c>
       <c r="AN110">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="AO110">
-        <v>0.72</v>
+        <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ110">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR110">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AS110">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AT110">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AU110">
         <v>9</v>
@@ -23928,7 +23934,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24000,25 +24006,25 @@
         <v>1.77</v>
       </c>
       <c r="AN111">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AO111">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ111">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR111">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AS111">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AT111">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AU111">
         <v>7</v>
@@ -24206,25 +24212,25 @@
         <v>2.05</v>
       </c>
       <c r="AN112">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AO112">
+        <v>1.22</v>
+      </c>
+      <c r="AP112">
+        <v>2</v>
+      </c>
+      <c r="AQ112">
+        <v>1.07</v>
+      </c>
+      <c r="AR112">
+        <v>1.84</v>
+      </c>
+      <c r="AS112">
         <v>1.39</v>
       </c>
-      <c r="AP112">
-        <v>1.68</v>
-      </c>
-      <c r="AQ112">
-        <v>1.44</v>
-      </c>
-      <c r="AR112">
-        <v>1.68</v>
-      </c>
-      <c r="AS112">
-        <v>1.58</v>
-      </c>
       <c r="AT112">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24412,25 +24418,25 @@
         <v>2.65</v>
       </c>
       <c r="AN113">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AO113">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ113">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR113">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AS113">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AT113">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AU113">
         <v>4</v>
@@ -24546,7 +24552,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24618,25 +24624,25 @@
         <v>1.57</v>
       </c>
       <c r="AN114">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AO114">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AP114">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ114">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR114">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AS114">
         <v>1.76</v>
       </c>
       <c r="AT114">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
       <c r="AU114">
         <v>6</v>
@@ -24824,25 +24830,25 @@
         <v>1.85</v>
       </c>
       <c r="AN115">
+        <v>2.33</v>
+      </c>
+      <c r="AO115">
         <v>1.67</v>
       </c>
-      <c r="AO115">
-        <v>1.61</v>
-      </c>
       <c r="AP115">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ115">
+        <v>1.33</v>
+      </c>
+      <c r="AR115">
+        <v>1.76</v>
+      </c>
+      <c r="AS115">
         <v>1.68</v>
       </c>
-      <c r="AR115">
-        <v>1.68</v>
-      </c>
-      <c r="AS115">
-        <v>1.67</v>
-      </c>
       <c r="AT115">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -25030,25 +25036,25 @@
         <v>1.36</v>
       </c>
       <c r="AN116">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AO116">
-        <v>1.26</v>
+        <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ116">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR116">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AS116">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AT116">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="AU116">
         <v>7</v>
@@ -25236,25 +25242,25 @@
         <v>1.09</v>
       </c>
       <c r="AN117">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AO117">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AP117">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ117">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR117">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AS117">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AT117">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="AU117">
         <v>3</v>
@@ -25370,7 +25376,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25442,25 +25448,25 @@
         <v>1.22</v>
       </c>
       <c r="AN118">
-        <v>0.74</v>
+        <v>1.11</v>
       </c>
       <c r="AO118">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ118">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR118">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AS118">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AT118">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25576,7 +25582,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25648,25 +25654,25 @@
         <v>1.5</v>
       </c>
       <c r="AN119">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AO119">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR119">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AS119">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AT119">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="AU119">
         <v>12</v>
@@ -25782,7 +25788,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25854,25 +25860,25 @@
         <v>2.1</v>
       </c>
       <c r="AN120">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AO120">
+        <v>1.11</v>
+      </c>
+      <c r="AP120">
+        <v>2</v>
+      </c>
+      <c r="AQ120">
+        <v>0.71</v>
+      </c>
+      <c r="AR120">
+        <v>1.76</v>
+      </c>
+      <c r="AS120">
         <v>1.37</v>
       </c>
-      <c r="AP120">
-        <v>1.68</v>
-      </c>
-      <c r="AQ120">
-        <v>1.2</v>
-      </c>
-      <c r="AR120">
-        <v>1.78</v>
-      </c>
-      <c r="AS120">
-        <v>1.56</v>
-      </c>
       <c r="AT120">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26060,25 +26066,25 @@
         <v>1.67</v>
       </c>
       <c r="AN121">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AO121">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AP121">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR121">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AS121">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AT121">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="AU121">
         <v>6</v>
@@ -26194,7 +26200,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26266,25 +26272,25 @@
         <v>1.55</v>
       </c>
       <c r="AN122">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AO122">
-        <v>1.25</v>
+        <v>0.7</v>
       </c>
       <c r="AP122">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ122">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR122">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AS122">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AT122">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26400,7 +26406,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26472,25 +26478,25 @@
         <v>1.93</v>
       </c>
       <c r="AN123">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO123">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ123">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR123">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AS123">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT123">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="AU123">
         <v>6</v>
@@ -26678,25 +26684,25 @@
         <v>2.25</v>
       </c>
       <c r="AN124">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AO124">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR124">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AS124">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT124">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26884,25 +26890,25 @@
         <v>1.67</v>
       </c>
       <c r="AN125">
+        <v>1.7</v>
+      </c>
+      <c r="AO125">
+        <v>1.2</v>
+      </c>
+      <c r="AP125">
+        <v>2</v>
+      </c>
+      <c r="AQ125">
+        <v>1.07</v>
+      </c>
+      <c r="AR125">
         <v>1.65</v>
       </c>
-      <c r="AO125">
-        <v>1.45</v>
-      </c>
-      <c r="AP125">
-        <v>1.68</v>
-      </c>
-      <c r="AQ125">
-        <v>1.44</v>
-      </c>
-      <c r="AR125">
-        <v>1.62</v>
-      </c>
       <c r="AS125">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AT125">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="AU125">
         <v>8</v>
@@ -27018,7 +27024,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27090,25 +27096,25 @@
         <v>1.3</v>
       </c>
       <c r="AN126">
+        <v>1.6</v>
+      </c>
+      <c r="AO126">
         <v>1.5</v>
       </c>
-      <c r="AO126">
-        <v>1.7</v>
-      </c>
       <c r="AP126">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ126">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR126">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AS126">
         <v>1.8</v>
       </c>
       <c r="AT126">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27296,25 +27302,25 @@
         <v>1.55</v>
       </c>
       <c r="AN127">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AO127">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AP127">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ127">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR127">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AS127">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AT127">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AU127">
         <v>4</v>
@@ -27430,7 +27436,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27502,22 +27508,22 @@
         <v>1.36</v>
       </c>
       <c r="AN128">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AO128">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="AP128">
+        <v>0.83</v>
+      </c>
+      <c r="AQ128">
         <v>0.92</v>
       </c>
-      <c r="AQ128">
-        <v>1.48</v>
-      </c>
       <c r="AR128">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AS128">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AT128">
         <v>3.11</v>
@@ -27636,7 +27642,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27708,25 +27714,25 @@
         <v>1.35</v>
       </c>
       <c r="AN129">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AO129">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR129">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AS129">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AT129">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="AU129">
         <v>8</v>
@@ -27842,7 +27848,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27914,25 +27920,25 @@
         <v>1.52</v>
       </c>
       <c r="AN130">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AO130">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AP130">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AQ130">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR130">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AS130">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AT130">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28048,7 +28054,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28120,25 +28126,25 @@
         <v>3.3</v>
       </c>
       <c r="AN131">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AO131">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP131">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ131">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR131">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AS131">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AT131">
-        <v>2.94</v>
+        <v>3.16</v>
       </c>
       <c r="AU131">
         <v>11</v>
@@ -28326,25 +28332,25 @@
         <v>2.15</v>
       </c>
       <c r="AN132">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AO132">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
       </c>
       <c r="AS132">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AT132">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28460,7 +28466,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28532,25 +28538,25 @@
         <v>1.31</v>
       </c>
       <c r="AN133">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO133">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AP133">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ133">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR133">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS133">
         <v>1.48</v>
       </c>
       <c r="AT133">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28666,7 +28672,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28738,25 +28744,25 @@
         <v>2.95</v>
       </c>
       <c r="AN134">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AO134">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="AP134">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ134">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR134">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AS134">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AT134">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -28872,7 +28878,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -28944,25 +28950,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AO135">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AQ135">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR135">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AS135">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AT135">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="AU135">
         <v>12</v>
@@ -29078,7 +29084,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29150,25 +29156,25 @@
         <v>2.1</v>
       </c>
       <c r="AN136">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AO136">
-        <v>1.23</v>
+        <v>0.91</v>
       </c>
       <c r="AP136">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ136">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR136">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AS136">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AT136">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="AU136">
         <v>9</v>
@@ -29284,7 +29290,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29356,25 +29362,25 @@
         <v>1.62</v>
       </c>
       <c r="AN137">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AO137">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AP137">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ137">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
+        <v>1.97</v>
+      </c>
+      <c r="AS137">
         <v>1.81</v>
       </c>
-      <c r="AS137">
-        <v>1.8</v>
-      </c>
       <c r="AT137">
-        <v>3.61</v>
+        <v>3.78</v>
       </c>
       <c r="AU137">
         <v>4</v>
@@ -29490,7 +29496,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29562,25 +29568,25 @@
         <v>2.35</v>
       </c>
       <c r="AN138">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AO138">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="AP138">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR138">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS138">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AT138">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AU138">
         <v>12</v>
@@ -29696,7 +29702,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29768,25 +29774,25 @@
         <v>1.55</v>
       </c>
       <c r="AN139">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AO139">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AP139">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ139">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR139">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS139">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AT139">
-        <v>3.17</v>
+        <v>2.89</v>
       </c>
       <c r="AU139">
         <v>3</v>
@@ -29974,25 +29980,25 @@
         <v>1.8</v>
       </c>
       <c r="AN140">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AO140">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AP140">
+        <v>2.08</v>
+      </c>
+      <c r="AQ140">
+        <v>1.33</v>
+      </c>
+      <c r="AR140">
+        <v>1.98</v>
+      </c>
+      <c r="AS140">
         <v>1.68</v>
       </c>
-      <c r="AQ140">
-        <v>1.68</v>
-      </c>
-      <c r="AR140">
-        <v>1.78</v>
-      </c>
-      <c r="AS140">
-        <v>1.74</v>
-      </c>
       <c r="AT140">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30180,25 +30186,25 @@
         <v>1.6</v>
       </c>
       <c r="AN141">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="AO141">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AP141">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ141">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR141">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AS141">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AT141">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="AU141">
         <v>6</v>
@@ -30386,25 +30392,25 @@
         <v>1.15</v>
       </c>
       <c r="AN142">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="AO142">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="AP142">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="AQ142">
-        <v>1.48</v>
+        <v>0.83</v>
       </c>
       <c r="AR142">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AS142">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AT142">
-        <v>3.17</v>
+        <v>2.98</v>
       </c>
       <c r="AU142">
         <v>5</v>
@@ -30592,25 +30598,25 @@
         <v>1.21</v>
       </c>
       <c r="AN143">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
       <c r="AO143">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AP143">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="AQ143">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AR143">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AS143">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AT143">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="AU143">
         <v>9</v>
@@ -30726,7 +30732,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30798,25 +30804,25 @@
         <v>1.74</v>
       </c>
       <c r="AN144">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AO144">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AP144">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="AR144">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AS144">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AT144">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="AU144">
         <v>10</v>
@@ -30932,7 +30938,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31004,25 +31010,25 @@
         <v>1.34</v>
       </c>
       <c r="AN145">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="AO145">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AP145">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AQ145">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR145">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AS145">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT145">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31138,7 +31144,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31210,25 +31216,25 @@
         <v>2.1</v>
       </c>
       <c r="AN146">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="AO146">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AQ146">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR146">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AS146">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AT146">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="AU146">
         <v>6</v>
@@ -31344,7 +31350,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31416,25 +31422,25 @@
         <v>2.3</v>
       </c>
       <c r="AN147">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AO147">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="AP147">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AQ147">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="AR147">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AS147">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AT147">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31550,7 +31556,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31622,25 +31628,25 @@
         <v>1.48</v>
       </c>
       <c r="AN148">
+        <v>1.82</v>
+      </c>
+      <c r="AO148">
+        <v>1.5</v>
+      </c>
+      <c r="AP148">
+        <v>1.75</v>
+      </c>
+      <c r="AQ148">
         <v>1.46</v>
       </c>
-      <c r="AO148">
-        <v>1.71</v>
-      </c>
-      <c r="AP148">
-        <v>1.44</v>
-      </c>
-      <c r="AQ148">
-        <v>1.68</v>
-      </c>
       <c r="AR148">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AS148">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AT148">
-        <v>3.45</v>
+        <v>3.68</v>
       </c>
       <c r="AU148">
         <v>8</v>
@@ -31756,7 +31762,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -31828,25 +31834,25 @@
         <v>1.71</v>
       </c>
       <c r="AN149">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AO149">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="AP149">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ149">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AR149">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AS149">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AT149">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="AU149">
         <v>3</v>
@@ -32034,25 +32040,25 @@
         <v>1.79</v>
       </c>
       <c r="AN150">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AO150">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AP150">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="AQ150">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AR150">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AS150">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AT150">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32168,7 +32174,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32240,25 +32246,25 @@
         <v>3</v>
       </c>
       <c r="AN151">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AO151">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AP151">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
-        <v>0.68</v>
+        <v>0.31</v>
       </c>
       <c r="AR151">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AS151">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AT151">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="AU151">
         <v>12</v>
@@ -32325,6 +32331,624 @@
       </c>
       <c r="BP151">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7784933</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45717.58333333334</v>
+      </c>
+      <c r="F152">
+        <v>26</v>
+      </c>
+      <c r="G152" t="s">
+        <v>79</v>
+      </c>
+      <c r="H152" t="s">
+        <v>77</v>
+      </c>
+      <c r="I152">
+        <v>2</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>2</v>
+      </c>
+      <c r="L152">
+        <v>2</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152" t="s">
+        <v>197</v>
+      </c>
+      <c r="P152" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q152">
+        <v>2.16</v>
+      </c>
+      <c r="R152">
+        <v>2.39</v>
+      </c>
+      <c r="S152">
+        <v>4.9</v>
+      </c>
+      <c r="T152">
+        <v>1.31</v>
+      </c>
+      <c r="U152">
+        <v>3.15</v>
+      </c>
+      <c r="V152">
+        <v>2.4</v>
+      </c>
+      <c r="W152">
+        <v>1.51</v>
+      </c>
+      <c r="X152">
+        <v>5.5</v>
+      </c>
+      <c r="Y152">
+        <v>1.12</v>
+      </c>
+      <c r="Z152">
+        <v>1.67</v>
+      </c>
+      <c r="AA152">
+        <v>3.94</v>
+      </c>
+      <c r="AB152">
+        <v>4.6</v>
+      </c>
+      <c r="AC152">
+        <v>1.04</v>
+      </c>
+      <c r="AD152">
+        <v>10</v>
+      </c>
+      <c r="AE152">
+        <v>1.22</v>
+      </c>
+      <c r="AF152">
+        <v>3.95</v>
+      </c>
+      <c r="AG152">
+        <v>1.65</v>
+      </c>
+      <c r="AH152">
+        <v>2.05</v>
+      </c>
+      <c r="AI152">
+        <v>1.69</v>
+      </c>
+      <c r="AJ152">
+        <v>2.05</v>
+      </c>
+      <c r="AK152">
+        <v>1.19</v>
+      </c>
+      <c r="AL152">
+        <v>1.22</v>
+      </c>
+      <c r="AM152">
+        <v>2.1</v>
+      </c>
+      <c r="AN152">
+        <v>1.92</v>
+      </c>
+      <c r="AO152">
+        <v>0.77</v>
+      </c>
+      <c r="AP152">
+        <v>2</v>
+      </c>
+      <c r="AQ152">
+        <v>0.71</v>
+      </c>
+      <c r="AR152">
+        <v>1.84</v>
+      </c>
+      <c r="AS152">
+        <v>1.47</v>
+      </c>
+      <c r="AT152">
+        <v>3.31</v>
+      </c>
+      <c r="AU152">
+        <v>7</v>
+      </c>
+      <c r="AV152">
+        <v>6</v>
+      </c>
+      <c r="AW152">
+        <v>7</v>
+      </c>
+      <c r="AX152">
+        <v>6</v>
+      </c>
+      <c r="AY152">
+        <v>16</v>
+      </c>
+      <c r="AZ152">
+        <v>13</v>
+      </c>
+      <c r="BA152">
+        <v>10</v>
+      </c>
+      <c r="BB152">
+        <v>2</v>
+      </c>
+      <c r="BC152">
+        <v>12</v>
+      </c>
+      <c r="BD152">
+        <v>1.5</v>
+      </c>
+      <c r="BE152">
+        <v>7</v>
+      </c>
+      <c r="BF152">
+        <v>2.8</v>
+      </c>
+      <c r="BG152">
+        <v>1.27</v>
+      </c>
+      <c r="BH152">
+        <v>3.3</v>
+      </c>
+      <c r="BI152">
+        <v>1.47</v>
+      </c>
+      <c r="BJ152">
+        <v>2.43</v>
+      </c>
+      <c r="BK152">
+        <v>1.77</v>
+      </c>
+      <c r="BL152">
+        <v>1.9</v>
+      </c>
+      <c r="BM152">
+        <v>2.18</v>
+      </c>
+      <c r="BN152">
+        <v>1.58</v>
+      </c>
+      <c r="BO152">
+        <v>2.8</v>
+      </c>
+      <c r="BP152">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7784934</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45717.58333333334</v>
+      </c>
+      <c r="F153">
+        <v>26</v>
+      </c>
+      <c r="G153" t="s">
+        <v>72</v>
+      </c>
+      <c r="H153" t="s">
+        <v>80</v>
+      </c>
+      <c r="I153">
+        <v>3</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>3</v>
+      </c>
+      <c r="L153">
+        <v>4</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>4</v>
+      </c>
+      <c r="O153" t="s">
+        <v>198</v>
+      </c>
+      <c r="P153" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q153">
+        <v>3.95</v>
+      </c>
+      <c r="R153">
+        <v>2.25</v>
+      </c>
+      <c r="S153">
+        <v>2.35</v>
+      </c>
+      <c r="T153">
+        <v>1.28</v>
+      </c>
+      <c r="U153">
+        <v>3.3</v>
+      </c>
+      <c r="V153">
+        <v>2.3</v>
+      </c>
+      <c r="W153">
+        <v>1.55</v>
+      </c>
+      <c r="X153">
+        <v>5.25</v>
+      </c>
+      <c r="Y153">
+        <v>1.1</v>
+      </c>
+      <c r="Z153">
+        <v>3.74</v>
+      </c>
+      <c r="AA153">
+        <v>3.95</v>
+      </c>
+      <c r="AB153">
+        <v>1.82</v>
+      </c>
+      <c r="AC153">
+        <v>1.04</v>
+      </c>
+      <c r="AD153">
+        <v>10</v>
+      </c>
+      <c r="AE153">
+        <v>1.2</v>
+      </c>
+      <c r="AF153">
+        <v>4.33</v>
+      </c>
+      <c r="AG153">
+        <v>1.57</v>
+      </c>
+      <c r="AH153">
+        <v>2.32</v>
+      </c>
+      <c r="AI153">
+        <v>1.5</v>
+      </c>
+      <c r="AJ153">
+        <v>2.35</v>
+      </c>
+      <c r="AK153">
+        <v>1.9</v>
+      </c>
+      <c r="AL153">
+        <v>1.2</v>
+      </c>
+      <c r="AM153">
+        <v>1.25</v>
+      </c>
+      <c r="AN153">
+        <v>1.08</v>
+      </c>
+      <c r="AO153">
+        <v>1.15</v>
+      </c>
+      <c r="AP153">
+        <v>1.23</v>
+      </c>
+      <c r="AQ153">
+        <v>1.07</v>
+      </c>
+      <c r="AR153">
+        <v>1.28</v>
+      </c>
+      <c r="AS153">
+        <v>1.42</v>
+      </c>
+      <c r="AT153">
+        <v>2.7</v>
+      </c>
+      <c r="AU153">
+        <v>7</v>
+      </c>
+      <c r="AV153">
+        <v>5</v>
+      </c>
+      <c r="AW153">
+        <v>8</v>
+      </c>
+      <c r="AX153">
+        <v>16</v>
+      </c>
+      <c r="AY153">
+        <v>17</v>
+      </c>
+      <c r="AZ153">
+        <v>21</v>
+      </c>
+      <c r="BA153">
+        <v>3</v>
+      </c>
+      <c r="BB153">
+        <v>4</v>
+      </c>
+      <c r="BC153">
+        <v>7</v>
+      </c>
+      <c r="BD153">
+        <v>2.4</v>
+      </c>
+      <c r="BE153">
+        <v>6.75</v>
+      </c>
+      <c r="BF153">
+        <v>1.68</v>
+      </c>
+      <c r="BG153">
+        <v>1.27</v>
+      </c>
+      <c r="BH153">
+        <v>3.3</v>
+      </c>
+      <c r="BI153">
+        <v>1.46</v>
+      </c>
+      <c r="BJ153">
+        <v>2.43</v>
+      </c>
+      <c r="BK153">
+        <v>1.76</v>
+      </c>
+      <c r="BL153">
+        <v>1.91</v>
+      </c>
+      <c r="BM153">
+        <v>2.18</v>
+      </c>
+      <c r="BN153">
+        <v>1.58</v>
+      </c>
+      <c r="BO153">
+        <v>2.8</v>
+      </c>
+      <c r="BP153">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7784935</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45717.6875</v>
+      </c>
+      <c r="F154">
+        <v>26</v>
+      </c>
+      <c r="G154" t="s">
+        <v>74</v>
+      </c>
+      <c r="H154" t="s">
+        <v>76</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="O154" t="s">
+        <v>83</v>
+      </c>
+      <c r="P154" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q154">
+        <v>2.75</v>
+      </c>
+      <c r="R154">
+        <v>2.15</v>
+      </c>
+      <c r="S154">
+        <v>3.45</v>
+      </c>
+      <c r="T154">
+        <v>1.33</v>
+      </c>
+      <c r="U154">
+        <v>3</v>
+      </c>
+      <c r="V154">
+        <v>2.45</v>
+      </c>
+      <c r="W154">
+        <v>1.48</v>
+      </c>
+      <c r="X154">
+        <v>6.6</v>
+      </c>
+      <c r="Y154">
+        <v>1.05</v>
+      </c>
+      <c r="Z154">
+        <v>2.35</v>
+      </c>
+      <c r="AA154">
+        <v>3.45</v>
+      </c>
+      <c r="AB154">
+        <v>2.82</v>
+      </c>
+      <c r="AC154">
+        <v>1.05</v>
+      </c>
+      <c r="AD154">
+        <v>9.5</v>
+      </c>
+      <c r="AE154">
+        <v>1.25</v>
+      </c>
+      <c r="AF154">
+        <v>3.8</v>
+      </c>
+      <c r="AG154">
+        <v>1.61</v>
+      </c>
+      <c r="AH154">
+        <v>2.05</v>
+      </c>
+      <c r="AI154">
+        <v>1.6</v>
+      </c>
+      <c r="AJ154">
+        <v>2.15</v>
+      </c>
+      <c r="AK154">
+        <v>1.36</v>
+      </c>
+      <c r="AL154">
+        <v>1.25</v>
+      </c>
+      <c r="AM154">
+        <v>1.62</v>
+      </c>
+      <c r="AN154">
+        <v>2</v>
+      </c>
+      <c r="AO154">
+        <v>1.33</v>
+      </c>
+      <c r="AP154">
+        <v>1.86</v>
+      </c>
+      <c r="AQ154">
+        <v>1.46</v>
+      </c>
+      <c r="AR154">
+        <v>1.84</v>
+      </c>
+      <c r="AS154">
+        <v>1.61</v>
+      </c>
+      <c r="AT154">
+        <v>3.45</v>
+      </c>
+      <c r="AU154">
+        <v>7</v>
+      </c>
+      <c r="AV154">
+        <v>4</v>
+      </c>
+      <c r="AW154">
+        <v>8</v>
+      </c>
+      <c r="AX154">
+        <v>9</v>
+      </c>
+      <c r="AY154">
+        <v>17</v>
+      </c>
+      <c r="AZ154">
+        <v>13</v>
+      </c>
+      <c r="BA154">
+        <v>6</v>
+      </c>
+      <c r="BB154">
+        <v>2</v>
+      </c>
+      <c r="BC154">
+        <v>8</v>
+      </c>
+      <c r="BD154">
+        <v>1.65</v>
+      </c>
+      <c r="BE154">
+        <v>6.75</v>
+      </c>
+      <c r="BF154">
+        <v>2.48</v>
+      </c>
+      <c r="BG154">
+        <v>1.34</v>
+      </c>
+      <c r="BH154">
+        <v>2.9</v>
+      </c>
+      <c r="BI154">
+        <v>1.58</v>
+      </c>
+      <c r="BJ154">
+        <v>2.15</v>
+      </c>
+      <c r="BK154">
+        <v>1.96</v>
+      </c>
+      <c r="BL154">
+        <v>1.72</v>
+      </c>
+      <c r="BM154">
+        <v>2.5</v>
+      </c>
+      <c r="BN154">
+        <v>1.44</v>
+      </c>
+      <c r="BO154">
+        <v>3.3</v>
+      </c>
+      <c r="BP154">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="284">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -864,6 +864,9 @@
   <si>
     <t>['63']</t>
   </si>
+  <si>
+    <t>['24', '49', '88']</t>
+  </si>
 </sst>
 </file>
 
@@ -1224,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1558,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1767,7 +1770,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -4442,7 +4445,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ16">
         <v>1.46</v>
@@ -5063,7 +5066,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ19">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -6090,7 +6093,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ24">
         <v>1.33</v>
@@ -8356,7 +8359,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ35">
         <v>1.07</v>
@@ -9183,7 +9186,7 @@
         <v>2</v>
       </c>
       <c r="AQ39">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR39">
         <v>2.16</v>
@@ -10007,7 +10010,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
@@ -11240,7 +11243,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ49">
         <v>0.31</v>
@@ -12685,7 +12688,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ56">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR56">
         <v>1.56</v>
@@ -14742,7 +14745,7 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ66">
         <v>0.83</v>
@@ -15363,7 +15366,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
@@ -17214,7 +17217,7 @@
         <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ78">
         <v>0.54</v>
@@ -18041,7 +18044,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR82">
         <v>1.87</v>
@@ -19480,10 +19483,10 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ89">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR89">
         <v>1.82</v>
@@ -21955,7 +21958,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ101">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR101">
         <v>1.77</v>
@@ -23394,7 +23397,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ108">
         <v>0.92</v>
@@ -24630,7 +24633,7 @@
         <v>1.56</v>
       </c>
       <c r="AP114">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ114">
         <v>1.46</v>
@@ -26075,7 +26078,7 @@
         <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR121">
         <v>1.67</v>
@@ -26484,7 +26487,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ123">
         <v>0.71</v>
@@ -28547,7 +28550,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ133">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR133">
         <v>1.28</v>
@@ -28956,7 +28959,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29986,7 +29989,7 @@
         <v>1.45</v>
       </c>
       <c r="AP140">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ140">
         <v>1.33</v>
@@ -30195,7 +30198,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ141">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR141">
         <v>1.74</v>
@@ -32949,6 +32952,212 @@
       </c>
       <c r="BP154">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7784936</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45718.42708333334</v>
+      </c>
+      <c r="F155">
+        <v>26</v>
+      </c>
+      <c r="G155" t="s">
+        <v>70</v>
+      </c>
+      <c r="H155" t="s">
+        <v>81</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>3</v>
+      </c>
+      <c r="N155">
+        <v>3</v>
+      </c>
+      <c r="O155" t="s">
+        <v>83</v>
+      </c>
+      <c r="P155" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q155">
+        <v>2.46</v>
+      </c>
+      <c r="R155">
+        <v>2.31</v>
+      </c>
+      <c r="S155">
+        <v>4.1</v>
+      </c>
+      <c r="T155">
+        <v>1.33</v>
+      </c>
+      <c r="U155">
+        <v>3.05</v>
+      </c>
+      <c r="V155">
+        <v>2.45</v>
+      </c>
+      <c r="W155">
+        <v>1.49</v>
+      </c>
+      <c r="X155">
+        <v>5.7</v>
+      </c>
+      <c r="Y155">
+        <v>1.11</v>
+      </c>
+      <c r="Z155">
+        <v>1.91</v>
+      </c>
+      <c r="AA155">
+        <v>3.64</v>
+      </c>
+      <c r="AB155">
+        <v>3.68</v>
+      </c>
+      <c r="AC155">
+        <v>1.05</v>
+      </c>
+      <c r="AD155">
+        <v>9.5</v>
+      </c>
+      <c r="AE155">
+        <v>1.23</v>
+      </c>
+      <c r="AF155">
+        <v>3.85</v>
+      </c>
+      <c r="AG155">
+        <v>1.67</v>
+      </c>
+      <c r="AH155">
+        <v>2</v>
+      </c>
+      <c r="AI155">
+        <v>1.62</v>
+      </c>
+      <c r="AJ155">
+        <v>2.16</v>
+      </c>
+      <c r="AK155">
+        <v>1.27</v>
+      </c>
+      <c r="AL155">
+        <v>1.26</v>
+      </c>
+      <c r="AM155">
+        <v>1.79</v>
+      </c>
+      <c r="AN155">
+        <v>2.08</v>
+      </c>
+      <c r="AO155">
+        <v>1.42</v>
+      </c>
+      <c r="AP155">
+        <v>1.93</v>
+      </c>
+      <c r="AQ155">
+        <v>1.54</v>
+      </c>
+      <c r="AR155">
+        <v>2</v>
+      </c>
+      <c r="AS155">
+        <v>1.59</v>
+      </c>
+      <c r="AT155">
+        <v>3.59</v>
+      </c>
+      <c r="AU155">
+        <v>-1</v>
+      </c>
+      <c r="AV155">
+        <v>-1</v>
+      </c>
+      <c r="AW155">
+        <v>-1</v>
+      </c>
+      <c r="AX155">
+        <v>-1</v>
+      </c>
+      <c r="AY155">
+        <v>-1</v>
+      </c>
+      <c r="AZ155">
+        <v>-1</v>
+      </c>
+      <c r="BA155">
+        <v>-1</v>
+      </c>
+      <c r="BB155">
+        <v>-1</v>
+      </c>
+      <c r="BC155">
+        <v>-1</v>
+      </c>
+      <c r="BD155">
+        <v>1.68</v>
+      </c>
+      <c r="BE155">
+        <v>6.75</v>
+      </c>
+      <c r="BF155">
+        <v>2.43</v>
+      </c>
+      <c r="BG155">
+        <v>1.34</v>
+      </c>
+      <c r="BH155">
+        <v>2.9</v>
+      </c>
+      <c r="BI155">
+        <v>1.57</v>
+      </c>
+      <c r="BJ155">
+        <v>2.2</v>
+      </c>
+      <c r="BK155">
+        <v>1.92</v>
+      </c>
+      <c r="BL155">
+        <v>1.75</v>
+      </c>
+      <c r="BM155">
+        <v>2.45</v>
+      </c>
+      <c r="BN155">
+        <v>1.46</v>
+      </c>
+      <c r="BO155">
+        <v>3.15</v>
+      </c>
+      <c r="BP155">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="287">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -613,6 +613,12 @@
     <t>['4', '35', '40', '78']</t>
   </si>
   <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['49', '63']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -866,6 +872,9 @@
   </si>
   <si>
     <t>['24', '49', '88']</t>
+  </si>
+  <si>
+    <t>['88', '89']</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1483,7 +1492,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1689,7 +1698,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1767,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3">
         <v>1.54</v>
@@ -2101,7 +2110,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2307,7 +2316,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2513,7 +2522,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2719,7 +2728,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2800,7 +2809,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3131,7 +3140,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3209,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3337,7 +3346,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3543,7 +3552,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3830,7 +3839,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3955,7 +3964,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4161,7 +4170,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4239,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ15">
         <v>1.46</v>
@@ -4779,7 +4788,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4985,7 +4994,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5603,7 +5612,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5681,10 +5690,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR22">
         <v>0.55</v>
@@ -6015,7 +6024,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6096,7 +6105,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR24">
         <v>1.94</v>
@@ -6427,7 +6436,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6839,7 +6848,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6917,7 +6926,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>0.71</v>
@@ -7251,7 +7260,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7535,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -8156,7 +8165,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR34">
         <v>2.41</v>
@@ -8487,7 +8496,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8693,7 +8702,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8774,7 +8783,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR37">
         <v>1.76</v>
@@ -8899,7 +8908,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8977,7 +8986,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
         <v>1.46</v>
@@ -9105,7 +9114,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9311,7 +9320,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9723,7 +9732,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9804,7 +9813,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ42">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR42">
         <v>1.16</v>
@@ -9929,7 +9938,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10213,7 +10222,7 @@
         <v>1.33</v>
       </c>
       <c r="AP44">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44">
         <v>1.07</v>
@@ -10547,7 +10556,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -11165,7 +11174,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11371,7 +11380,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11577,7 +11586,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -12276,7 +12285,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -12401,7 +12410,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12607,7 +12616,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12685,7 +12694,7 @@
         <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>1.54</v>
@@ -12894,7 +12903,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR57">
         <v>1.51</v>
@@ -13225,7 +13234,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13715,7 +13724,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ61">
         <v>1.25</v>
@@ -14049,7 +14058,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14255,7 +14264,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14461,7 +14470,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14748,7 +14757,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ66">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR66">
         <v>1.86</v>
@@ -14873,7 +14882,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15079,7 +15088,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15157,7 +15166,7 @@
         <v>0.4</v>
       </c>
       <c r="AP68">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ68">
         <v>0.92</v>
@@ -15285,7 +15294,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15491,7 +15500,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15697,7 +15706,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15981,7 +15990,7 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
         <v>1.25</v>
@@ -16109,7 +16118,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16190,7 +16199,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16396,7 +16405,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -16727,7 +16736,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17757,7 +17766,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17835,7 +17844,7 @@
         <v>1.43</v>
       </c>
       <c r="AP81">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ81">
         <v>1.46</v>
@@ -17963,7 +17972,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18169,7 +18178,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18250,7 +18259,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18375,7 +18384,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18453,7 +18462,7 @@
         <v>0.83</v>
       </c>
       <c r="AP84">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ84">
         <v>1.07</v>
@@ -18581,7 +18590,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18787,7 +18796,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18868,7 +18877,7 @@
         <v>2</v>
       </c>
       <c r="AQ86">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -18993,7 +19002,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19071,7 +19080,7 @@
         <v>0.14</v>
       </c>
       <c r="AP87">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
         <v>0.31</v>
@@ -20307,10 +20316,10 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR93">
         <v>0.95</v>
@@ -20435,7 +20444,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20641,7 +20650,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21053,7 +21062,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21259,7 +21268,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21337,7 +21346,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ98">
         <v>0.54</v>
@@ -21465,7 +21474,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21546,7 +21555,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -21671,7 +21680,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22083,7 +22092,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22289,7 +22298,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22495,7 +22504,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22576,7 +22585,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR104">
         <v>1.23</v>
@@ -22701,7 +22710,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22779,7 +22788,7 @@
         <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ105">
         <v>0.71</v>
@@ -23113,7 +23122,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23319,7 +23328,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23525,7 +23534,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23937,7 +23946,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24555,7 +24564,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24842,7 +24851,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25045,10 +25054,10 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ116">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR116">
         <v>1.51</v>
@@ -25251,7 +25260,7 @@
         <v>1.22</v>
       </c>
       <c r="AP117">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ117">
         <v>1.46</v>
@@ -25379,7 +25388,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25585,7 +25594,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25791,7 +25800,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26203,7 +26212,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26284,7 +26293,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ122">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26409,7 +26418,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -27027,7 +27036,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27311,7 +27320,7 @@
         <v>0.4</v>
       </c>
       <c r="AP127">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ127">
         <v>0.31</v>
@@ -27439,7 +27448,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27517,7 +27526,7 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ128">
         <v>0.92</v>
@@ -27645,7 +27654,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27851,7 +27860,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28057,7 +28066,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28344,7 +28353,7 @@
         <v>2</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
@@ -28469,7 +28478,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28675,7 +28684,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28881,7 +28890,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29087,7 +29096,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29293,7 +29302,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29499,7 +29508,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29705,7 +29714,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29992,7 +30001,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30404,7 +30413,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ142">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR142">
         <v>1.27</v>
@@ -30607,7 +30616,7 @@
         <v>1.25</v>
       </c>
       <c r="AP143">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ143">
         <v>1.07</v>
@@ -30735,7 +30744,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30941,7 +30950,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31019,7 +31028,7 @@
         <v>1.18</v>
       </c>
       <c r="AP145">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ145">
         <v>1.46</v>
@@ -31147,7 +31156,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31353,7 +31362,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31559,7 +31568,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31765,7 +31774,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -32177,7 +32186,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -33001,7 +33010,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33094,31 +33103,31 @@
         <v>3.59</v>
       </c>
       <c r="AU155">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV155">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW155">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AX155">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY155">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AZ155">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BA155">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB155">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC155">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD155">
         <v>1.68</v>
@@ -33158,6 +33167,418 @@
       </c>
       <c r="BP155">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7784937</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45718.52083333334</v>
+      </c>
+      <c r="F156">
+        <v>26</v>
+      </c>
+      <c r="G156" t="s">
+        <v>78</v>
+      </c>
+      <c r="H156" t="s">
+        <v>73</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156" t="s">
+        <v>199</v>
+      </c>
+      <c r="P156" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q156">
+        <v>4</v>
+      </c>
+      <c r="R156">
+        <v>2.27</v>
+      </c>
+      <c r="S156">
+        <v>2.55</v>
+      </c>
+      <c r="T156">
+        <v>1.35</v>
+      </c>
+      <c r="U156">
+        <v>2.95</v>
+      </c>
+      <c r="V156">
+        <v>2.5</v>
+      </c>
+      <c r="W156">
+        <v>1.47</v>
+      </c>
+      <c r="X156">
+        <v>5.95</v>
+      </c>
+      <c r="Y156">
+        <v>1.1</v>
+      </c>
+      <c r="Z156">
+        <v>3.45</v>
+      </c>
+      <c r="AA156">
+        <v>3.59</v>
+      </c>
+      <c r="AB156">
+        <v>2</v>
+      </c>
+      <c r="AC156">
+        <v>1.05</v>
+      </c>
+      <c r="AD156">
+        <v>9.5</v>
+      </c>
+      <c r="AE156">
+        <v>1.24</v>
+      </c>
+      <c r="AF156">
+        <v>3.7</v>
+      </c>
+      <c r="AG156">
+        <v>1.79</v>
+      </c>
+      <c r="AH156">
+        <v>1.95</v>
+      </c>
+      <c r="AI156">
+        <v>1.64</v>
+      </c>
+      <c r="AJ156">
+        <v>2.12</v>
+      </c>
+      <c r="AK156">
+        <v>1.75</v>
+      </c>
+      <c r="AL156">
+        <v>1.27</v>
+      </c>
+      <c r="AM156">
+        <v>1.29</v>
+      </c>
+      <c r="AN156">
+        <v>0.83</v>
+      </c>
+      <c r="AO156">
+        <v>0.83</v>
+      </c>
+      <c r="AP156">
+        <v>1</v>
+      </c>
+      <c r="AQ156">
+        <v>0.77</v>
+      </c>
+      <c r="AR156">
+        <v>1.56</v>
+      </c>
+      <c r="AS156">
+        <v>1.77</v>
+      </c>
+      <c r="AT156">
+        <v>3.33</v>
+      </c>
+      <c r="AU156">
+        <v>2</v>
+      </c>
+      <c r="AV156">
+        <v>5</v>
+      </c>
+      <c r="AW156">
+        <v>4</v>
+      </c>
+      <c r="AX156">
+        <v>14</v>
+      </c>
+      <c r="AY156">
+        <v>7</v>
+      </c>
+      <c r="AZ156">
+        <v>24</v>
+      </c>
+      <c r="BA156">
+        <v>3</v>
+      </c>
+      <c r="BB156">
+        <v>12</v>
+      </c>
+      <c r="BC156">
+        <v>15</v>
+      </c>
+      <c r="BD156">
+        <v>2.23</v>
+      </c>
+      <c r="BE156">
+        <v>6.75</v>
+      </c>
+      <c r="BF156">
+        <v>1.79</v>
+      </c>
+      <c r="BG156">
+        <v>1.25</v>
+      </c>
+      <c r="BH156">
+        <v>3.4</v>
+      </c>
+      <c r="BI156">
+        <v>1.46</v>
+      </c>
+      <c r="BJ156">
+        <v>2.45</v>
+      </c>
+      <c r="BK156">
+        <v>1.75</v>
+      </c>
+      <c r="BL156">
+        <v>1.93</v>
+      </c>
+      <c r="BM156">
+        <v>2.18</v>
+      </c>
+      <c r="BN156">
+        <v>1.58</v>
+      </c>
+      <c r="BO156">
+        <v>2.8</v>
+      </c>
+      <c r="BP156">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7784938</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45718.52083333334</v>
+      </c>
+      <c r="F157">
+        <v>26</v>
+      </c>
+      <c r="G157" t="s">
+        <v>71</v>
+      </c>
+      <c r="H157" t="s">
+        <v>75</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>2</v>
+      </c>
+      <c r="M157">
+        <v>2</v>
+      </c>
+      <c r="N157">
+        <v>4</v>
+      </c>
+      <c r="O157" t="s">
+        <v>200</v>
+      </c>
+      <c r="P157" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q157">
+        <v>3.95</v>
+      </c>
+      <c r="R157">
+        <v>2.26</v>
+      </c>
+      <c r="S157">
+        <v>2.55</v>
+      </c>
+      <c r="T157">
+        <v>1.35</v>
+      </c>
+      <c r="U157">
+        <v>2.95</v>
+      </c>
+      <c r="V157">
+        <v>2.5</v>
+      </c>
+      <c r="W157">
+        <v>1.47</v>
+      </c>
+      <c r="X157">
+        <v>5.95</v>
+      </c>
+      <c r="Y157">
+        <v>1.1</v>
+      </c>
+      <c r="Z157">
+        <v>3.41</v>
+      </c>
+      <c r="AA157">
+        <v>3.62</v>
+      </c>
+      <c r="AB157">
+        <v>1.99</v>
+      </c>
+      <c r="AC157">
+        <v>1.05</v>
+      </c>
+      <c r="AD157">
+        <v>9.5</v>
+      </c>
+      <c r="AE157">
+        <v>1.24</v>
+      </c>
+      <c r="AF157">
+        <v>3.65</v>
+      </c>
+      <c r="AG157">
+        <v>1.6</v>
+      </c>
+      <c r="AH157">
+        <v>2.1</v>
+      </c>
+      <c r="AI157">
+        <v>1.64</v>
+      </c>
+      <c r="AJ157">
+        <v>2.13</v>
+      </c>
+      <c r="AK157">
+        <v>1.71</v>
+      </c>
+      <c r="AL157">
+        <v>1.28</v>
+      </c>
+      <c r="AM157">
+        <v>1.3</v>
+      </c>
+      <c r="AN157">
+        <v>1.42</v>
+      </c>
+      <c r="AO157">
+        <v>1.33</v>
+      </c>
+      <c r="AP157">
+        <v>1.38</v>
+      </c>
+      <c r="AQ157">
+        <v>1.31</v>
+      </c>
+      <c r="AR157">
+        <v>1.15</v>
+      </c>
+      <c r="AS157">
+        <v>1.68</v>
+      </c>
+      <c r="AT157">
+        <v>2.83</v>
+      </c>
+      <c r="AU157">
+        <v>6</v>
+      </c>
+      <c r="AV157">
+        <v>4</v>
+      </c>
+      <c r="AW157">
+        <v>8</v>
+      </c>
+      <c r="AX157">
+        <v>7</v>
+      </c>
+      <c r="AY157">
+        <v>18</v>
+      </c>
+      <c r="AZ157">
+        <v>11</v>
+      </c>
+      <c r="BA157">
+        <v>5</v>
+      </c>
+      <c r="BB157">
+        <v>5</v>
+      </c>
+      <c r="BC157">
+        <v>10</v>
+      </c>
+      <c r="BD157">
+        <v>2.9</v>
+      </c>
+      <c r="BE157">
+        <v>7</v>
+      </c>
+      <c r="BF157">
+        <v>1.49</v>
+      </c>
+      <c r="BG157">
+        <v>1.27</v>
+      </c>
+      <c r="BH157">
+        <v>3.3</v>
+      </c>
+      <c r="BI157">
+        <v>1.47</v>
+      </c>
+      <c r="BJ157">
+        <v>2.43</v>
+      </c>
+      <c r="BK157">
+        <v>1.76</v>
+      </c>
+      <c r="BL157">
+        <v>1.9</v>
+      </c>
+      <c r="BM157">
+        <v>2.18</v>
+      </c>
+      <c r="BN157">
+        <v>1.58</v>
+      </c>
+      <c r="BO157">
+        <v>2.8</v>
+      </c>
+      <c r="BP157">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,15 @@
     <t>['49', '63']</t>
   </si>
   <si>
+    <t>['45', '78', '86']</t>
+  </si>
+  <si>
+    <t>['36', '90+6']</t>
+  </si>
+  <si>
+    <t>['16', '57', '66']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -875,6 +884,9 @@
   </si>
   <si>
     <t>['88', '89']</t>
+  </si>
+  <si>
+    <t>['44']</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP157"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1492,7 +1504,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1573,7 +1585,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1698,7 +1710,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1776,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
         <v>1.54</v>
@@ -2110,7 +2122,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2188,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ5">
         <v>0.71</v>
@@ -2316,7 +2328,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2522,7 +2534,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2728,7 +2740,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3015,7 +3027,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3140,7 +3152,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3346,7 +3358,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3552,7 +3564,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3836,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ13">
         <v>0.77</v>
@@ -3964,7 +3976,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4045,7 +4057,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ14">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4170,7 +4182,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4788,7 +4800,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4994,7 +5006,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5072,7 +5084,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ19">
         <v>1.54</v>
@@ -5487,7 +5499,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR21">
         <v>1.73</v>
@@ -5612,7 +5624,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5690,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>0.77</v>
@@ -5896,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR23">
         <v>1.97</v>
@@ -6024,7 +6036,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6311,7 +6323,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ25">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR25">
         <v>3.42</v>
@@ -6436,7 +6448,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6723,7 +6735,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -6848,7 +6860,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7260,7 +7272,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7544,10 +7556,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -7750,10 +7762,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ32">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR32">
         <v>1.68</v>
@@ -8496,7 +8508,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8702,7 +8714,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8780,7 +8792,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ37">
         <v>1.31</v>
@@ -8908,7 +8920,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9114,7 +9126,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9320,7 +9332,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9732,7 +9744,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9938,7 +9950,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10016,7 +10028,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43">
         <v>1.54</v>
@@ -10222,7 +10234,7 @@
         <v>1.33</v>
       </c>
       <c r="AP44">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
         <v>1.07</v>
@@ -10431,7 +10443,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR45">
         <v>2.03</v>
@@ -10556,7 +10568,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10634,10 +10646,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR46">
         <v>1.42</v>
@@ -11174,7 +11186,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11255,7 +11267,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ49">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR49">
         <v>1.86</v>
@@ -11380,7 +11392,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11586,7 +11598,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11667,7 +11679,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR51">
         <v>1.66</v>
@@ -11873,7 +11885,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR52">
         <v>1.22</v>
@@ -12410,7 +12422,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12488,7 +12500,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ55">
         <v>1.46</v>
@@ -12616,7 +12628,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12900,7 +12912,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ57">
         <v>1.31</v>
@@ -13234,7 +13246,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13521,7 +13533,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ60">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13724,7 +13736,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
         <v>1.25</v>
@@ -13933,7 +13945,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR62">
         <v>1.82</v>
@@ -14058,7 +14070,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14264,7 +14276,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14470,7 +14482,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14882,7 +14894,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15088,7 +15100,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15166,10 +15178,10 @@
         <v>0.4</v>
       </c>
       <c r="AP68">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR68">
         <v>1.02</v>
@@ -15294,7 +15306,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15500,7 +15512,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15578,10 +15590,10 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15706,7 +15718,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15784,7 +15796,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ71">
         <v>1.46</v>
@@ -16118,7 +16130,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16611,7 +16623,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -16736,7 +16748,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16814,7 +16826,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ76">
         <v>0.71</v>
@@ -17435,7 +17447,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR79">
         <v>1.77</v>
@@ -17641,7 +17653,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ80">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR80">
         <v>1.35</v>
@@ -17766,7 +17778,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17844,7 +17856,7 @@
         <v>1.43</v>
       </c>
       <c r="AP81">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>1.46</v>
@@ -17972,7 +17984,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18178,7 +18190,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18384,7 +18396,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18590,7 +18602,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18668,7 +18680,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ85">
         <v>1.25</v>
@@ -18796,7 +18808,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -19002,7 +19014,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19083,7 +19095,7 @@
         <v>1</v>
       </c>
       <c r="AQ87">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR87">
         <v>1.52</v>
@@ -19698,7 +19710,7 @@
         <v>0.71</v>
       </c>
       <c r="AP90">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ90">
         <v>0.54</v>
@@ -20113,7 +20125,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR92">
         <v>1.84</v>
@@ -20316,7 +20328,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
         <v>1.31</v>
@@ -20444,7 +20456,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20525,7 +20537,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -20650,7 +20662,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21062,7 +21074,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21140,7 +21152,7 @@
         <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ97">
         <v>1.07</v>
@@ -21268,7 +21280,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21474,7 +21486,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21680,7 +21692,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22092,7 +22104,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22173,7 +22185,7 @@
         <v>2</v>
       </c>
       <c r="AQ102">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR102">
         <v>1.93</v>
@@ -22298,7 +22310,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22376,7 +22388,7 @@
         <v>1.63</v>
       </c>
       <c r="AP103">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ103">
         <v>1.46</v>
@@ -22504,7 +22516,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22710,7 +22722,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22788,7 +22800,7 @@
         <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105">
         <v>0.71</v>
@@ -22997,7 +23009,7 @@
         <v>2</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR106">
         <v>1.73</v>
@@ -23122,7 +23134,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23200,7 +23212,7 @@
         <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ107">
         <v>1.46</v>
@@ -23328,7 +23340,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23409,7 +23421,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ108">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23534,7 +23546,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23818,10 +23830,10 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ110">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -23946,7 +23958,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24027,7 +24039,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24564,7 +24576,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -25260,7 +25272,7 @@
         <v>1.22</v>
       </c>
       <c r="AP117">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ117">
         <v>1.46</v>
@@ -25388,7 +25400,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25594,7 +25606,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25672,10 +25684,10 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR119">
         <v>1.76</v>
@@ -25800,7 +25812,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26212,7 +26224,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26418,7 +26430,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26705,7 +26717,7 @@
         <v>2</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR124">
         <v>1.92</v>
@@ -27036,7 +27048,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27320,10 +27332,10 @@
         <v>0.4</v>
       </c>
       <c r="AP127">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ127">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR127">
         <v>1.01</v>
@@ -27448,7 +27460,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27529,7 +27541,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR128">
         <v>1.49</v>
@@ -27654,7 +27666,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27860,7 +27872,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27938,7 +27950,7 @@
         <v>1.5</v>
       </c>
       <c r="AP130">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ130">
         <v>1.25</v>
@@ -28066,7 +28078,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28144,7 +28156,7 @@
         <v>0.7</v>
       </c>
       <c r="AP131">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ131">
         <v>0.54</v>
@@ -28478,7 +28490,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28684,7 +28696,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28890,7 +28902,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -28971,7 +28983,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR135">
         <v>1.87</v>
@@ -29096,7 +29108,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29174,7 +29186,7 @@
         <v>0.91</v>
       </c>
       <c r="AP136">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ136">
         <v>0.71</v>
@@ -29302,7 +29314,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29508,7 +29520,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29589,7 +29601,7 @@
         <v>2</v>
       </c>
       <c r="AQ138">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -29714,7 +29726,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -30616,7 +30628,7 @@
         <v>1.25</v>
       </c>
       <c r="AP143">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ143">
         <v>1.07</v>
@@ -30744,7 +30756,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30825,7 +30837,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR144">
         <v>1.79</v>
@@ -30950,7 +30962,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31156,7 +31168,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31237,7 +31249,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR146">
         <v>1.86</v>
@@ -31362,7 +31374,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31568,7 +31580,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31646,7 +31658,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ148">
         <v>1.46</v>
@@ -31774,7 +31786,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -32058,7 +32070,7 @@
         <v>1.36</v>
       </c>
       <c r="AP150">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ150">
         <v>1.25</v>
@@ -32186,7 +32198,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32267,7 +32279,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR151">
         <v>1.93</v>
@@ -33010,7 +33022,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33422,7 +33434,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33500,7 +33512,7 @@
         <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157">
         <v>1.31</v>
@@ -33579,6 +33591,624 @@
       </c>
       <c r="BP157">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7784939</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45724.58333333334</v>
+      </c>
+      <c r="F158">
+        <v>27</v>
+      </c>
+      <c r="G158" t="s">
+        <v>73</v>
+      </c>
+      <c r="H158" t="s">
+        <v>74</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158">
+        <v>3</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>3</v>
+      </c>
+      <c r="O158" t="s">
+        <v>201</v>
+      </c>
+      <c r="P158" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q158">
+        <v>2.5</v>
+      </c>
+      <c r="R158">
+        <v>2.2</v>
+      </c>
+      <c r="S158">
+        <v>3.7</v>
+      </c>
+      <c r="T158">
+        <v>1.3</v>
+      </c>
+      <c r="U158">
+        <v>3.2</v>
+      </c>
+      <c r="V158">
+        <v>2.4</v>
+      </c>
+      <c r="W158">
+        <v>1.5</v>
+      </c>
+      <c r="X158">
+        <v>6.2</v>
+      </c>
+      <c r="Y158">
+        <v>1.06</v>
+      </c>
+      <c r="Z158">
+        <v>1.99</v>
+      </c>
+      <c r="AA158">
+        <v>3.84</v>
+      </c>
+      <c r="AB158">
+        <v>3.25</v>
+      </c>
+      <c r="AC158">
+        <v>1.04</v>
+      </c>
+      <c r="AD158">
+        <v>10</v>
+      </c>
+      <c r="AE158">
+        <v>1.22</v>
+      </c>
+      <c r="AF158">
+        <v>4.2</v>
+      </c>
+      <c r="AG158">
+        <v>1.57</v>
+      </c>
+      <c r="AH158">
+        <v>2.15</v>
+      </c>
+      <c r="AI158">
+        <v>1.55</v>
+      </c>
+      <c r="AJ158">
+        <v>2.25</v>
+      </c>
+      <c r="AK158">
+        <v>1.3</v>
+      </c>
+      <c r="AL158">
+        <v>1.22</v>
+      </c>
+      <c r="AM158">
+        <v>1.77</v>
+      </c>
+      <c r="AN158">
+        <v>2.08</v>
+      </c>
+      <c r="AO158">
+        <v>0.92</v>
+      </c>
+      <c r="AP158">
+        <v>2.14</v>
+      </c>
+      <c r="AQ158">
+        <v>0.85</v>
+      </c>
+      <c r="AR158">
+        <v>2.06</v>
+      </c>
+      <c r="AS158">
+        <v>1.65</v>
+      </c>
+      <c r="AT158">
+        <v>3.71</v>
+      </c>
+      <c r="AU158">
+        <v>7</v>
+      </c>
+      <c r="AV158">
+        <v>3</v>
+      </c>
+      <c r="AW158">
+        <v>5</v>
+      </c>
+      <c r="AX158">
+        <v>7</v>
+      </c>
+      <c r="AY158">
+        <v>13</v>
+      </c>
+      <c r="AZ158">
+        <v>13</v>
+      </c>
+      <c r="BA158">
+        <v>1</v>
+      </c>
+      <c r="BB158">
+        <v>7</v>
+      </c>
+      <c r="BC158">
+        <v>8</v>
+      </c>
+      <c r="BD158">
+        <v>1.83</v>
+      </c>
+      <c r="BE158">
+        <v>6.75</v>
+      </c>
+      <c r="BF158">
+        <v>2.17</v>
+      </c>
+      <c r="BG158">
+        <v>1.2</v>
+      </c>
+      <c r="BH158">
+        <v>3.8</v>
+      </c>
+      <c r="BI158">
+        <v>1.36</v>
+      </c>
+      <c r="BJ158">
+        <v>2.8</v>
+      </c>
+      <c r="BK158">
+        <v>1.61</v>
+      </c>
+      <c r="BL158">
+        <v>2.12</v>
+      </c>
+      <c r="BM158">
+        <v>1.95</v>
+      </c>
+      <c r="BN158">
+        <v>1.72</v>
+      </c>
+      <c r="BO158">
+        <v>2.45</v>
+      </c>
+      <c r="BP158">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7784940</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45724.58333333334</v>
+      </c>
+      <c r="F159">
+        <v>27</v>
+      </c>
+      <c r="G159" t="s">
+        <v>71</v>
+      </c>
+      <c r="H159" t="s">
+        <v>72</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>2</v>
+      </c>
+      <c r="L159">
+        <v>2</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>3</v>
+      </c>
+      <c r="O159" t="s">
+        <v>202</v>
+      </c>
+      <c r="P159" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q159">
+        <v>2.62</v>
+      </c>
+      <c r="R159">
+        <v>2.1</v>
+      </c>
+      <c r="S159">
+        <v>3.75</v>
+      </c>
+      <c r="T159">
+        <v>1.36</v>
+      </c>
+      <c r="U159">
+        <v>2.88</v>
+      </c>
+      <c r="V159">
+        <v>2.65</v>
+      </c>
+      <c r="W159">
+        <v>1.42</v>
+      </c>
+      <c r="X159">
+        <v>6.65</v>
+      </c>
+      <c r="Y159">
+        <v>1.05</v>
+      </c>
+      <c r="Z159">
+        <v>2.11</v>
+      </c>
+      <c r="AA159">
+        <v>3.63</v>
+      </c>
+      <c r="AB159">
+        <v>3.12</v>
+      </c>
+      <c r="AC159">
+        <v>1.05</v>
+      </c>
+      <c r="AD159">
+        <v>9</v>
+      </c>
+      <c r="AE159">
+        <v>1.28</v>
+      </c>
+      <c r="AF159">
+        <v>3.55</v>
+      </c>
+      <c r="AG159">
+        <v>1.91</v>
+      </c>
+      <c r="AH159">
+        <v>1.83</v>
+      </c>
+      <c r="AI159">
+        <v>1.67</v>
+      </c>
+      <c r="AJ159">
+        <v>2.05</v>
+      </c>
+      <c r="AK159">
+        <v>1.3</v>
+      </c>
+      <c r="AL159">
+        <v>1.25</v>
+      </c>
+      <c r="AM159">
+        <v>1.7</v>
+      </c>
+      <c r="AN159">
+        <v>1.38</v>
+      </c>
+      <c r="AO159">
+        <v>0.31</v>
+      </c>
+      <c r="AP159">
+        <v>1.5</v>
+      </c>
+      <c r="AQ159">
+        <v>0.29</v>
+      </c>
+      <c r="AR159">
+        <v>1.19</v>
+      </c>
+      <c r="AS159">
+        <v>1.21</v>
+      </c>
+      <c r="AT159">
+        <v>2.4</v>
+      </c>
+      <c r="AU159">
+        <v>7</v>
+      </c>
+      <c r="AV159">
+        <v>3</v>
+      </c>
+      <c r="AW159">
+        <v>17</v>
+      </c>
+      <c r="AX159">
+        <v>7</v>
+      </c>
+      <c r="AY159">
+        <v>24</v>
+      </c>
+      <c r="AZ159">
+        <v>12</v>
+      </c>
+      <c r="BA159">
+        <v>5</v>
+      </c>
+      <c r="BB159">
+        <v>3</v>
+      </c>
+      <c r="BC159">
+        <v>8</v>
+      </c>
+      <c r="BD159">
+        <v>1.97</v>
+      </c>
+      <c r="BE159">
+        <v>6.5</v>
+      </c>
+      <c r="BF159">
+        <v>2</v>
+      </c>
+      <c r="BG159">
+        <v>1.27</v>
+      </c>
+      <c r="BH159">
+        <v>3.3</v>
+      </c>
+      <c r="BI159">
+        <v>1.46</v>
+      </c>
+      <c r="BJ159">
+        <v>2.43</v>
+      </c>
+      <c r="BK159">
+        <v>1.76</v>
+      </c>
+      <c r="BL159">
+        <v>1.91</v>
+      </c>
+      <c r="BM159">
+        <v>2.18</v>
+      </c>
+      <c r="BN159">
+        <v>1.58</v>
+      </c>
+      <c r="BO159">
+        <v>2.8</v>
+      </c>
+      <c r="BP159">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7784941</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45724.6875</v>
+      </c>
+      <c r="F160">
+        <v>27</v>
+      </c>
+      <c r="G160" t="s">
+        <v>80</v>
+      </c>
+      <c r="H160" t="s">
+        <v>78</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160">
+        <v>2</v>
+      </c>
+      <c r="L160">
+        <v>3</v>
+      </c>
+      <c r="M160">
+        <v>1</v>
+      </c>
+      <c r="N160">
+        <v>4</v>
+      </c>
+      <c r="O160" t="s">
+        <v>203</v>
+      </c>
+      <c r="P160" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q160">
+        <v>2.4</v>
+      </c>
+      <c r="R160">
+        <v>2.2</v>
+      </c>
+      <c r="S160">
+        <v>3.95</v>
+      </c>
+      <c r="T160">
+        <v>1.3</v>
+      </c>
+      <c r="U160">
+        <v>3.2</v>
+      </c>
+      <c r="V160">
+        <v>2.4</v>
+      </c>
+      <c r="W160">
+        <v>1.5</v>
+      </c>
+      <c r="X160">
+        <v>5.4</v>
+      </c>
+      <c r="Y160">
+        <v>1.09</v>
+      </c>
+      <c r="Z160">
+        <v>1.84</v>
+      </c>
+      <c r="AA160">
+        <v>3.94</v>
+      </c>
+      <c r="AB160">
+        <v>3.64</v>
+      </c>
+      <c r="AC160">
+        <v>1.04</v>
+      </c>
+      <c r="AD160">
+        <v>10</v>
+      </c>
+      <c r="AE160">
+        <v>1.22</v>
+      </c>
+      <c r="AF160">
+        <v>4.2</v>
+      </c>
+      <c r="AG160">
+        <v>1.61</v>
+      </c>
+      <c r="AH160">
+        <v>2.05</v>
+      </c>
+      <c r="AI160">
+        <v>1.55</v>
+      </c>
+      <c r="AJ160">
+        <v>2.25</v>
+      </c>
+      <c r="AK160">
+        <v>1.25</v>
+      </c>
+      <c r="AL160">
+        <v>1.22</v>
+      </c>
+      <c r="AM160">
+        <v>1.83</v>
+      </c>
+      <c r="AN160">
+        <v>1.75</v>
+      </c>
+      <c r="AO160">
+        <v>1</v>
+      </c>
+      <c r="AP160">
+        <v>1.85</v>
+      </c>
+      <c r="AQ160">
+        <v>0.93</v>
+      </c>
+      <c r="AR160">
+        <v>1.88</v>
+      </c>
+      <c r="AS160">
+        <v>1.27</v>
+      </c>
+      <c r="AT160">
+        <v>3.15</v>
+      </c>
+      <c r="AU160">
+        <v>7</v>
+      </c>
+      <c r="AV160">
+        <v>3</v>
+      </c>
+      <c r="AW160">
+        <v>10</v>
+      </c>
+      <c r="AX160">
+        <v>3</v>
+      </c>
+      <c r="AY160">
+        <v>22</v>
+      </c>
+      <c r="AZ160">
+        <v>8</v>
+      </c>
+      <c r="BA160">
+        <v>6</v>
+      </c>
+      <c r="BB160">
+        <v>2</v>
+      </c>
+      <c r="BC160">
+        <v>8</v>
+      </c>
+      <c r="BD160">
+        <v>1.68</v>
+      </c>
+      <c r="BE160">
+        <v>6.75</v>
+      </c>
+      <c r="BF160">
+        <v>2.4</v>
+      </c>
+      <c r="BG160">
+        <v>1.21</v>
+      </c>
+      <c r="BH160">
+        <v>3.7</v>
+      </c>
+      <c r="BI160">
+        <v>1.38</v>
+      </c>
+      <c r="BJ160">
+        <v>2.7</v>
+      </c>
+      <c r="BK160">
+        <v>1.64</v>
+      </c>
+      <c r="BL160">
+        <v>2.08</v>
+      </c>
+      <c r="BM160">
+        <v>2</v>
+      </c>
+      <c r="BN160">
+        <v>1.7</v>
+      </c>
+      <c r="BO160">
+        <v>2.5</v>
+      </c>
+      <c r="BP160">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,9 @@
     <t>['16', '57', '66']</t>
   </si>
   <si>
+    <t>['3', '63']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -887,6 +890,12 @@
   </si>
   <si>
     <t>['44']</t>
+  </si>
+  <si>
+    <t>['8', '43', '90+5']</t>
+  </si>
+  <si>
+    <t>['13']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1513,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1710,7 +1719,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2122,7 +2131,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2328,7 +2337,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2409,7 +2418,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2534,7 +2543,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2612,10 +2621,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ7">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2740,7 +2749,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3024,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ9">
         <v>0.85</v>
@@ -3152,7 +3161,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3358,7 +3367,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3439,7 +3448,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3564,7 +3573,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3976,7 +3985,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4054,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ14">
         <v>0.29</v>
@@ -4182,7 +4191,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4263,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="AQ15">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR15">
         <v>1.44</v>
@@ -4469,7 +4478,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ16">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR16">
         <v>2.11</v>
@@ -4672,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ17">
         <v>0.71</v>
@@ -4800,7 +4809,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5006,7 +5015,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5496,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ21">
         <v>0.29</v>
@@ -5624,7 +5633,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6036,7 +6045,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6320,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ25">
         <v>0.85</v>
@@ -6448,7 +6457,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6529,7 +6538,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR26">
         <v>1.85</v>
@@ -6732,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ27">
         <v>0.29</v>
@@ -6860,7 +6869,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7272,7 +7281,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7350,10 +7359,10 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ30">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7971,7 +7980,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ33">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR33">
         <v>1.17</v>
@@ -8174,7 +8183,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
         <v>1.31</v>
@@ -8508,7 +8517,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8589,7 +8598,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ36">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR36">
         <v>1.64</v>
@@ -8714,7 +8723,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8920,7 +8929,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9001,7 +9010,7 @@
         <v>1</v>
       </c>
       <c r="AQ38">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR38">
         <v>1.38</v>
@@ -9126,7 +9135,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9332,7 +9341,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9616,10 +9625,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ41">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR41">
         <v>1.53</v>
@@ -9744,7 +9753,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9950,7 +9959,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10568,7 +10577,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10852,7 +10861,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ47">
         <v>0.71</v>
@@ -11058,10 +11067,10 @@
         <v>1.75</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ48">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR48">
         <v>1.38</v>
@@ -11186,7 +11195,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11392,7 +11401,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11470,7 +11479,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ50">
         <v>0.54</v>
@@ -11598,7 +11607,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11676,7 +11685,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ51">
         <v>0.85</v>
@@ -12088,10 +12097,10 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR53">
         <v>1.68</v>
@@ -12422,7 +12431,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12503,7 +12512,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ55">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR55">
         <v>1.62</v>
@@ -12628,7 +12637,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -13246,7 +13255,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13739,7 +13748,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR61">
         <v>1.01</v>
@@ -14070,7 +14079,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14151,7 +14160,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ63">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14276,7 +14285,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14354,7 +14363,7 @@
         <v>0.4</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ64">
         <v>0.54</v>
@@ -14482,7 +14491,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14560,7 +14569,7 @@
         <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ65">
         <v>1.07</v>
@@ -14894,7 +14903,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14972,10 +14981,10 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ67">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR67">
         <v>1.55</v>
@@ -15100,7 +15109,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15306,7 +15315,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15384,7 +15393,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ69">
         <v>1.54</v>
@@ -15512,7 +15521,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15718,7 +15727,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15799,7 +15808,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ71">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR71">
         <v>1.55</v>
@@ -16005,7 +16014,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16130,7 +16139,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16414,7 +16423,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
         <v>0.77</v>
@@ -16748,7 +16757,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17035,7 +17044,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ77">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR77">
         <v>1.84</v>
@@ -17444,7 +17453,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ79">
         <v>0.93</v>
@@ -17778,7 +17787,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17859,7 +17868,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR81">
         <v>0.99</v>
@@ -17984,7 +17993,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18190,7 +18199,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18268,7 +18277,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ83">
         <v>1.31</v>
@@ -18396,7 +18405,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18602,7 +18611,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18683,7 +18692,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ85">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR85">
         <v>1.7</v>
@@ -18808,7 +18817,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18886,7 +18895,7 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ86">
         <v>0.77</v>
@@ -19014,7 +19023,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19919,7 +19928,7 @@
         <v>2</v>
       </c>
       <c r="AQ91">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR91">
         <v>1.8</v>
@@ -20456,7 +20465,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20534,7 +20543,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20662,7 +20671,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20949,7 +20958,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21074,7 +21083,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21280,7 +21289,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21486,7 +21495,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21564,7 +21573,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ99">
         <v>0.77</v>
@@ -21692,7 +21701,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21770,10 +21779,10 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ100">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -22104,7 +22113,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22310,7 +22319,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22391,7 +22400,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ103">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR103">
         <v>1.81</v>
@@ -22516,7 +22525,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22722,7 +22731,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23134,7 +23143,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23215,7 +23224,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ107">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23340,7 +23349,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23546,7 +23555,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23624,7 +23633,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -23958,7 +23967,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24036,7 +24045,7 @@
         <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ111">
         <v>0.93</v>
@@ -24448,7 +24457,7 @@
         <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ113">
         <v>0.54</v>
@@ -24576,7 +24585,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24657,7 +24666,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ114">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR114">
         <v>1.86</v>
@@ -25275,7 +25284,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ117">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR117">
         <v>1</v>
@@ -25400,7 +25409,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25481,7 +25490,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ118">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25606,7 +25615,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25812,7 +25821,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26096,7 +26105,7 @@
         <v>1.56</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ121">
         <v>1.54</v>
@@ -26224,7 +26233,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26430,7 +26439,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26920,7 +26929,7 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ125">
         <v>1.07</v>
@@ -27048,7 +27057,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27126,10 +27135,10 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27460,7 +27469,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27666,7 +27675,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27744,10 +27753,10 @@
         <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ129">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR129">
         <v>1.71</v>
@@ -27872,7 +27881,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27953,7 +27962,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ130">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR130">
         <v>1.84</v>
@@ -28078,7 +28087,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28490,7 +28499,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28696,7 +28705,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28902,7 +28911,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29108,7 +29117,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29314,7 +29323,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29395,7 +29404,7 @@
         <v>2</v>
       </c>
       <c r="AQ137">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR137">
         <v>1.97</v>
@@ -29520,7 +29529,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29598,7 +29607,7 @@
         <v>0.36</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ138">
         <v>0.29</v>
@@ -29726,7 +29735,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29804,7 +29813,7 @@
         <v>1.09</v>
       </c>
       <c r="AP139">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ139">
         <v>1.07</v>
@@ -30216,7 +30225,7 @@
         <v>1.55</v>
       </c>
       <c r="AP141">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ141">
         <v>1.54</v>
@@ -30756,7 +30765,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30962,7 +30971,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31043,7 +31052,7 @@
         <v>1</v>
       </c>
       <c r="AQ145">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR145">
         <v>1.53</v>
@@ -31168,7 +31177,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31374,7 +31383,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31452,7 +31461,7 @@
         <v>0.58</v>
       </c>
       <c r="AP147">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ147">
         <v>0.54</v>
@@ -31580,7 +31589,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31661,7 +31670,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ148">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR148">
         <v>1.86</v>
@@ -31786,7 +31795,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -31864,7 +31873,7 @@
         <v>0.83</v>
       </c>
       <c r="AP149">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ149">
         <v>0.71</v>
@@ -32073,7 +32082,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ150">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR150">
         <v>2.1</v>
@@ -32198,7 +32207,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32897,7 +32906,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ154">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR154">
         <v>1.84</v>
@@ -33022,7 +33031,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33434,7 +33443,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33846,7 +33855,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -34209,6 +34218,624 @@
       </c>
       <c r="BP160">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7784942</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45725.42708333334</v>
+      </c>
+      <c r="F161">
+        <v>27</v>
+      </c>
+      <c r="G161" t="s">
+        <v>81</v>
+      </c>
+      <c r="H161" t="s">
+        <v>76</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>2</v>
+      </c>
+      <c r="K161">
+        <v>2</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>3</v>
+      </c>
+      <c r="N161">
+        <v>4</v>
+      </c>
+      <c r="O161" t="s">
+        <v>91</v>
+      </c>
+      <c r="P161" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q161">
+        <v>3.3</v>
+      </c>
+      <c r="R161">
+        <v>2.15</v>
+      </c>
+      <c r="S161">
+        <v>2.85</v>
+      </c>
+      <c r="T161">
+        <v>1.33</v>
+      </c>
+      <c r="U161">
+        <v>3</v>
+      </c>
+      <c r="V161">
+        <v>2.45</v>
+      </c>
+      <c r="W161">
+        <v>1.48</v>
+      </c>
+      <c r="X161">
+        <v>6</v>
+      </c>
+      <c r="Y161">
+        <v>1.11</v>
+      </c>
+      <c r="Z161">
+        <v>2.82</v>
+      </c>
+      <c r="AA161">
+        <v>3.39</v>
+      </c>
+      <c r="AB161">
+        <v>2.38</v>
+      </c>
+      <c r="AC161">
+        <v>1.05</v>
+      </c>
+      <c r="AD161">
+        <v>9.5</v>
+      </c>
+      <c r="AE161">
+        <v>1.25</v>
+      </c>
+      <c r="AF161">
+        <v>3.95</v>
+      </c>
+      <c r="AG161">
+        <v>1.67</v>
+      </c>
+      <c r="AH161">
+        <v>2</v>
+      </c>
+      <c r="AI161">
+        <v>1.55</v>
+      </c>
+      <c r="AJ161">
+        <v>2.25</v>
+      </c>
+      <c r="AK161">
+        <v>1.57</v>
+      </c>
+      <c r="AL161">
+        <v>1.25</v>
+      </c>
+      <c r="AM161">
+        <v>1.4</v>
+      </c>
+      <c r="AN161">
+        <v>1.46</v>
+      </c>
+      <c r="AO161">
+        <v>1.46</v>
+      </c>
+      <c r="AP161">
+        <v>1.36</v>
+      </c>
+      <c r="AQ161">
+        <v>1.57</v>
+      </c>
+      <c r="AR161">
+        <v>1.53</v>
+      </c>
+      <c r="AS161">
+        <v>1.59</v>
+      </c>
+      <c r="AT161">
+        <v>3.12</v>
+      </c>
+      <c r="AU161">
+        <v>7</v>
+      </c>
+      <c r="AV161">
+        <v>5</v>
+      </c>
+      <c r="AW161">
+        <v>6</v>
+      </c>
+      <c r="AX161">
+        <v>4</v>
+      </c>
+      <c r="AY161">
+        <v>19</v>
+      </c>
+      <c r="AZ161">
+        <v>9</v>
+      </c>
+      <c r="BA161">
+        <v>9</v>
+      </c>
+      <c r="BB161">
+        <v>2</v>
+      </c>
+      <c r="BC161">
+        <v>11</v>
+      </c>
+      <c r="BD161">
+        <v>2.15</v>
+      </c>
+      <c r="BE161">
+        <v>6.5</v>
+      </c>
+      <c r="BF161">
+        <v>1.84</v>
+      </c>
+      <c r="BG161">
+        <v>1.25</v>
+      </c>
+      <c r="BH161">
+        <v>3.4</v>
+      </c>
+      <c r="BI161">
+        <v>1.45</v>
+      </c>
+      <c r="BJ161">
+        <v>2.48</v>
+      </c>
+      <c r="BK161">
+        <v>1.73</v>
+      </c>
+      <c r="BL161">
+        <v>1.94</v>
+      </c>
+      <c r="BM161">
+        <v>2.15</v>
+      </c>
+      <c r="BN161">
+        <v>1.6</v>
+      </c>
+      <c r="BO161">
+        <v>2.75</v>
+      </c>
+      <c r="BP161">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7784944</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45725.52083333334</v>
+      </c>
+      <c r="F162">
+        <v>27</v>
+      </c>
+      <c r="G162" t="s">
+        <v>77</v>
+      </c>
+      <c r="H162" t="s">
+        <v>70</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>2</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>3</v>
+      </c>
+      <c r="O162" t="s">
+        <v>204</v>
+      </c>
+      <c r="P162" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q162">
+        <v>3.25</v>
+      </c>
+      <c r="R162">
+        <v>2.05</v>
+      </c>
+      <c r="S162">
+        <v>3.1</v>
+      </c>
+      <c r="T162">
+        <v>1.4</v>
+      </c>
+      <c r="U162">
+        <v>2.75</v>
+      </c>
+      <c r="V162">
+        <v>2.8</v>
+      </c>
+      <c r="W162">
+        <v>1.38</v>
+      </c>
+      <c r="X162">
+        <v>8</v>
+      </c>
+      <c r="Y162">
+        <v>1.08</v>
+      </c>
+      <c r="Z162">
+        <v>2.82</v>
+      </c>
+      <c r="AA162">
+        <v>3.12</v>
+      </c>
+      <c r="AB162">
+        <v>2.54</v>
+      </c>
+      <c r="AC162">
+        <v>1.06</v>
+      </c>
+      <c r="AD162">
+        <v>8.5</v>
+      </c>
+      <c r="AE162">
+        <v>1.35</v>
+      </c>
+      <c r="AF162">
+        <v>3.1</v>
+      </c>
+      <c r="AG162">
+        <v>1.98</v>
+      </c>
+      <c r="AH162">
+        <v>1.77</v>
+      </c>
+      <c r="AI162">
+        <v>1.73</v>
+      </c>
+      <c r="AJ162">
+        <v>1.95</v>
+      </c>
+      <c r="AK162">
+        <v>1.48</v>
+      </c>
+      <c r="AL162">
+        <v>1.28</v>
+      </c>
+      <c r="AM162">
+        <v>1.44</v>
+      </c>
+      <c r="AN162">
+        <v>1.67</v>
+      </c>
+      <c r="AO162">
+        <v>1.25</v>
+      </c>
+      <c r="AP162">
+        <v>1.77</v>
+      </c>
+      <c r="AQ162">
+        <v>1.15</v>
+      </c>
+      <c r="AR162">
+        <v>1.69</v>
+      </c>
+      <c r="AS162">
+        <v>1.53</v>
+      </c>
+      <c r="AT162">
+        <v>3.22</v>
+      </c>
+      <c r="AU162">
+        <v>5</v>
+      </c>
+      <c r="AV162">
+        <v>3</v>
+      </c>
+      <c r="AW162">
+        <v>8</v>
+      </c>
+      <c r="AX162">
+        <v>15</v>
+      </c>
+      <c r="AY162">
+        <v>15</v>
+      </c>
+      <c r="AZ162">
+        <v>20</v>
+      </c>
+      <c r="BA162">
+        <v>4</v>
+      </c>
+      <c r="BB162">
+        <v>7</v>
+      </c>
+      <c r="BC162">
+        <v>11</v>
+      </c>
+      <c r="BD162">
+        <v>1.9</v>
+      </c>
+      <c r="BE162">
+        <v>6.4</v>
+      </c>
+      <c r="BF162">
+        <v>2.08</v>
+      </c>
+      <c r="BG162">
+        <v>1.33</v>
+      </c>
+      <c r="BH162">
+        <v>2.95</v>
+      </c>
+      <c r="BI162">
+        <v>1.56</v>
+      </c>
+      <c r="BJ162">
+        <v>2.2</v>
+      </c>
+      <c r="BK162">
+        <v>1.9</v>
+      </c>
+      <c r="BL162">
+        <v>1.76</v>
+      </c>
+      <c r="BM162">
+        <v>2.43</v>
+      </c>
+      <c r="BN162">
+        <v>1.47</v>
+      </c>
+      <c r="BO162">
+        <v>3.15</v>
+      </c>
+      <c r="BP162">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7784943</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45725.52083333334</v>
+      </c>
+      <c r="F163">
+        <v>27</v>
+      </c>
+      <c r="G163" t="s">
+        <v>75</v>
+      </c>
+      <c r="H163" t="s">
+        <v>79</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>2</v>
+      </c>
+      <c r="O163" t="s">
+        <v>120</v>
+      </c>
+      <c r="P163" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q163">
+        <v>3.35</v>
+      </c>
+      <c r="R163">
+        <v>2.25</v>
+      </c>
+      <c r="S163">
+        <v>2.65</v>
+      </c>
+      <c r="T163">
+        <v>1.28</v>
+      </c>
+      <c r="U163">
+        <v>3.3</v>
+      </c>
+      <c r="V163">
+        <v>2.3</v>
+      </c>
+      <c r="W163">
+        <v>1.55</v>
+      </c>
+      <c r="X163">
+        <v>5</v>
+      </c>
+      <c r="Y163">
+        <v>1.15</v>
+      </c>
+      <c r="Z163">
+        <v>2.94</v>
+      </c>
+      <c r="AA163">
+        <v>3.56</v>
+      </c>
+      <c r="AB163">
+        <v>2.23</v>
+      </c>
+      <c r="AC163">
+        <v>1.04</v>
+      </c>
+      <c r="AD163">
+        <v>10</v>
+      </c>
+      <c r="AE163">
+        <v>1.2</v>
+      </c>
+      <c r="AF163">
+        <v>4.33</v>
+      </c>
+      <c r="AG163">
+        <v>1.6</v>
+      </c>
+      <c r="AH163">
+        <v>2.25</v>
+      </c>
+      <c r="AI163">
+        <v>1.48</v>
+      </c>
+      <c r="AJ163">
+        <v>2.4</v>
+      </c>
+      <c r="AK163">
+        <v>1.65</v>
+      </c>
+      <c r="AL163">
+        <v>1.22</v>
+      </c>
+      <c r="AM163">
+        <v>1.38</v>
+      </c>
+      <c r="AN163">
+        <v>2</v>
+      </c>
+      <c r="AO163">
+        <v>1.46</v>
+      </c>
+      <c r="AP163">
+        <v>1.93</v>
+      </c>
+      <c r="AQ163">
+        <v>1.43</v>
+      </c>
+      <c r="AR163">
+        <v>1.73</v>
+      </c>
+      <c r="AS163">
+        <v>1.81</v>
+      </c>
+      <c r="AT163">
+        <v>3.54</v>
+      </c>
+      <c r="AU163">
+        <v>7</v>
+      </c>
+      <c r="AV163">
+        <v>5</v>
+      </c>
+      <c r="AW163">
+        <v>7</v>
+      </c>
+      <c r="AX163">
+        <v>8</v>
+      </c>
+      <c r="AY163">
+        <v>17</v>
+      </c>
+      <c r="AZ163">
+        <v>15</v>
+      </c>
+      <c r="BA163">
+        <v>6</v>
+      </c>
+      <c r="BB163">
+        <v>4</v>
+      </c>
+      <c r="BC163">
+        <v>10</v>
+      </c>
+      <c r="BD163">
+        <v>1.94</v>
+      </c>
+      <c r="BE163">
+        <v>7</v>
+      </c>
+      <c r="BF163">
+        <v>2.02</v>
+      </c>
+      <c r="BG163">
+        <v>1.16</v>
+      </c>
+      <c r="BH163">
+        <v>4.4</v>
+      </c>
+      <c r="BI163">
+        <v>1.27</v>
+      </c>
+      <c r="BJ163">
+        <v>3.3</v>
+      </c>
+      <c r="BK163">
+        <v>1.46</v>
+      </c>
+      <c r="BL163">
+        <v>2.45</v>
+      </c>
+      <c r="BM163">
+        <v>1.74</v>
+      </c>
+      <c r="BN163">
+        <v>1.93</v>
+      </c>
+      <c r="BO163">
+        <v>2.14</v>
+      </c>
+      <c r="BP163">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -33966,13 +33966,13 @@
         <v>12</v>
       </c>
       <c r="BA159">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB159">
         <v>3</v>
       </c>
       <c r="BC159">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD159">
         <v>1.97</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,9 @@
     <t>['3', '63']</t>
   </si>
   <si>
+    <t>['28', '64']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -896,6 +899,12 @@
   </si>
   <si>
     <t>['13']</t>
+  </si>
+  <si>
+    <t>['26', '39', '52']</t>
+  </si>
+  <si>
+    <t>['10', '24']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1513,7 +1522,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1719,7 +1728,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2131,7 +2140,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2337,7 +2346,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2543,7 +2552,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2749,7 +2758,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2827,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8">
         <v>0.77</v>
@@ -3036,7 +3045,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ9">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3161,7 +3170,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3367,7 +3376,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3573,7 +3582,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3651,10 +3660,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ12">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR12">
         <v>2.07</v>
@@ -3857,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ13">
         <v>0.77</v>
@@ -3985,7 +3994,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4191,7 +4200,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4809,7 +4818,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5015,7 +5024,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5302,7 +5311,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ20">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR20">
         <v>1.02</v>
@@ -5633,7 +5642,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5917,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ23">
         <v>0.93</v>
@@ -6045,7 +6054,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6332,7 +6341,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ25">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>3.42</v>
@@ -6457,7 +6466,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6535,7 +6544,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ26">
         <v>1.43</v>
@@ -6869,7 +6878,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7156,7 +7165,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7281,7 +7290,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7774,7 +7783,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ32">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.68</v>
@@ -8517,7 +8526,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8723,7 +8732,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8801,7 +8810,7 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ37">
         <v>1.31</v>
@@ -8929,7 +8938,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9135,7 +9144,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9341,7 +9350,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9422,7 +9431,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ40">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR40">
         <v>1.54</v>
@@ -9753,7 +9762,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9959,7 +9968,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10037,7 +10046,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ43">
         <v>1.54</v>
@@ -10449,10 +10458,10 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>2.03</v>
@@ -10577,7 +10586,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -11195,7 +11204,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11401,7 +11410,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11482,7 +11491,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ50">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR50">
         <v>1.38</v>
@@ -11607,7 +11616,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11688,7 +11697,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ51">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.66</v>
@@ -12431,7 +12440,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12509,7 +12518,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ55">
         <v>1.57</v>
@@ -12637,7 +12646,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -13127,7 +13136,7 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ58">
         <v>0.71</v>
@@ -13255,7 +13264,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14079,7 +14088,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14285,7 +14294,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14366,7 +14375,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ64">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14491,7 +14500,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14903,7 +14912,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15109,7 +15118,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15190,7 +15199,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.02</v>
@@ -15315,7 +15324,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15521,7 +15530,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15599,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ70">
         <v>0.29</v>
@@ -15727,7 +15736,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16139,7 +16148,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16217,7 +16226,7 @@
         <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ73">
         <v>1.31</v>
@@ -16757,7 +16766,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16835,7 +16844,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ76">
         <v>0.71</v>
@@ -17250,7 +17259,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ78">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -17662,7 +17671,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ80">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR80">
         <v>1.35</v>
@@ -17787,7 +17796,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17993,7 +18002,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18071,7 +18080,7 @@
         <v>2.17</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ82">
         <v>1.54</v>
@@ -18199,7 +18208,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18405,7 +18414,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18611,7 +18620,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18817,7 +18826,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -19023,7 +19032,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19719,10 +19728,10 @@
         <v>0.71</v>
       </c>
       <c r="AP90">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ90">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -20134,7 +20143,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.84</v>
@@ -20465,7 +20474,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20671,7 +20680,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20955,7 +20964,7 @@
         <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ96">
         <v>1.15</v>
@@ -21083,7 +21092,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21289,7 +21298,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21370,7 +21379,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21495,7 +21504,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21701,7 +21710,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22113,7 +22122,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22191,7 +22200,7 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ102">
         <v>0.29</v>
@@ -22319,7 +22328,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22397,7 +22406,7 @@
         <v>1.63</v>
       </c>
       <c r="AP103">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ103">
         <v>1.43</v>
@@ -22525,7 +22534,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22731,7 +22740,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23143,7 +23152,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23349,7 +23358,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23430,7 +23439,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ108">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23555,7 +23564,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23967,7 +23976,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24251,7 +24260,7 @@
         <v>1.22</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ112">
         <v>1.07</v>
@@ -24460,7 +24469,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ113">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR113">
         <v>1.39</v>
@@ -24585,7 +24594,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -25409,7 +25418,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25615,7 +25624,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25693,10 +25702,10 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ119">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.76</v>
@@ -25821,7 +25830,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26233,7 +26242,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26439,7 +26448,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26723,7 +26732,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ124">
         <v>0.93</v>
@@ -27057,7 +27066,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27469,7 +27478,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27550,7 +27559,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.49</v>
@@ -27675,7 +27684,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27881,7 +27890,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27959,7 +27968,7 @@
         <v>1.5</v>
       </c>
       <c r="AP130">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ130">
         <v>1.15</v>
@@ -28087,7 +28096,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28168,7 +28177,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ131">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR131">
         <v>1.95</v>
@@ -28499,7 +28508,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28705,7 +28714,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28786,7 +28795,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ134">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR134">
         <v>1.83</v>
@@ -28911,7 +28920,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29117,7 +29126,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29323,7 +29332,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29401,7 +29410,7 @@
         <v>1.64</v>
       </c>
       <c r="AP137">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ137">
         <v>1.43</v>
@@ -29529,7 +29538,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29735,7 +29744,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -30765,7 +30774,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30846,7 +30855,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.79</v>
@@ -30971,7 +30980,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31177,7 +31186,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31383,7 +31392,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31464,7 +31473,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ147">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR147">
         <v>1.5</v>
@@ -31589,7 +31598,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31667,7 +31676,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ148">
         <v>1.43</v>
@@ -31795,7 +31804,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -32207,7 +32216,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32285,7 +32294,7 @@
         <v>0.33</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ151">
         <v>0.29</v>
@@ -33031,7 +33040,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33443,7 +33452,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33730,7 +33739,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ158">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>2.06</v>
@@ -33855,7 +33864,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -34139,7 +34148,7 @@
         <v>1</v>
       </c>
       <c r="AP160">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ160">
         <v>0.93</v>
@@ -34267,7 +34276,7 @@
         <v>91</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34473,7 +34482,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34679,7 +34688,7 @@
         <v>120</v>
       </c>
       <c r="P163" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q163">
         <v>3.35</v>
@@ -34836,6 +34845,418 @@
       </c>
       <c r="BP163">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7784945</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45731.58333333334</v>
+      </c>
+      <c r="F164">
+        <v>28</v>
+      </c>
+      <c r="G164" t="s">
+        <v>76</v>
+      </c>
+      <c r="H164" t="s">
+        <v>71</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
+        <v>2</v>
+      </c>
+      <c r="K164">
+        <v>3</v>
+      </c>
+      <c r="L164">
+        <v>2</v>
+      </c>
+      <c r="M164">
+        <v>3</v>
+      </c>
+      <c r="N164">
+        <v>5</v>
+      </c>
+      <c r="O164" t="s">
+        <v>205</v>
+      </c>
+      <c r="P164" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q164">
+        <v>1.91</v>
+      </c>
+      <c r="R164">
+        <v>2.5</v>
+      </c>
+      <c r="S164">
+        <v>6.5</v>
+      </c>
+      <c r="T164">
+        <v>1.3</v>
+      </c>
+      <c r="U164">
+        <v>3.4</v>
+      </c>
+      <c r="V164">
+        <v>2.5</v>
+      </c>
+      <c r="W164">
+        <v>1.5</v>
+      </c>
+      <c r="X164">
+        <v>6</v>
+      </c>
+      <c r="Y164">
+        <v>1.13</v>
+      </c>
+      <c r="Z164">
+        <v>1.43</v>
+      </c>
+      <c r="AA164">
+        <v>4.5</v>
+      </c>
+      <c r="AB164">
+        <v>6.8</v>
+      </c>
+      <c r="AC164">
+        <v>1.02</v>
+      </c>
+      <c r="AD164">
+        <v>12.5</v>
+      </c>
+      <c r="AE164">
+        <v>1.2</v>
+      </c>
+      <c r="AF164">
+        <v>4.41</v>
+      </c>
+      <c r="AG164">
+        <v>1.57</v>
+      </c>
+      <c r="AH164">
+        <v>2.15</v>
+      </c>
+      <c r="AI164">
+        <v>1.8</v>
+      </c>
+      <c r="AJ164">
+        <v>1.91</v>
+      </c>
+      <c r="AK164">
+        <v>1.12</v>
+      </c>
+      <c r="AL164">
+        <v>1.18</v>
+      </c>
+      <c r="AM164">
+        <v>2.65</v>
+      </c>
+      <c r="AN164">
+        <v>2</v>
+      </c>
+      <c r="AO164">
+        <v>0.54</v>
+      </c>
+      <c r="AP164">
+        <v>1.86</v>
+      </c>
+      <c r="AQ164">
+        <v>0.71</v>
+      </c>
+      <c r="AR164">
+        <v>1.99</v>
+      </c>
+      <c r="AS164">
+        <v>1.2</v>
+      </c>
+      <c r="AT164">
+        <v>3.19</v>
+      </c>
+      <c r="AU164">
+        <v>7</v>
+      </c>
+      <c r="AV164">
+        <v>5</v>
+      </c>
+      <c r="AW164">
+        <v>8</v>
+      </c>
+      <c r="AX164">
+        <v>11</v>
+      </c>
+      <c r="AY164">
+        <v>16</v>
+      </c>
+      <c r="AZ164">
+        <v>19</v>
+      </c>
+      <c r="BA164">
+        <v>8</v>
+      </c>
+      <c r="BB164">
+        <v>4</v>
+      </c>
+      <c r="BC164">
+        <v>12</v>
+      </c>
+      <c r="BD164">
+        <v>1.17</v>
+      </c>
+      <c r="BE164">
+        <v>12.5</v>
+      </c>
+      <c r="BF164">
+        <v>6.2</v>
+      </c>
+      <c r="BG164">
+        <v>1.13</v>
+      </c>
+      <c r="BH164">
+        <v>4.55</v>
+      </c>
+      <c r="BI164">
+        <v>1.28</v>
+      </c>
+      <c r="BJ164">
+        <v>3.08</v>
+      </c>
+      <c r="BK164">
+        <v>1.58</v>
+      </c>
+      <c r="BL164">
+        <v>2.31</v>
+      </c>
+      <c r="BM164">
+        <v>1.93</v>
+      </c>
+      <c r="BN164">
+        <v>1.87</v>
+      </c>
+      <c r="BO164">
+        <v>2.42</v>
+      </c>
+      <c r="BP164">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7784946</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45731.58333333334</v>
+      </c>
+      <c r="F165">
+        <v>28</v>
+      </c>
+      <c r="G165" t="s">
+        <v>80</v>
+      </c>
+      <c r="H165" t="s">
+        <v>74</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>2</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>2</v>
+      </c>
+      <c r="N165">
+        <v>2</v>
+      </c>
+      <c r="O165" t="s">
+        <v>83</v>
+      </c>
+      <c r="P165" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q165">
+        <v>3</v>
+      </c>
+      <c r="R165">
+        <v>2.38</v>
+      </c>
+      <c r="S165">
+        <v>3.1</v>
+      </c>
+      <c r="T165">
+        <v>1.3</v>
+      </c>
+      <c r="U165">
+        <v>3.4</v>
+      </c>
+      <c r="V165">
+        <v>2.38</v>
+      </c>
+      <c r="W165">
+        <v>1.53</v>
+      </c>
+      <c r="X165">
+        <v>6</v>
+      </c>
+      <c r="Y165">
+        <v>1.13</v>
+      </c>
+      <c r="Z165">
+        <v>2.5</v>
+      </c>
+      <c r="AA165">
+        <v>3.45</v>
+      </c>
+      <c r="AB165">
+        <v>2.63</v>
+      </c>
+      <c r="AC165">
+        <v>1.02</v>
+      </c>
+      <c r="AD165">
+        <v>12.5</v>
+      </c>
+      <c r="AE165">
+        <v>1.18</v>
+      </c>
+      <c r="AF165">
+        <v>4.79</v>
+      </c>
+      <c r="AG165">
+        <v>1.53</v>
+      </c>
+      <c r="AH165">
+        <v>2.2</v>
+      </c>
+      <c r="AI165">
+        <v>1.5</v>
+      </c>
+      <c r="AJ165">
+        <v>2.5</v>
+      </c>
+      <c r="AK165">
+        <v>1.46</v>
+      </c>
+      <c r="AL165">
+        <v>1.3</v>
+      </c>
+      <c r="AM165">
+        <v>1.54</v>
+      </c>
+      <c r="AN165">
+        <v>1.85</v>
+      </c>
+      <c r="AO165">
+        <v>0.85</v>
+      </c>
+      <c r="AP165">
+        <v>1.71</v>
+      </c>
+      <c r="AQ165">
+        <v>1</v>
+      </c>
+      <c r="AR165">
+        <v>1.89</v>
+      </c>
+      <c r="AS165">
+        <v>1.61</v>
+      </c>
+      <c r="AT165">
+        <v>3.5</v>
+      </c>
+      <c r="AU165">
+        <v>6</v>
+      </c>
+      <c r="AV165">
+        <v>7</v>
+      </c>
+      <c r="AW165">
+        <v>8</v>
+      </c>
+      <c r="AX165">
+        <v>9</v>
+      </c>
+      <c r="AY165">
+        <v>16</v>
+      </c>
+      <c r="AZ165">
+        <v>18</v>
+      </c>
+      <c r="BA165">
+        <v>8</v>
+      </c>
+      <c r="BB165">
+        <v>6</v>
+      </c>
+      <c r="BC165">
+        <v>14</v>
+      </c>
+      <c r="BD165">
+        <v>1.9</v>
+      </c>
+      <c r="BE165">
+        <v>6.65</v>
+      </c>
+      <c r="BF165">
+        <v>2.4</v>
+      </c>
+      <c r="BG165">
+        <v>1.15</v>
+      </c>
+      <c r="BH165">
+        <v>4.3</v>
+      </c>
+      <c r="BI165">
+        <v>1.31</v>
+      </c>
+      <c r="BJ165">
+        <v>2.92</v>
+      </c>
+      <c r="BK165">
+        <v>1.64</v>
+      </c>
+      <c r="BL165">
+        <v>2.24</v>
+      </c>
+      <c r="BM165">
+        <v>2.02</v>
+      </c>
+      <c r="BN165">
+        <v>1.78</v>
+      </c>
+      <c r="BO165">
+        <v>2.54</v>
+      </c>
+      <c r="BP165">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="299">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -634,6 +634,9 @@
     <t>['28', '64']</t>
   </si>
   <si>
+    <t>['32', '34', '76']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -905,6 +908,9 @@
   </si>
   <si>
     <t>['10', '24']</t>
+  </si>
+  <si>
+    <t>['5', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP166"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1522,7 +1528,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1728,7 +1734,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2140,7 +2146,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2346,7 +2352,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2552,7 +2558,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2758,7 +2764,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3170,7 +3176,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3251,7 +3257,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3376,7 +3382,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3582,7 +3588,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3994,7 +4000,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4072,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ14">
         <v>0.29</v>
@@ -4200,7 +4206,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4818,7 +4824,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5024,7 +5030,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5642,7 +5648,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6054,7 +6060,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6135,7 +6141,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ24">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
         <v>1.94</v>
@@ -6338,7 +6344,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6466,7 +6472,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6878,7 +6884,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7290,7 +7296,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -8192,10 +8198,10 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ34">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR34">
         <v>2.41</v>
@@ -8526,7 +8532,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8732,7 +8738,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8813,7 +8819,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ37">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR37">
         <v>1.76</v>
@@ -8938,7 +8944,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9144,7 +9150,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9350,7 +9356,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9762,7 +9768,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9968,7 +9974,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10586,7 +10592,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10870,7 +10876,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ47">
         <v>0.71</v>
@@ -11204,7 +11210,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11410,7 +11416,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11616,7 +11622,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -12106,7 +12112,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ53">
         <v>1.15</v>
@@ -12440,7 +12446,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12646,7 +12652,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12933,7 +12939,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ57">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR57">
         <v>1.51</v>
@@ -13264,7 +13270,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -14088,7 +14094,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14294,7 +14300,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14500,7 +14506,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14912,7 +14918,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14990,7 +14996,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ67">
         <v>1.57</v>
@@ -15118,7 +15124,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15324,7 +15330,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15530,7 +15536,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15736,7 +15742,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16148,7 +16154,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16229,7 +16235,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ73">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16432,7 +16438,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ74">
         <v>0.77</v>
@@ -16766,7 +16772,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17796,7 +17802,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18002,7 +18008,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18208,7 +18214,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18289,7 +18295,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ83">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18414,7 +18420,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18620,7 +18626,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18826,7 +18832,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -19032,7 +19038,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -20349,7 +20355,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR93">
         <v>0.95</v>
@@ -20474,7 +20480,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20552,7 +20558,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20680,7 +20686,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21092,7 +21098,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21298,7 +21304,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21504,7 +21510,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21710,7 +21716,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22122,7 +22128,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22328,7 +22334,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22534,7 +22540,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22615,7 +22621,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ104">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR104">
         <v>1.23</v>
@@ -22740,7 +22746,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23152,7 +23158,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23358,7 +23364,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23564,7 +23570,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23642,7 +23648,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -23976,7 +23982,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24466,7 +24472,7 @@
         <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ113">
         <v>0.71</v>
@@ -24594,7 +24600,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24881,7 +24887,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ115">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25418,7 +25424,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25624,7 +25630,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25830,7 +25836,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26242,7 +26248,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26448,7 +26454,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -27066,7 +27072,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27144,7 +27150,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ126">
         <v>1.43</v>
@@ -27478,7 +27484,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27684,7 +27690,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27890,7 +27896,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28096,7 +28102,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28383,7 +28389,7 @@
         <v>2</v>
       </c>
       <c r="AQ132">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
@@ -28508,7 +28514,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28714,7 +28720,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28920,7 +28926,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29126,7 +29132,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29332,7 +29338,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29538,7 +29544,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29744,7 +29750,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29822,7 +29828,7 @@
         <v>1.09</v>
       </c>
       <c r="AP139">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ139">
         <v>1.07</v>
@@ -30031,7 +30037,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ140">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30774,7 +30780,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30980,7 +30986,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31186,7 +31192,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31392,7 +31398,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31470,7 +31476,7 @@
         <v>0.58</v>
       </c>
       <c r="AP147">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ147">
         <v>0.71</v>
@@ -31598,7 +31604,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31804,7 +31810,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -32216,7 +32222,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -33040,7 +33046,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33452,7 +33458,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33533,7 +33539,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ157">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -33864,7 +33870,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -34276,7 +34282,7 @@
         <v>91</v>
       </c>
       <c r="P161" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34354,7 +34360,7 @@
         <v>1.46</v>
       </c>
       <c r="AP161">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ161">
         <v>1.57</v>
@@ -34482,7 +34488,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34688,7 +34694,7 @@
         <v>120</v>
       </c>
       <c r="P163" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q163">
         <v>3.35</v>
@@ -34894,7 +34900,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35100,7 +35106,7 @@
         <v>83</v>
       </c>
       <c r="P165" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35257,6 +35263,212 @@
       </c>
       <c r="BP165">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7784947</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45731.6875</v>
+      </c>
+      <c r="F166">
+        <v>28</v>
+      </c>
+      <c r="G166" t="s">
+        <v>81</v>
+      </c>
+      <c r="H166" t="s">
+        <v>75</v>
+      </c>
+      <c r="I166">
+        <v>2</v>
+      </c>
+      <c r="J166">
+        <v>1</v>
+      </c>
+      <c r="K166">
+        <v>3</v>
+      </c>
+      <c r="L166">
+        <v>3</v>
+      </c>
+      <c r="M166">
+        <v>2</v>
+      </c>
+      <c r="N166">
+        <v>5</v>
+      </c>
+      <c r="O166" t="s">
+        <v>206</v>
+      </c>
+      <c r="P166" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q166">
+        <v>2.75</v>
+      </c>
+      <c r="R166">
+        <v>2.25</v>
+      </c>
+      <c r="S166">
+        <v>3.6</v>
+      </c>
+      <c r="T166">
+        <v>1.33</v>
+      </c>
+      <c r="U166">
+        <v>3.25</v>
+      </c>
+      <c r="V166">
+        <v>2.63</v>
+      </c>
+      <c r="W166">
+        <v>1.44</v>
+      </c>
+      <c r="X166">
+        <v>6.5</v>
+      </c>
+      <c r="Y166">
+        <v>1.11</v>
+      </c>
+      <c r="Z166">
+        <v>2.21</v>
+      </c>
+      <c r="AA166">
+        <v>3.5</v>
+      </c>
+      <c r="AB166">
+        <v>3.01</v>
+      </c>
+      <c r="AC166">
+        <v>1.03</v>
+      </c>
+      <c r="AD166">
+        <v>11</v>
+      </c>
+      <c r="AE166">
+        <v>1.2</v>
+      </c>
+      <c r="AF166">
+        <v>4.41</v>
+      </c>
+      <c r="AG166">
+        <v>1.79</v>
+      </c>
+      <c r="AH166">
+        <v>1.95</v>
+      </c>
+      <c r="AI166">
+        <v>1.57</v>
+      </c>
+      <c r="AJ166">
+        <v>2.25</v>
+      </c>
+      <c r="AK166">
+        <v>1.36</v>
+      </c>
+      <c r="AL166">
+        <v>1.3</v>
+      </c>
+      <c r="AM166">
+        <v>1.66</v>
+      </c>
+      <c r="AN166">
+        <v>1.36</v>
+      </c>
+      <c r="AO166">
+        <v>1.31</v>
+      </c>
+      <c r="AP166">
+        <v>1.47</v>
+      </c>
+      <c r="AQ166">
+        <v>1.21</v>
+      </c>
+      <c r="AR166">
+        <v>1.55</v>
+      </c>
+      <c r="AS166">
+        <v>1.65</v>
+      </c>
+      <c r="AT166">
+        <v>3.2</v>
+      </c>
+      <c r="AU166">
+        <v>11</v>
+      </c>
+      <c r="AV166">
+        <v>7</v>
+      </c>
+      <c r="AW166">
+        <v>15</v>
+      </c>
+      <c r="AX166">
+        <v>4</v>
+      </c>
+      <c r="AY166">
+        <v>34</v>
+      </c>
+      <c r="AZ166">
+        <v>11</v>
+      </c>
+      <c r="BA166">
+        <v>6</v>
+      </c>
+      <c r="BB166">
+        <v>4</v>
+      </c>
+      <c r="BC166">
+        <v>10</v>
+      </c>
+      <c r="BD166">
+        <v>1.58</v>
+      </c>
+      <c r="BE166">
+        <v>7.1</v>
+      </c>
+      <c r="BF166">
+        <v>3.12</v>
+      </c>
+      <c r="BG166">
+        <v>1.14</v>
+      </c>
+      <c r="BH166">
+        <v>4.4</v>
+      </c>
+      <c r="BI166">
+        <v>1.3</v>
+      </c>
+      <c r="BJ166">
+        <v>2.97</v>
+      </c>
+      <c r="BK166">
+        <v>1.61</v>
+      </c>
+      <c r="BL166">
+        <v>2.25</v>
+      </c>
+      <c r="BM166">
+        <v>2</v>
+      </c>
+      <c r="BN166">
+        <v>1.8</v>
+      </c>
+      <c r="BO166">
+        <v>2.54</v>
+      </c>
+      <c r="BP166">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="301">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,15 @@
     <t>['32', '34', '76']</t>
   </si>
   <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['50', '56']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -796,9 +805,6 @@
     <t>['83']</t>
   </si>
   <si>
-    <t>['90+4']</t>
-  </si>
-  <si>
     <t>['35', '38', '64', '90+8']</t>
   </si>
   <si>
@@ -871,9 +877,6 @@
     <t>['70', '76']</t>
   </si>
   <si>
-    <t>['67']</t>
-  </si>
-  <si>
     <t>['76', '79']</t>
   </si>
   <si>
@@ -911,6 +914,9 @@
   </si>
   <si>
     <t>['5', '90+6']</t>
+  </si>
+  <si>
+    <t>['1', '78']</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP166"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1528,7 +1534,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1606,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -1734,7 +1740,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2146,7 +2152,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2227,7 +2233,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ5">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2352,7 +2358,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2558,7 +2564,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2764,7 +2770,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2845,7 +2851,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ8">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3176,7 +3182,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3382,7 +3388,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3460,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11">
         <v>1.15</v>
@@ -3588,7 +3594,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3875,7 +3881,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ13">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4000,7 +4006,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4081,7 +4087,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ14">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4206,7 +4212,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4490,7 +4496,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.57</v>
@@ -4699,7 +4705,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ17">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR17">
         <v>1.15</v>
@@ -4824,7 +4830,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5030,7 +5036,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5523,7 +5529,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ21">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR21">
         <v>1.73</v>
@@ -5648,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5729,7 +5735,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR22">
         <v>0.55</v>
@@ -6060,7 +6066,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6138,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>1.21</v>
@@ -6472,7 +6478,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6759,7 +6765,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ27">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -6884,7 +6890,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6965,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR28">
         <v>1.22</v>
@@ -7168,7 +7174,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ29">
         <v>0.71</v>
@@ -7296,7 +7302,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -8404,7 +8410,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1.07</v>
@@ -8532,7 +8538,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8738,7 +8744,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8944,7 +8950,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9150,7 +9156,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9228,7 +9234,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ39">
         <v>1.54</v>
@@ -9356,7 +9362,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9768,7 +9774,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9849,7 +9855,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ42">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR42">
         <v>1.16</v>
@@ -9974,7 +9980,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10592,7 +10598,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10879,7 +10885,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ47">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR47">
         <v>1.94</v>
@@ -11210,7 +11216,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11288,10 +11294,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR49">
         <v>1.86</v>
@@ -11416,7 +11422,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11622,7 +11628,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -12318,10 +12324,10 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ54">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -12446,7 +12452,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12652,7 +12658,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -13145,7 +13151,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ58">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13270,7 +13276,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13348,7 +13354,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ59">
         <v>1.07</v>
@@ -13557,7 +13563,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ60">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -14094,7 +14100,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14300,7 +14306,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14506,7 +14512,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14790,10 +14796,10 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR66">
         <v>1.86</v>
@@ -14918,7 +14924,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15124,7 +15130,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15330,7 +15336,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15536,7 +15542,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15617,7 +15623,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ70">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15742,7 +15748,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16154,7 +16160,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16441,7 +16447,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ74">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -16644,10 +16650,10 @@
         <v>0.17</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -16772,7 +16778,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16853,7 +16859,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ76">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -17262,7 +17268,7 @@
         <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>0.71</v>
@@ -17802,7 +17808,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18008,7 +18014,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18214,7 +18220,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18420,7 +18426,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18626,7 +18632,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18832,7 +18838,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18913,7 +18919,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ86">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19038,7 +19044,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19119,7 +19125,7 @@
         <v>1</v>
       </c>
       <c r="AQ87">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR87">
         <v>1.52</v>
@@ -19325,7 +19331,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ88">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19528,7 +19534,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
         <v>1.54</v>
@@ -19940,7 +19946,7 @@
         <v>1.57</v>
       </c>
       <c r="AP91">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ91">
         <v>1.57</v>
@@ -20146,7 +20152,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20480,7 +20486,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20686,7 +20692,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20767,7 +20773,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ95">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR95">
         <v>1.3</v>
@@ -21098,7 +21104,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21304,7 +21310,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21510,7 +21516,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21591,7 +21597,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ99">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -21716,7 +21722,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22128,7 +22134,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22209,7 +22215,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ102">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR102">
         <v>1.93</v>
@@ -22334,7 +22340,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22540,7 +22546,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22746,7 +22752,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22827,7 +22833,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ105">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR105">
         <v>0.93</v>
@@ -23030,7 +23036,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ106">
         <v>0.93</v>
@@ -23158,7 +23164,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23364,7 +23370,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23442,7 +23448,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23570,7 +23576,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23857,7 +23863,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ110">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -23982,7 +23988,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24600,7 +24606,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24678,7 +24684,7 @@
         <v>1.56</v>
       </c>
       <c r="AP114">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>1.43</v>
@@ -25093,7 +25099,7 @@
         <v>1</v>
       </c>
       <c r="AQ116">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR116">
         <v>1.51</v>
@@ -25424,7 +25430,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25630,7 +25636,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25836,7 +25842,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25914,10 +25920,10 @@
         <v>1.11</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ120">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR120">
         <v>1.76</v>
@@ -26248,7 +26254,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26329,7 +26335,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ122">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26454,7 +26460,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26532,10 +26538,10 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR123">
         <v>1.87</v>
@@ -27072,7 +27078,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27359,7 +27365,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ127">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR127">
         <v>1.01</v>
@@ -27484,7 +27490,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27690,7 +27696,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27896,7 +27902,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28102,7 +28108,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28386,7 +28392,7 @@
         <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ132">
         <v>1.21</v>
@@ -28514,7 +28520,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28720,7 +28726,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28926,7 +28932,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29004,7 +29010,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ135">
         <v>0.93</v>
@@ -29132,7 +29138,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29213,7 +29219,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ136">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR136">
         <v>2.08</v>
@@ -29338,7 +29344,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29544,7 +29550,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29625,7 +29631,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ138">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -29750,7 +29756,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -30034,7 +30040,7 @@
         <v>1.45</v>
       </c>
       <c r="AP140">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>1.21</v>
@@ -30449,7 +30455,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ142">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR142">
         <v>1.27</v>
@@ -30780,7 +30786,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>285</v>
+        <v>208</v>
       </c>
       <c r="Q144">
         <v>2.5</v>
@@ -30858,7 +30864,7 @@
         <v>0.91</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -30986,7 +30992,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31192,7 +31198,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31398,7 +31404,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31604,7 +31610,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31810,7 +31816,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -31891,7 +31897,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ149">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR149">
         <v>1.79</v>
@@ -32222,7 +32228,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32303,7 +32309,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ151">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR151">
         <v>1.93</v>
@@ -32506,10 +32512,10 @@
         <v>0.77</v>
       </c>
       <c r="AP152">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ152">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR152">
         <v>1.84</v>
@@ -33046,7 +33052,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33124,7 +33130,7 @@
         <v>1.42</v>
       </c>
       <c r="AP155">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
         <v>1.54</v>
@@ -33333,7 +33339,7 @@
         <v>1</v>
       </c>
       <c r="AQ156">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR156">
         <v>1.56</v>
@@ -33458,7 +33464,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33870,7 +33876,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -33951,7 +33957,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ159">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34282,7 +34288,7 @@
         <v>91</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34488,7 +34494,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34694,7 +34700,7 @@
         <v>120</v>
       </c>
       <c r="P163" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q163">
         <v>3.35</v>
@@ -34900,7 +34906,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35106,7 +35112,7 @@
         <v>83</v>
       </c>
       <c r="P165" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35312,7 +35318,7 @@
         <v>206</v>
       </c>
       <c r="P166" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35469,6 +35475,624 @@
       </c>
       <c r="BP166">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7784948</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45732.42708333334</v>
+      </c>
+      <c r="F167">
+        <v>28</v>
+      </c>
+      <c r="G167" t="s">
+        <v>78</v>
+      </c>
+      <c r="H167" t="s">
+        <v>77</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>2</v>
+      </c>
+      <c r="O167" t="s">
+        <v>207</v>
+      </c>
+      <c r="P167" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q167">
+        <v>3.2</v>
+      </c>
+      <c r="R167">
+        <v>2.05</v>
+      </c>
+      <c r="S167">
+        <v>3.6</v>
+      </c>
+      <c r="T167">
+        <v>1.44</v>
+      </c>
+      <c r="U167">
+        <v>2.63</v>
+      </c>
+      <c r="V167">
+        <v>3.4</v>
+      </c>
+      <c r="W167">
+        <v>1.3</v>
+      </c>
+      <c r="X167">
+        <v>10</v>
+      </c>
+      <c r="Y167">
+        <v>1.06</v>
+      </c>
+      <c r="Z167">
+        <v>2.56</v>
+      </c>
+      <c r="AA167">
+        <v>3.06</v>
+      </c>
+      <c r="AB167">
+        <v>2.83</v>
+      </c>
+      <c r="AC167">
+        <v>1.04</v>
+      </c>
+      <c r="AD167">
+        <v>9.5</v>
+      </c>
+      <c r="AE167">
+        <v>1.35</v>
+      </c>
+      <c r="AF167">
+        <v>3.14</v>
+      </c>
+      <c r="AG167">
+        <v>2.05</v>
+      </c>
+      <c r="AH167">
+        <v>1.61</v>
+      </c>
+      <c r="AI167">
+        <v>1.83</v>
+      </c>
+      <c r="AJ167">
+        <v>1.83</v>
+      </c>
+      <c r="AK167">
+        <v>1.38</v>
+      </c>
+      <c r="AL167">
+        <v>1.33</v>
+      </c>
+      <c r="AM167">
+        <v>1.53</v>
+      </c>
+      <c r="AN167">
+        <v>1</v>
+      </c>
+      <c r="AO167">
+        <v>0.71</v>
+      </c>
+      <c r="AP167">
+        <v>1</v>
+      </c>
+      <c r="AQ167">
+        <v>0.73</v>
+      </c>
+      <c r="AR167">
+        <v>1.48</v>
+      </c>
+      <c r="AS167">
+        <v>1.46</v>
+      </c>
+      <c r="AT167">
+        <v>2.94</v>
+      </c>
+      <c r="AU167">
+        <v>3</v>
+      </c>
+      <c r="AV167">
+        <v>6</v>
+      </c>
+      <c r="AW167">
+        <v>7</v>
+      </c>
+      <c r="AX167">
+        <v>8</v>
+      </c>
+      <c r="AY167">
+        <v>12</v>
+      </c>
+      <c r="AZ167">
+        <v>18</v>
+      </c>
+      <c r="BA167">
+        <v>6</v>
+      </c>
+      <c r="BB167">
+        <v>3</v>
+      </c>
+      <c r="BC167">
+        <v>9</v>
+      </c>
+      <c r="BD167">
+        <v>1.91</v>
+      </c>
+      <c r="BE167">
+        <v>6.6</v>
+      </c>
+      <c r="BF167">
+        <v>2.39</v>
+      </c>
+      <c r="BG167">
+        <v>1.17</v>
+      </c>
+      <c r="BH167">
+        <v>3.95</v>
+      </c>
+      <c r="BI167">
+        <v>1.36</v>
+      </c>
+      <c r="BJ167">
+        <v>2.78</v>
+      </c>
+      <c r="BK167">
+        <v>1.7</v>
+      </c>
+      <c r="BL167">
+        <v>2.11</v>
+      </c>
+      <c r="BM167">
+        <v>2.13</v>
+      </c>
+      <c r="BN167">
+        <v>1.69</v>
+      </c>
+      <c r="BO167">
+        <v>2.7</v>
+      </c>
+      <c r="BP167">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7784949</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45732.52083333334</v>
+      </c>
+      <c r="F168">
+        <v>28</v>
+      </c>
+      <c r="G168" t="s">
+        <v>79</v>
+      </c>
+      <c r="H168" t="s">
+        <v>73</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="M168">
+        <v>2</v>
+      </c>
+      <c r="N168">
+        <v>3</v>
+      </c>
+      <c r="O168" t="s">
+        <v>208</v>
+      </c>
+      <c r="P168" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q168">
+        <v>2.75</v>
+      </c>
+      <c r="R168">
+        <v>2.38</v>
+      </c>
+      <c r="S168">
+        <v>3.4</v>
+      </c>
+      <c r="T168">
+        <v>1.3</v>
+      </c>
+      <c r="U168">
+        <v>3.4</v>
+      </c>
+      <c r="V168">
+        <v>2.5</v>
+      </c>
+      <c r="W168">
+        <v>1.5</v>
+      </c>
+      <c r="X168">
+        <v>6</v>
+      </c>
+      <c r="Y168">
+        <v>1.13</v>
+      </c>
+      <c r="Z168">
+        <v>2.22</v>
+      </c>
+      <c r="AA168">
+        <v>3.4</v>
+      </c>
+      <c r="AB168">
+        <v>3.07</v>
+      </c>
+      <c r="AC168">
+        <v>1.03</v>
+      </c>
+      <c r="AD168">
+        <v>12</v>
+      </c>
+      <c r="AE168">
+        <v>1.19</v>
+      </c>
+      <c r="AF168">
+        <v>4.56</v>
+      </c>
+      <c r="AG168">
+        <v>1.55</v>
+      </c>
+      <c r="AH168">
+        <v>2.2</v>
+      </c>
+      <c r="AI168">
+        <v>1.5</v>
+      </c>
+      <c r="AJ168">
+        <v>2.5</v>
+      </c>
+      <c r="AK168">
+        <v>1.36</v>
+      </c>
+      <c r="AL168">
+        <v>1.28</v>
+      </c>
+      <c r="AM168">
+        <v>1.65</v>
+      </c>
+      <c r="AN168">
+        <v>2</v>
+      </c>
+      <c r="AO168">
+        <v>0.77</v>
+      </c>
+      <c r="AP168">
+        <v>1.86</v>
+      </c>
+      <c r="AQ168">
+        <v>0.93</v>
+      </c>
+      <c r="AR168">
+        <v>1.83</v>
+      </c>
+      <c r="AS168">
+        <v>1.8</v>
+      </c>
+      <c r="AT168">
+        <v>3.63</v>
+      </c>
+      <c r="AU168">
+        <v>7</v>
+      </c>
+      <c r="AV168">
+        <v>9</v>
+      </c>
+      <c r="AW168">
+        <v>14</v>
+      </c>
+      <c r="AX168">
+        <v>6</v>
+      </c>
+      <c r="AY168">
+        <v>23</v>
+      </c>
+      <c r="AZ168">
+        <v>19</v>
+      </c>
+      <c r="BA168">
+        <v>3</v>
+      </c>
+      <c r="BB168">
+        <v>2</v>
+      </c>
+      <c r="BC168">
+        <v>5</v>
+      </c>
+      <c r="BD168">
+        <v>1.96</v>
+      </c>
+      <c r="BE168">
+        <v>6.75</v>
+      </c>
+      <c r="BF168">
+        <v>2.3</v>
+      </c>
+      <c r="BG168">
+        <v>1.13</v>
+      </c>
+      <c r="BH168">
+        <v>4.6</v>
+      </c>
+      <c r="BI168">
+        <v>1.28</v>
+      </c>
+      <c r="BJ168">
+        <v>3.08</v>
+      </c>
+      <c r="BK168">
+        <v>1.6</v>
+      </c>
+      <c r="BL168">
+        <v>2.28</v>
+      </c>
+      <c r="BM168">
+        <v>1.93</v>
+      </c>
+      <c r="BN168">
+        <v>1.86</v>
+      </c>
+      <c r="BO168">
+        <v>2.39</v>
+      </c>
+      <c r="BP168">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7784950</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45732.52083333334</v>
+      </c>
+      <c r="F169">
+        <v>28</v>
+      </c>
+      <c r="G169" t="s">
+        <v>70</v>
+      </c>
+      <c r="H169" t="s">
+        <v>72</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>2</v>
+      </c>
+      <c r="M169">
+        <v>1</v>
+      </c>
+      <c r="N169">
+        <v>3</v>
+      </c>
+      <c r="O169" t="s">
+        <v>209</v>
+      </c>
+      <c r="P169" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q169">
+        <v>1.91</v>
+      </c>
+      <c r="R169">
+        <v>2.6</v>
+      </c>
+      <c r="S169">
+        <v>6.5</v>
+      </c>
+      <c r="T169">
+        <v>1.29</v>
+      </c>
+      <c r="U169">
+        <v>3.5</v>
+      </c>
+      <c r="V169">
+        <v>2.25</v>
+      </c>
+      <c r="W169">
+        <v>1.57</v>
+      </c>
+      <c r="X169">
+        <v>5.5</v>
+      </c>
+      <c r="Y169">
+        <v>1.14</v>
+      </c>
+      <c r="Z169">
+        <v>1.39</v>
+      </c>
+      <c r="AA169">
+        <v>4.9</v>
+      </c>
+      <c r="AB169">
+        <v>6.8</v>
+      </c>
+      <c r="AC169">
+        <v>1.02</v>
+      </c>
+      <c r="AD169">
+        <v>14.5</v>
+      </c>
+      <c r="AE169">
+        <v>1.17</v>
+      </c>
+      <c r="AF169">
+        <v>4.92</v>
+      </c>
+      <c r="AG169">
+        <v>1.47</v>
+      </c>
+      <c r="AH169">
+        <v>2.57</v>
+      </c>
+      <c r="AI169">
+        <v>1.73</v>
+      </c>
+      <c r="AJ169">
+        <v>2</v>
+      </c>
+      <c r="AK169">
+        <v>1.11</v>
+      </c>
+      <c r="AL169">
+        <v>1.17</v>
+      </c>
+      <c r="AM169">
+        <v>2.8</v>
+      </c>
+      <c r="AN169">
+        <v>1.93</v>
+      </c>
+      <c r="AO169">
+        <v>0.29</v>
+      </c>
+      <c r="AP169">
+        <v>2</v>
+      </c>
+      <c r="AQ169">
+        <v>0.27</v>
+      </c>
+      <c r="AR169">
+        <v>1.99</v>
+      </c>
+      <c r="AS169">
+        <v>1.2</v>
+      </c>
+      <c r="AT169">
+        <v>3.19</v>
+      </c>
+      <c r="AU169">
+        <v>-1</v>
+      </c>
+      <c r="AV169">
+        <v>-1</v>
+      </c>
+      <c r="AW169">
+        <v>-1</v>
+      </c>
+      <c r="AX169">
+        <v>-1</v>
+      </c>
+      <c r="AY169">
+        <v>-1</v>
+      </c>
+      <c r="AZ169">
+        <v>-1</v>
+      </c>
+      <c r="BA169">
+        <v>-1</v>
+      </c>
+      <c r="BB169">
+        <v>-1</v>
+      </c>
+      <c r="BC169">
+        <v>-1</v>
+      </c>
+      <c r="BD169">
+        <v>1.22</v>
+      </c>
+      <c r="BE169">
+        <v>11</v>
+      </c>
+      <c r="BF169">
+        <v>5.45</v>
+      </c>
+      <c r="BG169">
+        <v>1.19</v>
+      </c>
+      <c r="BH169">
+        <v>3.76</v>
+      </c>
+      <c r="BI169">
+        <v>1.4</v>
+      </c>
+      <c r="BJ169">
+        <v>2.64</v>
+      </c>
+      <c r="BK169">
+        <v>1.74</v>
+      </c>
+      <c r="BL169">
+        <v>2.06</v>
+      </c>
+      <c r="BM169">
+        <v>2.2</v>
+      </c>
+      <c r="BN169">
+        <v>1.64</v>
+      </c>
+      <c r="BO169">
+        <v>2.78</v>
+      </c>
+      <c r="BP169">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -36029,31 +36029,31 @@
         <v>3.19</v>
       </c>
       <c r="AU169">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV169">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW169">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX169">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY169">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ169">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BA169">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BB169">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC169">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD169">
         <v>1.22</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="302">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -918,6 +918,9 @@
   <si>
     <t>['1', '78']</t>
   </si>
+  <si>
+    <t>['31', '83']</t>
+  </si>
 </sst>
 </file>
 
@@ -1278,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1612,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -2027,7 +2030,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ4">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2230,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ5">
         <v>0.73</v>
@@ -2645,7 +2648,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ7">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3054,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3675,7 +3678,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ12">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR12">
         <v>2.07</v>
@@ -4496,10 +4499,10 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ16">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR16">
         <v>2.11</v>
@@ -4911,7 +4914,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ18">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>1.45</v>
@@ -5114,7 +5117,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ19">
         <v>1.54</v>
@@ -5323,7 +5326,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ20">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR20">
         <v>1.02</v>
@@ -5526,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21">
         <v>0.27</v>
@@ -6144,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ24">
         <v>1.21</v>
@@ -7177,7 +7180,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ29">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7380,7 +7383,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ30">
         <v>1.43</v>
@@ -7792,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8001,7 +8004,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ33">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>1.17</v>
@@ -8410,10 +8413,10 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ35">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.92</v>
@@ -9031,7 +9034,7 @@
         <v>1</v>
       </c>
       <c r="AQ38">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR38">
         <v>1.38</v>
@@ -9443,7 +9446,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ40">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR40">
         <v>1.54</v>
@@ -9646,7 +9649,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ41">
         <v>1.15</v>
@@ -10267,7 +10270,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10676,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ46">
         <v>0.93</v>
@@ -11294,7 +11297,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ49">
         <v>0.27</v>
@@ -11500,10 +11503,10 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ50">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR50">
         <v>1.38</v>
@@ -12533,7 +12536,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ55">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR55">
         <v>1.62</v>
@@ -12942,7 +12945,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ57">
         <v>1.21</v>
@@ -13357,7 +13360,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ59">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.76</v>
@@ -14387,7 +14390,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ64">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14590,10 +14593,10 @@
         <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ65">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14796,7 +14799,7 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ66">
         <v>0.93</v>
@@ -15005,7 +15008,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ67">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.55</v>
@@ -15414,7 +15417,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ69">
         <v>1.54</v>
@@ -15826,7 +15829,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ71">
         <v>1.43</v>
@@ -17065,7 +17068,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ77">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR77">
         <v>1.84</v>
@@ -17268,10 +17271,10 @@
         <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ78">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -18298,7 +18301,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ83">
         <v>1.21</v>
@@ -18507,7 +18510,7 @@
         <v>1</v>
       </c>
       <c r="AQ84">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>1.54</v>
@@ -18710,7 +18713,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ85">
         <v>1.15</v>
@@ -19534,7 +19537,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ89">
         <v>1.54</v>
@@ -19743,7 +19746,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ90">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -19949,7 +19952,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR91">
         <v>1.8</v>
@@ -21182,10 +21185,10 @@
         <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ97">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21391,7 +21394,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21594,7 +21597,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99">
         <v>0.93</v>
@@ -23242,10 +23245,10 @@
         <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ107">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23448,7 +23451,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23657,7 +23660,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ109">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>1.41</v>
@@ -23860,7 +23863,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ110">
         <v>0.27</v>
@@ -24066,7 +24069,7 @@
         <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ111">
         <v>0.93</v>
@@ -24275,7 +24278,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.84</v>
@@ -24481,7 +24484,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ113">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR113">
         <v>1.39</v>
@@ -24684,7 +24687,7 @@
         <v>1.56</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ114">
         <v>1.43</v>
@@ -25305,7 +25308,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ117">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR117">
         <v>1</v>
@@ -26538,7 +26541,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ123">
         <v>0.73</v>
@@ -26953,7 +26956,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ125">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.65</v>
@@ -27774,10 +27777,10 @@
         <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ129">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR129">
         <v>1.71</v>
@@ -28186,10 +28189,10 @@
         <v>0.7</v>
       </c>
       <c r="AP131">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ131">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR131">
         <v>1.95</v>
@@ -28807,7 +28810,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ134">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR134">
         <v>1.83</v>
@@ -29010,7 +29013,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ135">
         <v>0.93</v>
@@ -29216,7 +29219,7 @@
         <v>0.91</v>
       </c>
       <c r="AP136">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ136">
         <v>0.73</v>
@@ -29837,7 +29840,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ139">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.48</v>
@@ -30040,7 +30043,7 @@
         <v>1.45</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ140">
         <v>1.21</v>
@@ -30246,7 +30249,7 @@
         <v>1.55</v>
       </c>
       <c r="AP141">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ141">
         <v>1.54</v>
@@ -30661,7 +30664,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ143">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR143">
         <v>1.03</v>
@@ -31073,7 +31076,7 @@
         <v>1</v>
       </c>
       <c r="AQ145">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR145">
         <v>1.53</v>
@@ -31485,7 +31488,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ147">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR147">
         <v>1.5</v>
@@ -32100,7 +32103,7 @@
         <v>1.36</v>
       </c>
       <c r="AP150">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ150">
         <v>1.15</v>
@@ -32721,7 +32724,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ153">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR153">
         <v>1.28</v>
@@ -32927,7 +32930,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ154">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR154">
         <v>1.84</v>
@@ -33130,7 +33133,7 @@
         <v>1.42</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ155">
         <v>1.54</v>
@@ -33748,7 +33751,7 @@
         <v>0.92</v>
       </c>
       <c r="AP158">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -34369,7 +34372,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ161">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR161">
         <v>1.53</v>
@@ -34572,7 +34575,7 @@
         <v>1.25</v>
       </c>
       <c r="AP162">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ162">
         <v>1.15</v>
@@ -34987,7 +34990,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ164">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR164">
         <v>1.99</v>
@@ -36014,7 +36017,7 @@
         <v>0.29</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ169">
         <v>0.27</v>
@@ -36093,6 +36096,624 @@
       </c>
       <c r="BP169">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7784951</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45745.58333333334</v>
+      </c>
+      <c r="F170">
+        <v>29</v>
+      </c>
+      <c r="G170" t="s">
+        <v>77</v>
+      </c>
+      <c r="H170" t="s">
+        <v>71</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>2</v>
+      </c>
+      <c r="O170" t="s">
+        <v>126</v>
+      </c>
+      <c r="P170" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q170">
+        <v>2.38</v>
+      </c>
+      <c r="R170">
+        <v>2.2</v>
+      </c>
+      <c r="S170">
+        <v>5</v>
+      </c>
+      <c r="T170">
+        <v>1.4</v>
+      </c>
+      <c r="U170">
+        <v>2.75</v>
+      </c>
+      <c r="V170">
+        <v>3</v>
+      </c>
+      <c r="W170">
+        <v>1.36</v>
+      </c>
+      <c r="X170">
+        <v>8</v>
+      </c>
+      <c r="Y170">
+        <v>1.08</v>
+      </c>
+      <c r="Z170">
+        <v>1.72</v>
+      </c>
+      <c r="AA170">
+        <v>3.68</v>
+      </c>
+      <c r="AB170">
+        <v>4.6</v>
+      </c>
+      <c r="AC170">
+        <v>1.05</v>
+      </c>
+      <c r="AD170">
+        <v>9</v>
+      </c>
+      <c r="AE170">
+        <v>1.3</v>
+      </c>
+      <c r="AF170">
+        <v>3.4</v>
+      </c>
+      <c r="AG170">
+        <v>1.92</v>
+      </c>
+      <c r="AH170">
+        <v>1.82</v>
+      </c>
+      <c r="AI170">
+        <v>1.83</v>
+      </c>
+      <c r="AJ170">
+        <v>1.83</v>
+      </c>
+      <c r="AK170">
+        <v>1.2</v>
+      </c>
+      <c r="AL170">
+        <v>1.26</v>
+      </c>
+      <c r="AM170">
+        <v>2.05</v>
+      </c>
+      <c r="AN170">
+        <v>1.77</v>
+      </c>
+      <c r="AO170">
+        <v>0.71</v>
+      </c>
+      <c r="AP170">
+        <v>1.71</v>
+      </c>
+      <c r="AQ170">
+        <v>0.73</v>
+      </c>
+      <c r="AR170">
+        <v>1.68</v>
+      </c>
+      <c r="AS170">
+        <v>1.23</v>
+      </c>
+      <c r="AT170">
+        <v>2.91</v>
+      </c>
+      <c r="AU170">
+        <v>7</v>
+      </c>
+      <c r="AV170">
+        <v>6</v>
+      </c>
+      <c r="AW170">
+        <v>10</v>
+      </c>
+      <c r="AX170">
+        <v>10</v>
+      </c>
+      <c r="AY170">
+        <v>23</v>
+      </c>
+      <c r="AZ170">
+        <v>17</v>
+      </c>
+      <c r="BA170">
+        <v>5</v>
+      </c>
+      <c r="BB170">
+        <v>5</v>
+      </c>
+      <c r="BC170">
+        <v>10</v>
+      </c>
+      <c r="BD170">
+        <v>1.35</v>
+      </c>
+      <c r="BE170">
+        <v>7</v>
+      </c>
+      <c r="BF170">
+        <v>3.55</v>
+      </c>
+      <c r="BG170">
+        <v>1.3</v>
+      </c>
+      <c r="BH170">
+        <v>3.05</v>
+      </c>
+      <c r="BI170">
+        <v>1.53</v>
+      </c>
+      <c r="BJ170">
+        <v>2.28</v>
+      </c>
+      <c r="BK170">
+        <v>1.86</v>
+      </c>
+      <c r="BL170">
+        <v>1.81</v>
+      </c>
+      <c r="BM170">
+        <v>2.33</v>
+      </c>
+      <c r="BN170">
+        <v>1.5</v>
+      </c>
+      <c r="BO170">
+        <v>2.95</v>
+      </c>
+      <c r="BP170">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7784952</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45745.58333333334</v>
+      </c>
+      <c r="F171">
+        <v>29</v>
+      </c>
+      <c r="G171" t="s">
+        <v>73</v>
+      </c>
+      <c r="H171" t="s">
+        <v>80</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171" t="s">
+        <v>115</v>
+      </c>
+      <c r="P171" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q171">
+        <v>2.3</v>
+      </c>
+      <c r="R171">
+        <v>2.5</v>
+      </c>
+      <c r="S171">
+        <v>4.33</v>
+      </c>
+      <c r="T171">
+        <v>1.29</v>
+      </c>
+      <c r="U171">
+        <v>3.5</v>
+      </c>
+      <c r="V171">
+        <v>2.25</v>
+      </c>
+      <c r="W171">
+        <v>1.57</v>
+      </c>
+      <c r="X171">
+        <v>5.5</v>
+      </c>
+      <c r="Y171">
+        <v>1.14</v>
+      </c>
+      <c r="Z171">
+        <v>1.71</v>
+      </c>
+      <c r="AA171">
+        <v>3.97</v>
+      </c>
+      <c r="AB171">
+        <v>4.3</v>
+      </c>
+      <c r="AC171">
+        <v>1.01</v>
+      </c>
+      <c r="AD171">
+        <v>13</v>
+      </c>
+      <c r="AE171">
+        <v>1.17</v>
+      </c>
+      <c r="AF171">
+        <v>5</v>
+      </c>
+      <c r="AG171">
+        <v>1.52</v>
+      </c>
+      <c r="AH171">
+        <v>2.43</v>
+      </c>
+      <c r="AI171">
+        <v>1.53</v>
+      </c>
+      <c r="AJ171">
+        <v>2.38</v>
+      </c>
+      <c r="AK171">
+        <v>1.23</v>
+      </c>
+      <c r="AL171">
+        <v>1.23</v>
+      </c>
+      <c r="AM171">
+        <v>2</v>
+      </c>
+      <c r="AN171">
+        <v>2.14</v>
+      </c>
+      <c r="AO171">
+        <v>1.07</v>
+      </c>
+      <c r="AP171">
+        <v>2.2</v>
+      </c>
+      <c r="AQ171">
+        <v>1</v>
+      </c>
+      <c r="AR171">
+        <v>2.02</v>
+      </c>
+      <c r="AS171">
+        <v>1.47</v>
+      </c>
+      <c r="AT171">
+        <v>3.49</v>
+      </c>
+      <c r="AU171">
+        <v>8</v>
+      </c>
+      <c r="AV171">
+        <v>3</v>
+      </c>
+      <c r="AW171">
+        <v>6</v>
+      </c>
+      <c r="AX171">
+        <v>7</v>
+      </c>
+      <c r="AY171">
+        <v>18</v>
+      </c>
+      <c r="AZ171">
+        <v>13</v>
+      </c>
+      <c r="BA171">
+        <v>9</v>
+      </c>
+      <c r="BB171">
+        <v>2</v>
+      </c>
+      <c r="BC171">
+        <v>11</v>
+      </c>
+      <c r="BD171">
+        <v>1.49</v>
+      </c>
+      <c r="BE171">
+        <v>7</v>
+      </c>
+      <c r="BF171">
+        <v>2.8</v>
+      </c>
+      <c r="BG171">
+        <v>1.19</v>
+      </c>
+      <c r="BH171">
+        <v>3.95</v>
+      </c>
+      <c r="BI171">
+        <v>1.34</v>
+      </c>
+      <c r="BJ171">
+        <v>2.9</v>
+      </c>
+      <c r="BK171">
+        <v>1.56</v>
+      </c>
+      <c r="BL171">
+        <v>2.2</v>
+      </c>
+      <c r="BM171">
+        <v>1.88</v>
+      </c>
+      <c r="BN171">
+        <v>1.78</v>
+      </c>
+      <c r="BO171">
+        <v>2.35</v>
+      </c>
+      <c r="BP171">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7784953</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45745.6875</v>
+      </c>
+      <c r="F172">
+        <v>29</v>
+      </c>
+      <c r="G172" t="s">
+        <v>70</v>
+      </c>
+      <c r="H172" t="s">
+        <v>76</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>2</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172" t="s">
+        <v>83</v>
+      </c>
+      <c r="P172" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q172">
+        <v>2.88</v>
+      </c>
+      <c r="R172">
+        <v>2.25</v>
+      </c>
+      <c r="S172">
+        <v>3.4</v>
+      </c>
+      <c r="T172">
+        <v>1.33</v>
+      </c>
+      <c r="U172">
+        <v>3.25</v>
+      </c>
+      <c r="V172">
+        <v>2.63</v>
+      </c>
+      <c r="W172">
+        <v>1.44</v>
+      </c>
+      <c r="X172">
+        <v>7</v>
+      </c>
+      <c r="Y172">
+        <v>1.1</v>
+      </c>
+      <c r="Z172">
+        <v>2.31</v>
+      </c>
+      <c r="AA172">
+        <v>3.25</v>
+      </c>
+      <c r="AB172">
+        <v>3.04</v>
+      </c>
+      <c r="AC172">
+        <v>1.05</v>
+      </c>
+      <c r="AD172">
+        <v>9.5</v>
+      </c>
+      <c r="AE172">
+        <v>1.25</v>
+      </c>
+      <c r="AF172">
+        <v>3.8</v>
+      </c>
+      <c r="AG172">
+        <v>1.7</v>
+      </c>
+      <c r="AH172">
+        <v>1.95</v>
+      </c>
+      <c r="AI172">
+        <v>1.57</v>
+      </c>
+      <c r="AJ172">
+        <v>2.25</v>
+      </c>
+      <c r="AK172">
+        <v>1.4</v>
+      </c>
+      <c r="AL172">
+        <v>1.28</v>
+      </c>
+      <c r="AM172">
+        <v>1.6</v>
+      </c>
+      <c r="AN172">
+        <v>2</v>
+      </c>
+      <c r="AO172">
+        <v>1.57</v>
+      </c>
+      <c r="AP172">
+        <v>1.88</v>
+      </c>
+      <c r="AQ172">
+        <v>1.67</v>
+      </c>
+      <c r="AR172">
+        <v>1.98</v>
+      </c>
+      <c r="AS172">
+        <v>1.56</v>
+      </c>
+      <c r="AT172">
+        <v>3.54</v>
+      </c>
+      <c r="AU172">
+        <v>10</v>
+      </c>
+      <c r="AV172">
+        <v>4</v>
+      </c>
+      <c r="AW172">
+        <v>7</v>
+      </c>
+      <c r="AX172">
+        <v>7</v>
+      </c>
+      <c r="AY172">
+        <v>20</v>
+      </c>
+      <c r="AZ172">
+        <v>15</v>
+      </c>
+      <c r="BA172">
+        <v>9</v>
+      </c>
+      <c r="BB172">
+        <v>5</v>
+      </c>
+      <c r="BC172">
+        <v>14</v>
+      </c>
+      <c r="BD172">
+        <v>1.88</v>
+      </c>
+      <c r="BE172">
+        <v>6.4</v>
+      </c>
+      <c r="BF172">
+        <v>2.12</v>
+      </c>
+      <c r="BG172">
+        <v>1.36</v>
+      </c>
+      <c r="BH172">
+        <v>2.8</v>
+      </c>
+      <c r="BI172">
+        <v>1.61</v>
+      </c>
+      <c r="BJ172">
+        <v>2.12</v>
+      </c>
+      <c r="BK172">
+        <v>1.98</v>
+      </c>
+      <c r="BL172">
+        <v>1.7</v>
+      </c>
+      <c r="BM172">
+        <v>2.55</v>
+      </c>
+      <c r="BN172">
+        <v>1.43</v>
+      </c>
+      <c r="BO172">
+        <v>3.4</v>
+      </c>
+      <c r="BP172">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -921,6 +921,15 @@
   <si>
     <t>['31', '83']</t>
   </si>
+  <si>
+    <t>['49', '70']</t>
+  </si>
+  <si>
+    <t>['3', '15', '27', '79']</t>
+  </si>
+  <si>
+    <t>['45+2', '68']</t>
+  </si>
 </sst>
 </file>
 
@@ -1281,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1824,7 +1833,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2027,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -2439,10 +2448,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ6">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3263,10 +3272,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ10">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -4293,10 +4302,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ15">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR15">
         <v>1.44</v>
@@ -4911,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5120,7 +5129,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ19">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -5323,7 +5332,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20">
         <v>0.73</v>
@@ -6150,7 +6159,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ24">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>1.94</v>
@@ -6562,7 +6571,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ26">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR26">
         <v>1.85</v>
@@ -6971,7 +6980,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ28">
         <v>0.73</v>
@@ -7386,7 +7395,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ30">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -8001,7 +8010,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ33">
         <v>1.67</v>
@@ -8210,7 +8219,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ34">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>2.41</v>
@@ -8619,7 +8628,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ36">
         <v>1.15</v>
@@ -8828,7 +8837,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ37">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>1.76</v>
@@ -9031,7 +9040,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ38">
         <v>1.67</v>
@@ -9240,7 +9249,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ39">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR39">
         <v>2.16</v>
@@ -9443,7 +9452,7 @@
         <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ40">
         <v>0.73</v>
@@ -9855,7 +9864,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ42">
         <v>0.93</v>
@@ -10064,7 +10073,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ43">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
@@ -11094,7 +11103,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ48">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR48">
         <v>1.38</v>
@@ -11915,7 +11924,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ52">
         <v>0.93</v>
@@ -12739,10 +12748,10 @@
         <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ56">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR56">
         <v>1.56</v>
@@ -12948,7 +12957,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ57">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
         <v>1.51</v>
@@ -13563,7 +13572,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ60">
         <v>0.27</v>
@@ -13975,7 +13984,7 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ62">
         <v>0.93</v>
@@ -14181,10 +14190,10 @@
         <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ63">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -15420,7 +15429,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ69">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
@@ -15832,7 +15841,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ71">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR71">
         <v>1.55</v>
@@ -16035,7 +16044,7 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ72">
         <v>1.15</v>
@@ -16244,7 +16253,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ73">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -17065,7 +17074,7 @@
         <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ77">
         <v>1.67</v>
@@ -17683,7 +17692,7 @@
         <v>0.83</v>
       </c>
       <c r="AP80">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17892,7 +17901,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR81">
         <v>0.99</v>
@@ -18098,7 +18107,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ82">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR82">
         <v>1.87</v>
@@ -18304,7 +18313,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ83">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18507,7 +18516,7 @@
         <v>0.83</v>
       </c>
       <c r="AP84">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -19125,7 +19134,7 @@
         <v>0.14</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ87">
         <v>0.27</v>
@@ -19331,7 +19340,7 @@
         <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ88">
         <v>0.73</v>
@@ -19540,7 +19549,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ89">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR89">
         <v>1.82</v>
@@ -20364,7 +20373,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>0.95</v>
@@ -20773,7 +20782,7 @@
         <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ95">
         <v>0.73</v>
@@ -21391,7 +21400,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ98">
         <v>0.73</v>
@@ -22009,10 +22018,10 @@
         <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ101">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR101">
         <v>1.77</v>
@@ -22424,7 +22433,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ103">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR103">
         <v>1.81</v>
@@ -22627,10 +22636,10 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ104">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
         <v>1.23</v>
@@ -24690,7 +24699,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ114">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR114">
         <v>1.86</v>
@@ -24893,10 +24902,10 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ115">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25099,7 +25108,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ116">
         <v>0.93</v>
@@ -25511,7 +25520,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ118">
         <v>1.15</v>
@@ -26132,7 +26141,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ121">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR121">
         <v>1.67</v>
@@ -26335,7 +26344,7 @@
         <v>0.7</v>
       </c>
       <c r="AP122">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ122">
         <v>0.93</v>
@@ -27162,7 +27171,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ126">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR126">
         <v>1.41</v>
@@ -27571,7 +27580,7 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -28398,7 +28407,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ132">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
@@ -28601,10 +28610,10 @@
         <v>1.4</v>
       </c>
       <c r="AP133">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ133">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR133">
         <v>1.28</v>
@@ -28807,7 +28816,7 @@
         <v>0.64</v>
       </c>
       <c r="AP134">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ134">
         <v>0.73</v>
@@ -29428,7 +29437,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ137">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR137">
         <v>1.97</v>
@@ -30046,7 +30055,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ140">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30252,7 +30261,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ141">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR141">
         <v>1.74</v>
@@ -30455,7 +30464,7 @@
         <v>0.91</v>
       </c>
       <c r="AP142">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ142">
         <v>0.93</v>
@@ -31073,7 +31082,7 @@
         <v>1.18</v>
       </c>
       <c r="AP145">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ145">
         <v>1.67</v>
@@ -31279,7 +31288,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ146">
         <v>0.93</v>
@@ -31694,7 +31703,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ148">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR148">
         <v>1.86</v>
@@ -32721,7 +32730,7 @@
         <v>1.15</v>
       </c>
       <c r="AP153">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -32927,7 +32936,7 @@
         <v>1.33</v>
       </c>
       <c r="AP154">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ154">
         <v>1.67</v>
@@ -33136,7 +33145,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ155">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR155">
         <v>2</v>
@@ -33339,7 +33348,7 @@
         <v>0.83</v>
       </c>
       <c r="AP156">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ156">
         <v>0.93</v>
@@ -33548,7 +33557,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ157">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -34784,7 +34793,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ163">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR163">
         <v>1.73</v>
@@ -35402,7 +35411,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ166">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR166">
         <v>1.55</v>
@@ -35605,7 +35614,7 @@
         <v>0.71</v>
       </c>
       <c r="AP167">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ167">
         <v>0.73</v>
@@ -36714,6 +36723,624 @@
       </c>
       <c r="BP172">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7784954</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45746.38541666666</v>
+      </c>
+      <c r="F173">
+        <v>29</v>
+      </c>
+      <c r="G173" t="s">
+        <v>72</v>
+      </c>
+      <c r="H173" t="s">
+        <v>79</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>2</v>
+      </c>
+      <c r="N173">
+        <v>2</v>
+      </c>
+      <c r="O173" t="s">
+        <v>83</v>
+      </c>
+      <c r="P173" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q173">
+        <v>5.5</v>
+      </c>
+      <c r="R173">
+        <v>2.5</v>
+      </c>
+      <c r="S173">
+        <v>2</v>
+      </c>
+      <c r="T173">
+        <v>1.25</v>
+      </c>
+      <c r="U173">
+        <v>3.75</v>
+      </c>
+      <c r="V173">
+        <v>2.2</v>
+      </c>
+      <c r="W173">
+        <v>1.62</v>
+      </c>
+      <c r="X173">
+        <v>5</v>
+      </c>
+      <c r="Y173">
+        <v>1.17</v>
+      </c>
+      <c r="Z173">
+        <v>5.5</v>
+      </c>
+      <c r="AA173">
+        <v>4.6</v>
+      </c>
+      <c r="AB173">
+        <v>1.49</v>
+      </c>
+      <c r="AC173">
+        <v>1.01</v>
+      </c>
+      <c r="AD173">
+        <v>13</v>
+      </c>
+      <c r="AE173">
+        <v>1.15</v>
+      </c>
+      <c r="AF173">
+        <v>5.25</v>
+      </c>
+      <c r="AG173">
+        <v>1.45</v>
+      </c>
+      <c r="AH173">
+        <v>2.63</v>
+      </c>
+      <c r="AI173">
+        <v>1.62</v>
+      </c>
+      <c r="AJ173">
+        <v>2.2</v>
+      </c>
+      <c r="AK173">
+        <v>2.45</v>
+      </c>
+      <c r="AL173">
+        <v>1.19</v>
+      </c>
+      <c r="AM173">
+        <v>1.15</v>
+      </c>
+      <c r="AN173">
+        <v>1.23</v>
+      </c>
+      <c r="AO173">
+        <v>1.43</v>
+      </c>
+      <c r="AP173">
+        <v>1.14</v>
+      </c>
+      <c r="AQ173">
+        <v>1.53</v>
+      </c>
+      <c r="AR173">
+        <v>1.3</v>
+      </c>
+      <c r="AS173">
+        <v>1.79</v>
+      </c>
+      <c r="AT173">
+        <v>3.09</v>
+      </c>
+      <c r="AU173">
+        <v>4</v>
+      </c>
+      <c r="AV173">
+        <v>9</v>
+      </c>
+      <c r="AW173">
+        <v>4</v>
+      </c>
+      <c r="AX173">
+        <v>10</v>
+      </c>
+      <c r="AY173">
+        <v>9</v>
+      </c>
+      <c r="AZ173">
+        <v>21</v>
+      </c>
+      <c r="BA173">
+        <v>2</v>
+      </c>
+      <c r="BB173">
+        <v>3</v>
+      </c>
+      <c r="BC173">
+        <v>5</v>
+      </c>
+      <c r="BD173">
+        <v>3.05</v>
+      </c>
+      <c r="BE173">
+        <v>7</v>
+      </c>
+      <c r="BF173">
+        <v>1.45</v>
+      </c>
+      <c r="BG173">
+        <v>1.22</v>
+      </c>
+      <c r="BH173">
+        <v>3.65</v>
+      </c>
+      <c r="BI173">
+        <v>1.4</v>
+      </c>
+      <c r="BJ173">
+        <v>2.65</v>
+      </c>
+      <c r="BK173">
+        <v>1.65</v>
+      </c>
+      <c r="BL173">
+        <v>2.06</v>
+      </c>
+      <c r="BM173">
+        <v>2.02</v>
+      </c>
+      <c r="BN173">
+        <v>1.68</v>
+      </c>
+      <c r="BO173">
+        <v>2.55</v>
+      </c>
+      <c r="BP173">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7784956</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45746.47916666666</v>
+      </c>
+      <c r="F174">
+        <v>29</v>
+      </c>
+      <c r="G174" t="s">
+        <v>74</v>
+      </c>
+      <c r="H174" t="s">
+        <v>75</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>3</v>
+      </c>
+      <c r="K174">
+        <v>3</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <v>4</v>
+      </c>
+      <c r="N174">
+        <v>5</v>
+      </c>
+      <c r="O174" t="s">
+        <v>208</v>
+      </c>
+      <c r="P174" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q174">
+        <v>2.5</v>
+      </c>
+      <c r="R174">
+        <v>2.3</v>
+      </c>
+      <c r="S174">
+        <v>4</v>
+      </c>
+      <c r="T174">
+        <v>1.33</v>
+      </c>
+      <c r="U174">
+        <v>3.25</v>
+      </c>
+      <c r="V174">
+        <v>2.63</v>
+      </c>
+      <c r="W174">
+        <v>1.44</v>
+      </c>
+      <c r="X174">
+        <v>6.5</v>
+      </c>
+      <c r="Y174">
+        <v>1.11</v>
+      </c>
+      <c r="Z174">
+        <v>1.92</v>
+      </c>
+      <c r="AA174">
+        <v>3.79</v>
+      </c>
+      <c r="AB174">
+        <v>3.5</v>
+      </c>
+      <c r="AC174">
+        <v>1.04</v>
+      </c>
+      <c r="AD174">
+        <v>10</v>
+      </c>
+      <c r="AE174">
+        <v>1.22</v>
+      </c>
+      <c r="AF174">
+        <v>4</v>
+      </c>
+      <c r="AG174">
+        <v>1.65</v>
+      </c>
+      <c r="AH174">
+        <v>2</v>
+      </c>
+      <c r="AI174">
+        <v>1.62</v>
+      </c>
+      <c r="AJ174">
+        <v>2.2</v>
+      </c>
+      <c r="AK174">
+        <v>1.26</v>
+      </c>
+      <c r="AL174">
+        <v>1.25</v>
+      </c>
+      <c r="AM174">
+        <v>1.87</v>
+      </c>
+      <c r="AN174">
+        <v>1.86</v>
+      </c>
+      <c r="AO174">
+        <v>1.21</v>
+      </c>
+      <c r="AP174">
+        <v>1.73</v>
+      </c>
+      <c r="AQ174">
+        <v>1.33</v>
+      </c>
+      <c r="AR174">
+        <v>1.86</v>
+      </c>
+      <c r="AS174">
+        <v>1.64</v>
+      </c>
+      <c r="AT174">
+        <v>3.5</v>
+      </c>
+      <c r="AU174">
+        <v>4</v>
+      </c>
+      <c r="AV174">
+        <v>9</v>
+      </c>
+      <c r="AW174">
+        <v>8</v>
+      </c>
+      <c r="AX174">
+        <v>4</v>
+      </c>
+      <c r="AY174">
+        <v>13</v>
+      </c>
+      <c r="AZ174">
+        <v>14</v>
+      </c>
+      <c r="BA174">
+        <v>6</v>
+      </c>
+      <c r="BB174">
+        <v>2</v>
+      </c>
+      <c r="BC174">
+        <v>8</v>
+      </c>
+      <c r="BD174">
+        <v>1.49</v>
+      </c>
+      <c r="BE174">
+        <v>7</v>
+      </c>
+      <c r="BF174">
+        <v>2.9</v>
+      </c>
+      <c r="BG174">
+        <v>1.28</v>
+      </c>
+      <c r="BH174">
+        <v>3.2</v>
+      </c>
+      <c r="BI174">
+        <v>1.48</v>
+      </c>
+      <c r="BJ174">
+        <v>2.4</v>
+      </c>
+      <c r="BK174">
+        <v>1.78</v>
+      </c>
+      <c r="BL174">
+        <v>1.89</v>
+      </c>
+      <c r="BM174">
+        <v>2.23</v>
+      </c>
+      <c r="BN174">
+        <v>1.56</v>
+      </c>
+      <c r="BO174">
+        <v>2.85</v>
+      </c>
+      <c r="BP174">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7784955</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45746.47916666666</v>
+      </c>
+      <c r="F175">
+        <v>29</v>
+      </c>
+      <c r="G175" t="s">
+        <v>78</v>
+      </c>
+      <c r="H175" t="s">
+        <v>81</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>3</v>
+      </c>
+      <c r="O175" t="s">
+        <v>101</v>
+      </c>
+      <c r="P175" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q175">
+        <v>3.4</v>
+      </c>
+      <c r="R175">
+        <v>2.1</v>
+      </c>
+      <c r="S175">
+        <v>3.25</v>
+      </c>
+      <c r="T175">
+        <v>1.4</v>
+      </c>
+      <c r="U175">
+        <v>2.75</v>
+      </c>
+      <c r="V175">
+        <v>3</v>
+      </c>
+      <c r="W175">
+        <v>1.36</v>
+      </c>
+      <c r="X175">
+        <v>8</v>
+      </c>
+      <c r="Y175">
+        <v>1.08</v>
+      </c>
+      <c r="Z175">
+        <v>2.73</v>
+      </c>
+      <c r="AA175">
+        <v>3.23</v>
+      </c>
+      <c r="AB175">
+        <v>2.54</v>
+      </c>
+      <c r="AC175">
+        <v>1.06</v>
+      </c>
+      <c r="AD175">
+        <v>8.5</v>
+      </c>
+      <c r="AE175">
+        <v>1.3</v>
+      </c>
+      <c r="AF175">
+        <v>3.35</v>
+      </c>
+      <c r="AG175">
+        <v>1.95</v>
+      </c>
+      <c r="AH175">
+        <v>1.79</v>
+      </c>
+      <c r="AI175">
+        <v>1.73</v>
+      </c>
+      <c r="AJ175">
+        <v>2</v>
+      </c>
+      <c r="AK175">
+        <v>1.5</v>
+      </c>
+      <c r="AL175">
+        <v>1.29</v>
+      </c>
+      <c r="AM175">
+        <v>1.46</v>
+      </c>
+      <c r="AN175">
+        <v>1</v>
+      </c>
+      <c r="AO175">
+        <v>1.54</v>
+      </c>
+      <c r="AP175">
+        <v>0.93</v>
+      </c>
+      <c r="AQ175">
+        <v>1.64</v>
+      </c>
+      <c r="AR175">
+        <v>1.47</v>
+      </c>
+      <c r="AS175">
+        <v>1.6</v>
+      </c>
+      <c r="AT175">
+        <v>3.07</v>
+      </c>
+      <c r="AU175">
+        <v>3</v>
+      </c>
+      <c r="AV175">
+        <v>8</v>
+      </c>
+      <c r="AW175">
+        <v>7</v>
+      </c>
+      <c r="AX175">
+        <v>13</v>
+      </c>
+      <c r="AY175">
+        <v>11</v>
+      </c>
+      <c r="AZ175">
+        <v>24</v>
+      </c>
+      <c r="BA175">
+        <v>4</v>
+      </c>
+      <c r="BB175">
+        <v>10</v>
+      </c>
+      <c r="BC175">
+        <v>14</v>
+      </c>
+      <c r="BD175">
+        <v>1.81</v>
+      </c>
+      <c r="BE175">
+        <v>6.75</v>
+      </c>
+      <c r="BF175">
+        <v>2.18</v>
+      </c>
+      <c r="BG175">
+        <v>1.25</v>
+      </c>
+      <c r="BH175">
+        <v>3.4</v>
+      </c>
+      <c r="BI175">
+        <v>1.43</v>
+      </c>
+      <c r="BJ175">
+        <v>2.55</v>
+      </c>
+      <c r="BK175">
+        <v>1.72</v>
+      </c>
+      <c r="BL175">
+        <v>1.95</v>
+      </c>
+      <c r="BM175">
+        <v>2.14</v>
+      </c>
+      <c r="BN175">
+        <v>1.6</v>
+      </c>
+      <c r="BO175">
+        <v>2.7</v>
+      </c>
+      <c r="BP175">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -930,6 +930,9 @@
   <si>
     <t>['45+2', '68']</t>
   </si>
+  <si>
+    <t>['37', '78']</t>
+  </si>
 </sst>
 </file>
 
@@ -1290,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1830,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3">
         <v>1.64</v>
@@ -2860,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3481,7 +3484,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ11">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3684,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
         <v>0.73</v>
@@ -3893,7 +3896,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ13">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5744,10 +5747,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR22">
         <v>0.55</v>
@@ -6568,7 +6571,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ26">
         <v>1.53</v>
@@ -7598,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
         <v>0.93</v>
@@ -8631,7 +8634,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ36">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR36">
         <v>1.64</v>
@@ -9661,7 +9664,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ41">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR41">
         <v>1.53</v>
@@ -9867,7 +9870,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ42">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR42">
         <v>1.16</v>
@@ -10276,7 +10279,7 @@
         <v>1.33</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10482,7 +10485,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -12133,7 +12136,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ53">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR53">
         <v>1.68</v>
@@ -12339,7 +12342,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ54">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -13160,7 +13163,7 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ58">
         <v>0.73</v>
@@ -13778,10 +13781,10 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ61">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR61">
         <v>1.01</v>
@@ -14811,7 +14814,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ66">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR66">
         <v>1.86</v>
@@ -15220,7 +15223,7 @@
         <v>0.4</v>
       </c>
       <c r="AP68">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -16047,7 +16050,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ72">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16250,7 +16253,7 @@
         <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ73">
         <v>1.33</v>
@@ -16459,7 +16462,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ74">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -17898,7 +17901,7 @@
         <v>1.43</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ81">
         <v>1.53</v>
@@ -18104,7 +18107,7 @@
         <v>2.17</v>
       </c>
       <c r="AP82">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ82">
         <v>1.64</v>
@@ -18725,7 +18728,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ85">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR85">
         <v>1.7</v>
@@ -18931,7 +18934,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ86">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -20370,7 +20373,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20988,10 +20991,10 @@
         <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21609,7 +21612,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ99">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR99">
         <v>1.55</v>
@@ -21815,7 +21818,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ100">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -22224,7 +22227,7 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ102">
         <v>0.27</v>
@@ -22842,7 +22845,7 @@
         <v>0.88</v>
       </c>
       <c r="AP105">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ105">
         <v>0.73</v>
@@ -24284,7 +24287,7 @@
         <v>1.22</v>
       </c>
       <c r="AP112">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -25111,7 +25114,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ116">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR116">
         <v>1.51</v>
@@ -25314,7 +25317,7 @@
         <v>1.22</v>
       </c>
       <c r="AP117">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ117">
         <v>1.67</v>
@@ -25523,7 +25526,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ118">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -26347,7 +26350,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ122">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26756,7 +26759,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ124">
         <v>0.93</v>
@@ -27374,7 +27377,7 @@
         <v>0.4</v>
       </c>
       <c r="AP127">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ127">
         <v>0.27</v>
@@ -27995,7 +27998,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ130">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR130">
         <v>1.84</v>
@@ -29434,7 +29437,7 @@
         <v>1.64</v>
       </c>
       <c r="AP137">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ137">
         <v>1.53</v>
@@ -30467,7 +30470,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ142">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR142">
         <v>1.27</v>
@@ -30670,7 +30673,7 @@
         <v>1.25</v>
       </c>
       <c r="AP143">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ143">
         <v>1</v>
@@ -32115,7 +32118,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ150">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR150">
         <v>2.1</v>
@@ -32318,7 +32321,7 @@
         <v>0.33</v>
       </c>
       <c r="AP151">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ151">
         <v>0.27</v>
@@ -33351,7 +33354,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ156">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR156">
         <v>1.56</v>
@@ -33554,7 +33557,7 @@
         <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ157">
         <v>1.33</v>
@@ -33966,7 +33969,7 @@
         <v>0.31</v>
       </c>
       <c r="AP159">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ159">
         <v>0.27</v>
@@ -34587,7 +34590,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ162">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR162">
         <v>1.69</v>
@@ -34996,7 +34999,7 @@
         <v>0.54</v>
       </c>
       <c r="AP164">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ164">
         <v>0.73</v>
@@ -35823,7 +35826,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ168">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR168">
         <v>1.83</v>
@@ -37341,6 +37344,418 @@
       </c>
       <c r="BP175">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7784957</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45748.64583333334</v>
+      </c>
+      <c r="F176">
+        <v>30</v>
+      </c>
+      <c r="G176" t="s">
+        <v>76</v>
+      </c>
+      <c r="H176" t="s">
+        <v>73</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>83</v>
+      </c>
+      <c r="P176" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q176">
+        <v>2.75</v>
+      </c>
+      <c r="R176">
+        <v>2.25</v>
+      </c>
+      <c r="S176">
+        <v>3.1</v>
+      </c>
+      <c r="T176">
+        <v>1.28</v>
+      </c>
+      <c r="U176">
+        <v>3.3</v>
+      </c>
+      <c r="V176">
+        <v>2.25</v>
+      </c>
+      <c r="W176">
+        <v>1.55</v>
+      </c>
+      <c r="X176">
+        <v>5.25</v>
+      </c>
+      <c r="Y176">
+        <v>1.14</v>
+      </c>
+      <c r="Z176">
+        <v>2.38</v>
+      </c>
+      <c r="AA176">
+        <v>3.74</v>
+      </c>
+      <c r="AB176">
+        <v>2.62</v>
+      </c>
+      <c r="AC176">
+        <v>1.04</v>
+      </c>
+      <c r="AD176">
+        <v>10</v>
+      </c>
+      <c r="AE176">
+        <v>1.2</v>
+      </c>
+      <c r="AF176">
+        <v>4.33</v>
+      </c>
+      <c r="AG176">
+        <v>1.53</v>
+      </c>
+      <c r="AH176">
+        <v>2.33</v>
+      </c>
+      <c r="AI176">
+        <v>1.51</v>
+      </c>
+      <c r="AJ176">
+        <v>2.37</v>
+      </c>
+      <c r="AK176">
+        <v>1.42</v>
+      </c>
+      <c r="AL176">
+        <v>1.27</v>
+      </c>
+      <c r="AM176">
+        <v>1.58</v>
+      </c>
+      <c r="AN176">
+        <v>1.86</v>
+      </c>
+      <c r="AO176">
+        <v>0.93</v>
+      </c>
+      <c r="AP176">
+        <v>1.73</v>
+      </c>
+      <c r="AQ176">
+        <v>1.07</v>
+      </c>
+      <c r="AR176">
+        <v>1.98</v>
+      </c>
+      <c r="AS176">
+        <v>1.82</v>
+      </c>
+      <c r="AT176">
+        <v>3.8</v>
+      </c>
+      <c r="AU176">
+        <v>4</v>
+      </c>
+      <c r="AV176">
+        <v>6</v>
+      </c>
+      <c r="AW176">
+        <v>7</v>
+      </c>
+      <c r="AX176">
+        <v>5</v>
+      </c>
+      <c r="AY176">
+        <v>14</v>
+      </c>
+      <c r="AZ176">
+        <v>12</v>
+      </c>
+      <c r="BA176">
+        <v>3</v>
+      </c>
+      <c r="BB176">
+        <v>6</v>
+      </c>
+      <c r="BC176">
+        <v>9</v>
+      </c>
+      <c r="BD176">
+        <v>1.8</v>
+      </c>
+      <c r="BE176">
+        <v>6.75</v>
+      </c>
+      <c r="BF176">
+        <v>2.18</v>
+      </c>
+      <c r="BG176">
+        <v>1.27</v>
+      </c>
+      <c r="BH176">
+        <v>3.3</v>
+      </c>
+      <c r="BI176">
+        <v>1.47</v>
+      </c>
+      <c r="BJ176">
+        <v>2.4</v>
+      </c>
+      <c r="BK176">
+        <v>1.78</v>
+      </c>
+      <c r="BL176">
+        <v>1.89</v>
+      </c>
+      <c r="BM176">
+        <v>2.2</v>
+      </c>
+      <c r="BN176">
+        <v>1.56</v>
+      </c>
+      <c r="BO176">
+        <v>2.8</v>
+      </c>
+      <c r="BP176">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7784958</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45748.64583333334</v>
+      </c>
+      <c r="F177">
+        <v>30</v>
+      </c>
+      <c r="G177" t="s">
+        <v>71</v>
+      </c>
+      <c r="H177" t="s">
+        <v>70</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>2</v>
+      </c>
+      <c r="N177">
+        <v>2</v>
+      </c>
+      <c r="O177" t="s">
+        <v>83</v>
+      </c>
+      <c r="P177" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q177">
+        <v>4.1</v>
+      </c>
+      <c r="R177">
+        <v>2.25</v>
+      </c>
+      <c r="S177">
+        <v>2.3</v>
+      </c>
+      <c r="T177">
+        <v>1.32</v>
+      </c>
+      <c r="U177">
+        <v>3.1</v>
+      </c>
+      <c r="V177">
+        <v>2.45</v>
+      </c>
+      <c r="W177">
+        <v>1.49</v>
+      </c>
+      <c r="X177">
+        <v>5.75</v>
+      </c>
+      <c r="Y177">
+        <v>1.11</v>
+      </c>
+      <c r="Z177">
+        <v>4.3</v>
+      </c>
+      <c r="AA177">
+        <v>4.1</v>
+      </c>
+      <c r="AB177">
+        <v>1.69</v>
+      </c>
+      <c r="AC177">
+        <v>1.04</v>
+      </c>
+      <c r="AD177">
+        <v>10</v>
+      </c>
+      <c r="AE177">
+        <v>1.22</v>
+      </c>
+      <c r="AF177">
+        <v>4</v>
+      </c>
+      <c r="AG177">
+        <v>1.58</v>
+      </c>
+      <c r="AH177">
+        <v>2.23</v>
+      </c>
+      <c r="AI177">
+        <v>1.68</v>
+      </c>
+      <c r="AJ177">
+        <v>2.05</v>
+      </c>
+      <c r="AK177">
+        <v>1.93</v>
+      </c>
+      <c r="AL177">
+        <v>1.26</v>
+      </c>
+      <c r="AM177">
+        <v>1.24</v>
+      </c>
+      <c r="AN177">
+        <v>1.5</v>
+      </c>
+      <c r="AO177">
+        <v>1.15</v>
+      </c>
+      <c r="AP177">
+        <v>1.4</v>
+      </c>
+      <c r="AQ177">
+        <v>1.29</v>
+      </c>
+      <c r="AR177">
+        <v>1.29</v>
+      </c>
+      <c r="AS177">
+        <v>1.54</v>
+      </c>
+      <c r="AT177">
+        <v>2.83</v>
+      </c>
+      <c r="AU177">
+        <v>2</v>
+      </c>
+      <c r="AV177">
+        <v>5</v>
+      </c>
+      <c r="AW177">
+        <v>6</v>
+      </c>
+      <c r="AX177">
+        <v>5</v>
+      </c>
+      <c r="AY177">
+        <v>13</v>
+      </c>
+      <c r="AZ177">
+        <v>13</v>
+      </c>
+      <c r="BA177">
+        <v>3</v>
+      </c>
+      <c r="BB177">
+        <v>2</v>
+      </c>
+      <c r="BC177">
+        <v>5</v>
+      </c>
+      <c r="BD177">
+        <v>2.95</v>
+      </c>
+      <c r="BE177">
+        <v>6.75</v>
+      </c>
+      <c r="BF177">
+        <v>1.47</v>
+      </c>
+      <c r="BG177">
+        <v>1.3</v>
+      </c>
+      <c r="BH177">
+        <v>3.15</v>
+      </c>
+      <c r="BI177">
+        <v>1.52</v>
+      </c>
+      <c r="BJ177">
+        <v>2.3</v>
+      </c>
+      <c r="BK177">
+        <v>1.84</v>
+      </c>
+      <c r="BL177">
+        <v>1.82</v>
+      </c>
+      <c r="BM177">
+        <v>2.32</v>
+      </c>
+      <c r="BN177">
+        <v>1.52</v>
+      </c>
+      <c r="BO177">
+        <v>3</v>
+      </c>
+      <c r="BP177">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="310">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,12 @@
     <t>['50', '56']</t>
   </si>
   <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['89', '90+5']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -932,6 +938,12 @@
   </si>
   <si>
     <t>['37', '78']</t>
+  </si>
+  <si>
+    <t>['80', '90+4']</t>
+  </si>
+  <si>
+    <t>['5', '74']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1549,7 +1561,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1755,7 +1767,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2167,7 +2179,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2373,7 +2385,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2579,7 +2591,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2785,7 +2797,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3069,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3197,7 +3209,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3403,7 +3415,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3609,7 +3621,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -4021,7 +4033,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4099,10 +4111,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ14">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4227,7 +4239,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4845,7 +4857,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5051,7 +5063,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5541,10 +5553,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ21">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR21">
         <v>1.73</v>
@@ -5669,7 +5681,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6081,7 +6093,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6365,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6493,7 +6505,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6780,7 +6792,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ27">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -6905,7 +6917,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7317,7 +7329,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7395,7 +7407,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ30">
         <v>1.53</v>
@@ -8219,7 +8231,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8553,7 +8565,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8759,7 +8771,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8965,7 +8977,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9171,7 +9183,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9377,7 +9389,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9661,7 +9673,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ41">
         <v>1.29</v>
@@ -9789,7 +9801,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9995,7 +10007,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10613,7 +10625,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10897,7 +10909,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ47">
         <v>0.73</v>
@@ -11231,7 +11243,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11312,7 +11324,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ49">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR49">
         <v>1.86</v>
@@ -11437,7 +11449,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11515,7 +11527,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ50">
         <v>0.73</v>
@@ -11643,7 +11655,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -12133,7 +12145,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ53">
         <v>1.29</v>
@@ -12467,7 +12479,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12673,7 +12685,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -13291,7 +13303,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13578,7 +13590,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -14115,7 +14127,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14321,7 +14333,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14527,7 +14539,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14605,7 +14617,7 @@
         <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14939,7 +14951,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15017,7 +15029,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ67">
         <v>1.67</v>
@@ -15145,7 +15157,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15351,7 +15363,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15429,7 +15441,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ69">
         <v>1.64</v>
@@ -15557,7 +15569,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15638,7 +15650,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ70">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15763,7 +15775,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16175,7 +16187,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16459,7 +16471,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
         <v>1.07</v>
@@ -16668,7 +16680,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -16793,7 +16805,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17823,7 +17835,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18029,7 +18041,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18235,7 +18247,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18313,7 +18325,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ83">
         <v>1.33</v>
@@ -18441,7 +18453,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18647,7 +18659,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18853,7 +18865,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -19059,7 +19071,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19140,7 +19152,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ87">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR87">
         <v>1.52</v>
@@ -20501,7 +20513,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20579,7 +20591,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20707,7 +20719,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21119,7 +21131,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21325,7 +21337,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21609,7 +21621,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ99">
         <v>1.07</v>
@@ -21737,7 +21749,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22149,7 +22161,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22230,7 +22242,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ102">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR102">
         <v>1.93</v>
@@ -22355,7 +22367,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22561,7 +22573,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22767,7 +22779,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23179,7 +23191,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23385,7 +23397,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23591,7 +23603,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23669,7 +23681,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23878,7 +23890,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ110">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -24003,7 +24015,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24081,7 +24093,7 @@
         <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111">
         <v>0.93</v>
@@ -24493,7 +24505,7 @@
         <v>0.78</v>
       </c>
       <c r="AP113">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ113">
         <v>0.73</v>
@@ -24621,7 +24633,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -25445,7 +25457,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25651,7 +25663,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25857,7 +25869,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26269,7 +26281,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26475,7 +26487,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -27093,7 +27105,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27171,7 +27183,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ126">
         <v>1.53</v>
@@ -27380,7 +27392,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ127">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR127">
         <v>1.01</v>
@@ -27505,7 +27517,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27711,7 +27723,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27789,7 +27801,7 @@
         <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ129">
         <v>1.67</v>
@@ -27917,7 +27929,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28123,7 +28135,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28535,7 +28547,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28741,7 +28753,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28947,7 +28959,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29153,7 +29165,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29359,7 +29371,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29565,7 +29577,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29646,7 +29658,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ138">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -29771,7 +29783,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -29849,7 +29861,7 @@
         <v>1.09</v>
       </c>
       <c r="AP139">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30261,7 +30273,7 @@
         <v>1.55</v>
       </c>
       <c r="AP141">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ141">
         <v>1.64</v>
@@ -31007,7 +31019,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31213,7 +31225,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31419,7 +31431,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31497,7 +31509,7 @@
         <v>0.58</v>
       </c>
       <c r="AP147">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ147">
         <v>0.73</v>
@@ -31625,7 +31637,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31831,7 +31843,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -32243,7 +32255,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32324,7 +32336,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ151">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR151">
         <v>1.93</v>
@@ -33067,7 +33079,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33479,7 +33491,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33891,7 +33903,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -33972,7 +33984,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ159">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34303,7 +34315,7 @@
         <v>91</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34381,7 +34393,7 @@
         <v>1.46</v>
       </c>
       <c r="AP161">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ161">
         <v>1.67</v>
@@ -34509,7 +34521,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34587,7 +34599,7 @@
         <v>1.25</v>
       </c>
       <c r="AP162">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ162">
         <v>1.29</v>
@@ -34715,7 +34727,7 @@
         <v>120</v>
       </c>
       <c r="P163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q163">
         <v>3.35</v>
@@ -34921,7 +34933,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35127,7 +35139,7 @@
         <v>83</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35333,7 +35345,7 @@
         <v>206</v>
       </c>
       <c r="P166" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35411,7 +35423,7 @@
         <v>1.31</v>
       </c>
       <c r="AP166">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ166">
         <v>1.33</v>
@@ -35745,7 +35757,7 @@
         <v>208</v>
       </c>
       <c r="P168" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35951,7 +35963,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q169">
         <v>1.91</v>
@@ -36032,7 +36044,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ169">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="AR169">
         <v>1.99</v>
@@ -36235,7 +36247,7 @@
         <v>0.71</v>
       </c>
       <c r="AP170">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ170">
         <v>0.73</v>
@@ -36569,7 +36581,7 @@
         <v>83</v>
       </c>
       <c r="P172" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q172">
         <v>2.88</v>
@@ -36775,7 +36787,7 @@
         <v>83</v>
       </c>
       <c r="P173" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>5.5</v>
@@ -36981,7 +36993,7 @@
         <v>208</v>
       </c>
       <c r="P174" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37187,7 +37199,7 @@
         <v>101</v>
       </c>
       <c r="P175" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37393,7 +37405,7 @@
         <v>83</v>
       </c>
       <c r="P176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q176">
         <v>2.75</v>
@@ -37599,7 +37611,7 @@
         <v>83</v>
       </c>
       <c r="P177" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q177">
         <v>4.1</v>
@@ -37756,6 +37768,418 @@
       </c>
       <c r="BP177">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7784959</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45749.64583333334</v>
+      </c>
+      <c r="F178">
+        <v>30</v>
+      </c>
+      <c r="G178" t="s">
+        <v>77</v>
+      </c>
+      <c r="H178" t="s">
+        <v>72</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>2</v>
+      </c>
+      <c r="N178">
+        <v>3</v>
+      </c>
+      <c r="O178" t="s">
+        <v>210</v>
+      </c>
+      <c r="P178" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q178">
+        <v>2.05</v>
+      </c>
+      <c r="R178">
+        <v>2.4</v>
+      </c>
+      <c r="S178">
+        <v>5.5</v>
+      </c>
+      <c r="T178">
+        <v>1.33</v>
+      </c>
+      <c r="U178">
+        <v>3.25</v>
+      </c>
+      <c r="V178">
+        <v>2.5</v>
+      </c>
+      <c r="W178">
+        <v>1.5</v>
+      </c>
+      <c r="X178">
+        <v>6.5</v>
+      </c>
+      <c r="Y178">
+        <v>1.11</v>
+      </c>
+      <c r="Z178">
+        <v>1.52</v>
+      </c>
+      <c r="AA178">
+        <v>4.3</v>
+      </c>
+      <c r="AB178">
+        <v>5.6</v>
+      </c>
+      <c r="AC178">
+        <v>1.03</v>
+      </c>
+      <c r="AD178">
+        <v>11</v>
+      </c>
+      <c r="AE178">
+        <v>1.2</v>
+      </c>
+      <c r="AF178">
+        <v>4.33</v>
+      </c>
+      <c r="AG178">
+        <v>1.79</v>
+      </c>
+      <c r="AH178">
+        <v>1.95</v>
+      </c>
+      <c r="AI178">
+        <v>1.8</v>
+      </c>
+      <c r="AJ178">
+        <v>1.91</v>
+      </c>
+      <c r="AK178">
+        <v>1.14</v>
+      </c>
+      <c r="AL178">
+        <v>1.22</v>
+      </c>
+      <c r="AM178">
+        <v>2.37</v>
+      </c>
+      <c r="AN178">
+        <v>1.71</v>
+      </c>
+      <c r="AO178">
+        <v>0.27</v>
+      </c>
+      <c r="AP178">
+        <v>1.6</v>
+      </c>
+      <c r="AQ178">
+        <v>0.44</v>
+      </c>
+      <c r="AR178">
+        <v>1.69</v>
+      </c>
+      <c r="AS178">
+        <v>1.19</v>
+      </c>
+      <c r="AT178">
+        <v>2.88</v>
+      </c>
+      <c r="AU178">
+        <v>7</v>
+      </c>
+      <c r="AV178">
+        <v>4</v>
+      </c>
+      <c r="AW178">
+        <v>9</v>
+      </c>
+      <c r="AX178">
+        <v>8</v>
+      </c>
+      <c r="AY178">
+        <v>18</v>
+      </c>
+      <c r="AZ178">
+        <v>14</v>
+      </c>
+      <c r="BA178">
+        <v>3</v>
+      </c>
+      <c r="BB178">
+        <v>5</v>
+      </c>
+      <c r="BC178">
+        <v>8</v>
+      </c>
+      <c r="BD178">
+        <v>1.41</v>
+      </c>
+      <c r="BE178">
+        <v>7</v>
+      </c>
+      <c r="BF178">
+        <v>3.3</v>
+      </c>
+      <c r="BG178">
+        <v>1.29</v>
+      </c>
+      <c r="BH178">
+        <v>3.15</v>
+      </c>
+      <c r="BI178">
+        <v>1.5</v>
+      </c>
+      <c r="BJ178">
+        <v>2.33</v>
+      </c>
+      <c r="BK178">
+        <v>1.81</v>
+      </c>
+      <c r="BL178">
+        <v>1.85</v>
+      </c>
+      <c r="BM178">
+        <v>2.28</v>
+      </c>
+      <c r="BN178">
+        <v>1.53</v>
+      </c>
+      <c r="BO178">
+        <v>2.9</v>
+      </c>
+      <c r="BP178">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7784960</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45749.64583333334</v>
+      </c>
+      <c r="F179">
+        <v>30</v>
+      </c>
+      <c r="G179" t="s">
+        <v>81</v>
+      </c>
+      <c r="H179" t="s">
+        <v>74</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179">
+        <v>2</v>
+      </c>
+      <c r="M179">
+        <v>2</v>
+      </c>
+      <c r="N179">
+        <v>4</v>
+      </c>
+      <c r="O179" t="s">
+        <v>211</v>
+      </c>
+      <c r="P179" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q179">
+        <v>2.95</v>
+      </c>
+      <c r="R179">
+        <v>2.1</v>
+      </c>
+      <c r="S179">
+        <v>3.2</v>
+      </c>
+      <c r="T179">
+        <v>1.34</v>
+      </c>
+      <c r="U179">
+        <v>2.95</v>
+      </c>
+      <c r="V179">
+        <v>2.5</v>
+      </c>
+      <c r="W179">
+        <v>1.46</v>
+      </c>
+      <c r="X179">
+        <v>6</v>
+      </c>
+      <c r="Y179">
+        <v>1.11</v>
+      </c>
+      <c r="Z179">
+        <v>2.45</v>
+      </c>
+      <c r="AA179">
+        <v>3.39</v>
+      </c>
+      <c r="AB179">
+        <v>2.73</v>
+      </c>
+      <c r="AC179">
+        <v>1.05</v>
+      </c>
+      <c r="AD179">
+        <v>9.5</v>
+      </c>
+      <c r="AE179">
+        <v>1.25</v>
+      </c>
+      <c r="AF179">
+        <v>3.7</v>
+      </c>
+      <c r="AG179">
+        <v>1.82</v>
+      </c>
+      <c r="AH179">
+        <v>1.92</v>
+      </c>
+      <c r="AI179">
+        <v>1.62</v>
+      </c>
+      <c r="AJ179">
+        <v>2.15</v>
+      </c>
+      <c r="AK179">
+        <v>1.43</v>
+      </c>
+      <c r="AL179">
+        <v>1.3</v>
+      </c>
+      <c r="AM179">
+        <v>1.52</v>
+      </c>
+      <c r="AN179">
+        <v>1.47</v>
+      </c>
+      <c r="AO179">
+        <v>1</v>
+      </c>
+      <c r="AP179">
+        <v>1.44</v>
+      </c>
+      <c r="AQ179">
+        <v>1</v>
+      </c>
+      <c r="AR179">
+        <v>1.64</v>
+      </c>
+      <c r="AS179">
+        <v>1.64</v>
+      </c>
+      <c r="AT179">
+        <v>3.28</v>
+      </c>
+      <c r="AU179">
+        <v>8</v>
+      </c>
+      <c r="AV179">
+        <v>6</v>
+      </c>
+      <c r="AW179">
+        <v>11</v>
+      </c>
+      <c r="AX179">
+        <v>8</v>
+      </c>
+      <c r="AY179">
+        <v>23</v>
+      </c>
+      <c r="AZ179">
+        <v>14</v>
+      </c>
+      <c r="BA179">
+        <v>5</v>
+      </c>
+      <c r="BB179">
+        <v>3</v>
+      </c>
+      <c r="BC179">
+        <v>8</v>
+      </c>
+      <c r="BD179">
+        <v>2.1</v>
+      </c>
+      <c r="BE179">
+        <v>6.4</v>
+      </c>
+      <c r="BF179">
+        <v>1.89</v>
+      </c>
+      <c r="BG179">
+        <v>1.33</v>
+      </c>
+      <c r="BH179">
+        <v>2.95</v>
+      </c>
+      <c r="BI179">
+        <v>1.55</v>
+      </c>
+      <c r="BJ179">
+        <v>2.25</v>
+      </c>
+      <c r="BK179">
+        <v>1.89</v>
+      </c>
+      <c r="BL179">
+        <v>1.77</v>
+      </c>
+      <c r="BM179">
+        <v>2.4</v>
+      </c>
+      <c r="BN179">
+        <v>1.48</v>
+      </c>
+      <c r="BO179">
+        <v>3.15</v>
+      </c>
+      <c r="BP179">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="312">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -650,6 +650,12 @@
   </si>
   <si>
     <t>['89', '90+5']</t>
+  </si>
+  <si>
+    <t>['16', '40']</t>
+  </si>
+  <si>
+    <t>['2']</t>
   </si>
   <si>
     <t>['25']</t>
@@ -1305,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP179"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1561,7 +1567,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1642,7 +1648,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ2">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1767,7 +1773,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2179,7 +2185,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2385,7 +2391,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2591,7 +2597,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2669,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ7">
         <v>1.67</v>
@@ -2797,7 +2803,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3209,7 +3215,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3415,7 +3421,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3493,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ11">
         <v>1.29</v>
@@ -3621,7 +3627,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -4033,7 +4039,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4239,7 +4245,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4729,7 +4735,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ17">
         <v>0.73</v>
@@ -4857,7 +4863,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5063,7 +5069,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5681,7 +5687,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5968,7 +5974,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ23">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR23">
         <v>1.97</v>
@@ -6093,7 +6099,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6505,7 +6511,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6789,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ27">
         <v>0.44</v>
@@ -6917,7 +6923,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7201,7 +7207,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ29">
         <v>0.73</v>
@@ -7329,7 +7335,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7616,7 +7622,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -8565,7 +8571,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8771,7 +8777,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8977,7 +8983,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9183,7 +9189,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9261,7 +9267,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ39">
         <v>1.64</v>
@@ -9389,7 +9395,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9801,7 +9807,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -10007,7 +10013,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10625,7 +10631,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10706,7 +10712,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ46">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR46">
         <v>1.42</v>
@@ -11115,7 +11121,7 @@
         <v>1.75</v>
       </c>
       <c r="AP48">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ48">
         <v>1.53</v>
@@ -11243,7 +11249,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11449,7 +11455,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11655,7 +11661,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11733,7 +11739,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11942,7 +11948,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ52">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR52">
         <v>1.22</v>
@@ -12351,7 +12357,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ54">
         <v>1.07</v>
@@ -12479,7 +12485,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12685,7 +12691,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -13303,7 +13309,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13381,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -14002,7 +14008,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ62">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR62">
         <v>1.82</v>
@@ -14127,7 +14133,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14333,7 +14339,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14411,7 +14417,7 @@
         <v>0.4</v>
       </c>
       <c r="AP64">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ64">
         <v>0.73</v>
@@ -14539,7 +14545,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14951,7 +14957,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15157,7 +15163,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15363,7 +15369,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15569,7 +15575,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15775,7 +15781,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16187,7 +16193,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16677,7 +16683,7 @@
         <v>0.17</v>
       </c>
       <c r="AP75">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ75">
         <v>0.44</v>
@@ -16805,7 +16811,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17501,10 +17507,10 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ79">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR79">
         <v>1.77</v>
@@ -17835,7 +17841,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18041,7 +18047,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18247,7 +18253,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18453,7 +18459,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18659,7 +18665,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18865,7 +18871,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18943,7 +18949,7 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ86">
         <v>1.07</v>
@@ -19071,7 +19077,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19973,7 +19979,7 @@
         <v>1.57</v>
       </c>
       <c r="AP91">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ91">
         <v>1.67</v>
@@ -20179,7 +20185,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20513,7 +20519,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20594,7 +20600,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ94">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -20719,7 +20725,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21131,7 +21137,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21337,7 +21343,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21749,7 +21755,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21827,7 +21833,7 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ100">
         <v>1.29</v>
@@ -22161,7 +22167,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22367,7 +22373,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22573,7 +22579,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22779,7 +22785,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23063,10 +23069,10 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ106">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR106">
         <v>1.73</v>
@@ -23191,7 +23197,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23397,7 +23403,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23603,7 +23609,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -24015,7 +24021,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24096,7 +24102,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ111">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24633,7 +24639,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -25457,7 +25463,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25663,7 +25669,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25869,7 +25875,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25947,7 +25953,7 @@
         <v>1.11</v>
       </c>
       <c r="AP120">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ120">
         <v>0.73</v>
@@ -26153,7 +26159,7 @@
         <v>1.56</v>
       </c>
       <c r="AP121">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ121">
         <v>1.64</v>
@@ -26281,7 +26287,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26487,7 +26493,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26774,7 +26780,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ124">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR124">
         <v>1.92</v>
@@ -26977,7 +26983,7 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27105,7 +27111,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27517,7 +27523,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27723,7 +27729,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27929,7 +27935,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28135,7 +28141,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28419,7 +28425,7 @@
         <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ132">
         <v>1.33</v>
@@ -28547,7 +28553,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28753,7 +28759,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28959,7 +28965,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29040,7 +29046,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ135">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR135">
         <v>1.87</v>
@@ -29165,7 +29171,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29371,7 +29377,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29577,7 +29583,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29655,7 +29661,7 @@
         <v>0.36</v>
       </c>
       <c r="AP138">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ138">
         <v>0.44</v>
@@ -29783,7 +29789,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -30891,7 +30897,7 @@
         <v>0.91</v>
       </c>
       <c r="AP144">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -31019,7 +31025,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31225,7 +31231,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31306,7 +31312,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ146">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR146">
         <v>1.86</v>
@@ -31431,7 +31437,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31637,7 +31643,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31843,7 +31849,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -31921,7 +31927,7 @@
         <v>0.83</v>
       </c>
       <c r="AP149">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ149">
         <v>0.73</v>
@@ -32255,7 +32261,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32539,7 +32545,7 @@
         <v>0.77</v>
       </c>
       <c r="AP152">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ152">
         <v>0.73</v>
@@ -33079,7 +33085,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33491,7 +33497,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33903,7 +33909,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -34190,7 +34196,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ160">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR160">
         <v>1.88</v>
@@ -34315,7 +34321,7 @@
         <v>91</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34521,7 +34527,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34727,7 +34733,7 @@
         <v>120</v>
       </c>
       <c r="P163" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q163">
         <v>3.35</v>
@@ -34805,7 +34811,7 @@
         <v>1.46</v>
       </c>
       <c r="AP163">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ163">
         <v>1.53</v>
@@ -34933,7 +34939,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35139,7 +35145,7 @@
         <v>83</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35345,7 +35351,7 @@
         <v>206</v>
       </c>
       <c r="P166" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35757,7 +35763,7 @@
         <v>208</v>
       </c>
       <c r="P168" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35835,7 +35841,7 @@
         <v>0.77</v>
       </c>
       <c r="AP168">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ168">
         <v>1.07</v>
@@ -35963,7 +35969,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q169">
         <v>1.91</v>
@@ -36581,7 +36587,7 @@
         <v>83</v>
       </c>
       <c r="P172" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q172">
         <v>2.88</v>
@@ -36787,7 +36793,7 @@
         <v>83</v>
       </c>
       <c r="P173" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q173">
         <v>5.5</v>
@@ -36993,7 +36999,7 @@
         <v>208</v>
       </c>
       <c r="P174" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37199,7 +37205,7 @@
         <v>101</v>
       </c>
       <c r="P175" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37405,7 +37411,7 @@
         <v>83</v>
       </c>
       <c r="P176" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q176">
         <v>2.75</v>
@@ -37611,7 +37617,7 @@
         <v>83</v>
       </c>
       <c r="P177" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q177">
         <v>4.1</v>
@@ -37817,7 +37823,7 @@
         <v>210</v>
       </c>
       <c r="P178" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q178">
         <v>2.05</v>
@@ -38023,7 +38029,7 @@
         <v>211</v>
       </c>
       <c r="P179" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q179">
         <v>2.95</v>
@@ -38180,6 +38186,418 @@
       </c>
       <c r="BP179">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7784961</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45750.64583333334</v>
+      </c>
+      <c r="F180">
+        <v>30</v>
+      </c>
+      <c r="G180" t="s">
+        <v>79</v>
+      </c>
+      <c r="H180" t="s">
+        <v>78</v>
+      </c>
+      <c r="I180">
+        <v>2</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>2</v>
+      </c>
+      <c r="L180">
+        <v>2</v>
+      </c>
+      <c r="M180">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>3</v>
+      </c>
+      <c r="O180" t="s">
+        <v>212</v>
+      </c>
+      <c r="P180" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q180">
+        <v>1.95</v>
+      </c>
+      <c r="R180">
+        <v>2.37</v>
+      </c>
+      <c r="S180">
+        <v>5.25</v>
+      </c>
+      <c r="T180">
+        <v>1.29</v>
+      </c>
+      <c r="U180">
+        <v>3.25</v>
+      </c>
+      <c r="V180">
+        <v>2.3</v>
+      </c>
+      <c r="W180">
+        <v>1.53</v>
+      </c>
+      <c r="X180">
+        <v>5.25</v>
+      </c>
+      <c r="Y180">
+        <v>1.13</v>
+      </c>
+      <c r="Z180">
+        <v>1.48</v>
+      </c>
+      <c r="AA180">
+        <v>4.4</v>
+      </c>
+      <c r="AB180">
+        <v>5.9</v>
+      </c>
+      <c r="AC180">
+        <v>1.04</v>
+      </c>
+      <c r="AD180">
+        <v>10</v>
+      </c>
+      <c r="AE180">
+        <v>1.2</v>
+      </c>
+      <c r="AF180">
+        <v>4.33</v>
+      </c>
+      <c r="AG180">
+        <v>1.6</v>
+      </c>
+      <c r="AH180">
+        <v>2.15</v>
+      </c>
+      <c r="AI180">
+        <v>1.75</v>
+      </c>
+      <c r="AJ180">
+        <v>1.95</v>
+      </c>
+      <c r="AK180">
+        <v>1.13</v>
+      </c>
+      <c r="AL180">
+        <v>1.2</v>
+      </c>
+      <c r="AM180">
+        <v>2.5</v>
+      </c>
+      <c r="AN180">
+        <v>1.86</v>
+      </c>
+      <c r="AO180">
+        <v>0.93</v>
+      </c>
+      <c r="AP180">
+        <v>1.93</v>
+      </c>
+      <c r="AQ180">
+        <v>0.87</v>
+      </c>
+      <c r="AR180">
+        <v>1.88</v>
+      </c>
+      <c r="AS180">
+        <v>1.24</v>
+      </c>
+      <c r="AT180">
+        <v>3.12</v>
+      </c>
+      <c r="AU180">
+        <v>8</v>
+      </c>
+      <c r="AV180">
+        <v>2</v>
+      </c>
+      <c r="AW180">
+        <v>7</v>
+      </c>
+      <c r="AX180">
+        <v>9</v>
+      </c>
+      <c r="AY180">
+        <v>18</v>
+      </c>
+      <c r="AZ180">
+        <v>14</v>
+      </c>
+      <c r="BA180">
+        <v>5</v>
+      </c>
+      <c r="BB180">
+        <v>3</v>
+      </c>
+      <c r="BC180">
+        <v>8</v>
+      </c>
+      <c r="BD180">
+        <v>1.42</v>
+      </c>
+      <c r="BE180">
+        <v>7</v>
+      </c>
+      <c r="BF180">
+        <v>3.15</v>
+      </c>
+      <c r="BG180">
+        <v>1.18</v>
+      </c>
+      <c r="BH180">
+        <v>4.1</v>
+      </c>
+      <c r="BI180">
+        <v>1.32</v>
+      </c>
+      <c r="BJ180">
+        <v>3</v>
+      </c>
+      <c r="BK180">
+        <v>1.52</v>
+      </c>
+      <c r="BL180">
+        <v>2.28</v>
+      </c>
+      <c r="BM180">
+        <v>1.84</v>
+      </c>
+      <c r="BN180">
+        <v>1.83</v>
+      </c>
+      <c r="BO180">
+        <v>2.25</v>
+      </c>
+      <c r="BP180">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7784962</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45750.64583333334</v>
+      </c>
+      <c r="F181">
+        <v>30</v>
+      </c>
+      <c r="G181" t="s">
+        <v>75</v>
+      </c>
+      <c r="H181" t="s">
+        <v>80</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="K181">
+        <v>2</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>1</v>
+      </c>
+      <c r="N181">
+        <v>2</v>
+      </c>
+      <c r="O181" t="s">
+        <v>213</v>
+      </c>
+      <c r="P181" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q181">
+        <v>2.65</v>
+      </c>
+      <c r="R181">
+        <v>2.3</v>
+      </c>
+      <c r="S181">
+        <v>3.25</v>
+      </c>
+      <c r="T181">
+        <v>1.26</v>
+      </c>
+      <c r="U181">
+        <v>3.5</v>
+      </c>
+      <c r="V181">
+        <v>2.1</v>
+      </c>
+      <c r="W181">
+        <v>1.63</v>
+      </c>
+      <c r="X181">
+        <v>4.6</v>
+      </c>
+      <c r="Y181">
+        <v>1.16</v>
+      </c>
+      <c r="Z181">
+        <v>2.19</v>
+      </c>
+      <c r="AA181">
+        <v>3.62</v>
+      </c>
+      <c r="AB181">
+        <v>2.96</v>
+      </c>
+      <c r="AC181">
+        <v>1.01</v>
+      </c>
+      <c r="AD181">
+        <v>13</v>
+      </c>
+      <c r="AE181">
+        <v>1.17</v>
+      </c>
+      <c r="AF181">
+        <v>5</v>
+      </c>
+      <c r="AG181">
+        <v>1.52</v>
+      </c>
+      <c r="AH181">
+        <v>2.43</v>
+      </c>
+      <c r="AI181">
+        <v>1.44</v>
+      </c>
+      <c r="AJ181">
+        <v>2.55</v>
+      </c>
+      <c r="AK181">
+        <v>1.38</v>
+      </c>
+      <c r="AL181">
+        <v>1.27</v>
+      </c>
+      <c r="AM181">
+        <v>1.63</v>
+      </c>
+      <c r="AN181">
+        <v>1.93</v>
+      </c>
+      <c r="AO181">
+        <v>1</v>
+      </c>
+      <c r="AP181">
+        <v>1.87</v>
+      </c>
+      <c r="AQ181">
+        <v>1</v>
+      </c>
+      <c r="AR181">
+        <v>1.72</v>
+      </c>
+      <c r="AS181">
+        <v>1.44</v>
+      </c>
+      <c r="AT181">
+        <v>3.16</v>
+      </c>
+      <c r="AU181">
+        <v>5</v>
+      </c>
+      <c r="AV181">
+        <v>4</v>
+      </c>
+      <c r="AW181">
+        <v>11</v>
+      </c>
+      <c r="AX181">
+        <v>10</v>
+      </c>
+      <c r="AY181">
+        <v>20</v>
+      </c>
+      <c r="AZ181">
+        <v>16</v>
+      </c>
+      <c r="BA181">
+        <v>4</v>
+      </c>
+      <c r="BB181">
+        <v>2</v>
+      </c>
+      <c r="BC181">
+        <v>6</v>
+      </c>
+      <c r="BD181">
+        <v>1.74</v>
+      </c>
+      <c r="BE181">
+        <v>6.75</v>
+      </c>
+      <c r="BF181">
+        <v>2.32</v>
+      </c>
+      <c r="BG181">
+        <v>1.21</v>
+      </c>
+      <c r="BH181">
+        <v>3.7</v>
+      </c>
+      <c r="BI181">
+        <v>1.38</v>
+      </c>
+      <c r="BJ181">
+        <v>2.7</v>
+      </c>
+      <c r="BK181">
+        <v>1.63</v>
+      </c>
+      <c r="BL181">
+        <v>2.08</v>
+      </c>
+      <c r="BM181">
+        <v>2</v>
+      </c>
+      <c r="BN181">
+        <v>1.7</v>
+      </c>
+      <c r="BO181">
+        <v>2.5</v>
+      </c>
+      <c r="BP181">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -656,6 +656,12 @@
   </si>
   <si>
     <t>['2']</t>
+  </si>
+  <si>
+    <t>['90+6', '90+8']</t>
+  </si>
+  <si>
+    <t>['60']</t>
   </si>
   <si>
     <t>['25']</t>
@@ -1311,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1567,7 +1573,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1773,7 +1779,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1854,7 +1860,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ3">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2057,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -2185,7 +2191,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2263,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ5">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2391,7 +2397,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2469,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ6">
         <v>1.53</v>
@@ -2597,7 +2603,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2803,7 +2809,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3215,7 +3221,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3421,7 +3427,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3627,7 +3633,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3708,7 +3714,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR12">
         <v>2.07</v>
@@ -4039,7 +4045,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4245,7 +4251,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4738,7 +4744,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ17">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR17">
         <v>1.15</v>
@@ -4863,7 +4869,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4941,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5069,7 +5075,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5147,10 +5153,10 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ19">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -5353,10 +5359,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ20">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR20">
         <v>1.02</v>
@@ -5687,7 +5693,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6099,7 +6105,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6511,7 +6517,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6923,7 +6929,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7004,7 +7010,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ28">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR28">
         <v>1.22</v>
@@ -7210,7 +7216,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ29">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7335,7 +7341,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7825,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8031,7 +8037,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ33">
         <v>1.67</v>
@@ -8571,7 +8577,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8649,7 +8655,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ36">
         <v>1.29</v>
@@ -8777,7 +8783,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8983,7 +8989,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9189,7 +9195,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9270,7 +9276,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ39">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR39">
         <v>2.16</v>
@@ -9395,7 +9401,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9473,10 +9479,10 @@
         <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ40">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR40">
         <v>1.54</v>
@@ -9807,7 +9813,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9885,7 +9891,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ42">
         <v>1.07</v>
@@ -10013,7 +10019,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10094,7 +10100,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ43">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR43">
         <v>1.61</v>
@@ -10631,7 +10637,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10709,7 +10715,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ46">
         <v>0.87</v>
@@ -10918,7 +10924,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ47">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR47">
         <v>1.94</v>
@@ -11249,7 +11255,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11455,7 +11461,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11536,7 +11542,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ50">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR50">
         <v>1.38</v>
@@ -11661,7 +11667,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11945,7 +11951,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ52">
         <v>0.87</v>
@@ -12485,7 +12491,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12691,7 +12697,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12772,7 +12778,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ56">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR56">
         <v>1.56</v>
@@ -12975,7 +12981,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -13184,7 +13190,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ58">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13309,7 +13315,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13593,7 +13599,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ60">
         <v>0.44</v>
@@ -14005,7 +14011,7 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ62">
         <v>0.87</v>
@@ -14133,7 +14139,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14211,7 +14217,7 @@
         <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ63">
         <v>1.53</v>
@@ -14339,7 +14345,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14420,7 +14426,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ64">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14545,7 +14551,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14957,7 +14963,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15163,7 +15169,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15369,7 +15375,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15450,7 +15456,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ69">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
@@ -15575,7 +15581,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15781,7 +15787,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15859,7 +15865,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ71">
         <v>1.53</v>
@@ -16193,7 +16199,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16811,7 +16817,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16892,7 +16898,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ76">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -17095,7 +17101,7 @@
         <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ77">
         <v>1.67</v>
@@ -17304,7 +17310,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ78">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -17713,7 +17719,7 @@
         <v>0.83</v>
       </c>
       <c r="AP80">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17841,7 +17847,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18047,7 +18053,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18128,7 +18134,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ82">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR82">
         <v>1.87</v>
@@ -18253,7 +18259,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18459,7 +18465,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18665,7 +18671,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18743,7 +18749,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ85">
         <v>1.29</v>
@@ -18871,7 +18877,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -19077,7 +19083,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19361,10 +19367,10 @@
         <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ88">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19570,7 +19576,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ89">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR89">
         <v>1.82</v>
@@ -19776,7 +19782,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ90">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -20519,7 +20525,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20725,7 +20731,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20803,10 +20809,10 @@
         <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ95">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR95">
         <v>1.3</v>
@@ -21137,7 +21143,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21215,7 +21221,7 @@
         <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21343,7 +21349,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21424,7 +21430,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ98">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21755,7 +21761,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22039,10 +22045,10 @@
         <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ101">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR101">
         <v>1.77</v>
@@ -22167,7 +22173,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22373,7 +22379,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22579,7 +22585,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22657,7 +22663,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ104">
         <v>1.33</v>
@@ -22785,7 +22791,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22866,7 +22872,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ105">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR105">
         <v>0.93</v>
@@ -23197,7 +23203,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23275,7 +23281,7 @@
         <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ107">
         <v>1.67</v>
@@ -23403,7 +23409,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23609,7 +23615,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23893,7 +23899,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ110">
         <v>0.44</v>
@@ -24021,7 +24027,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24514,7 +24520,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ113">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR113">
         <v>1.39</v>
@@ -24639,7 +24645,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24923,7 +24929,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -25463,7 +25469,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25541,7 +25547,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ118">
         <v>1.29</v>
@@ -25669,7 +25675,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25875,7 +25881,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25956,7 +25962,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ120">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR120">
         <v>1.76</v>
@@ -26162,7 +26168,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ121">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR121">
         <v>1.67</v>
@@ -26287,7 +26293,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26365,7 +26371,7 @@
         <v>0.7</v>
       </c>
       <c r="AP122">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ122">
         <v>1.07</v>
@@ -26493,7 +26499,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -26574,7 +26580,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ123">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR123">
         <v>1.87</v>
@@ -27111,7 +27117,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27523,7 +27529,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27729,7 +27735,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27935,7 +27941,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28141,7 +28147,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28219,10 +28225,10 @@
         <v>0.7</v>
       </c>
       <c r="AP131">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ131">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR131">
         <v>1.95</v>
@@ -28553,7 +28559,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28631,10 +28637,10 @@
         <v>1.4</v>
       </c>
       <c r="AP133">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ133">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR133">
         <v>1.28</v>
@@ -28759,7 +28765,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28837,10 +28843,10 @@
         <v>0.64</v>
       </c>
       <c r="AP134">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ134">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR134">
         <v>1.83</v>
@@ -28965,7 +28971,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29171,7 +29177,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29249,10 +29255,10 @@
         <v>0.91</v>
       </c>
       <c r="AP136">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ136">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR136">
         <v>2.08</v>
@@ -29377,7 +29383,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29583,7 +29589,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29789,7 +29795,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -30282,7 +30288,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ141">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR141">
         <v>1.74</v>
@@ -30485,7 +30491,7 @@
         <v>0.91</v>
       </c>
       <c r="AP142">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ142">
         <v>1.07</v>
@@ -31025,7 +31031,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31231,7 +31237,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31309,7 +31315,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ146">
         <v>0.87</v>
@@ -31437,7 +31443,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31518,7 +31524,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ147">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR147">
         <v>1.5</v>
@@ -31643,7 +31649,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31849,7 +31855,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -31930,7 +31936,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ149">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR149">
         <v>1.79</v>
@@ -32133,7 +32139,7 @@
         <v>1.36</v>
       </c>
       <c r="AP150">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ150">
         <v>1.29</v>
@@ -32261,7 +32267,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32548,7 +32554,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ152">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR152">
         <v>1.84</v>
@@ -32751,7 +32757,7 @@
         <v>1.15</v>
       </c>
       <c r="AP153">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -32957,7 +32963,7 @@
         <v>1.33</v>
       </c>
       <c r="AP154">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ154">
         <v>1.67</v>
@@ -33085,7 +33091,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33166,7 +33172,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ155">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR155">
         <v>2</v>
@@ -33497,7 +33503,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33781,7 +33787,7 @@
         <v>0.92</v>
       </c>
       <c r="AP158">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -33909,7 +33915,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -34321,7 +34327,7 @@
         <v>91</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34527,7 +34533,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34733,7 +34739,7 @@
         <v>120</v>
       </c>
       <c r="P163" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q163">
         <v>3.35</v>
@@ -34939,7 +34945,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35020,7 +35026,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ164">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR164">
         <v>1.99</v>
@@ -35145,7 +35151,7 @@
         <v>83</v>
       </c>
       <c r="P165" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35351,7 +35357,7 @@
         <v>206</v>
       </c>
       <c r="P166" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35638,7 +35644,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ167">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR167">
         <v>1.48</v>
@@ -35763,7 +35769,7 @@
         <v>208</v>
       </c>
       <c r="P168" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35969,7 +35975,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q169">
         <v>1.91</v>
@@ -36256,7 +36262,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ170">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR170">
         <v>1.68</v>
@@ -36459,7 +36465,7 @@
         <v>1.07</v>
       </c>
       <c r="AP171">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ171">
         <v>1</v>
@@ -36587,7 +36593,7 @@
         <v>83</v>
       </c>
       <c r="P172" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q172">
         <v>2.88</v>
@@ -36793,7 +36799,7 @@
         <v>83</v>
       </c>
       <c r="P173" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q173">
         <v>5.5</v>
@@ -36871,7 +36877,7 @@
         <v>1.43</v>
       </c>
       <c r="AP173">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ173">
         <v>1.53</v>
@@ -36999,7 +37005,7 @@
         <v>208</v>
       </c>
       <c r="P174" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37077,7 +37083,7 @@
         <v>1.21</v>
       </c>
       <c r="AP174">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ174">
         <v>1.33</v>
@@ -37205,7 +37211,7 @@
         <v>101</v>
       </c>
       <c r="P175" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37286,7 +37292,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ175">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR175">
         <v>1.47</v>
@@ -37411,7 +37417,7 @@
         <v>83</v>
       </c>
       <c r="P176" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q176">
         <v>2.75</v>
@@ -37617,7 +37623,7 @@
         <v>83</v>
       </c>
       <c r="P177" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q177">
         <v>4.1</v>
@@ -37823,7 +37829,7 @@
         <v>210</v>
       </c>
       <c r="P178" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q178">
         <v>2.05</v>
@@ -38029,7 +38035,7 @@
         <v>211</v>
       </c>
       <c r="P179" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q179">
         <v>2.95</v>
@@ -38598,6 +38604,624 @@
       </c>
       <c r="BP181">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7784963</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F182">
+        <v>31</v>
+      </c>
+      <c r="G182" t="s">
+        <v>74</v>
+      </c>
+      <c r="H182" t="s">
+        <v>77</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>2</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>2</v>
+      </c>
+      <c r="O182" t="s">
+        <v>214</v>
+      </c>
+      <c r="P182" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q182">
+        <v>2.63</v>
+      </c>
+      <c r="R182">
+        <v>2.25</v>
+      </c>
+      <c r="S182">
+        <v>3.75</v>
+      </c>
+      <c r="T182">
+        <v>1.33</v>
+      </c>
+      <c r="U182">
+        <v>3.25</v>
+      </c>
+      <c r="V182">
+        <v>2.63</v>
+      </c>
+      <c r="W182">
+        <v>1.44</v>
+      </c>
+      <c r="X182">
+        <v>6.5</v>
+      </c>
+      <c r="Y182">
+        <v>1.11</v>
+      </c>
+      <c r="Z182">
+        <v>2.03</v>
+      </c>
+      <c r="AA182">
+        <v>3.36</v>
+      </c>
+      <c r="AB182">
+        <v>3.56</v>
+      </c>
+      <c r="AC182">
+        <v>2.92</v>
+      </c>
+      <c r="AD182">
+        <v>1.4</v>
+      </c>
+      <c r="AE182">
+        <v>1.3</v>
+      </c>
+      <c r="AF182">
+        <v>3.61</v>
+      </c>
+      <c r="AG182">
+        <v>1.77</v>
+      </c>
+      <c r="AH182">
+        <v>1.98</v>
+      </c>
+      <c r="AI182">
+        <v>1.62</v>
+      </c>
+      <c r="AJ182">
+        <v>2.2</v>
+      </c>
+      <c r="AK182">
+        <v>1.26</v>
+      </c>
+      <c r="AL182">
+        <v>1.28</v>
+      </c>
+      <c r="AM182">
+        <v>1.88</v>
+      </c>
+      <c r="AN182">
+        <v>1.73</v>
+      </c>
+      <c r="AO182">
+        <v>0.73</v>
+      </c>
+      <c r="AP182">
+        <v>1.81</v>
+      </c>
+      <c r="AQ182">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR182">
+        <v>1.82</v>
+      </c>
+      <c r="AS182">
+        <v>1.48</v>
+      </c>
+      <c r="AT182">
+        <v>3.3</v>
+      </c>
+      <c r="AU182">
+        <v>5</v>
+      </c>
+      <c r="AV182">
+        <v>4</v>
+      </c>
+      <c r="AW182">
+        <v>16</v>
+      </c>
+      <c r="AX182">
+        <v>3</v>
+      </c>
+      <c r="AY182">
+        <v>25</v>
+      </c>
+      <c r="AZ182">
+        <v>7</v>
+      </c>
+      <c r="BA182">
+        <v>15</v>
+      </c>
+      <c r="BB182">
+        <v>2</v>
+      </c>
+      <c r="BC182">
+        <v>17</v>
+      </c>
+      <c r="BD182">
+        <v>1.51</v>
+      </c>
+      <c r="BE182">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF182">
+        <v>3.1</v>
+      </c>
+      <c r="BG182">
+        <v>1.16</v>
+      </c>
+      <c r="BH182">
+        <v>4.05</v>
+      </c>
+      <c r="BI182">
+        <v>1.34</v>
+      </c>
+      <c r="BJ182">
+        <v>2.78</v>
+      </c>
+      <c r="BK182">
+        <v>1.62</v>
+      </c>
+      <c r="BL182">
+        <v>2.1</v>
+      </c>
+      <c r="BM182">
+        <v>2.04</v>
+      </c>
+      <c r="BN182">
+        <v>1.69</v>
+      </c>
+      <c r="BO182">
+        <v>2.67</v>
+      </c>
+      <c r="BP182">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7784964</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F183">
+        <v>31</v>
+      </c>
+      <c r="G183" t="s">
+        <v>72</v>
+      </c>
+      <c r="H183" t="s">
+        <v>81</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183" t="s">
+        <v>83</v>
+      </c>
+      <c r="P183" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q183">
+        <v>4.33</v>
+      </c>
+      <c r="R183">
+        <v>2.25</v>
+      </c>
+      <c r="S183">
+        <v>2.5</v>
+      </c>
+      <c r="T183">
+        <v>1.36</v>
+      </c>
+      <c r="U183">
+        <v>3</v>
+      </c>
+      <c r="V183">
+        <v>2.63</v>
+      </c>
+      <c r="W183">
+        <v>1.44</v>
+      </c>
+      <c r="X183">
+        <v>7</v>
+      </c>
+      <c r="Y183">
+        <v>1.1</v>
+      </c>
+      <c r="Z183">
+        <v>3.75</v>
+      </c>
+      <c r="AA183">
+        <v>3.6</v>
+      </c>
+      <c r="AB183">
+        <v>1.9</v>
+      </c>
+      <c r="AC183">
+        <v>3.98</v>
+      </c>
+      <c r="AD183">
+        <v>1.24</v>
+      </c>
+      <c r="AE183">
+        <v>1.19</v>
+      </c>
+      <c r="AF183">
+        <v>4.85</v>
+      </c>
+      <c r="AG183">
+        <v>1.77</v>
+      </c>
+      <c r="AH183">
+        <v>1.98</v>
+      </c>
+      <c r="AI183">
+        <v>1.67</v>
+      </c>
+      <c r="AJ183">
+        <v>2.1</v>
+      </c>
+      <c r="AK183">
+        <v>2.02</v>
+      </c>
+      <c r="AL183">
+        <v>1.25</v>
+      </c>
+      <c r="AM183">
+        <v>1.24</v>
+      </c>
+      <c r="AN183">
+        <v>1.14</v>
+      </c>
+      <c r="AO183">
+        <v>1.64</v>
+      </c>
+      <c r="AP183">
+        <v>1.13</v>
+      </c>
+      <c r="AQ183">
+        <v>1.6</v>
+      </c>
+      <c r="AR183">
+        <v>1.28</v>
+      </c>
+      <c r="AS183">
+        <v>1.64</v>
+      </c>
+      <c r="AT183">
+        <v>2.92</v>
+      </c>
+      <c r="AU183">
+        <v>2</v>
+      </c>
+      <c r="AV183">
+        <v>2</v>
+      </c>
+      <c r="AW183">
+        <v>8</v>
+      </c>
+      <c r="AX183">
+        <v>15</v>
+      </c>
+      <c r="AY183">
+        <v>12</v>
+      </c>
+      <c r="AZ183">
+        <v>22</v>
+      </c>
+      <c r="BA183">
+        <v>7</v>
+      </c>
+      <c r="BB183">
+        <v>5</v>
+      </c>
+      <c r="BC183">
+        <v>12</v>
+      </c>
+      <c r="BD183">
+        <v>3.22</v>
+      </c>
+      <c r="BE183">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF183">
+        <v>1.48</v>
+      </c>
+      <c r="BG183">
+        <v>1.16</v>
+      </c>
+      <c r="BH183">
+        <v>4.05</v>
+      </c>
+      <c r="BI183">
+        <v>1.34</v>
+      </c>
+      <c r="BJ183">
+        <v>2.78</v>
+      </c>
+      <c r="BK183">
+        <v>1.62</v>
+      </c>
+      <c r="BL183">
+        <v>2.1</v>
+      </c>
+      <c r="BM183">
+        <v>2.06</v>
+      </c>
+      <c r="BN183">
+        <v>1.68</v>
+      </c>
+      <c r="BO183">
+        <v>2.67</v>
+      </c>
+      <c r="BP183">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7784965</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45752.64583333334</v>
+      </c>
+      <c r="F184">
+        <v>31</v>
+      </c>
+      <c r="G184" t="s">
+        <v>73</v>
+      </c>
+      <c r="H184" t="s">
+        <v>71</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+      <c r="N184">
+        <v>2</v>
+      </c>
+      <c r="O184" t="s">
+        <v>215</v>
+      </c>
+      <c r="P184" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q184">
+        <v>1.8</v>
+      </c>
+      <c r="R184">
+        <v>2.75</v>
+      </c>
+      <c r="S184">
+        <v>6.5</v>
+      </c>
+      <c r="T184">
+        <v>1.22</v>
+      </c>
+      <c r="U184">
+        <v>4</v>
+      </c>
+      <c r="V184">
+        <v>2.1</v>
+      </c>
+      <c r="W184">
+        <v>1.67</v>
+      </c>
+      <c r="X184">
+        <v>4.5</v>
+      </c>
+      <c r="Y184">
+        <v>1.18</v>
+      </c>
+      <c r="Z184">
+        <v>1.35</v>
+      </c>
+      <c r="AA184">
+        <v>5.3</v>
+      </c>
+      <c r="AB184">
+        <v>7.2</v>
+      </c>
+      <c r="AC184">
+        <v>0</v>
+      </c>
+      <c r="AD184">
+        <v>0</v>
+      </c>
+      <c r="AE184">
+        <v>1.2</v>
+      </c>
+      <c r="AF184">
+        <v>4.74</v>
+      </c>
+      <c r="AG184">
+        <v>1.48</v>
+      </c>
+      <c r="AH184">
+        <v>2.54</v>
+      </c>
+      <c r="AI184">
+        <v>1.67</v>
+      </c>
+      <c r="AJ184">
+        <v>2.1</v>
+      </c>
+      <c r="AK184">
+        <v>1.07</v>
+      </c>
+      <c r="AL184">
+        <v>1.16</v>
+      </c>
+      <c r="AM184">
+        <v>3.14</v>
+      </c>
+      <c r="AN184">
+        <v>2.2</v>
+      </c>
+      <c r="AO184">
+        <v>0.73</v>
+      </c>
+      <c r="AP184">
+        <v>2.13</v>
+      </c>
+      <c r="AQ184">
+        <v>0.75</v>
+      </c>
+      <c r="AR184">
+        <v>2.01</v>
+      </c>
+      <c r="AS184">
+        <v>1.26</v>
+      </c>
+      <c r="AT184">
+        <v>3.27</v>
+      </c>
+      <c r="AU184">
+        <v>10</v>
+      </c>
+      <c r="AV184">
+        <v>4</v>
+      </c>
+      <c r="AW184">
+        <v>16</v>
+      </c>
+      <c r="AX184">
+        <v>11</v>
+      </c>
+      <c r="AY184">
+        <v>30</v>
+      </c>
+      <c r="AZ184">
+        <v>17</v>
+      </c>
+      <c r="BA184">
+        <v>9</v>
+      </c>
+      <c r="BB184">
+        <v>4</v>
+      </c>
+      <c r="BC184">
+        <v>13</v>
+      </c>
+      <c r="BD184">
+        <v>1.18</v>
+      </c>
+      <c r="BE184">
+        <v>12.5</v>
+      </c>
+      <c r="BF184">
+        <v>6.15</v>
+      </c>
+      <c r="BG184">
+        <v>1.13</v>
+      </c>
+      <c r="BH184">
+        <v>4.5</v>
+      </c>
+      <c r="BI184">
+        <v>1.28</v>
+      </c>
+      <c r="BJ184">
+        <v>3.08</v>
+      </c>
+      <c r="BK184">
+        <v>1.53</v>
+      </c>
+      <c r="BL184">
+        <v>2.28</v>
+      </c>
+      <c r="BM184">
+        <v>1.9</v>
+      </c>
+      <c r="BN184">
+        <v>1.8</v>
+      </c>
+      <c r="BO184">
+        <v>2.42</v>
+      </c>
+      <c r="BP184">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -662,6 +662,12 @@
   </si>
   <si>
     <t>['60']</t>
+  </si>
+  <si>
+    <t>['14', '55', '72']</t>
+  </si>
+  <si>
+    <t>['63', '82']</t>
   </si>
   <si>
     <t>['25']</t>
@@ -1317,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP184"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,7 +1579,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1779,7 +1785,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -2191,7 +2197,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2397,7 +2403,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2603,7 +2609,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2684,7 +2690,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ7">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2809,7 +2815,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -3221,7 +3227,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3299,10 +3305,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3427,7 +3433,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3505,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3633,7 +3639,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3917,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ13">
         <v>1.07</v>
@@ -4045,7 +4051,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -4251,7 +4257,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4329,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ15">
         <v>1.53</v>
@@ -4538,7 +4544,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ16">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR16">
         <v>2.11</v>
@@ -4869,7 +4875,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5075,7 +5081,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5693,7 +5699,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5977,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ23">
         <v>0.87</v>
@@ -6105,7 +6111,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6186,7 +6192,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR24">
         <v>1.94</v>
@@ -6517,7 +6523,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6929,7 +6935,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -7007,7 +7013,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ28">
         <v>0.6899999999999999</v>
@@ -7213,7 +7219,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>0.75</v>
@@ -7341,7 +7347,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -8040,7 +8046,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR33">
         <v>1.17</v>
@@ -8246,7 +8252,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR34">
         <v>2.41</v>
@@ -8577,7 +8583,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8658,7 +8664,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ36">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR36">
         <v>1.64</v>
@@ -8783,7 +8789,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8861,10 +8867,10 @@
         <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR37">
         <v>1.76</v>
@@ -8989,7 +8995,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -9067,10 +9073,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ38">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR38">
         <v>1.38</v>
@@ -9195,7 +9201,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9273,7 +9279,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
         <v>1.6</v>
@@ -9401,7 +9407,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9688,7 +9694,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ41">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR41">
         <v>1.53</v>
@@ -9813,7 +9819,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -10019,7 +10025,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10097,7 +10103,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ43">
         <v>1.6</v>
@@ -10637,7 +10643,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -11255,7 +11261,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11461,7 +11467,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11667,7 +11673,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -12160,7 +12166,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ53">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR53">
         <v>1.68</v>
@@ -12363,7 +12369,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>1.07</v>
@@ -12491,7 +12497,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12569,10 +12575,10 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ55">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR55">
         <v>1.62</v>
@@ -12697,7 +12703,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12775,7 +12781,7 @@
         <v>1.75</v>
       </c>
       <c r="AP56">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ56">
         <v>1.6</v>
@@ -12984,7 +12990,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR57">
         <v>1.51</v>
@@ -13315,7 +13321,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13393,7 +13399,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13808,7 +13814,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ61">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR61">
         <v>1.01</v>
@@ -14139,7 +14145,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -14345,7 +14351,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14551,7 +14557,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14963,7 +14969,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -15044,7 +15050,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR67">
         <v>1.55</v>
@@ -15169,7 +15175,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15375,7 +15381,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15581,7 +15587,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15659,7 +15665,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ70">
         <v>0.44</v>
@@ -15787,7 +15793,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16071,10 +16077,10 @@
         <v>1.6</v>
       </c>
       <c r="AP72">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ72">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR72">
         <v>1.54</v>
@@ -16199,7 +16205,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16280,7 +16286,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16689,7 +16695,7 @@
         <v>0.17</v>
       </c>
       <c r="AP75">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>0.44</v>
@@ -16817,7 +16823,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16895,7 +16901,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ76">
         <v>0.6899999999999999</v>
@@ -17104,7 +17110,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR77">
         <v>1.84</v>
@@ -17847,7 +17853,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18053,7 +18059,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18259,7 +18265,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18340,7 +18346,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18465,7 +18471,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18543,7 +18549,7 @@
         <v>0.83</v>
       </c>
       <c r="AP84">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18671,7 +18677,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18752,7 +18758,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ85">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR85">
         <v>1.7</v>
@@ -18877,7 +18883,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -19083,7 +19089,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19161,7 +19167,7 @@
         <v>0.14</v>
       </c>
       <c r="AP87">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ87">
         <v>0.44</v>
@@ -19779,7 +19785,7 @@
         <v>0.71</v>
       </c>
       <c r="AP90">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ90">
         <v>0.75</v>
@@ -19985,10 +19991,10 @@
         <v>1.57</v>
       </c>
       <c r="AP91">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ91">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR91">
         <v>1.8</v>
@@ -20191,7 +20197,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20400,7 +20406,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR93">
         <v>0.95</v>
@@ -20525,7 +20531,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20731,7 +20737,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -21018,7 +21024,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ96">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21143,7 +21149,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21349,7 +21355,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21427,7 +21433,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ98">
         <v>0.75</v>
@@ -21761,7 +21767,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21842,7 +21848,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ100">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -22173,7 +22179,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22379,7 +22385,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22457,7 +22463,7 @@
         <v>1.63</v>
       </c>
       <c r="AP103">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ103">
         <v>1.53</v>
@@ -22585,7 +22591,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22666,7 +22672,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR104">
         <v>1.23</v>
@@ -22791,7 +22797,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -23075,7 +23081,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>0.87</v>
@@ -23203,7 +23209,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23284,7 +23290,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ107">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23409,7 +23415,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23615,7 +23621,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -24027,7 +24033,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24645,7 +24651,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24932,7 +24938,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25135,7 +25141,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ116">
         <v>1.07</v>
@@ -25344,7 +25350,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ117">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR117">
         <v>1</v>
@@ -25469,7 +25475,7 @@
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q118">
         <v>4.2</v>
@@ -25550,7 +25556,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ118">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25675,7 +25681,7 @@
         <v>170</v>
       </c>
       <c r="P119" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q119">
         <v>2.95</v>
@@ -25753,7 +25759,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -25881,7 +25887,7 @@
         <v>171</v>
       </c>
       <c r="P120" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25959,7 +25965,7 @@
         <v>1.11</v>
       </c>
       <c r="AP120">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
         <v>0.6899999999999999</v>
@@ -26293,7 +26299,7 @@
         <v>128</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26499,7 +26505,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q123">
         <v>2.5</v>
@@ -27117,7 +27123,7 @@
         <v>83</v>
       </c>
       <c r="P126" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27529,7 +27535,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q128">
         <v>3.45</v>
@@ -27607,7 +27613,7 @@
         <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27735,7 +27741,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27816,7 +27822,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ129">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR129">
         <v>1.71</v>
@@ -27941,7 +27947,7 @@
         <v>179</v>
       </c>
       <c r="P130" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28019,10 +28025,10 @@
         <v>1.5</v>
       </c>
       <c r="AP130">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ130">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR130">
         <v>1.84</v>
@@ -28147,7 +28153,7 @@
         <v>180</v>
       </c>
       <c r="P131" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q131">
         <v>1.71</v>
@@ -28431,10 +28437,10 @@
         <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR132">
         <v>1.81</v>
@@ -28559,7 +28565,7 @@
         <v>83</v>
       </c>
       <c r="P133" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q133">
         <v>3.6</v>
@@ -28765,7 +28771,7 @@
         <v>182</v>
       </c>
       <c r="P134" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>1.78</v>
@@ -28971,7 +28977,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29177,7 +29183,7 @@
         <v>184</v>
       </c>
       <c r="P136" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q136">
         <v>2.15</v>
@@ -29383,7 +29389,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q137">
         <v>2.7</v>
@@ -29589,7 +29595,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q138">
         <v>2</v>
@@ -29795,7 +29801,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q139">
         <v>2.8</v>
@@ -30082,7 +30088,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30903,7 +30909,7 @@
         <v>0.91</v>
       </c>
       <c r="AP144">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -31031,7 +31037,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q145">
         <v>3.7</v>
@@ -31109,10 +31115,10 @@
         <v>1.18</v>
       </c>
       <c r="AP145">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ145">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR145">
         <v>1.53</v>
@@ -31237,7 +31243,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q146">
         <v>2.18</v>
@@ -31443,7 +31449,7 @@
         <v>193</v>
       </c>
       <c r="P147" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31649,7 +31655,7 @@
         <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31727,7 +31733,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ148">
         <v>1.53</v>
@@ -31855,7 +31861,7 @@
         <v>195</v>
       </c>
       <c r="P149" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q149">
         <v>2.55</v>
@@ -32142,7 +32148,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ150">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR150">
         <v>2.1</v>
@@ -32267,7 +32273,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q151">
         <v>1.71</v>
@@ -32551,7 +32557,7 @@
         <v>0.77</v>
       </c>
       <c r="AP152">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ152">
         <v>0.6899999999999999</v>
@@ -32966,7 +32972,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ154">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR154">
         <v>1.84</v>
@@ -33091,7 +33097,7 @@
         <v>83</v>
       </c>
       <c r="P155" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q155">
         <v>2.46</v>
@@ -33375,7 +33381,7 @@
         <v>0.83</v>
       </c>
       <c r="AP156">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ156">
         <v>1.07</v>
@@ -33503,7 +33509,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q157">
         <v>3.95</v>
@@ -33584,7 +33590,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ157">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -33915,7 +33921,7 @@
         <v>202</v>
       </c>
       <c r="P159" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q159">
         <v>2.62</v>
@@ -34199,7 +34205,7 @@
         <v>1</v>
       </c>
       <c r="AP160">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ160">
         <v>0.87</v>
@@ -34327,7 +34333,7 @@
         <v>91</v>
       </c>
       <c r="P161" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34408,7 +34414,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ161">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR161">
         <v>1.53</v>
@@ -34533,7 +34539,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34614,7 +34620,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ162">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR162">
         <v>1.69</v>
@@ -34739,7 +34745,7 @@
         <v>120</v>
       </c>
       <c r="P163" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q163">
         <v>3.35</v>
@@ -34945,7 +34951,7 @@
         <v>205</v>
       </c>
       <c r="P164" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q164">
         <v>1.91</v>
@@ -35151,7 +35157,7 @@
         <v>83</v>
       </c>
       <c r="P165" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35229,7 +35235,7 @@
         <v>0.85</v>
       </c>
       <c r="AP165">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35357,7 +35363,7 @@
         <v>206</v>
       </c>
       <c r="P166" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35438,7 +35444,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ166">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR166">
         <v>1.55</v>
@@ -35641,7 +35647,7 @@
         <v>0.71</v>
       </c>
       <c r="AP167">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ167">
         <v>0.6899999999999999</v>
@@ -35769,7 +35775,7 @@
         <v>208</v>
       </c>
       <c r="P168" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35847,7 +35853,7 @@
         <v>0.77</v>
       </c>
       <c r="AP168">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ168">
         <v>1.07</v>
@@ -35975,7 +35981,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q169">
         <v>1.91</v>
@@ -36593,7 +36599,7 @@
         <v>83</v>
       </c>
       <c r="P172" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q172">
         <v>2.88</v>
@@ -36674,7 +36680,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ172">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR172">
         <v>1.98</v>
@@ -36799,7 +36805,7 @@
         <v>83</v>
       </c>
       <c r="P173" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q173">
         <v>5.5</v>
@@ -37005,7 +37011,7 @@
         <v>208</v>
       </c>
       <c r="P174" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37086,7 +37092,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ174">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR174">
         <v>1.86</v>
@@ -37211,7 +37217,7 @@
         <v>101</v>
       </c>
       <c r="P175" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37289,7 +37295,7 @@
         <v>1.54</v>
       </c>
       <c r="AP175">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ175">
         <v>1.6</v>
@@ -37417,7 +37423,7 @@
         <v>83</v>
       </c>
       <c r="P176" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q176">
         <v>2.75</v>
@@ -37623,7 +37629,7 @@
         <v>83</v>
       </c>
       <c r="P177" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q177">
         <v>4.1</v>
@@ -37704,7 +37710,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ177">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR177">
         <v>1.29</v>
@@ -37829,7 +37835,7 @@
         <v>210</v>
       </c>
       <c r="P178" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q178">
         <v>2.05</v>
@@ -38035,7 +38041,7 @@
         <v>211</v>
       </c>
       <c r="P179" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q179">
         <v>2.95</v>
@@ -38319,7 +38325,7 @@
         <v>0.93</v>
       </c>
       <c r="AP180">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ180">
         <v>0.87</v>
@@ -39222,6 +39228,624 @@
       </c>
       <c r="BP184">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7784966</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45753.38541666666</v>
+      </c>
+      <c r="F185">
+        <v>31</v>
+      </c>
+      <c r="G185" t="s">
+        <v>80</v>
+      </c>
+      <c r="H185" t="s">
+        <v>76</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>1</v>
+      </c>
+      <c r="O185" t="s">
+        <v>96</v>
+      </c>
+      <c r="P185" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q185">
+        <v>4</v>
+      </c>
+      <c r="R185">
+        <v>2.3</v>
+      </c>
+      <c r="S185">
+        <v>2.6</v>
+      </c>
+      <c r="T185">
+        <v>1.33</v>
+      </c>
+      <c r="U185">
+        <v>3.25</v>
+      </c>
+      <c r="V185">
+        <v>2.63</v>
+      </c>
+      <c r="W185">
+        <v>1.44</v>
+      </c>
+      <c r="X185">
+        <v>6.5</v>
+      </c>
+      <c r="Y185">
+        <v>1.11</v>
+      </c>
+      <c r="Z185">
+        <v>3.77</v>
+      </c>
+      <c r="AA185">
+        <v>3.47</v>
+      </c>
+      <c r="AB185">
+        <v>1.94</v>
+      </c>
+      <c r="AC185">
+        <v>1.05</v>
+      </c>
+      <c r="AD185">
+        <v>9.5</v>
+      </c>
+      <c r="AE185">
+        <v>1.22</v>
+      </c>
+      <c r="AF185">
+        <v>4</v>
+      </c>
+      <c r="AG185">
+        <v>1.65</v>
+      </c>
+      <c r="AH185">
+        <v>2</v>
+      </c>
+      <c r="AI185">
+        <v>1.62</v>
+      </c>
+      <c r="AJ185">
+        <v>2.2</v>
+      </c>
+      <c r="AK185">
+        <v>1.8</v>
+      </c>
+      <c r="AL185">
+        <v>1.29</v>
+      </c>
+      <c r="AM185">
+        <v>1.26</v>
+      </c>
+      <c r="AN185">
+        <v>1.71</v>
+      </c>
+      <c r="AO185">
+        <v>1.67</v>
+      </c>
+      <c r="AP185">
+        <v>1.8</v>
+      </c>
+      <c r="AQ185">
+        <v>1.56</v>
+      </c>
+      <c r="AR185">
+        <v>1.9</v>
+      </c>
+      <c r="AS185">
+        <v>1.54</v>
+      </c>
+      <c r="AT185">
+        <v>3.44</v>
+      </c>
+      <c r="AU185">
+        <v>10</v>
+      </c>
+      <c r="AV185">
+        <v>4</v>
+      </c>
+      <c r="AW185">
+        <v>10</v>
+      </c>
+      <c r="AX185">
+        <v>12</v>
+      </c>
+      <c r="AY185">
+        <v>22</v>
+      </c>
+      <c r="AZ185">
+        <v>19</v>
+      </c>
+      <c r="BA185">
+        <v>5</v>
+      </c>
+      <c r="BB185">
+        <v>6</v>
+      </c>
+      <c r="BC185">
+        <v>11</v>
+      </c>
+      <c r="BD185">
+        <v>2.4</v>
+      </c>
+      <c r="BE185">
+        <v>6.5</v>
+      </c>
+      <c r="BF185">
+        <v>1.7</v>
+      </c>
+      <c r="BG185">
+        <v>1.28</v>
+      </c>
+      <c r="BH185">
+        <v>3.2</v>
+      </c>
+      <c r="BI185">
+        <v>1.48</v>
+      </c>
+      <c r="BJ185">
+        <v>2.4</v>
+      </c>
+      <c r="BK185">
+        <v>1.78</v>
+      </c>
+      <c r="BL185">
+        <v>1.88</v>
+      </c>
+      <c r="BM185">
+        <v>2.23</v>
+      </c>
+      <c r="BN185">
+        <v>1.56</v>
+      </c>
+      <c r="BO185">
+        <v>2.9</v>
+      </c>
+      <c r="BP185">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7784968</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45753.47916666666</v>
+      </c>
+      <c r="F186">
+        <v>31</v>
+      </c>
+      <c r="G186" t="s">
+        <v>78</v>
+      </c>
+      <c r="H186" t="s">
+        <v>75</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>3</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>4</v>
+      </c>
+      <c r="O186" t="s">
+        <v>216</v>
+      </c>
+      <c r="P186" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q186">
+        <v>3.5</v>
+      </c>
+      <c r="R186">
+        <v>2.3</v>
+      </c>
+      <c r="S186">
+        <v>2.75</v>
+      </c>
+      <c r="T186">
+        <v>1.33</v>
+      </c>
+      <c r="U186">
+        <v>3.25</v>
+      </c>
+      <c r="V186">
+        <v>2.5</v>
+      </c>
+      <c r="W186">
+        <v>1.5</v>
+      </c>
+      <c r="X186">
+        <v>6.5</v>
+      </c>
+      <c r="Y186">
+        <v>1.11</v>
+      </c>
+      <c r="Z186">
+        <v>3.2</v>
+      </c>
+      <c r="AA186">
+        <v>3.3</v>
+      </c>
+      <c r="AB186">
+        <v>2.2</v>
+      </c>
+      <c r="AC186">
+        <v>1.05</v>
+      </c>
+      <c r="AD186">
+        <v>9.5</v>
+      </c>
+      <c r="AE186">
+        <v>1.22</v>
+      </c>
+      <c r="AF186">
+        <v>4.2</v>
+      </c>
+      <c r="AG186">
+        <v>1.89</v>
+      </c>
+      <c r="AH186">
+        <v>1.85</v>
+      </c>
+      <c r="AI186">
+        <v>1.57</v>
+      </c>
+      <c r="AJ186">
+        <v>2.25</v>
+      </c>
+      <c r="AK186">
+        <v>1.63</v>
+      </c>
+      <c r="AL186">
+        <v>1.3</v>
+      </c>
+      <c r="AM186">
+        <v>1.34</v>
+      </c>
+      <c r="AN186">
+        <v>0.93</v>
+      </c>
+      <c r="AO186">
+        <v>1.33</v>
+      </c>
+      <c r="AP186">
+        <v>1.06</v>
+      </c>
+      <c r="AQ186">
+        <v>1.25</v>
+      </c>
+      <c r="AR186">
+        <v>1.44</v>
+      </c>
+      <c r="AS186">
+        <v>1.63</v>
+      </c>
+      <c r="AT186">
+        <v>3.07</v>
+      </c>
+      <c r="AU186">
+        <v>6</v>
+      </c>
+      <c r="AV186">
+        <v>4</v>
+      </c>
+      <c r="AW186">
+        <v>6</v>
+      </c>
+      <c r="AX186">
+        <v>14</v>
+      </c>
+      <c r="AY186">
+        <v>13</v>
+      </c>
+      <c r="AZ186">
+        <v>25</v>
+      </c>
+      <c r="BA186">
+        <v>2</v>
+      </c>
+      <c r="BB186">
+        <v>5</v>
+      </c>
+      <c r="BC186">
+        <v>7</v>
+      </c>
+      <c r="BD186">
+        <v>2.05</v>
+      </c>
+      <c r="BE186">
+        <v>6.75</v>
+      </c>
+      <c r="BF186">
+        <v>1.94</v>
+      </c>
+      <c r="BG186">
+        <v>1.22</v>
+      </c>
+      <c r="BH186">
+        <v>3.65</v>
+      </c>
+      <c r="BI186">
+        <v>1.4</v>
+      </c>
+      <c r="BJ186">
+        <v>2.63</v>
+      </c>
+      <c r="BK186">
+        <v>1.67</v>
+      </c>
+      <c r="BL186">
+        <v>2.02</v>
+      </c>
+      <c r="BM186">
+        <v>2.05</v>
+      </c>
+      <c r="BN186">
+        <v>1.65</v>
+      </c>
+      <c r="BO186">
+        <v>2.55</v>
+      </c>
+      <c r="BP186">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7784967</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45753.47916666666</v>
+      </c>
+      <c r="F187">
+        <v>31</v>
+      </c>
+      <c r="G187" t="s">
+        <v>79</v>
+      </c>
+      <c r="H187" t="s">
+        <v>70</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>2</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>2</v>
+      </c>
+      <c r="O187" t="s">
+        <v>217</v>
+      </c>
+      <c r="P187" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q187">
+        <v>2.3</v>
+      </c>
+      <c r="R187">
+        <v>2.38</v>
+      </c>
+      <c r="S187">
+        <v>4.5</v>
+      </c>
+      <c r="T187">
+        <v>1.33</v>
+      </c>
+      <c r="U187">
+        <v>3.25</v>
+      </c>
+      <c r="V187">
+        <v>2.5</v>
+      </c>
+      <c r="W187">
+        <v>1.5</v>
+      </c>
+      <c r="X187">
+        <v>6</v>
+      </c>
+      <c r="Y187">
+        <v>1.13</v>
+      </c>
+      <c r="Z187">
+        <v>1.72</v>
+      </c>
+      <c r="AA187">
+        <v>3.74</v>
+      </c>
+      <c r="AB187">
+        <v>4.5</v>
+      </c>
+      <c r="AC187">
+        <v>1.04</v>
+      </c>
+      <c r="AD187">
+        <v>10</v>
+      </c>
+      <c r="AE187">
+        <v>1.22</v>
+      </c>
+      <c r="AF187">
+        <v>4.2</v>
+      </c>
+      <c r="AG187">
+        <v>1.61</v>
+      </c>
+      <c r="AH187">
+        <v>2.1</v>
+      </c>
+      <c r="AI187">
+        <v>1.62</v>
+      </c>
+      <c r="AJ187">
+        <v>2.2</v>
+      </c>
+      <c r="AK187">
+        <v>1.2</v>
+      </c>
+      <c r="AL187">
+        <v>1.26</v>
+      </c>
+      <c r="AM187">
+        <v>2.05</v>
+      </c>
+      <c r="AN187">
+        <v>1.93</v>
+      </c>
+      <c r="AO187">
+        <v>1.29</v>
+      </c>
+      <c r="AP187">
+        <v>2</v>
+      </c>
+      <c r="AQ187">
+        <v>1.2</v>
+      </c>
+      <c r="AR187">
+        <v>1.88</v>
+      </c>
+      <c r="AS187">
+        <v>1.52</v>
+      </c>
+      <c r="AT187">
+        <v>3.4</v>
+      </c>
+      <c r="AU187">
+        <v>6</v>
+      </c>
+      <c r="AV187">
+        <v>6</v>
+      </c>
+      <c r="AW187">
+        <v>6</v>
+      </c>
+      <c r="AX187">
+        <v>10</v>
+      </c>
+      <c r="AY187">
+        <v>14</v>
+      </c>
+      <c r="AZ187">
+        <v>19</v>
+      </c>
+      <c r="BA187">
+        <v>3</v>
+      </c>
+      <c r="BB187">
+        <v>1</v>
+      </c>
+      <c r="BC187">
+        <v>4</v>
+      </c>
+      <c r="BD187">
+        <v>1.47</v>
+      </c>
+      <c r="BE187">
+        <v>6.75</v>
+      </c>
+      <c r="BF187">
+        <v>3.05</v>
+      </c>
+      <c r="BG187">
+        <v>1.3</v>
+      </c>
+      <c r="BH187">
+        <v>3.05</v>
+      </c>
+      <c r="BI187">
+        <v>1.53</v>
+      </c>
+      <c r="BJ187">
+        <v>2.25</v>
+      </c>
+      <c r="BK187">
+        <v>1.86</v>
+      </c>
+      <c r="BL187">
+        <v>1.8</v>
+      </c>
+      <c r="BM187">
+        <v>2.35</v>
+      </c>
+      <c r="BN187">
+        <v>1.5</v>
+      </c>
+      <c r="BO187">
+        <v>3.05</v>
+      </c>
+      <c r="BP187">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -38662,73 +38662,73 @@
         <v>83</v>
       </c>
       <c r="Q182">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R182">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S182">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T182">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U182">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V182">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="W182">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X182">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Y182">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z182">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA182">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AB182">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AC182">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD182">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE182">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF182">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="AG182">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH182">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI182">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ182">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK182">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL182">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AM182">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AN182">
         <v>1.73</v>
@@ -38779,43 +38779,43 @@
         <v>17</v>
       </c>
       <c r="BD182">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BE182">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BF182">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BG182">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BH182">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BI182">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BJ182">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BK182">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BL182">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BM182">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BN182">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BO182">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="BP182">
-        <v>1.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Switzerland Super League_20242025.xlsx
@@ -1816,10 +1816,10 @@
         <v>4</v>
       </c>
       <c r="AY2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA2">
         <v>9</v>
@@ -2022,10 +2022,10 @@
         <v>9</v>
       </c>
       <c r="AY3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2228,10 +2228,10 @@
         <v>8</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ4">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BA4">
         <v>6</v>
@@ -2434,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="AY5">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ5">
         <v>11</v>
@@ -2640,10 +2640,10 @@
         <v>3</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA6">
         <v>4</v>
@@ -2846,10 +2846,10 @@
         <v>5</v>
       </c>
       <c r="AY7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA7">
         <v>8</v>
@@ -3052,10 +3052,10 @@
         <v>9</v>
       </c>
       <c r="AY8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA8">
         <v>6</v>
@@ -3258,10 +3258,10 @@
         <v>7</v>
       </c>
       <c r="AY9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ9">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA9">
         <v>7</v>
@@ -3464,10 +3464,10 @@
         <v>2</v>
       </c>
       <c r="AY10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA10">
         <v>9</v>
@@ -3670,10 +3670,10 @@
         <v>1</v>
       </c>
       <c r="AY11">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AZ11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA11">
         <v>4</v>
@@ -3876,10 +3876,10 @@
         <v>5</v>
       </c>
       <c r="AY12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA12">
         <v>3</v>
@@ -4082,10 +4082,10 @@
         <v>6</v>
       </c>
       <c r="AY13">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA13">
         <v>6</v>
@@ -4288,10 +4288,10 @@
         <v>3</v>
       </c>
       <c r="AY14">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="AZ14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA14">
         <v>6</v>
@@ -4494,10 +4494,10 @@
         <v>5</v>
       </c>
       <c r="AY15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA15">
         <v>9</v>
@@ -4700,10 +4700,10 @@
         <v>3</v>
       </c>
       <c r="AY16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA16">
         <v>7</v>
@@ -4906,10 +4906,10 @@
         <v>10</v>
       </c>
       <c r="AY17">
+        <v>10</v>
+      </c>
+      <c r="AZ17">
         <v>13</v>
-      </c>
-      <c r="AZ17">
-        <v>16</v>
       </c>
       <c r="BA17">
         <v>3</v>
@@ -5112,10 +5112,10 @@
         <v>1</v>
       </c>
       <c r="AY18">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ18">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA18">
         <v>8</v>
@@ -5318,10 +5318,10 @@
         <v>10</v>
       </c>
       <c r="AY19">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BA19">
         <v>4</v>
@@ -5524,10 +5524,10 @@
         <v>10</v>
       </c>
       <c r="AY20">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA20">
         <v>8</v>
@@ -5730,10 +5730,10 @@
         <v>3</v>
       </c>
       <c r="AY21">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA21">
         <v>5</v>
@@ -5936,10 +5936,10 @@
         <v>5</v>
       </c>
       <c r="AY22">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA22">
         <v>4</v>
@@ -6142,10 +6142,10 @@
         <v>5</v>
       </c>
       <c r="AY23">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ23">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA23">
         <v>6</v>
@@ -6348,7 +6348,7 @@
         <v>3</v>
       </c>
       <c r="AY24">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ24">
         <v>9</v>
@@ -6554,10 +6554,10 @@
         <v>6</v>
       </c>
       <c r="AY25">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ25">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA25">
         <v>11</v>
@@ -6760,10 +6760,10 @@
         <v>7</v>
       </c>
       <c r="AY26">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ26">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA26">
         <v>6</v>
@@ -6966,10 +6966,10 @@
         <v>4</v>
       </c>
       <c r="AY27">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ27">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA27">
         <v>5</v>
@@ -7172,10 +7172,10 @@
         <v>5</v>
       </c>
       <c r="AY28">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ28">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA28">
         <v>3</v>
@@ -7378,10 +7378,10 @@
         <v>1</v>
       </c>
       <c r="AY29">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA29">
         <v>4</v>
@@ -7584,7 +7584,7 @@
         <v>4</v>
       </c>
       <c r="AY30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ30">
         <v>11</v>
@@ -7790,10 +7790,10 @@
         <v>4</v>
       </c>
       <c r="AY31">
+        <v>7</v>
+      </c>
+      <c r="AZ31">
         <v>8</v>
-      </c>
-      <c r="AZ31">
-        <v>11</v>
       </c>
       <c r="BA31">
         <v>3</v>
@@ -7996,10 +7996,10 @@
         <v>6</v>
       </c>
       <c r="AY32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ32">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA32">
         <v>1</v>
@@ -8202,10 +8202,10 @@
         <v>10</v>
       </c>
       <c r="AY33">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ33">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BA33">
         <v>5</v>
@@ -8408,10 +8408,10 @@
         <v>5</v>
       </c>
       <c r="AY34">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ34">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA34">
         <v>7</v>
@@ -8614,10 +8614,10 @@
         <v>4</v>
       </c>
       <c r="AY35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ35">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA35">
         <v>3</v>
@@ -8820,10 +8820,10 @@
         <v>4</v>
       </c>
       <c r="AY36">
+        <v>11</v>
+      </c>
+      <c r="AZ36">
         <v>12</v>
-      </c>
-      <c r="AZ36">
-        <v>13</v>
       </c>
       <c r="BA36">
         <v>6</v>
@@ -9026,10 +9026,10 @@
         <v>4</v>
       </c>
       <c r="AY37">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ37">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA37">
         <v>5</v>
@@ -9232,10 +9232,10 @@
         <v>6</v>
       </c>
       <c r="AY38">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ38">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA38">
         <v>9</v>
@@ -9438,10 +9438,10 @@
         <v>4</v>
       </c>
       <c r="AY39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ39">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA39">
         <v>4</v>
@@ -9644,10 +9644,10 @@
         <v>6</v>
       </c>
       <c r="AY40">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ40">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA40">
         <v>4</v>
@@ -9850,10 +9850,10 @@
         <v>10</v>
       </c>
       <c r="AY41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ41">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA41">
         <v>1</v>
@@ -10056,10 +10056,10 @@
         <v>6</v>
       </c>
       <c r="AY42">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ42">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA42">
         <v>4</v>
@@ -10262,10 +10262,10 @@
         <v>2</v>
       </c>
       <c r="AY43">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA43">
         <v>3</v>
@@ -10468,10 +10468,10 @@
         <v>5</v>
       </c>
       <c r="AY44">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ44">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA44">
         <v>5</v>
@@ -10674,10 +10674,10 @@
         <v>5</v>
       </c>
       <c r="AY45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AZ45">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA45">
         <v>2</v>
@@ -10880,10 +10880,10 @@
         <v>4</v>
       </c>
       <c r="AY46">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ46">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA46">
         <v>6</v>
@@ -11086,10 +11086,10 @@
         <v>9</v>
       </c>
       <c r="AY47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ47">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA47">
         <v>4</v>
@@ -11292,7 +11292,7 @@
         <v>4</v>
       </c>
       <c r="AY48">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ48">
         <v>8</v>
@@ -11498,10 +11498,10 @@
         <v>10</v>
       </c>
       <c r="AY49">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ49">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA49">
         <v>14</v>
@@ -11704,10 +11704,10 @@
         <v>6</v>
       </c>
       <c r="AY50">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AZ50">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA50">
         <v>6</v>
@@ -11910,10 +11910,10 @@
         <v>1</v>
       </c>
       <c r="AY51">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA51">
         <v>15</v>
@@ -12116,10 +12116,10 @@
         <v>10</v>
       </c>
       <c r="AY52">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ52">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA52">
         <v>4</v>
@@ -12325,7 +12325,7 @@
         <v>8</v>
       </c>
       <c r="AZ53">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA53">
         <v>6</v>
@@ -12528,10 +12528,10 @@
         <v>4</v>
       </c>
       <c r="AY54">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ54">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA54">
         <v>10</v>
@@ -12734,10 +12734,10 @@
         <v>5</v>
       </c>
       <c r="AY55">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ55">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA55">
         <v>6</v>
@@ -12943,16 +12943,16 @@
         <v>11</v>
       </c>
       <c r="AZ56">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB56">
         <v>6</v>
       </c>
       <c r="BC56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD56">
         <v>1.94</v>
@@ -13146,10 +13146,10 @@
         <v>9</v>
       </c>
       <c r="AY57">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ57">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA57">
         <v>7</v>
@@ -13352,10 +13352,10 @@
         <v>4</v>
       </c>
       <c r="AY58">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ58">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA58">
         <v>2</v>
@@ -14176,10 +14176,10 @@
         <v>6</v>
       </c>
       <c r="AY62">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ62">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA62">
         <v>5</v>
@@ -14382,10 +14382,10 @@
         <v>7</v>
       </c>
       <c r="AY63">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ63">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA63">
         <v>6</v>
@@ -14588,10 +14588,10 @@
         <v>3</v>
       </c>
       <c r="AY64">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AZ64">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA64">
         <v>15</v>
@@ -14794,10 +14794,10 @@
         <v>4</v>
       </c>
       <c r="AY65">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ65">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA65">
         <v>1</v>
@@ -15000,10 +15000,10 @@
         <v>6</v>
       </c>
       <c r="AY66">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ66">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA66">
         <v>1</v>
@@ -15206,10 +15206,10 @@
         <v>5</v>
       </c>
       <c r="AY67">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ67">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA67">
         <v>6</v>
@@ -15412,10 +15412,10 @@
         <v>5</v>
       </c>
       <c r="AY68">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ68">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BA68">
         <v>1</v>
@@ -15618,10 +15618,10 @@
         <v>6</v>
       </c>
       <c r="AY69">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AZ69">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA69">
         <v>9</v>
@@ -15824,10 +15824,10 @@
         <v>12</v>
       </c>
       <c r="AY70">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ70">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="BA70">
         <v>2</v>
@@ -16030,10 +16030,10 @@
         <v>1</v>
       </c>
       <c r="AY71">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ71">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA71">
         <v>4</v>
@@ -16648,10 +16648,10 @@
         <v>4</v>
       </c>
       <c r="AY74">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ74">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA74">
         <v>4</v>
@@ -16857,7 +16857,7 @@
         <v>10</v>
       </c>
       <c r="AZ75">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA75">
         <v>2</v>
@@ -17060,10 +17060,10 @@
         <v>5</v>
       </c>
       <c r="AY76">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ76">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA76">
         <v>8</v>
@@ -17266,10 +17266,10 @@
         <v>4</v>
       </c>
       <c r="AY77">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ77">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA77">
         <v>2</v>
@@ -17472,10 +17472,10 @@
         <v>6</v>
       </c>
       <c r="AY78">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ78">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA78">
         <v>2</v>
@@ -17678,10 +17678,10 @@
         <v>7</v>
       </c>
       <c r="AY79">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ79">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA79">
         <v>2</v>
@@ -17884,10 +17884,10 @@
         <v>6</v>
       </c>
       <c r="AY80">
+        <v>6</v>
+      </c>
+      <c r="AZ80">
         <v>9</v>
-      </c>
-      <c r="AZ80">
-        <v>12</v>
       </c>
       <c r="BA80">
         <v>5</v>
@@ -18090,10 +18090,10 @@
         <v>8</v>
       </c>
       <c r="AY81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ81">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA81">
         <v>1</v>
@@ -18296,10 +18296,10 @@
         <v>5</v>
       </c>
       <c r="AY82">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ82">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA82">
         <v>8</v>
@@ -18502,10 +18502,10 @@
         <v>2</v>
       </c>
       <c r="AY83">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ83">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA83">
         <v>3</v>
@@ -18708,10 +18708,10 @@
         <v>5</v>
       </c>
       <c r="AY84">
+        <v>10</v>
+      </c>
+      <c r="AZ84">
         <v>11</v>
-      </c>
-      <c r="AZ84">
-        <v>15</v>
       </c>
       <c r="BA84">
         <v>4</v>
@@ -18914,10 +18914,10 @@
         <v>4</v>
       </c>
       <c r="AY85">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ85">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA85">
         <v>8</v>
@@ -19538,13 +19538,13 @@
         <v>-1</v>
       </c>
       <c r="BA88">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BB88">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BC88">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BD88">
         <v>0</v>
@@ -19944,10 +19944,10 @@
         <v>5</v>
       </c>
       <c r="AY90">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ90">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA90">
         <v>4</v>
@@ -20356,10 +20356,10 @@
         <v>8</v>
       </c>
       <c r="AY92">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ92">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA92">
         <v>3</v>
@@ -20562,10 +20562,10 @@
         <v>3</v>
       </c>
       <c r="AY93">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ93">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA93">
         <v>7</v>
@@ -20768,10 +20768,10 @@
         <v>5</v>
       </c>
       <c r="AY94">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ94">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA94">
         <v>0</v>
@@ -20974,10 +20974,10 @@
         <v>5</v>
       </c>
       <c r="AY95">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AZ95">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA95">
         <v>4</v>
@@ -21180,10 +21180,10 @@
         <v>4</v>
       </c>
       <c r="AY96">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ96">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA96">
         <v>7</v>
@@ -21386,10 +21386,10 @@
         <v>3</v>
       </c>
       <c r="AY97">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ97">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA97">
         <v>5</v>
@@ -21592,10 +21592,10 @@
         <v>5</v>
       </c>
       <c r="AY98">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ98">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA98">
         <v>4</v>
@@ -21798,10 +21798,10 @@
         <v>7</v>
       </c>
       <c r="AY99">
+        <v>11</v>
+      </c>
+      <c r="AZ99">
         <v>12</v>
-      </c>
-      <c r="AZ99">
-        <v>15</v>
       </c>
       <c r="BA99">
         <v>5</v>
@@ -22004,10 +22004,10 @@
         <v>2</v>
       </c>
       <c r="AY100">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ100">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA100">
         <v>6</v>
@@ -22210,7 +22210,7 @@
         <v>5</v>
       </c>
       <c r="AY101">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ101">
         <v>7</v>
@@ -22416,10 +22416,10 @@
         <v>5</v>
       </c>
       <c r="AY102">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ102">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA102">
         <v>8</v>
@@ -22622,7 +22622,7 @@
         <v>8</v>
       </c>
       <c r="AY103">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ103">
         <v>14</v>
@@ -22828,10 +22828,10 @@
         <v>13</v>
       </c>
       <c r="AY104">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ104">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BA104">
         <v>7</v>
@@ -23034,10 +23034,10 @@
         <v>5</v>
       </c>
       <c r="AY105">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ105">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA105">
         <v>4</v>
@@ -23240,10 +23240,10 @@
         <v>6</v>
       </c>
       <c r="AY106">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ106">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA106">
         <v>6</v>
@@ -23446,10 +23446,10 @@
         <v>2</v>
       </c>
       <c r="AY107">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AZ107">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA107">
         <v>10</v>
@@ -23652,10 +23652,10 @@
         <v>3</v>
       </c>
       <c r="AY108">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ108">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA108">
         <v>8</v>
@@ -23858,10 +23858,10 @@
         <v>2</v>
       </c>
       <c r="AY109">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA109">
         <v>6</v>
@@ -24064,7 +24064,7 @@
         <v>1</v>
       </c>
       <c r="AY110">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ110">
         <v>5</v>
@@ -24270,10 +24270,10 @@
         <v>6</v>
       </c>
       <c r="AY111">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AZ111">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA111">
         <v>11</v>
@@ -24476,7 +24476,7 @@
         <v>6</v>
       </c>
       <c r="AY112">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AZ112">
         <v>11</v>
@@ -24682,7 +24682,7 @@
         <v>3</v>
       </c>
       <c r="AY113">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ113">
         <v>9</v>
@@ -24888,10 +24888,10 @@
         <v>6</v>
       </c>
       <c r="AY114">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ114">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA114">
         <v>7</v>
@@ -25094,10 +25094,10 @@
         <v>16</v>
       </c>
       <c r="AY115">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ115">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BA115">
         <v>6</v>
@@ -25300,10 +25300,10 @@
         <v>11</v>
       </c>
       <c r="AY116">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ116">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BA116">
         <v>6</v>
@@ -25506,19 +25506,19 @@
         <v>9</v>
       </c>
       <c r="AY117">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ117">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA117">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB117">
         <v>2</v>
       </c>
       <c r="BC117">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD117">
         <v>3.2</v>
@@ -25712,7 +25712,7 @@
         <v>8</v>
       </c>
       <c r="AY118">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ118">
         <v>15</v>
@@ -25918,10 +25918,10 @@
         <v>6</v>
       </c>
       <c r="AY119">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ119">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -26124,10 +26124,10 @@
         <v>11</v>
       </c>
       <c r="AY120">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ120">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA120">
         <v>10</v>
@@ -26330,10 +26330,10 @@
         <v>8</v>
       </c>
       <c r="AY121">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ121">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA121">
         <v>6</v>
@@ -26536,7 +26536,7 @@
         <v>4</v>
       </c>
       <c r="AY122">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ122">
         <v>8</v>
@@ -26742,7 +26742,7 @@
         <v>6</v>
       </c>
       <c r="AY123">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ123">
         <v>10</v>
@@ -26948,7 +26948,7 @@
         <v>6</v>
       </c>
       <c r="AY124">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ124">
         <v>12</v>
@@ -27154,10 +27154,10 @@
         <v>7</v>
       </c>
       <c r="AY125">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ125">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA125">
         <v>4</v>
@@ -27360,10 +27360,10 @@
         <v>11</v>
       </c>
       <c r="AY126">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ126">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA126">
         <v>2</v>
@@ -27566,10 +27566,10 @@
         <v>9</v>
       </c>
       <c r="AY127">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ127">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA127">
         <v>6</v>
@@ -27772,10 +27772,10 @@
         <v>8</v>
       </c>
       <c r="AY128">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ128">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA128">
         <v>4</v>
@@ -27978,7 +27978,7 @@
         <v>8</v>
       </c>
       <c r="AY129">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ129">
         <v>20</v>
@@ -28184,10 +28184,10 @@
         <v>2</v>
       </c>
       <c r="AY130">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AZ130">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA130">
         <v>7</v>
@@ -28390,7 +28390,7 @@
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AZ131">
         <v>7</v>
@@ -28596,10 +28596,10 @@
         <v>21</v>
       </c>
       <c r="AY132">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ132">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BA132">
         <v>4</v>
@@ -28802,10 +28802,10 @@
         <v>14</v>
       </c>
       <c r="AY133">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ133">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BA133">
         <v>2</v>
@@ -29011,7 +29011,7 @@
         <v>18</v>
       </c>
       <c r="AZ134">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA134">
         <v>5</v>
@@ -29214,10 +29214,10 @@
         <v>4</v>
       </c>
       <c r="AY135">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="AZ135">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA135">
         <v>10</v>
@@ -29420,10 +29420,10 @@
         <v>9</v>
       </c>
       <c r="AY136">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ136">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA136">
         <v>5</v>
@@ -29626,10 +29626,10 @@
         <v>4</v>
       </c>
       <c r="AY137">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ137">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA137">
         <v>10</v>
@@ -29832,19 +29832,19 @@
         <v>8</v>
       </c>
       <c r="AY138">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AZ138">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB138">
         <v>4</v>
       </c>
       <c r="BC138">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD138">
         <v>1.3</v>
@@ -30038,19 +30038,19 @@
         <v>6</v>
       </c>
       <c r="AY139">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AZ139">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA139">
         <v>8</v>
       </c>
       <c r="BB139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC139">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD139">
         <v>2.07</v>
@@ -30244,10 +30244,10 @@
         <v>9</v>
       </c>
       <c r="AY140">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ140">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA140">
         <v>1</v>
@@ -30450,10 +30450,10 @@
         <v>9</v>
       </c>
       <c r="AY141">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ141">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA141">
         <v>5</v>
@@ -30656,10 +30656,10 @@
         <v>12</v>
       </c>
       <c r="AY142">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ142">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA142">
         <v>4</v>
@@ -30865,7 +30865,7 @@
         <v>22</v>
       </c>
       <c r="AZ143">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA143">
         <v>2</v>
@@ -31068,10 +31068,10 @@
         <v>9</v>
       </c>
       <c r="AY144">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ144">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA144">
         <v>9</v>
@@ -31274,10 +31274,10 @@
         <v>4</v>
       </c>
       <c r="AY145">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ145">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA145">
         <v>5</v>
@@ -31483,7 +31483,7 @@
         <v>15</v>
       </c>
       <c r="AZ146">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA146">
         <v>7</v>
@@ -31686,7 +31686,7 @@
         <v>5</v>
       </c>
       <c r="AY147">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ147">
         <v>11</v>
@@ -31892,7 +31892,7 @@
         <v>8</v>
       </c>
       <c r="AY148">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AZ148">
         <v>15</v>
@@ -32098,10 +32098,10 @@
         <v>19</v>
       </c>
       <c r="AY149">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ149">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BA149">
         <v>1</v>
@@ -32304,7 +32304,7 @@
         <v>3</v>
       </c>
       <c r="AY150">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ150">
         <v>9</v>
@@ -32510,10 +32510,10 @@
         <v>10</v>
       </c>
       <c r="AY151">
+        <v>13</v>
+      </c>
+      <c r="AZ151">
         <v>14</v>
-      </c>
-      <c r="AZ151">
-        <v>17</v>
       </c>
       <c r="BA151">
         <v>3</v>
@@ -32716,10 +32716,10 @@
         <v>6</v>
       </c>
       <c r="AY152">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ152">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA152">
         <v>10</v>
@@ -32922,7 +32922,7 @@
         <v>16</v>
       </c>
       <c r="AY153">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ153">
         <v>21</v>
@@ -33128,7 +33128,7 @@
         <v>9</v>
       </c>
       <c r="AY154">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ154">
         <v>13</v>
@@ -33540,10 +33540,10 @@
         <v>14</v>
       </c>
       <c r="AY156">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ156">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA156">
         <v>3</v>
@@ -33746,7 +33746,7 @@
         <v>7</v>
       </c>
       <c r="AY157">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ157">
         <v>11</v>
@@ -33952,10 +33952,10 @@
         <v>7</v>
       </c>
       <c r="AY158">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ158">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA158">
         <v>1</v>
@@ -34161,7 +34161,7 @@
         <v>24</v>
       </c>
       <c r="AZ159">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA159">
         <v>6</v>
@@ -34364,10 +34364,10 @@
         <v>3</v>
       </c>
       <c r="AY160">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ160">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA160">
         <v>6</v>
@@ -34570,7 +34570,7 @@
         <v>4</v>
       </c>
       <c r="AY161">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ161">
         <v>9</v>
@@ -34776,10 +34776,10 @@
         <v>8</v>
       </c>
       <c r="AY162">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ162">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA162">
         <v>6</v>
@@ -34982,10 +34982,10 @@
         <v>15</v>
       </c>
       <c r="AY163">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ163">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA163">
         <v>4</v>
@@ -35188,10 +35188,10 @@
         <v>11</v>
       </c>
       <c r="AY164">
+        <v>15</v>
+      </c>
+      <c r="AZ164">
         <v>16</v>
-      </c>
-      <c r="AZ164">
-        <v>19</v>
       </c>
       <c r="BA164">
         <v>8</v>
@@ -35394,10 +35394,10 @@
         <v>9</v>
       </c>
       <c r="AY165">
+        <v>14</v>
+      </c>
+      <c r="AZ165">
         <v>16</v>
-      </c>
-      <c r="AZ165">
-        <v>18</v>
       </c>
       <c r="BA165">
         <v>8</v>
@@ -35600,7 +35600,7 @@
         <v>4</v>
       </c>
       <c r="AY166">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AZ166">
         <v>11</v>
@@ -35806,10 +35806,10 @@
         <v>8</v>
       </c>
       <c r="AY167">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ167">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA167">
         <v>6</v>
@@ -36012,10 +36012,10 @@
         <v>6</v>
       </c>
       <c r="AY168">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ168">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA168">
         <v>3</v>
@@ -36218,7 +36218,7 @@
         <v>1</v>
       </c>
       <c r="AY169">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ169">
         <v>5</v>
@@ -36424,10 +36424,10 @@
         <v>7</v>
       </c>
       <c r="AY170">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ170">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA170">
         <v>9</v>
@@ -36630,10 +36630,10 @@
         <v>10</v>
       </c>
       <c r="AY171">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ171">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA171">
         <v>5</v>
@@ -36836,10 +36836,10 @@
         <v>7</v>
       </c>
       <c r="AY172">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ172">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA172">
         <v>9</v>
@@ -37042,10 +37042,10 @@
         <v>10</v>
       </c>
       <c r="AY173">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ173">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA173">
         <v>2</v>
@@ -37248,10 +37248,10 @@
         <v>13</v>
       </c>
       <c r="AY174">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ174">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA174">
         <v>4</v>
@@ -37454,10 +37454,10 @@
         <v>4</v>
       </c>
       <c r="AY175">
+        <v>12</v>
+      </c>
+      <c r="AZ175">
         <v>13</v>
-      </c>
-      <c r="AZ175">
-        <v>14</v>
       </c>
       <c r="BA175">
         <v>6</v>
@@ -37660,10 +37660,10 @@
         <v>5</v>
       </c>
       <c r="AY176">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ176">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA176">
         <v>3</v>
@@ -37866,10 +37866,10 @@
         <v>5</v>
       </c>
       <c r="AY177">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ177">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA177">
         <v>3</v>
@@ -38072,10 +38072,10 @@
         <v>8</v>
       </c>
       <c r="AY178">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ178">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA178">
         <v>3</v>
@@ -38278,7 +38278,7 @@
         <v>8</v>
       </c>
       <c r="AY179">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ179">
         <v>14</v>
@@ -38484,10 +38484,10 @@
         <v>9</v>
       </c>
       <c r="AY180">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ180">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA180">
         <v>5</v>
@@ -38690,10 +38690,10 @@
         <v>10</v>
       </c>
       <c r="AY181">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ181">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA181">
         <v>4</v>
@@ -38896,10 +38896,10 @@
         <v>15</v>
       </c>
       <c r="AY182">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ182">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA182">
         <v>7</v>
@@ -39102,7 +39102,7 @@
         <v>3</v>
       </c>
       <c r="AY183">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ183">
         <v>7</v>
@@ -39308,10 +39308,10 @@
         <v>11</v>
       </c>
       <c r="AY184">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AZ184">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA184">
         <v>9</v>
@@ -39514,10 +39514,10 @@
         <v>12</v>
       </c>
       <c r="AY185">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ185">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA185">
         <v>5</v>
@@ -39720,10 +39720,10 @@
         <v>10</v>
       </c>
       <c r="AY186">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ186">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA186">
         <v>3</v>
@@ -39926,10 +39926,10 @@
         <v>14</v>
       </c>
       <c r="AY187">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ187">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BA187">
         <v>2</v>
@@ -40132,10 +40132,10 @@
         <v>18</v>
       </c>
       <c r="AY188">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ188">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA188">
         <v>4</v>
@@ -40338,7 +40338,7 @@
         <v>4</v>
       </c>
       <c r="AY189">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ189">
         <v>10</v>
@@ -40544,10 +40544,10 @@
         <v>9</v>
       </c>
       <c r="AY190">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ190">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BA190">
         <v>5</v>
@@ -40750,10 +40750,10 @@
         <v>7</v>
       </c>
       <c r="AY191">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ191">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA191">
         <v>7</v>
@@ -40956,10 +40956,10 @@
         <v>12</v>
       </c>
       <c r="AY192">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ192">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA192">
         <v>5</v>
@@ -41162,10 +41162,10 @@
         <v>13</v>
       </c>
       <c r="AY193">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ193">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA193">
         <v>2</v>
@@ -41368,10 +41368,10 @@
         <v>12</v>
       </c>
       <c r="AY194">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ194">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA194">
         <v>4</v>
@@ -41574,10 +41574,10 @@
         <v>4</v>
       </c>
       <c r="AY195">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ195">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA195">
         <v>5</v>
@@ -41780,10 +41780,10 @@
         <v>14</v>
       </c>
       <c r="AY196">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ196">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA196">
         <v>8</v>
@@ -41986,10 +41986,10 @@
         <v>10</v>
       </c>
       <c r="AY197">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ197">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA197">
         <v>2</v>
@@ -42195,7 +42195,7 @@
         <v>14</v>
       </c>
       <c r="AZ198">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA198">
         <v>5</v>
@@ -42398,10 +42398,10 @@
         <v>10</v>
       </c>
       <c r="AY199">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ199">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BA199">
         <v>7</v>
@@ -42604,10 +42604,10 @@
         <v>8</v>
       </c>
       <c r="AY200">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ200">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA200">
         <v>3</v>
@@ -42810,10 +42810,10 @@
         <v>8</v>
       </c>
       <c r="AY201">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ201">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA201">
         <v>5</v>
@@ -43019,16 +43019,16 @@
         <v>6</v>
       </c>
       <c r="AZ202">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA202">
         <v>1</v>
       </c>
       <c r="BB202">
+        <v>5</v>
+      </c>
+      <c r="BC202">
         <v>6</v>
-      </c>
-      <c r="BC202">
-        <v>7</v>
       </c>
       <c r="BD202">
         <v>2.2</v>
@@ -43222,10 +43222,10 @@
         <v>6</v>
       </c>
       <c r="AY203">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ203">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA203">
         <v>10</v>
@@ -43428,10 +43428,10 @@
         <v>4</v>
       </c>
       <c r="AY204">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ204">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA204">
         <v>11</v>
@@ -43634,10 +43634,10 @@
         <v>7</v>
       </c>
       <c r="AY205">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ205">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA205">
         <v>7</v>
@@ -43840,7 +43840,7 @@
         <v>8</v>
       </c>
       <c r="AY206">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ206">
         <v>16</v>
@@ -44046,10 +44046,10 @@
         <v>4</v>
       </c>
       <c r="AY207">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ207">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA207">
         <v>6</v>
@@ -44252,7 +44252,7 @@
         <v>6</v>
       </c>
       <c r="AY208">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ208">
         <v>8</v>
@@ -44458,10 +44458,10 @@
         <v>7</v>
       </c>
       <c r="AY209">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AZ209">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA209">
         <v>5</v>
@@ -44664,10 +44664,10 @@
         <v>9</v>
       </c>
       <c r="AY210">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ210">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA210">
         <v>6</v>
@@ -44870,10 +44870,10 @@
         <v>14</v>
       </c>
       <c r="AY211">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ211">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BA211">
         <v>7</v>
@@ -45076,10 +45076,10 @@
         <v>8</v>
       </c>
       <c r="AY212">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ212">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA212">
         <v>8</v>
@@ -45282,10 +45282,10 @@
         <v>7</v>
       </c>
       <c r="AY213">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ213">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA213">
         <v>1</v>
@@ -45488,10 +45488,10 @@
         <v>10</v>
       </c>
       <c r="AY214">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AZ214">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA214">
         <v>5</v>
@@ -45900,10 +45900,10 @@
         <v>7</v>
       </c>
       <c r="AY216">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ216">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA216">
         <v>10</v>
@@ -46106,10 +46106,10 @@
         <v>6</v>
       </c>
       <c r="AY217">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ217">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA217">
         <v>4</v>
@@ -46312,10 +46312,10 @@
         <v>9</v>
       </c>
       <c r="AY218">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ218">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA218">
         <v>9</v>
@@ -46518,10 +46518,10 @@
         <v>4</v>
       </c>
       <c r="AY219">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ219">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA219">
         <v>9</v>
@@ -46724,7 +46724,7 @@
         <v>13</v>
       </c>
       <c r="AY220">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ220">
         <v>17</v>
@@ -46930,10 +46930,10 @@
         <v>15</v>
       </c>
       <c r="AY221">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ221">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BA221">
         <v>3</v>
@@ -47136,7 +47136,7 @@
         <v>4</v>
       </c>
       <c r="AY222">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ222">
         <v>7</v>
@@ -47345,7 +47345,7 @@
         <v>14</v>
       </c>
       <c r="AZ223">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA223">
         <v>2</v>
@@ -47548,10 +47548,10 @@
         <v>8</v>
       </c>
       <c r="AY224">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ224">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA224">
         <v>10</v>
@@ -47754,10 +47754,10 @@
         <v>6</v>
       </c>
       <c r="AY225">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ225">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA225">
         <v>10</v>
@@ -47960,10 +47960,10 @@
         <v>4</v>
       </c>
       <c r="AY226">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ226">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA226">
         <v>4</v>
@@ -48169,7 +48169,7 @@
         <v>14</v>
       </c>
       <c r="AZ227">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA227">
         <v>3</v>
@@ -48372,10 +48372,10 @@
         <v>11</v>
       </c>
       <c r="AY228">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ228">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA228">
         <v>5</v>
@@ -48578,7 +48578,7 @@
         <v>6</v>
       </c>
       <c r="AY229">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ229">
         <v>12</v>
